--- a/고객제안서_월배당ETF.xlsx
+++ b/고객제안서_월배당ETF.xlsx
@@ -12,7 +12,7 @@
     <sheet name="사용법" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="채택종목">'ETF데이터'!$A$4:$A$12</definedName>
+    <definedName name="채택종목">'ETF데이터'!$A$4:$A$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="K2" s="3">
-        <f>IFERROR(MATCH($C$9,'ETF데이터'!$A$4:$A$12,0),0)</f>
+        <f>IFERROR(MATCH($C$9,'ETF데이터'!$A$4:$A$23,0),0)</f>
         <v/>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>ACE 미국빅테크7+데일리타겟커버드콜(합성)</t>
+          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="C14" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$B$4:$B$12,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$B$4:$B$23,$K$2))</f>
         <v/>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="F14" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$G$4:$G$12,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$G$4:$G$23,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="C15" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$C$4:$C$12,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$C$4:$C$23,$K$2))</f>
         <v/>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="F15" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$H$4:$H$12,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$H$4:$H$23,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="C16" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$D$4:$D$12,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$D$4:$D$23,$K$2))</f>
         <v/>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="F16" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$I$4:$I$12,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$I$4:$I$23,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C17" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$E$4:$E$12,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$E$4:$E$23,$K$2))</f>
         <v/>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="F17" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$J$4:$J$12,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$J$4:$J$23,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="C18" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$F$4:$F$12,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$F$4:$F$23,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>5. 채택 ETF 비교 (1억원 투자 기준)</t>
+          <t>5. 채택 ETF 비교 (1억원 투자 기준) — 연 분배율 상위 12종목 / 전체 20종목</t>
         </is>
       </c>
     </row>
@@ -1702,90 +1702,192 @@
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="28">
+        <f>'ETF데이터'!$A$13</f>
+        <v/>
+      </c>
+      <c r="B56" s="28">
+        <f>'ETF데이터'!$B$13</f>
+        <v/>
+      </c>
+      <c r="C56" s="23">
+        <f>'ETF데이터'!$D$13</f>
+        <v/>
+      </c>
+      <c r="D56" s="29">
+        <f>'ETF데이터'!$J$13</f>
+        <v/>
+      </c>
+      <c r="E56" s="30">
+        <f>'ETF데이터'!$J$13/12</f>
+        <v/>
+      </c>
+      <c r="F56" s="23">
+        <f>IF($C56=0,0,ROUNDDOWN(100000000/$C56,0)*$C56*$D56/12)</f>
+        <v/>
+      </c>
+      <c r="G56" s="23">
+        <f>$F56*(1-$C$10)</f>
+        <v/>
+      </c>
+      <c r="H56" s="29">
+        <f>'ETF데이터'!$H$13</f>
+        <v/>
+      </c>
+    </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="27">
+        <f>'ETF데이터'!$A$14</f>
+        <v/>
+      </c>
+      <c r="B57" s="27">
+        <f>'ETF데이터'!$B$14</f>
+        <v/>
+      </c>
+      <c r="C57" s="14">
+        <f>'ETF데이터'!$D$14</f>
+        <v/>
+      </c>
+      <c r="D57" s="13">
+        <f>'ETF데이터'!$J$14</f>
+        <v/>
+      </c>
+      <c r="E57" s="18">
+        <f>'ETF데이터'!$J$14/12</f>
+        <v/>
+      </c>
+      <c r="F57" s="14">
+        <f>IF($C57=0,0,ROUNDDOWN(100000000/$C57,0)*$C57*$D57/12)</f>
+        <v/>
+      </c>
+      <c r="G57" s="14">
+        <f>$F57*(1-$C$10)</f>
+        <v/>
+      </c>
+      <c r="H57" s="13">
+        <f>'ETF데이터'!$H$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="28">
+        <f>'ETF데이터'!$A$15</f>
+        <v/>
+      </c>
+      <c r="B58" s="28">
+        <f>'ETF데이터'!$B$15</f>
+        <v/>
+      </c>
+      <c r="C58" s="23">
+        <f>'ETF데이터'!$D$15</f>
+        <v/>
+      </c>
+      <c r="D58" s="29">
+        <f>'ETF데이터'!$J$15</f>
+        <v/>
+      </c>
+      <c r="E58" s="30">
+        <f>'ETF데이터'!$J$15/12</f>
+        <v/>
+      </c>
+      <c r="F58" s="23">
+        <f>IF($C58=0,0,ROUNDDOWN(100000000/$C58,0)*$C58*$D58/12)</f>
+        <v/>
+      </c>
+      <c r="G58" s="23">
+        <f>$F58*(1-$C$10)</f>
+        <v/>
+      </c>
+      <c r="H58" s="29">
+        <f>'ETF데이터'!$H$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>※ 유동성·변동성 기준을 통과한 종목만 실었습니다. 제외 종목과 사유는 [ETF데이터] 장에 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="4" customHeight="1">
-      <c r="A59" s="5" t="n"/>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n"/>
-    </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="62" ht="4" customHeight="1">
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>6. 유의사항</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="31" t="inlineStr">
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 이 자료는 투자 권유가 아니라 참고 자료입니다. 최종 투자 판단과 그 결과는 투자자 본인에게 귀속됩니다.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="31" t="inlineStr">
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  · ETF 는 예금자보호법의 보호를 받지 않으며, 원금 손실이 발생할 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · 분배금은 확정되지 않습니다. 커버드콜 ETF 의 분배 재원은 옵션 프리미엄이므로, 시장 변동성이 낮아지면 분배금도 함께 줄어듭니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · 분배금의 일부가 원금에서 지급될 수 있습니다(자본 환급). 이 경우 기준가가 그만큼 낮아집니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · 표시된 연 분배율은 최근 12개월 실제 분배금 합계를 현재가로 나눈 값(사후 수치)이며, 앞으로의 수익률을 보장하지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 세율은 국내 상장 ETF 분배금 기준 15.4%(배당소득세 14% + 지방소득세 1.4%)를 적용했습니다. 금융소득종합과세 대상자는 실효세율이 달라집니다.</t>
+          <t xml:space="preserve">  · 분배금은 확정되지 않습니다. 커버드콜 ETF 의 분배 재원은 옵션 프리미엄이므로, 시장 변동성이 낮아지면 분배금도 함께 줄어듭니다.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="17" customHeight="1">
       <c r="A67" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 매매수수료·거래세·환율 변동은 반영하지 않았습니다. 총보수는 분배율에 이미 반영되어 있습니다(기준가 차감).</t>
+          <t xml:space="preserve">  · 분배금의 일부가 원금에서 지급될 수 있습니다(자본 환급). 이 경우 기준가가 그만큼 낮아집니다.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="32" t="inlineStr">
         <is>
+          <t xml:space="preserve">  · 표시된 연 분배율은 최근 12개월 실제 분배금 합계를 현재가로 나눈 값(사후 수치)이며, 앞으로의 수익률을 보장하지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 세율은 국내 상장 ETF 분배금 기준 15.4%(배당소득세 14% + 지방소득세 1.4%)를 적용했습니다. 금융소득종합과세 대상자는 실효세율이 달라집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 매매수수료·거래세·환율 변동은 반영하지 않았습니다. 총보수는 분배율에 이미 반영되어 있습니다(기준가 차감).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="32" t="inlineStr">
+        <is>
           <t xml:space="preserve">  · 수량은 정수 매수를 가정해 내림 처리했습니다. 남는 금액은 '미투자 잔액'에 표시됩니다.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T03:21:40.133Z · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 1년 변동성 25% 이하, 분배 이력 12개월 이상</t>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T03:40:59.675Z · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 1년 변동성 25% 이하, 분배 이력 12개월 이상</t>
         </is>
       </c>
     </row>
@@ -1793,16 +1895,16 @@
   <mergeCells count="12">
     <mergeCell ref="A70:H70"/>
     <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A62:H62"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A69:H69"/>
     <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A64:H64"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="A66:H66"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A61:H61"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="선택할 수 없는 종목" error="목록에 있는 ETF 중에서 고르십시오. 유동성·변동성 기준을 통과한 종목만 담겨 있습니다." promptTitle="ETF 선택" prompt="▼ 를 눌러 ETF 를 고르십시오." type="list">
@@ -1819,7 +1921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1934,25 +2036,25 @@
         </is>
       </c>
       <c r="D4" s="35" t="n">
-        <v>9895</v>
+        <v>9890</v>
       </c>
       <c r="E4" s="35" t="n">
         <v>176941500000</v>
       </c>
       <c r="F4" s="35" t="n">
-        <v>2871660428</v>
+        <v>2871796983</v>
       </c>
       <c r="G4" s="36" t="n">
         <v>0.005384</v>
       </c>
       <c r="H4" s="36" t="n">
-        <v>0.2007</v>
+        <v>0.2139</v>
       </c>
       <c r="I4" s="36" t="n">
         <v>0.0297</v>
       </c>
       <c r="J4" s="36" t="n">
-        <v>0.267812</v>
+        <v>0.267947</v>
       </c>
       <c r="K4" s="35" t="n">
         <v>29</v>
@@ -1986,25 +2088,25 @@
         </is>
       </c>
       <c r="D5" s="35" t="n">
-        <v>8785</v>
+        <v>8780</v>
       </c>
       <c r="E5" s="35" t="n">
         <v>1002716000000</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>13530710290</v>
+        <v>13538688373</v>
       </c>
       <c r="G5" s="36" t="n">
         <v>0.005108000000000001</v>
       </c>
       <c r="H5" s="36" t="n">
-        <v>0.1726</v>
+        <v>0.1938</v>
       </c>
       <c r="I5" s="36" t="n">
         <v>0.0166</v>
       </c>
       <c r="J5" s="36" t="n">
-        <v>0.229937</v>
+        <v>0.230068</v>
       </c>
       <c r="K5" s="35" t="n">
         <v>22</v>
@@ -2024,46 +2126,46 @@
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
         <is>
-          <t>ACE 미국500데일리타겟커버드콜(합성)</t>
+          <t>RISE 미국테크100데일리고정커버드콜</t>
         </is>
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>480030</t>
+          <t>491620</t>
         </is>
       </c>
       <c r="C6" s="34" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>KB자산운용</t>
         </is>
       </c>
       <c r="D6" s="35" t="n">
-        <v>9555</v>
+        <v>10235</v>
       </c>
       <c r="E6" s="35" t="n">
-        <v>160608000000</v>
+        <v>560567000000</v>
       </c>
       <c r="F6" s="35" t="n">
-        <v>1353291479</v>
+        <v>7569401285</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>0.005391</v>
+        <v>0.005748</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>0.1277</v>
+        <v>0.2021</v>
       </c>
       <c r="I6" s="36" t="n">
-        <v>0.0199</v>
+        <v>0.0166</v>
       </c>
       <c r="J6" s="36" t="n">
-        <v>0.203349</v>
+        <v>0.219834</v>
       </c>
       <c r="K6" s="35" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L6" s="34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M6" s="34" t="inlineStr">
@@ -2076,46 +2178,46 @@
     <row r="7">
       <c r="A7" s="34" t="inlineStr">
         <is>
-          <t>KODEX 테슬라커버드콜채권혼합액티브</t>
+          <t>ACE 미국500데일리타겟커버드콜(합성)</t>
         </is>
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>475080</t>
+          <t>480030</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>7835</v>
+        <v>9545</v>
       </c>
       <c r="E7" s="35" t="n">
-        <v>285403500000</v>
+        <v>160608000000</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>1453498845</v>
+        <v>1353441866</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>0.005215</v>
+        <v>0.005391</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>0.1065</v>
+        <v>0.1502</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>0.0125</v>
+        <v>0.0199</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>0.164135</v>
+        <v>0.203562</v>
       </c>
       <c r="K7" s="35" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L7" s="34" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M7" s="34" t="inlineStr">
@@ -2128,46 +2230,46 @@
     <row r="8">
       <c r="A8" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국S&amp;P500데일리커버드콜OTM</t>
+          <t>RISE 미국배당100데일리고정커버드콜</t>
         </is>
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>0005A0</t>
+          <t>490600</t>
         </is>
       </c>
       <c r="C8" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>KB자산운용</t>
         </is>
       </c>
       <c r="D8" s="35" t="n">
-        <v>9235</v>
+        <v>8865</v>
       </c>
       <c r="E8" s="35" t="n">
-        <v>198660000000</v>
+        <v>168973500000</v>
       </c>
       <c r="F8" s="35" t="n">
-        <v>1972784396</v>
+        <v>2335548906</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>0.005639999999999999</v>
+        <v>0.005953000000000001</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>0.1242</v>
+        <v>0.1459</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>0.0124</v>
+        <v>0.01</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>0.160368</v>
+        <v>0.164354</v>
       </c>
       <c r="K8" s="35" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L8" s="34" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M8" s="34" t="inlineStr">
@@ -2180,12 +2282,12 @@
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국AI테크TOP10타겟커버드콜</t>
+          <t>KODEX 테슬라커버드콜채권혼합액티브</t>
         </is>
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>483280</t>
+          <t>475080</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
@@ -2194,28 +2296,28 @@
         </is>
       </c>
       <c r="D9" s="35" t="n">
-        <v>11510</v>
+        <v>7830</v>
       </c>
       <c r="E9" s="35" t="n">
-        <v>451950000000</v>
+        <v>285403500000</v>
       </c>
       <c r="F9" s="35" t="n">
-        <v>2928096453</v>
+        <v>1454332738</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>0.005830999999999999</v>
+        <v>0.005215</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>0.2195</v>
+        <v>0.1243</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>0.0123</v>
+        <v>0.0125</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>0.159861</v>
+        <v>0.16424</v>
       </c>
       <c r="K9" s="35" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L9" s="34" t="inlineStr">
         <is>
@@ -2232,42 +2334,42 @@
     <row r="10">
       <c r="A10" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국30년국채타겟커버드콜(합성 H)</t>
+          <t>TIGER 미국AI빅테크10타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>481060</t>
+          <t>493810</t>
         </is>
       </c>
       <c r="C10" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="D10" s="35" t="n">
-        <v>7260</v>
+        <v>11110</v>
       </c>
       <c r="E10" s="35" t="n">
-        <v>740576850000</v>
+        <v>240761500000</v>
       </c>
       <c r="F10" s="35" t="n">
-        <v>4086084405</v>
+        <v>1833470044</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>0.003244</v>
+        <v>0.004813</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.2183</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>0.0101</v>
+        <v>0.0124</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>0.132782</v>
+        <v>0.163456</v>
       </c>
       <c r="K10" s="35" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L10" s="34" t="inlineStr">
         <is>
@@ -2284,12 +2386,12 @@
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국배당다우존스타겟커버드콜</t>
+          <t>KODEX 미국S&amp;P500데일리커버드콜OTM</t>
         </is>
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>483290</t>
+          <t>0005A0</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
@@ -2298,28 +2400,28 @@
         </is>
       </c>
       <c r="D11" s="35" t="n">
-        <v>10220</v>
+        <v>9235</v>
       </c>
       <c r="E11" s="35" t="n">
-        <v>177915000000</v>
+        <v>198660000000</v>
       </c>
       <c r="F11" s="35" t="n">
-        <v>2277473311</v>
+        <v>1973049132</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>0.005798</v>
+        <v>0.005639999999999999</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>0.1321</v>
+        <v>0.1473</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>0.0098</v>
+        <v>0.0124</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>0.121918</v>
+        <v>0.160368</v>
       </c>
       <c r="K11" s="35" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L11" s="34" t="inlineStr">
         <is>
@@ -2336,690 +2438,660 @@
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
         <is>
+          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>486290</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="n">
+        <v>10235</v>
+      </c>
+      <c r="E12" s="35" t="n">
+        <v>2435426000000</v>
+      </c>
+      <c r="F12" s="35" t="n">
+        <v>29766278844</v>
+      </c>
+      <c r="G12" s="36" t="n">
+        <v>0.004563</v>
+      </c>
+      <c r="H12" s="36" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="I12" s="36" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="J12" s="36" t="n">
+        <v>0.160039</v>
+      </c>
+      <c r="K12" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="L12" s="34" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M12" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N12" s="34" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>KODEX 미국AI테크TOP10타겟커버드콜</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>483280</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>11505</v>
+      </c>
+      <c r="E13" s="35" t="n">
+        <v>451950000000</v>
+      </c>
+      <c r="F13" s="35" t="n">
+        <v>2928535970</v>
+      </c>
+      <c r="G13" s="36" t="n">
+        <v>0.005830999999999999</v>
+      </c>
+      <c r="H13" s="36" t="n">
+        <v>0.2452</v>
+      </c>
+      <c r="I13" s="36" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="J13" s="36" t="n">
+        <v>0.15993</v>
+      </c>
+      <c r="K13" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="L13" s="34" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M13" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N13" s="34" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>TIGER 미국30년국채커버드콜액티브(H)</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>476550</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="n">
+        <v>6690</v>
+      </c>
+      <c r="E14" s="35" t="n">
+        <v>756407750000</v>
+      </c>
+      <c r="F14" s="35" t="n">
+        <v>7955288250</v>
+      </c>
+      <c r="G14" s="36" t="n">
+        <v>0.007784</v>
+      </c>
+      <c r="H14" s="36" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="I14" s="36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J14" s="36" t="n">
+        <v>0.135426</v>
+      </c>
+      <c r="K14" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="L14" s="34" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M14" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N14" s="34" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>KODEX 미국30년국채타겟커버드콜(합성 H)</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>481060</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="n">
+        <v>7265</v>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>740576850000</v>
+      </c>
+      <c r="F15" s="35" t="n">
+        <v>4086810522</v>
+      </c>
+      <c r="G15" s="36" t="n">
+        <v>0.003244</v>
+      </c>
+      <c r="H15" s="36" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="I15" s="36" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="J15" s="36" t="n">
+        <v>0.132691</v>
+      </c>
+      <c r="K15" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="L15" s="34" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M15" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N15" s="34" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>SOL 미국30년국채커버드콜(합성)</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>473330</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="n">
+        <v>7780</v>
+      </c>
+      <c r="E16" s="35" t="n">
+        <v>272513750000</v>
+      </c>
+      <c r="F16" s="35" t="n">
+        <v>2163579550</v>
+      </c>
+      <c r="G16" s="36" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="H16" s="36" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="I16" s="36" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="J16" s="36" t="n">
+        <v>0.13072</v>
+      </c>
+      <c r="K16" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="L16" s="34" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M16" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N16" s="34" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>TIGER 미국나스닥100커버드콜(합성)</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>441680</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>10615</v>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>279306000000</v>
+      </c>
+      <c r="F17" s="35" t="n">
+        <v>960115974</v>
+      </c>
+      <c r="G17" s="36" t="n">
+        <v>0.004923</v>
+      </c>
+      <c r="H17" s="36" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="I17" s="36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J17" s="36" t="n">
+        <v>0.126236</v>
+      </c>
+      <c r="K17" s="35" t="n">
+        <v>47</v>
+      </c>
+      <c r="L17" s="34" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M17" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N17" s="34" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>KODEX 미국배당다우존스타겟커버드콜</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>483290</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="n">
+        <v>10230</v>
+      </c>
+      <c r="E18" s="35" t="n">
+        <v>177915000000</v>
+      </c>
+      <c r="F18" s="35" t="n">
+        <v>2277591278</v>
+      </c>
+      <c r="G18" s="36" t="n">
+        <v>0.005798</v>
+      </c>
+      <c r="H18" s="36" t="n">
+        <v>0.1572</v>
+      </c>
+      <c r="I18" s="36" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="J18" s="36" t="n">
+        <v>0.121799</v>
+      </c>
+      <c r="K18" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="L18" s="34" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M18" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N18" s="34" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>TIGER 미국배당다우존스타겟데일리커버드콜</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>0008S0</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="n">
+        <v>9770</v>
+      </c>
+      <c r="E19" s="35" t="n">
+        <v>315077000000</v>
+      </c>
+      <c r="F19" s="35" t="n">
+        <v>3345510671</v>
+      </c>
+      <c r="G19" s="36" t="n">
+        <v>0.004797</v>
+      </c>
+      <c r="H19" s="36" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="I19" s="36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J19" s="36" t="n">
+        <v>0.120471</v>
+      </c>
+      <c r="K19" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="L19" s="34" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M19" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N19" s="34" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>TIGER 미국S&amp;P500타겟데일리커버드콜</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>482730</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="n">
+        <v>11445</v>
+      </c>
+      <c r="E20" s="35" t="n">
+        <v>657225000000</v>
+      </c>
+      <c r="F20" s="35" t="n">
+        <v>4930903583</v>
+      </c>
+      <c r="G20" s="36" t="n">
+        <v>0.004313</v>
+      </c>
+      <c r="H20" s="36" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="I20" s="36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J20" s="36" t="n">
+        <v>0.107034</v>
+      </c>
+      <c r="K20" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="L20" s="34" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M20" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N20" s="34" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>TIGER 미국테크TOP10타겟커버드콜</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>474220</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="n">
+        <v>14695</v>
+      </c>
+      <c r="E21" s="35" t="n">
+        <v>413976000000</v>
+      </c>
+      <c r="F21" s="35" t="n">
+        <v>1732040955</v>
+      </c>
+      <c r="G21" s="36" t="n">
+        <v>0.006686</v>
+      </c>
+      <c r="H21" s="36" t="n">
+        <v>0.1938</v>
+      </c>
+      <c r="I21" s="36" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="J21" s="36" t="n">
+        <v>0.106703</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="L21" s="34" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M21" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N21" s="34" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>TIGER 미국배당다우존스타겟커버드콜2호</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>458760</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="n">
+        <v>10880</v>
+      </c>
+      <c r="E22" s="35" t="n">
+        <v>699584000000</v>
+      </c>
+      <c r="F22" s="35" t="n">
+        <v>3403357256</v>
+      </c>
+      <c r="G22" s="36" t="n">
+        <v>0.005643</v>
+      </c>
+      <c r="H22" s="36" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="I22" s="36" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J22" s="36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="L22" s="34" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M22" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N22" s="34" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
           <t>KODEX 미국배당커버드콜액티브</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>441640</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D23" s="35" t="n">
         <v>12340</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E23" s="35" t="n">
         <v>1701540000000</v>
       </c>
-      <c r="F12" s="35" t="n">
-        <v>12375893436</v>
-      </c>
-      <c r="G12" s="36" t="n">
+      <c r="F23" s="35" t="n">
+        <v>12378618519</v>
+      </c>
+      <c r="G23" s="36" t="n">
         <v>0.003631</v>
       </c>
-      <c r="H12" s="36" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="I12" s="36" t="n">
+      <c r="H23" s="36" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="I23" s="36" t="n">
         <v>0.007800000000000001</v>
       </c>
-      <c r="J12" s="36" t="n">
+      <c r="J23" s="36" t="n">
         <v>0.09594799999999999</v>
       </c>
-      <c r="K12" s="35" t="n">
+      <c r="K23" s="35" t="n">
         <v>48</v>
       </c>
-      <c r="L12" s="34" t="inlineStr">
+      <c r="L23" s="34" t="inlineStr">
         <is>
           <t>20260914</t>
         </is>
       </c>
-      <c r="M12" s="34" t="inlineStr">
+      <c r="M23" s="34" t="inlineStr">
         <is>
           <t>채택</t>
         </is>
       </c>
-      <c r="N12" s="34" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="37" t="inlineStr">
-        <is>
-          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
-        </is>
-      </c>
-      <c r="B13" s="37" t="inlineStr">
-        <is>
-          <t>480040</t>
-        </is>
-      </c>
-      <c r="C13" s="37" t="inlineStr">
-        <is>
-          <t>한국투신운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D13" s="38" t="n">
-        <v>13330</v>
-      </c>
-      <c r="E13" s="38" t="n">
-        <v>181016000000</v>
-      </c>
-      <c r="F13" s="38" t="n">
-        <v>3486448473</v>
-      </c>
-      <c r="G13" s="39" t="n">
-        <v>0.005406999999999999</v>
-      </c>
-      <c r="H13" s="39" t="n">
-        <v>0.3931</v>
-      </c>
-      <c r="I13" s="39" t="n">
-        <v>0.0303</v>
-      </c>
-      <c r="J13" s="39" t="n">
-        <v>0.261215</v>
-      </c>
-      <c r="K13" s="38" t="n">
-        <v>29</v>
-      </c>
-      <c r="L13" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M13" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N13" s="37" t="inlineStr">
-        <is>
-          <t>변동성 39.3%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="37" t="inlineStr">
-        <is>
-          <t>ACE 미국배당퀄리티+커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>0049M0</t>
-        </is>
-      </c>
-      <c r="C14" s="37" t="inlineStr">
-        <is>
-          <t>한국투신운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D14" s="38" t="n">
-        <v>11015</v>
-      </c>
-      <c r="E14" s="38" t="n">
-        <v>78171000000</v>
-      </c>
-      <c r="F14" s="38" t="n">
-        <v>379498783</v>
-      </c>
-      <c r="G14" s="39" t="n">
-        <v>0.005323</v>
-      </c>
-      <c r="H14" s="39" t="n">
-        <v>0.1032</v>
-      </c>
-      <c r="I14" s="39" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="J14" s="39" t="n">
-        <v>0.075624</v>
-      </c>
-      <c r="K14" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="L14" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M14" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N14" s="37" t="inlineStr">
-        <is>
-          <t>60일 거래대금 3.8억(기준 5억 미만)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="37" t="inlineStr">
-        <is>
-          <t>FOCUS AI반도체위클리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B15" s="37" t="inlineStr">
-        <is>
-          <t>0176P0</t>
-        </is>
-      </c>
-      <c r="C15" s="37" t="inlineStr">
-        <is>
-          <t>브이아이자산운용</t>
-        </is>
-      </c>
-      <c r="D15" s="38" t="n">
-        <v>12650</v>
-      </c>
-      <c r="E15" s="38" t="n">
-        <v>6864000000</v>
-      </c>
-      <c r="F15" s="38" t="n">
-        <v>168941906</v>
-      </c>
-      <c r="G15" s="39" t="n">
-        <v>0.003711</v>
-      </c>
-      <c r="H15" s="39" t="n">
-        <v>0.7903</v>
-      </c>
-      <c r="I15" s="39" t="n">
-        <v>0.0143</v>
-      </c>
-      <c r="J15" s="39" t="n"/>
-      <c r="K15" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M15" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N15" s="37" t="inlineStr">
-        <is>
-          <t>순자산 69억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 79.0%(기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>FOCUS 알리바바미국채커버드콜혼합</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>0073X0</t>
-        </is>
-      </c>
-      <c r="C16" s="37" t="inlineStr">
-        <is>
-          <t>브이아이자산운용</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="n">
-        <v>8655</v>
-      </c>
-      <c r="E16" s="38" t="n">
-        <v>4760250000</v>
-      </c>
-      <c r="F16" s="38" t="n">
-        <v>30593823</v>
-      </c>
-      <c r="G16" s="39" t="n">
-        <v>0.01601</v>
-      </c>
-      <c r="H16" s="39" t="n">
-        <v>0.1739</v>
-      </c>
-      <c r="I16" s="39" t="n">
-        <v>0.0091</v>
-      </c>
-      <c r="J16" s="39" t="n">
-        <v>0.148469</v>
-      </c>
-      <c r="K16" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="L16" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M16" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N16" s="37" t="inlineStr">
-        <is>
-          <t>순자산 48억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="37" t="inlineStr">
-        <is>
-          <t>KIWOOM 코스닥150커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B17" s="37" t="inlineStr">
-        <is>
-          <t>0198A0</t>
-        </is>
-      </c>
-      <c r="C17" s="37" t="inlineStr">
-        <is>
-          <t>키움투자자산운용</t>
-        </is>
-      </c>
-      <c r="D17" s="38" t="n">
-        <v>8390</v>
-      </c>
-      <c r="E17" s="38" t="n">
-        <v>72688500000</v>
-      </c>
-      <c r="F17" s="38" t="n">
-        <v>4939566816</v>
-      </c>
-      <c r="G17" s="39" t="n">
-        <v>0.006657</v>
-      </c>
-      <c r="H17" s="39" t="n"/>
-      <c r="I17" s="39" t="n">
-        <v>0.0243</v>
-      </c>
-      <c r="J17" s="39" t="n"/>
-      <c r="K17" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M17" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N17" s="37" t="inlineStr">
-        <is>
-          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 200커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>0219E0</t>
-        </is>
-      </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="n">
-        <v>8170</v>
-      </c>
-      <c r="E18" s="38" t="n">
-        <v>726902000000</v>
-      </c>
-      <c r="F18" s="38" t="n">
-        <v>46364463254</v>
-      </c>
-      <c r="G18" s="39" t="n">
-        <v>0.005278000000000001</v>
-      </c>
-      <c r="H18" s="39" t="n"/>
-      <c r="I18" s="39" t="n">
-        <v>0.0193</v>
-      </c>
-      <c r="J18" s="39" t="n"/>
-      <c r="K18" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M18" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N18" s="37" t="inlineStr">
-        <is>
-          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 200타겟위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B19" s="37" t="inlineStr">
-        <is>
-          <t>498400</t>
-        </is>
-      </c>
-      <c r="C19" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D19" s="38" t="n">
-        <v>19760</v>
-      </c>
-      <c r="E19" s="38" t="n">
-        <v>5759831000000</v>
-      </c>
-      <c r="F19" s="38" t="n">
-        <v>176372716854</v>
-      </c>
-      <c r="G19" s="39" t="n">
-        <v>0.005095</v>
-      </c>
-      <c r="H19" s="39" t="n">
-        <v>0.5544</v>
-      </c>
-      <c r="I19" s="39" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="J19" s="39" t="n">
-        <v>0.158198</v>
-      </c>
-      <c r="K19" s="38" t="n">
-        <v>21</v>
-      </c>
-      <c r="L19" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M19" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N19" s="37" t="inlineStr">
-        <is>
-          <t>변동성 55.4%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 금융고배당TOP10타겟위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B20" s="37" t="inlineStr">
-        <is>
-          <t>498410</t>
-        </is>
-      </c>
-      <c r="C20" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="n">
-        <v>11980</v>
-      </c>
-      <c r="E20" s="38" t="n">
-        <v>843040000000</v>
-      </c>
-      <c r="F20" s="38" t="n">
-        <v>22954159587</v>
-      </c>
-      <c r="G20" s="39" t="n">
-        <v>0.006697</v>
-      </c>
-      <c r="H20" s="39" t="n">
-        <v>0.3047</v>
-      </c>
-      <c r="I20" s="39" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="J20" s="39" t="n">
-        <v>0.157095</v>
-      </c>
-      <c r="K20" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="L20" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M20" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N20" s="37" t="inlineStr">
-        <is>
-          <t>변동성 30.5%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 미국S&amp;P500변동성확대시커버드콜</t>
-        </is>
-      </c>
-      <c r="B21" s="37" t="inlineStr">
-        <is>
-          <t>0089C0</t>
-        </is>
-      </c>
-      <c r="C21" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D21" s="38" t="n">
-        <v>11195</v>
-      </c>
-      <c r="E21" s="38" t="n">
-        <v>42541000000</v>
-      </c>
-      <c r="F21" s="38" t="n">
-        <v>369259763</v>
-      </c>
-      <c r="G21" s="39" t="n">
-        <v>0.006338</v>
-      </c>
-      <c r="H21" s="39" t="n">
-        <v>0.1316</v>
-      </c>
-      <c r="I21" s="39" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="J21" s="39" t="n">
-        <v>0.022242</v>
-      </c>
-      <c r="K21" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="L21" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M21" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N21" s="37" t="inlineStr">
-        <is>
-          <t>60일 거래대금 3.7억(기준 5억 미만)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 미국성장커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>0144L0</t>
-        </is>
-      </c>
-      <c r="C22" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D22" s="38" t="n">
-        <v>9310</v>
-      </c>
-      <c r="E22" s="38" t="n">
-        <v>339450000000</v>
-      </c>
-      <c r="F22" s="38" t="n">
-        <v>2519202827</v>
-      </c>
-      <c r="G22" s="39" t="n">
-        <v>0.006395</v>
-      </c>
-      <c r="H22" s="39" t="n">
-        <v>0.1605</v>
-      </c>
-      <c r="I22" s="39" t="n">
-        <v>0.009899999999999999</v>
-      </c>
-      <c r="J22" s="39" t="n"/>
-      <c r="K22" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M22" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N22" s="37" t="inlineStr">
-        <is>
-          <t>분배 이력 8개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 반도체타겟위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B23" s="37" t="inlineStr">
-        <is>
-          <t>0190G0</t>
-        </is>
-      </c>
-      <c r="C23" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D23" s="38" t="n">
-        <v>8700</v>
-      </c>
-      <c r="E23" s="38" t="n">
-        <v>166945000000</v>
-      </c>
-      <c r="F23" s="38" t="n">
-        <v>8915959999</v>
-      </c>
-      <c r="G23" s="39" t="n">
-        <v>0.006131</v>
-      </c>
-      <c r="H23" s="39" t="n">
-        <v>0.8618000000000001</v>
-      </c>
-      <c r="I23" s="39" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="J23" s="39" t="n"/>
-      <c r="K23" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M23" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N23" s="37" t="inlineStr">
-        <is>
-          <t>변동성 86.2%(기준 25% 초과), 분배 이력 4개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
+      <c r="N23" s="34" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="37" t="inlineStr">
         <is>
-          <t>PLUS 200위클리커버드콜채권혼합</t>
+          <t>ACE 고배당주Plus커버드콜액티브</t>
         </is>
       </c>
       <c r="B24" s="37" t="inlineStr">
         <is>
-          <t>0203D0</t>
+          <t>0199C0</t>
         </is>
       </c>
       <c r="C24" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D24" s="38" t="n">
-        <v>8820</v>
+        <v>9230</v>
       </c>
       <c r="E24" s="38" t="n">
-        <v>10560000000</v>
+        <v>138375000000</v>
       </c>
       <c r="F24" s="38" t="n">
-        <v>272818632</v>
+        <v>6507497157</v>
       </c>
       <c r="G24" s="39" t="n">
-        <v>0.004914</v>
+        <v>0.004522</v>
       </c>
       <c r="H24" s="39" t="n">
-        <v>0.3748</v>
+        <v>0.3598</v>
       </c>
       <c r="I24" s="39" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0179</v>
       </c>
       <c r="J24" s="39" t="n"/>
       <c r="K24" s="38" t="n">
@@ -3037,49 +3109,53 @@
       </c>
       <c r="N24" s="37" t="inlineStr">
         <is>
-          <t>순자산 106억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 37.5%(기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 36.0%(기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="37" t="inlineStr">
         <is>
-          <t>PLUS 200커버드콜액티브</t>
+          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
         </is>
       </c>
       <c r="B25" s="37" t="inlineStr">
         <is>
-          <t>0210E0</t>
+          <t>480040</t>
         </is>
       </c>
       <c r="C25" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>7160</v>
+        <v>13350</v>
       </c>
       <c r="E25" s="38" t="n">
-        <v>66881000000</v>
+        <v>181016000000</v>
       </c>
       <c r="F25" s="38" t="n">
-        <v>3119142383</v>
+        <v>3487093680</v>
       </c>
       <c r="G25" s="39" t="n">
-        <v>0.006020999999999999</v>
-      </c>
-      <c r="H25" s="39" t="n"/>
+        <v>0.005406999999999999</v>
+      </c>
+      <c r="H25" s="39" t="n">
+        <v>0.4411</v>
+      </c>
       <c r="I25" s="39" t="n">
-        <v>0.0194</v>
-      </c>
-      <c r="J25" s="39" t="n"/>
+        <v>0.0303</v>
+      </c>
+      <c r="J25" s="39" t="n">
+        <v>0.260824</v>
+      </c>
       <c r="K25" s="38" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="L25" s="37" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M25" s="37" t="inlineStr">
@@ -3089,53 +3165,53 @@
       </c>
       <c r="N25" s="37" t="inlineStr">
         <is>
-          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 44.1%(기준 25% 초과)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="37" t="inlineStr">
         <is>
-          <t>PLUS 고배당주위클리고정커버드콜</t>
+          <t>ACE 미국배당퀄리티+커버드콜액티브</t>
         </is>
       </c>
       <c r="B26" s="37" t="inlineStr">
         <is>
-          <t>0018C0</t>
+          <t>0049M0</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D26" s="38" t="n">
-        <v>10580</v>
+        <v>11015</v>
       </c>
       <c r="E26" s="38" t="n">
-        <v>80370000000</v>
+        <v>78171000000</v>
       </c>
       <c r="F26" s="38" t="n">
-        <v>1033420063</v>
+        <v>379512001</v>
       </c>
       <c r="G26" s="39" t="n">
-        <v>0.005958</v>
+        <v>0.005323</v>
       </c>
       <c r="H26" s="39" t="n">
-        <v>0.2777</v>
+        <v>0.1288</v>
       </c>
       <c r="I26" s="39" t="n">
-        <v>0.0124</v>
+        <v>0.006</v>
       </c>
       <c r="J26" s="39" t="n">
-        <v>0.168904</v>
+        <v>0.075624</v>
       </c>
       <c r="K26" s="38" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L26" s="37" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M26" s="37" t="inlineStr">
@@ -3145,49 +3221,47 @@
       </c>
       <c r="N26" s="37" t="inlineStr">
         <is>
-          <t>변동성 27.8%(기준 25% 초과)</t>
+          <t>60일 거래대금 3.8억(기준 5억 미만)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="37" t="inlineStr">
         <is>
-          <t>PLUS 고배당주위클리커버드콜</t>
+          <t>FOCUS AI반도체위클리고정커버드콜</t>
         </is>
       </c>
       <c r="B27" s="37" t="inlineStr">
         <is>
-          <t>489030</t>
+          <t>0176P0</t>
         </is>
       </c>
       <c r="C27" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>브이아이자산운용</t>
         </is>
       </c>
       <c r="D27" s="38" t="n">
-        <v>6460</v>
+        <v>12650</v>
       </c>
       <c r="E27" s="38" t="n">
-        <v>303208500000</v>
+        <v>6864000000</v>
       </c>
       <c r="F27" s="38" t="n">
-        <v>4298995360</v>
+        <v>168941906</v>
       </c>
       <c r="G27" s="39" t="n">
-        <v>0.008243</v>
+        <v>0.003711</v>
       </c>
       <c r="H27" s="39" t="n">
-        <v>0.2836</v>
+        <v>0.7998999999999999</v>
       </c>
       <c r="I27" s="39" t="n">
-        <v>0.0148</v>
-      </c>
-      <c r="J27" s="39" t="n">
-        <v>0.234985</v>
-      </c>
+        <v>0.0143</v>
+      </c>
+      <c r="J27" s="39" t="n"/>
       <c r="K27" s="38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L27" s="37" t="inlineStr">
         <is>
@@ -3201,53 +3275,53 @@
       </c>
       <c r="N27" s="37" t="inlineStr">
         <is>
-          <t>변동성 28.4%(기준 25% 초과)</t>
+          <t>순자산 69억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 80.0%(기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="37" t="inlineStr">
         <is>
-          <t>PLUS 미국배당증가성장주데일리커버드콜</t>
+          <t>FOCUS 알리바바미국채커버드콜혼합</t>
         </is>
       </c>
       <c r="B28" s="37" t="inlineStr">
         <is>
-          <t>494420</t>
+          <t>0073X0</t>
         </is>
       </c>
       <c r="C28" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>브이아이자산운용</t>
         </is>
       </c>
       <c r="D28" s="38" t="n">
-        <v>8670</v>
+        <v>8655</v>
       </c>
       <c r="E28" s="38" t="n">
-        <v>15588000000</v>
+        <v>4760250000</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>115226046</v>
+        <v>30593823</v>
       </c>
       <c r="G28" s="39" t="n">
-        <v>0.007707</v>
+        <v>0.01601</v>
       </c>
       <c r="H28" s="39" t="n">
-        <v>0.1232</v>
+        <v>0.165</v>
       </c>
       <c r="I28" s="39" t="n">
-        <v>0.0119</v>
+        <v>0.0091</v>
       </c>
       <c r="J28" s="39" t="n">
-        <v>0.14925</v>
+        <v>0.148469</v>
       </c>
       <c r="K28" s="38" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="L28" s="37" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M28" s="37" t="inlineStr">
@@ -3257,47 +3331,45 @@
       </c>
       <c r="N28" s="37" t="inlineStr">
         <is>
-          <t>순자산 156억(기준 300억 미만), 60일 거래대금 1.2억(기준 5억 미만)</t>
+          <t>순자산 48억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="37" t="inlineStr">
         <is>
-          <t>PLUS 차이나항셍테크위클리타겟커버드콜</t>
+          <t>KIWOOM 코스닥150커버드콜액티브</t>
         </is>
       </c>
       <c r="B29" s="37" t="inlineStr">
         <is>
-          <t>0128D0</t>
+          <t>0198A0</t>
         </is>
       </c>
       <c r="C29" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="D29" s="38" t="n">
-        <v>6395</v>
+        <v>8390</v>
       </c>
       <c r="E29" s="38" t="n">
-        <v>4476500000</v>
+        <v>72688500000</v>
       </c>
       <c r="F29" s="38" t="n">
-        <v>29887189</v>
+        <v>4940619075</v>
       </c>
       <c r="G29" s="39" t="n">
-        <v>0.01153</v>
-      </c>
-      <c r="H29" s="39" t="n">
-        <v>0.2227</v>
-      </c>
+        <v>0.006657</v>
+      </c>
+      <c r="H29" s="39" t="n"/>
       <c r="I29" s="39" t="n">
-        <v>0.0125</v>
+        <v>0.0243</v>
       </c>
       <c r="J29" s="39" t="n"/>
       <c r="K29" s="38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L29" s="37" t="inlineStr">
         <is>
@@ -3311,51 +3383,49 @@
       </c>
       <c r="N29" s="37" t="inlineStr">
         <is>
-          <t>순자산 45억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만), 분배 이력 9개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="37" t="inlineStr">
         <is>
-          <t>PLUS 테슬라위클리커버드콜채권혼합</t>
+          <t>KODEX 200커버드콜액티브</t>
         </is>
       </c>
       <c r="B30" s="37" t="inlineStr">
         <is>
-          <t>0132K0</t>
+          <t>0219E0</t>
         </is>
       </c>
       <c r="C30" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D30" s="38" t="n">
-        <v>7820</v>
+        <v>8155</v>
       </c>
       <c r="E30" s="38" t="n">
-        <v>108307000000</v>
+        <v>726902000000</v>
       </c>
       <c r="F30" s="38" t="n">
-        <v>1315612411</v>
+        <v>46375278871</v>
       </c>
       <c r="G30" s="39" t="n">
-        <v>0.006500000000000001</v>
-      </c>
-      <c r="H30" s="39" t="n">
-        <v>0.1107</v>
-      </c>
+        <v>0.005278000000000001</v>
+      </c>
+      <c r="H30" s="39" t="n"/>
       <c r="I30" s="39" t="n">
-        <v>0.02</v>
+        <v>0.0193</v>
       </c>
       <c r="J30" s="39" t="n"/>
       <c r="K30" s="38" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L30" s="37" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M30" s="37" t="inlineStr">
@@ -3365,53 +3435,53 @@
       </c>
       <c r="N30" s="37" t="inlineStr">
         <is>
-          <t>분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="37" t="inlineStr">
         <is>
-          <t>RISE 200고배당커버드콜ATM</t>
+          <t>KODEX 200타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B31" s="37" t="inlineStr">
         <is>
-          <t>290080</t>
+          <t>498400</t>
         </is>
       </c>
       <c r="C31" s="37" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D31" s="38" t="n">
-        <v>7410</v>
+        <v>19720</v>
       </c>
       <c r="E31" s="38" t="n">
-        <v>12614000000</v>
+        <v>5759831000000</v>
       </c>
       <c r="F31" s="38" t="n">
-        <v>168489528</v>
+        <v>176401662492</v>
       </c>
       <c r="G31" s="39" t="n">
-        <v>0.00636</v>
+        <v>0.005095</v>
       </c>
       <c r="H31" s="39" t="n">
-        <v>0.2843</v>
+        <v>0.5655</v>
       </c>
       <c r="I31" s="39" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0145</v>
       </c>
       <c r="J31" s="39" t="n">
-        <v>0.106883</v>
+        <v>0.158519</v>
       </c>
       <c r="K31" s="38" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="L31" s="37" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M31" s="37" t="inlineStr">
@@ -3421,49 +3491,49 @@
       </c>
       <c r="N31" s="37" t="inlineStr">
         <is>
-          <t>순자산 126억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 28.4%(기준 25% 초과)</t>
+          <t>변동성 56.6%(기준 25% 초과)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="37" t="inlineStr">
         <is>
-          <t>RISE 200위클리커버드콜</t>
+          <t>KODEX 금융고배당TOP10타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>475720</t>
+          <t>498410</t>
         </is>
       </c>
       <c r="C32" s="37" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D32" s="38" t="n">
-        <v>12395</v>
+        <v>11965</v>
       </c>
       <c r="E32" s="38" t="n">
-        <v>821275000000</v>
+        <v>843040000000</v>
       </c>
       <c r="F32" s="38" t="n">
-        <v>12907248624</v>
+        <v>22961390586</v>
       </c>
       <c r="G32" s="39" t="n">
-        <v>0.006305</v>
+        <v>0.006697</v>
       </c>
       <c r="H32" s="39" t="n">
-        <v>0.4251</v>
+        <v>0.3274</v>
       </c>
       <c r="I32" s="39" t="n">
-        <v>0.0185</v>
+        <v>0.0121</v>
       </c>
       <c r="J32" s="39" t="n">
-        <v>0.199274</v>
+        <v>0.157292</v>
       </c>
       <c r="K32" s="38" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L32" s="37" t="inlineStr">
         <is>
@@ -3477,47 +3547,55 @@
       </c>
       <c r="N32" s="37" t="inlineStr">
         <is>
-          <t>변동성 42.5%(기준 25% 초과)</t>
+          <t>변동성 32.7%(기준 25% 초과)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="37" t="inlineStr">
         <is>
-          <t>RISE 미국30년국채커버드콜(합성)</t>
+          <t>KODEX 미국S&amp;P500변동성확대시커버드콜</t>
         </is>
       </c>
       <c r="B33" s="37" t="inlineStr">
         <is>
-          <t>472830</t>
+          <t>0089C0</t>
         </is>
       </c>
       <c r="C33" s="37" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D33" s="38" t="n">
-        <v>7705</v>
+        <v>11170</v>
       </c>
       <c r="E33" s="38" t="n">
-        <v>42707250000</v>
+        <v>42541000000</v>
       </c>
       <c r="F33" s="38" t="n">
-        <v>286004344</v>
+        <v>369289199</v>
       </c>
       <c r="G33" s="39" t="n">
-        <v>0.003419</v>
+        <v>0.006338</v>
       </c>
       <c r="H33" s="39" t="n">
-        <v>0.1218</v>
-      </c>
-      <c r="I33" s="39" t="n"/>
-      <c r="J33" s="39" t="n"/>
+        <v>0.1398</v>
+      </c>
+      <c r="I33" s="39" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="J33" s="39" t="n">
+        <v>0.022292</v>
+      </c>
       <c r="K33" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="37" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="L33" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
       <c r="M33" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -3525,47 +3603,53 @@
       </c>
       <c r="N33" s="37" t="inlineStr">
         <is>
-          <t>60일 거래대금 2.9억(기준 5억 미만), 분배 이력 0개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>60일 거래대금 3.7억(기준 5억 미만)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="37" t="inlineStr">
         <is>
-          <t>RISE 미국AI밸류체인데일리고정커버드콜</t>
+          <t>KODEX 미국성장커버드콜액티브</t>
         </is>
       </c>
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>490590</t>
+          <t>0144L0</t>
         </is>
       </c>
       <c r="C34" s="37" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D34" s="38" t="n">
-        <v>13615</v>
+        <v>9305</v>
       </c>
       <c r="E34" s="38" t="n">
-        <v>760760000000</v>
+        <v>339450000000</v>
       </c>
       <c r="F34" s="38" t="n">
-        <v>10120990174</v>
+        <v>2519327575</v>
       </c>
       <c r="G34" s="39" t="n">
-        <v>0.00578</v>
+        <v>0.006395</v>
       </c>
       <c r="H34" s="39" t="n">
-        <v>0.3286</v>
-      </c>
-      <c r="I34" s="39" t="n"/>
+        <v>0.1816</v>
+      </c>
+      <c r="I34" s="39" t="n">
+        <v>0.009899999999999999</v>
+      </c>
       <c r="J34" s="39" t="n"/>
       <c r="K34" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="37" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="L34" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
       <c r="M34" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -3573,47 +3657,53 @@
       </c>
       <c r="N34" s="37" t="inlineStr">
         <is>
-          <t>변동성 32.9%(기준 25% 초과), 분배 이력 0개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>분배 이력 8개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="37" t="inlineStr">
         <is>
-          <t>RISE 미국S&amp;P500데일리고정커버드콜</t>
+          <t>KODEX 반도체타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B35" s="37" t="inlineStr">
         <is>
-          <t>0138T0</t>
+          <t>0190G0</t>
         </is>
       </c>
       <c r="C35" s="37" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>9230</v>
+        <v>8670</v>
       </c>
       <c r="E35" s="38" t="n">
-        <v>32305000000</v>
+        <v>166945000000</v>
       </c>
       <c r="F35" s="38" t="n">
-        <v>320046279</v>
+        <v>8916724632</v>
       </c>
       <c r="G35" s="39" t="n">
-        <v>0.006153</v>
+        <v>0.006131</v>
       </c>
       <c r="H35" s="39" t="n">
-        <v>0.1246</v>
-      </c>
-      <c r="I35" s="39" t="n"/>
+        <v>0.8571</v>
+      </c>
+      <c r="I35" s="39" t="n">
+        <v>0.0074</v>
+      </c>
       <c r="J35" s="39" t="n"/>
       <c r="K35" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="37" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="L35" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
       <c r="M35" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -3621,7 +3711,1569 @@
       </c>
       <c r="N35" s="37" t="inlineStr">
         <is>
-          <t>60일 거래대금 3.2억(기준 5억 미만), 분배 이력 0개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 85.7%(기준 25% 초과), 분배 이력 4개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 200위클리커버드콜채권혼합</t>
+        </is>
+      </c>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>0203D0</t>
+        </is>
+      </c>
+      <c r="C36" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D36" s="38" t="n">
+        <v>8805</v>
+      </c>
+      <c r="E36" s="38" t="n">
+        <v>10560000000</v>
+      </c>
+      <c r="F36" s="38" t="n">
+        <v>272946448</v>
+      </c>
+      <c r="G36" s="39" t="n">
+        <v>0.004914</v>
+      </c>
+      <c r="H36" s="39" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="I36" s="39" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="J36" s="39" t="n"/>
+      <c r="K36" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M36" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N36" s="37" t="inlineStr">
+        <is>
+          <t>순자산 106억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 38.1%(기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 200커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B37" s="37" t="inlineStr">
+        <is>
+          <t>0210E0</t>
+        </is>
+      </c>
+      <c r="C37" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D37" s="38" t="n">
+        <v>7135</v>
+      </c>
+      <c r="E37" s="38" t="n">
+        <v>66881000000</v>
+      </c>
+      <c r="F37" s="38" t="n">
+        <v>3119230075</v>
+      </c>
+      <c r="G37" s="39" t="n">
+        <v>0.006020999999999999</v>
+      </c>
+      <c r="H37" s="39" t="n"/>
+      <c r="I37" s="39" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="J37" s="39" t="n"/>
+      <c r="K37" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M37" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N37" s="37" t="inlineStr">
+        <is>
+          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 고배당주위클리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>0018C0</t>
+        </is>
+      </c>
+      <c r="C38" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D38" s="38" t="n">
+        <v>10575</v>
+      </c>
+      <c r="E38" s="38" t="n">
+        <v>80370000000</v>
+      </c>
+      <c r="F38" s="38" t="n">
+        <v>1033449479</v>
+      </c>
+      <c r="G38" s="39" t="n">
+        <v>0.005958</v>
+      </c>
+      <c r="H38" s="39" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="I38" s="39" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="J38" s="39" t="n">
+        <v>0.168983</v>
+      </c>
+      <c r="K38" s="38" t="n">
+        <v>19</v>
+      </c>
+      <c r="L38" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M38" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N38" s="37" t="inlineStr">
+        <is>
+          <t>변동성 26.7%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 고배당주위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>489030</t>
+        </is>
+      </c>
+      <c r="C39" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D39" s="38" t="n">
+        <v>6470</v>
+      </c>
+      <c r="E39" s="38" t="n">
+        <v>303208500000</v>
+      </c>
+      <c r="F39" s="38" t="n">
+        <v>4300148374</v>
+      </c>
+      <c r="G39" s="39" t="n">
+        <v>0.008243</v>
+      </c>
+      <c r="H39" s="39" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="I39" s="39" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="J39" s="39" t="n">
+        <v>0.234621</v>
+      </c>
+      <c r="K39" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="L39" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M39" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N39" s="37" t="inlineStr">
+        <is>
+          <t>변동성 30.7%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 미국배당증가성장주데일리커버드콜</t>
+        </is>
+      </c>
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>494420</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D40" s="38" t="n">
+        <v>8670</v>
+      </c>
+      <c r="E40" s="38" t="n">
+        <v>15588000000</v>
+      </c>
+      <c r="F40" s="38" t="n">
+        <v>115236450</v>
+      </c>
+      <c r="G40" s="39" t="n">
+        <v>0.007707</v>
+      </c>
+      <c r="H40" s="39" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="I40" s="39" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="J40" s="39" t="n">
+        <v>0.14925</v>
+      </c>
+      <c r="K40" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="L40" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M40" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N40" s="37" t="inlineStr">
+        <is>
+          <t>순자산 156억(기준 300억 미만), 60일 거래대금 1.2억(기준 5억 미만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 차이나항셍테크위클리타겟커버드콜</t>
+        </is>
+      </c>
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>0128D0</t>
+        </is>
+      </c>
+      <c r="C41" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D41" s="38" t="n">
+        <v>6395</v>
+      </c>
+      <c r="E41" s="38" t="n">
+        <v>4476500000</v>
+      </c>
+      <c r="F41" s="38" t="n">
+        <v>29887189</v>
+      </c>
+      <c r="G41" s="39" t="n">
+        <v>0.01153</v>
+      </c>
+      <c r="H41" s="39" t="n">
+        <v>0.2721</v>
+      </c>
+      <c r="I41" s="39" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J41" s="39" t="n"/>
+      <c r="K41" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="L41" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M41" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N41" s="37" t="inlineStr">
+        <is>
+          <t>순자산 45억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만), 변동성 27.2%(기준 25% 초과), 분배 이력 9개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 테슬라위클리커버드콜채권혼합</t>
+        </is>
+      </c>
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>0132K0</t>
+        </is>
+      </c>
+      <c r="C42" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D42" s="38" t="n">
+        <v>7817</v>
+      </c>
+      <c r="E42" s="38" t="n">
+        <v>108307000000</v>
+      </c>
+      <c r="F42" s="38" t="n">
+        <v>1315637734</v>
+      </c>
+      <c r="G42" s="39" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="H42" s="39" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="I42" s="39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J42" s="39" t="n"/>
+      <c r="K42" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="L42" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M42" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N42" s="37" t="inlineStr">
+        <is>
+          <t>분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="37" t="inlineStr">
+        <is>
+          <t>RISE 200고배당커버드콜ATM</t>
+        </is>
+      </c>
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>290080</t>
+        </is>
+      </c>
+      <c r="C43" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D43" s="38" t="n">
+        <v>7355</v>
+      </c>
+      <c r="E43" s="38" t="n">
+        <v>12614000000</v>
+      </c>
+      <c r="F43" s="38" t="n">
+        <v>168554500</v>
+      </c>
+      <c r="G43" s="39" t="n">
+        <v>0.00636</v>
+      </c>
+      <c r="H43" s="39" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="I43" s="39" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="J43" s="39" t="n">
+        <v>0.107682</v>
+      </c>
+      <c r="K43" s="38" t="n">
+        <v>49</v>
+      </c>
+      <c r="L43" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M43" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N43" s="37" t="inlineStr">
+        <is>
+          <t>순자산 126억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 31.0%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="37" t="inlineStr">
+        <is>
+          <t>RISE 200위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>475720</t>
+        </is>
+      </c>
+      <c r="C44" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D44" s="38" t="n">
+        <v>12380</v>
+      </c>
+      <c r="E44" s="38" t="n">
+        <v>821275000000</v>
+      </c>
+      <c r="F44" s="38" t="n">
+        <v>12908999692</v>
+      </c>
+      <c r="G44" s="39" t="n">
+        <v>0.006305</v>
+      </c>
+      <c r="H44" s="39" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="I44" s="39" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="J44" s="39" t="n">
+        <v>0.199515</v>
+      </c>
+      <c r="K44" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="L44" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M44" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N44" s="37" t="inlineStr">
+        <is>
+          <t>변동성 43.3%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t>RISE 미국30년국채커버드콜(합성)</t>
+        </is>
+      </c>
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>472830</t>
+        </is>
+      </c>
+      <c r="C45" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D45" s="38" t="n">
+        <v>7705</v>
+      </c>
+      <c r="E45" s="38" t="n">
+        <v>42707250000</v>
+      </c>
+      <c r="F45" s="38" t="n">
+        <v>286004344</v>
+      </c>
+      <c r="G45" s="39" t="n">
+        <v>0.003419</v>
+      </c>
+      <c r="H45" s="39" t="n">
+        <v>0.1409</v>
+      </c>
+      <c r="I45" s="39" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="J45" s="39" t="n">
+        <v>0.11499</v>
+      </c>
+      <c r="K45" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="L45" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M45" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N45" s="37" t="inlineStr">
+        <is>
+          <t>60일 거래대금 2.9억(기준 5억 미만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="37" t="inlineStr">
+        <is>
+          <t>RISE 미국AI밸류체인데일리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B46" s="37" t="inlineStr">
+        <is>
+          <t>490590</t>
+        </is>
+      </c>
+      <c r="C46" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D46" s="38" t="n">
+        <v>13615</v>
+      </c>
+      <c r="E46" s="38" t="n">
+        <v>760760000000</v>
+      </c>
+      <c r="F46" s="38" t="n">
+        <v>10122233904</v>
+      </c>
+      <c r="G46" s="39" t="n">
+        <v>0.00578</v>
+      </c>
+      <c r="H46" s="39" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="I46" s="39" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="J46" s="39" t="n">
+        <v>0.213147</v>
+      </c>
+      <c r="K46" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="L46" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M46" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N46" s="37" t="inlineStr">
+        <is>
+          <t>변동성 33.1%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="37" t="inlineStr">
+        <is>
+          <t>RISE 미국S&amp;P500데일리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B47" s="37" t="inlineStr">
+        <is>
+          <t>0138T0</t>
+        </is>
+      </c>
+      <c r="C47" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="n">
+        <v>9260</v>
+      </c>
+      <c r="E47" s="38" t="n">
+        <v>32305000000</v>
+      </c>
+      <c r="F47" s="38" t="n">
+        <v>320379491</v>
+      </c>
+      <c r="G47" s="39" t="n">
+        <v>0.006153</v>
+      </c>
+      <c r="H47" s="39" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="I47" s="39" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J47" s="39" t="n"/>
+      <c r="K47" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="L47" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M47" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N47" s="37" t="inlineStr">
+        <is>
+          <t>60일 거래대금 3.2억(기준 5억 미만), 분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="37" t="inlineStr">
+        <is>
+          <t>RISE 차이나테크TOP10위클리타겟커버드콜</t>
+        </is>
+      </c>
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>0094L0</t>
+        </is>
+      </c>
+      <c r="C48" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D48" s="38" t="n">
+        <v>7055</v>
+      </c>
+      <c r="E48" s="38" t="n">
+        <v>9870000000</v>
+      </c>
+      <c r="F48" s="38" t="n">
+        <v>60749389</v>
+      </c>
+      <c r="G48" s="39" t="n">
+        <v>0.011533</v>
+      </c>
+      <c r="H48" s="39" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="I48" s="39" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="J48" s="39" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="K48" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="L48" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M48" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N48" s="37" t="inlineStr">
+        <is>
+          <t>순자산 99억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만), 변동성 27.9%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="37" t="inlineStr">
+        <is>
+          <t>RISE 코리아밸류업위클리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>0094M0</t>
+        </is>
+      </c>
+      <c r="C49" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D49" s="38" t="n">
+        <v>16870</v>
+      </c>
+      <c r="E49" s="38" t="n">
+        <v>343230000000</v>
+      </c>
+      <c r="F49" s="38" t="n">
+        <v>9599979617</v>
+      </c>
+      <c r="G49" s="39" t="n">
+        <v>0.005637</v>
+      </c>
+      <c r="H49" s="39" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="I49" s="39" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="J49" s="39" t="n">
+        <v>0.248963</v>
+      </c>
+      <c r="K49" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="L49" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M49" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N49" s="37" t="inlineStr">
+        <is>
+          <t>변동성 45.8%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="37" t="inlineStr">
+        <is>
+          <t>RISE 코스닥커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B50" s="37" t="inlineStr">
+        <is>
+          <t>0223A0</t>
+        </is>
+      </c>
+      <c r="C50" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D50" s="38" t="n">
+        <v>10435</v>
+      </c>
+      <c r="E50" s="38" t="n">
+        <v>16624000000</v>
+      </c>
+      <c r="F50" s="38" t="n"/>
+      <c r="G50" s="39" t="n">
+        <v>0.003264</v>
+      </c>
+      <c r="H50" s="39" t="n"/>
+      <c r="I50" s="39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J50" s="39" t="n"/>
+      <c r="K50" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M50" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N50" s="37" t="inlineStr">
+        <is>
+          <t>순자산 166억(기준 300억 미만), 거래대금 미확인, 변동성 산출 불가(시세 이력 부족), 분배 이력 1개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="37" t="inlineStr">
+        <is>
+          <t>RISE 테슬라미국채타겟커버드콜혼합(합성)</t>
+        </is>
+      </c>
+      <c r="B51" s="37" t="inlineStr">
+        <is>
+          <t>0013R0</t>
+        </is>
+      </c>
+      <c r="C51" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D51" s="38" t="n">
+        <v>7620</v>
+      </c>
+      <c r="E51" s="38" t="n">
+        <v>27432000000</v>
+      </c>
+      <c r="F51" s="38" t="n">
+        <v>162123325</v>
+      </c>
+      <c r="G51" s="39" t="n">
+        <v>0.003495</v>
+      </c>
+      <c r="H51" s="39" t="n">
+        <v>0.1853</v>
+      </c>
+      <c r="I51" s="39" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="J51" s="39" t="n">
+        <v>0.183727</v>
+      </c>
+      <c r="K51" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="L51" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M51" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N51" s="37" t="inlineStr">
+        <is>
+          <t>순자산 274억(기준 300억 미만), 60일 거래대금 1.6억(기준 5억 미만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="37" t="inlineStr">
+        <is>
+          <t>SOL 200타겟위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B52" s="37" t="inlineStr">
+        <is>
+          <t>0167B0</t>
+        </is>
+      </c>
+      <c r="C52" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D52" s="38" t="n">
+        <v>11450</v>
+      </c>
+      <c r="E52" s="38" t="n">
+        <v>627507000000</v>
+      </c>
+      <c r="F52" s="38" t="n">
+        <v>21319332425</v>
+      </c>
+      <c r="G52" s="39" t="n">
+        <v>0.00345</v>
+      </c>
+      <c r="H52" s="39" t="n">
+        <v>0.6943</v>
+      </c>
+      <c r="I52" s="39" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="J52" s="39" t="n"/>
+      <c r="K52" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="L52" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M52" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N52" s="37" t="inlineStr">
+        <is>
+          <t>변동성 69.4%(기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>SOL 국제금커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B53" s="37" t="inlineStr">
+        <is>
+          <t>0022T0</t>
+        </is>
+      </c>
+      <c r="C53" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D53" s="38" t="n">
+        <v>12835</v>
+      </c>
+      <c r="E53" s="38" t="n">
+        <v>73074000000</v>
+      </c>
+      <c r="F53" s="38" t="n">
+        <v>1007373121</v>
+      </c>
+      <c r="G53" s="39" t="n">
+        <v>0.006737999999999999</v>
+      </c>
+      <c r="H53" s="39" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="I53" s="39" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="J53" s="39" t="n">
+        <v>0.04495499999999999</v>
+      </c>
+      <c r="K53" s="38" t="n">
+        <v>17</v>
+      </c>
+      <c r="L53" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M53" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N53" s="37" t="inlineStr">
+        <is>
+          <t>변동성 28.7%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t>SOL 미국500타겟데일리커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B54" s="37" t="inlineStr">
+        <is>
+          <t>494210</t>
+        </is>
+      </c>
+      <c r="C54" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D54" s="38" t="n">
+        <v>10630</v>
+      </c>
+      <c r="E54" s="38" t="n">
+        <v>7423500000</v>
+      </c>
+      <c r="F54" s="38" t="n">
+        <v>64447485</v>
+      </c>
+      <c r="G54" s="39" t="n">
+        <v>0.00621</v>
+      </c>
+      <c r="H54" s="39" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="I54" s="39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J54" s="39" t="n">
+        <v>0.126341</v>
+      </c>
+      <c r="K54" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="L54" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M54" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N54" s="37" t="inlineStr">
+        <is>
+          <t>순자산 74억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="37" t="inlineStr">
+        <is>
+          <t>SOL 팔란티어미국채커버드콜혼합</t>
+        </is>
+      </c>
+      <c r="B55" s="37" t="inlineStr">
+        <is>
+          <t>0040X0</t>
+        </is>
+      </c>
+      <c r="C55" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D55" s="38" t="n"/>
+      <c r="E55" s="38" t="n"/>
+      <c r="F55" s="38" t="n"/>
+      <c r="G55" s="39" t="n"/>
+      <c r="H55" s="39" t="n"/>
+      <c r="I55" s="39" t="n"/>
+      <c r="J55" s="39" t="n"/>
+      <c r="K55" s="38" t="n"/>
+      <c r="L55" s="37" t="n"/>
+      <c r="M55" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N55" s="37" t="inlineStr">
+        <is>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
+Call log:
+  - )</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="37" t="inlineStr">
+        <is>
+          <t>SOL 팔란티어커버드콜OTM채권혼합</t>
+        </is>
+      </c>
+      <c r="B56" s="37" t="inlineStr">
+        <is>
+          <t>0040Y0</t>
+        </is>
+      </c>
+      <c r="C56" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D56" s="38" t="n"/>
+      <c r="E56" s="38" t="n"/>
+      <c r="F56" s="38" t="n"/>
+      <c r="G56" s="39" t="n"/>
+      <c r="H56" s="39" t="n"/>
+      <c r="I56" s="39" t="n"/>
+      <c r="J56" s="39" t="n"/>
+      <c r="K56" s="38" t="n"/>
+      <c r="L56" s="37" t="n"/>
+      <c r="M56" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N56" s="37" t="inlineStr">
+        <is>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 200커버드콜</t>
+        </is>
+      </c>
+      <c r="B57" s="37" t="inlineStr">
+        <is>
+          <t>289480</t>
+        </is>
+      </c>
+      <c r="C57" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D57" s="38" t="n">
+        <v>12667</v>
+      </c>
+      <c r="E57" s="38" t="n">
+        <v>26512500000</v>
+      </c>
+      <c r="F57" s="38" t="n">
+        <v>429000383</v>
+      </c>
+      <c r="G57" s="39" t="n">
+        <v>0.007145</v>
+      </c>
+      <c r="H57" s="39" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="I57" s="39" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="J57" s="39" t="n">
+        <v>0.070419</v>
+      </c>
+      <c r="K57" s="38" t="n">
+        <v>51</v>
+      </c>
+      <c r="L57" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M57" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N57" s="37" t="inlineStr">
+        <is>
+          <t>순자산 265억(기준 300억 미만), 60일 거래대금 4.3억(기준 5억 미만), 변동성 38.3%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 200커버드콜OTM</t>
+        </is>
+      </c>
+      <c r="B58" s="37" t="inlineStr">
+        <is>
+          <t>166400</t>
+        </is>
+      </c>
+      <c r="C58" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D58" s="38" t="n">
+        <v>24020</v>
+      </c>
+      <c r="E58" s="38" t="n">
+        <v>11965000000</v>
+      </c>
+      <c r="F58" s="38" t="n">
+        <v>48230202</v>
+      </c>
+      <c r="G58" s="39" t="n">
+        <v>0.006403</v>
+      </c>
+      <c r="H58" s="39" t="n">
+        <v>0.4264</v>
+      </c>
+      <c r="I58" s="39" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="J58" s="39" t="n">
+        <v>0.039592</v>
+      </c>
+      <c r="K58" s="38" t="n">
+        <v>51</v>
+      </c>
+      <c r="L58" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M58" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N58" s="37" t="inlineStr">
+        <is>
+          <t>순자산 120억(기준 300억 미만), 60일 거래대금 0.5억(기준 5억 미만), 변동성 42.6%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 200타겟위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B59" s="37" t="inlineStr">
+        <is>
+          <t>0104N0</t>
+        </is>
+      </c>
+      <c r="C59" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D59" s="38" t="n">
+        <v>20277</v>
+      </c>
+      <c r="E59" s="38" t="n">
+        <v>208472000000</v>
+      </c>
+      <c r="F59" s="38" t="n">
+        <v>3412380553</v>
+      </c>
+      <c r="G59" s="39" t="n">
+        <v>0.003325</v>
+      </c>
+      <c r="H59" s="39" t="n">
+        <v>0.5911999999999999</v>
+      </c>
+      <c r="I59" s="39" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="J59" s="39" t="n">
+        <v>0.06066</v>
+      </c>
+      <c r="K59" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="L59" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M59" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N59" s="37" t="inlineStr">
+        <is>
+          <t>변동성 59.1%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 미국배당다우존스타겟커버드콜1호</t>
+        </is>
+      </c>
+      <c r="B60" s="37" t="inlineStr">
+        <is>
+          <t>458750</t>
+        </is>
+      </c>
+      <c r="C60" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D60" s="38" t="n">
+        <v>12835</v>
+      </c>
+      <c r="E60" s="38" t="n">
+        <v>66690000000</v>
+      </c>
+      <c r="F60" s="38" t="n">
+        <v>411171632</v>
+      </c>
+      <c r="G60" s="39" t="n">
+        <v>0.005842000000000001</v>
+      </c>
+      <c r="H60" s="39" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="I60" s="39" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="J60" s="39" t="n">
+        <v>0.059758</v>
+      </c>
+      <c r="K60" s="38" t="n">
+        <v>39</v>
+      </c>
+      <c r="L60" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M60" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N60" s="37" t="inlineStr">
+        <is>
+          <t>60일 거래대금 4.1억(기준 5억 미만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 반도체TOP10커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B61" s="37" t="inlineStr">
+        <is>
+          <t>0177R0</t>
+        </is>
+      </c>
+      <c r="C61" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D61" s="38" t="n">
+        <v>10810</v>
+      </c>
+      <c r="E61" s="38" t="n">
+        <v>818900000000</v>
+      </c>
+      <c r="F61" s="38" t="n">
+        <v>33027634212</v>
+      </c>
+      <c r="G61" s="39" t="n">
+        <v>0.005719999999999999</v>
+      </c>
+      <c r="H61" s="39" t="n">
+        <v>0.9128000000000001</v>
+      </c>
+      <c r="I61" s="39" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="J61" s="39" t="n"/>
+      <c r="K61" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="L61" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M61" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N61" s="37" t="inlineStr">
+        <is>
+          <t>변동성 91.3%(기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 배당커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B62" s="37" t="inlineStr">
+        <is>
+          <t>472150</t>
+        </is>
+      </c>
+      <c r="C62" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D62" s="38" t="n">
+        <v>19835</v>
+      </c>
+      <c r="E62" s="38" t="n">
+        <v>2396790000000</v>
+      </c>
+      <c r="F62" s="38" t="n">
+        <v>103328325983</v>
+      </c>
+      <c r="G62" s="39" t="n">
+        <v>0.006008</v>
+      </c>
+      <c r="H62" s="39" t="n">
+        <v>0.5731000000000001</v>
+      </c>
+      <c r="I62" s="39" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="J62" s="39" t="n">
+        <v>0.221074</v>
+      </c>
+      <c r="K62" s="38" t="n">
+        <v>33</v>
+      </c>
+      <c r="L62" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M62" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N62" s="37" t="inlineStr">
+        <is>
+          <t>변동성 57.3%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 엔비디아미국채커버드콜밸런스(합성)</t>
+        </is>
+      </c>
+      <c r="B63" s="37" t="inlineStr">
+        <is>
+          <t>0000D0</t>
+        </is>
+      </c>
+      <c r="C63" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D63" s="38" t="n">
+        <v>8735</v>
+      </c>
+      <c r="E63" s="38" t="n">
+        <v>60375000000</v>
+      </c>
+      <c r="F63" s="38" t="n">
+        <v>357325594</v>
+      </c>
+      <c r="G63" s="39" t="n">
+        <v>0.004741</v>
+      </c>
+      <c r="H63" s="39" t="n">
+        <v>0.1679</v>
+      </c>
+      <c r="I63" s="39" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="J63" s="39" t="n">
+        <v>0.137722</v>
+      </c>
+      <c r="K63" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="L63" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M63" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N63" s="37" t="inlineStr">
+        <is>
+          <t>60일 거래대금 3.6억(기준 5억 미만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 코리아배당다우존스위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B64" s="37" t="inlineStr">
+        <is>
+          <t>0104P0</t>
+        </is>
+      </c>
+      <c r="C64" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D64" s="38" t="n">
+        <v>10995</v>
+      </c>
+      <c r="E64" s="38" t="n">
+        <v>18742500000</v>
+      </c>
+      <c r="F64" s="38" t="n">
+        <v>267091677</v>
+      </c>
+      <c r="G64" s="39" t="n">
+        <v>0.004345</v>
+      </c>
+      <c r="H64" s="39" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="I64" s="39" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="J64" s="39" t="n"/>
+      <c r="K64" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="L64" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M64" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N64" s="37" t="inlineStr">
+        <is>
+          <t>순자산 187억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 31.1%(기준 25% 초과), 분배 이력 11개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
@@ -3711,14 +5363,14 @@
     <row r="12" ht="19" customHeight="1">
       <c r="B12" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 채택 9종목 — 유동성·변동성 기준을 통과한 월배당 커버드콜 ETF</t>
+          <t xml:space="preserve">     · 채택 20종목 — 유동성·변동성 기준을 통과한 월배당 커버드콜 ETF</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="B13" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 제외 23종목 — 사유는 [ETF데이터] 장 맨 오른쪽 칸에 적혀 있습니다.</t>
+          <t xml:space="preserve">     · 제외 41종목 — 사유는 [ETF데이터] 장 맨 오른쪽 칸에 적혀 있습니다.</t>
         </is>
       </c>
     </row>

--- a/고객제안서_월배당ETF.xlsx
+++ b/고객제안서_월배당ETF.xlsx
@@ -12,7 +12,9 @@
     <sheet name="사용법" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="채택종목">'ETF데이터'!$A$4:$A$23</definedName>
+    <definedName name="채택종목">'ETF데이터'!$A$4:$A$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'제안서'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'제안서'!$A$1:$H$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -641,7 +643,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -696,7 +698,7 @@
         </is>
       </c>
       <c r="K2" s="3">
-        <f>IFERROR(MATCH($C$9,'ETF데이터'!$A$4:$A$23,0),0)</f>
+        <f>IFERROR(MATCH($C$9,'ETF데이터'!$A$4:$A$25,0),0)</f>
         <v/>
       </c>
     </row>
@@ -814,7 +816,7 @@
         </is>
       </c>
       <c r="C14" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$B$4:$B$23,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$B$4:$B$25,$K$2))</f>
         <v/>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -823,7 +825,7 @@
         </is>
       </c>
       <c r="F14" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$G$4:$G$23,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$G$4:$G$25,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -834,7 +836,7 @@
         </is>
       </c>
       <c r="C15" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$C$4:$C$23,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$C$4:$C$25,$K$2))</f>
         <v/>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -843,7 +845,7 @@
         </is>
       </c>
       <c r="F15" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$H$4:$H$23,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$H$4:$H$25,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -854,7 +856,7 @@
         </is>
       </c>
       <c r="C16" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$D$4:$D$23,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$D$4:$D$25,$K$2))</f>
         <v/>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -863,7 +865,7 @@
         </is>
       </c>
       <c r="F16" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$I$4:$I$23,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$I$4:$I$25,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -874,7 +876,7 @@
         </is>
       </c>
       <c r="C17" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$E$4:$E$23,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$E$4:$E$25,$K$2))</f>
         <v/>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -883,7 +885,7 @@
         </is>
       </c>
       <c r="F17" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$J$4:$J$23,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$J$4:$J$25,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -894,7 +896,7 @@
         </is>
       </c>
       <c r="C18" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$F$4:$F$23,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$F$4:$F$25,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -1350,7 +1352,7 @@
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>5. 채택 ETF 비교 (1억원 투자 기준) — 연 분배율 상위 12종목 / 전체 20종목</t>
+          <t>5. 채택 ETF 비교 (1억원 투자 기준) — 연 분배율 상위 12종목 / 전체 22종목</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1889,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T03:40:59.675Z · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 1년 변동성 25% 이하, 분배 이력 12개월 이상</t>
+          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T03:46:41.846Z · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 1년 변동성 25% 이하, 분배 이력 12개월 이상</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1913,9 @@
       <formula1>=채택종목</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2022,46 +2026,46 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>ACE 미국빅테크7+데일리타겟커버드콜(합성)</t>
+          <t>SOL 팔란티어커버드콜OTM채권혼합</t>
         </is>
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>480020</t>
+          <t>0040Y0</t>
         </is>
       </c>
       <c r="C4" s="34" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="D4" s="35" t="n">
-        <v>9890</v>
+        <v>7930</v>
       </c>
       <c r="E4" s="35" t="n">
-        <v>176941500000</v>
+        <v>357021250000</v>
       </c>
       <c r="F4" s="35" t="n">
-        <v>2871796983</v>
+        <v>2991827697</v>
       </c>
       <c r="G4" s="36" t="n">
-        <v>0.005384</v>
+        <v>0.007532</v>
       </c>
       <c r="H4" s="36" t="n">
-        <v>0.2139</v>
+        <v>0.1637</v>
       </c>
       <c r="I4" s="36" t="n">
-        <v>0.0297</v>
+        <v>0.0194</v>
       </c>
       <c r="J4" s="36" t="n">
-        <v>0.267947</v>
+        <v>0.281841</v>
       </c>
       <c r="K4" s="35" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="L4" s="34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M4" s="34" t="inlineStr">
@@ -2074,46 +2078,46 @@
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국나스닥100데일리커버드콜OTM</t>
+          <t>ACE 미국빅테크7+데일리타겟커버드콜(합성)</t>
         </is>
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>494300</t>
+          <t>480020</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D5" s="35" t="n">
-        <v>8780</v>
+        <v>9895</v>
       </c>
       <c r="E5" s="35" t="n">
-        <v>1002716000000</v>
+        <v>176941500000</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>13538688373</v>
+        <v>2871808688</v>
       </c>
       <c r="G5" s="36" t="n">
-        <v>0.005108000000000001</v>
+        <v>0.005384</v>
       </c>
       <c r="H5" s="36" t="n">
-        <v>0.1938</v>
+        <v>0.2139</v>
       </c>
       <c r="I5" s="36" t="n">
-        <v>0.0166</v>
+        <v>0.0297</v>
       </c>
       <c r="J5" s="36" t="n">
-        <v>0.230068</v>
+        <v>0.267812</v>
       </c>
       <c r="K5" s="35" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L5" s="34" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M5" s="34" t="inlineStr">
@@ -2126,42 +2130,42 @@
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
         <is>
-          <t>RISE 미국테크100데일리고정커버드콜</t>
+          <t>SOL 팔란티어미국채커버드콜혼합</t>
         </is>
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>491620</t>
+          <t>0040X0</t>
         </is>
       </c>
       <c r="C6" s="34" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="D6" s="35" t="n">
-        <v>10235</v>
+        <v>9180</v>
       </c>
       <c r="E6" s="35" t="n">
-        <v>560567000000</v>
+        <v>169371000000</v>
       </c>
       <c r="F6" s="35" t="n">
-        <v>7569401285</v>
+        <v>1691560751</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>0.005748</v>
+        <v>0.007991</v>
       </c>
       <c r="H6" s="36" t="n">
-        <v>0.2021</v>
+        <v>0.2285</v>
       </c>
       <c r="I6" s="36" t="n">
-        <v>0.0166</v>
+        <v>0.0148</v>
       </c>
       <c r="J6" s="36" t="n">
-        <v>0.219834</v>
+        <v>0.250109</v>
       </c>
       <c r="K6" s="35" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L6" s="34" t="inlineStr">
         <is>
@@ -2178,46 +2182,46 @@
     <row r="7">
       <c r="A7" s="34" t="inlineStr">
         <is>
-          <t>ACE 미국500데일리타겟커버드콜(합성)</t>
+          <t>KODEX 미국나스닥100데일리커버드콜OTM</t>
         </is>
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>480030</t>
+          <t>494300</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>9545</v>
+        <v>8775</v>
       </c>
       <c r="E7" s="35" t="n">
-        <v>160608000000</v>
+        <v>1002716000000</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>1353441866</v>
+        <v>13538746518</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>0.005391</v>
+        <v>0.005108000000000001</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>0.1502</v>
+        <v>0.1938</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>0.0199</v>
+        <v>0.0166</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>0.203562</v>
+        <v>0.230199</v>
       </c>
       <c r="K7" s="35" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="L7" s="34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M7" s="34" t="inlineStr">
@@ -2230,12 +2234,12 @@
     <row r="8">
       <c r="A8" s="34" t="inlineStr">
         <is>
-          <t>RISE 미국배당100데일리고정커버드콜</t>
+          <t>RISE 미국테크100데일리고정커버드콜</t>
         </is>
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>490600</t>
+          <t>491620</t>
         </is>
       </c>
       <c r="C8" s="34" t="inlineStr">
@@ -2244,32 +2248,32 @@
         </is>
       </c>
       <c r="D8" s="35" t="n">
-        <v>8865</v>
+        <v>10235</v>
       </c>
       <c r="E8" s="35" t="n">
-        <v>168973500000</v>
+        <v>560567000000</v>
       </c>
       <c r="F8" s="35" t="n">
-        <v>2335548906</v>
+        <v>7569909350</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>0.005953000000000001</v>
+        <v>0.005748</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>0.1459</v>
+        <v>0.2021</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>0.01</v>
+        <v>0.0166</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>0.164354</v>
+        <v>0.219834</v>
       </c>
       <c r="K8" s="35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" s="34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M8" s="34" t="inlineStr">
@@ -2282,46 +2286,46 @@
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
         <is>
-          <t>KODEX 테슬라커버드콜채권혼합액티브</t>
+          <t>ACE 미국500데일리타겟커버드콜(합성)</t>
         </is>
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>475080</t>
+          <t>480030</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D9" s="35" t="n">
-        <v>7830</v>
+        <v>9555</v>
       </c>
       <c r="E9" s="35" t="n">
-        <v>285403500000</v>
+        <v>160608000000</v>
       </c>
       <c r="F9" s="35" t="n">
-        <v>1454332738</v>
+        <v>1353456781</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>0.005215</v>
+        <v>0.005391</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>0.1243</v>
+        <v>0.1502</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>0.0125</v>
+        <v>0.0199</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>0.16424</v>
+        <v>0.203349</v>
       </c>
       <c r="K9" s="35" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L9" s="34" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M9" s="34" t="inlineStr">
@@ -2334,42 +2338,42 @@
     <row r="10">
       <c r="A10" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국AI빅테크10타겟데일리커버드콜</t>
+          <t>RISE 미국배당100데일리고정커버드콜</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>493810</t>
+          <t>490600</t>
         </is>
       </c>
       <c r="C10" s="34" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>KB자산운용</t>
         </is>
       </c>
       <c r="D10" s="35" t="n">
-        <v>11110</v>
+        <v>8865</v>
       </c>
       <c r="E10" s="35" t="n">
-        <v>240761500000</v>
+        <v>168973500000</v>
       </c>
       <c r="F10" s="35" t="n">
-        <v>1833470044</v>
+        <v>2335576978</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>0.004813</v>
+        <v>0.005953000000000001</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>0.2183</v>
+        <v>0.1459</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>0.0124</v>
+        <v>0.01</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>0.163456</v>
+        <v>0.164354</v>
       </c>
       <c r="K10" s="35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L10" s="34" t="inlineStr">
         <is>
@@ -2386,12 +2390,12 @@
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국S&amp;P500데일리커버드콜OTM</t>
+          <t>KODEX 테슬라커버드콜채권혼합액티브</t>
         </is>
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>0005A0</t>
+          <t>475080</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
@@ -2400,28 +2404,28 @@
         </is>
       </c>
       <c r="D11" s="35" t="n">
-        <v>9235</v>
+        <v>7830</v>
       </c>
       <c r="E11" s="35" t="n">
-        <v>198660000000</v>
+        <v>285403500000</v>
       </c>
       <c r="F11" s="35" t="n">
-        <v>1973049132</v>
+        <v>1454588648</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>0.005639999999999999</v>
+        <v>0.005215</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>0.1473</v>
+        <v>0.1243</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>0.0124</v>
+        <v>0.0125</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>0.160368</v>
+        <v>0.16424</v>
       </c>
       <c r="K11" s="35" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L11" s="34" t="inlineStr">
         <is>
@@ -2438,12 +2442,12 @@
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
+          <t>TIGER 미국AI빅테크10타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>486290</t>
+          <t>493810</t>
         </is>
       </c>
       <c r="C12" s="34" t="inlineStr">
@@ -2452,32 +2456,32 @@
         </is>
       </c>
       <c r="D12" s="35" t="n">
-        <v>10235</v>
+        <v>11110</v>
       </c>
       <c r="E12" s="35" t="n">
-        <v>2435426000000</v>
+        <v>240761500000</v>
       </c>
       <c r="F12" s="35" t="n">
-        <v>29766278844</v>
+        <v>1833485783</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>0.004563</v>
+        <v>0.004813</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>0.2068</v>
+        <v>0.2183</v>
       </c>
       <c r="I12" s="36" t="n">
         <v>0.0124</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>0.160039</v>
+        <v>0.163456</v>
       </c>
       <c r="K12" s="35" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L12" s="34" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M12" s="34" t="inlineStr">
@@ -2490,12 +2494,12 @@
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국AI테크TOP10타겟커버드콜</t>
+          <t>KODEX 미국S&amp;P500데일리커버드콜OTM</t>
         </is>
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>483280</t>
+          <t>0005A0</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
@@ -2504,28 +2508,28 @@
         </is>
       </c>
       <c r="D13" s="35" t="n">
-        <v>11505</v>
+        <v>9240</v>
       </c>
       <c r="E13" s="35" t="n">
-        <v>451950000000</v>
+        <v>198660000000</v>
       </c>
       <c r="F13" s="35" t="n">
-        <v>2928535970</v>
+        <v>1973258151</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>0.005830999999999999</v>
+        <v>0.005639999999999999</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>0.2452</v>
+        <v>0.1473</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>0.0123</v>
+        <v>0.0124</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>0.15993</v>
+        <v>0.160281</v>
       </c>
       <c r="K13" s="35" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L13" s="34" t="inlineStr">
         <is>
@@ -2542,12 +2546,12 @@
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국30년국채커버드콜액티브(H)</t>
+          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>476550</t>
+          <t>486290</t>
         </is>
       </c>
       <c r="C14" s="34" t="inlineStr">
@@ -2556,28 +2560,28 @@
         </is>
       </c>
       <c r="D14" s="35" t="n">
-        <v>6690</v>
+        <v>10230</v>
       </c>
       <c r="E14" s="35" t="n">
-        <v>756407750000</v>
+        <v>2435426000000</v>
       </c>
       <c r="F14" s="35" t="n">
-        <v>7955288250</v>
+        <v>29766958577</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>0.007784</v>
+        <v>0.004563</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.2068</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>0.01</v>
+        <v>0.0124</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>0.135426</v>
+        <v>0.160117</v>
       </c>
       <c r="K14" s="35" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L14" s="34" t="inlineStr">
         <is>
@@ -2594,12 +2598,12 @@
     <row r="15">
       <c r="A15" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국30년국채타겟커버드콜(합성 H)</t>
+          <t>KODEX 미국AI테크TOP10타겟커버드콜</t>
         </is>
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>481060</t>
+          <t>483280</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
@@ -2608,32 +2612,32 @@
         </is>
       </c>
       <c r="D15" s="35" t="n">
-        <v>7265</v>
+        <v>11505</v>
       </c>
       <c r="E15" s="35" t="n">
-        <v>740576850000</v>
+        <v>451950000000</v>
       </c>
       <c r="F15" s="35" t="n">
-        <v>4086810522</v>
+        <v>2928583908</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>0.003244</v>
+        <v>0.005830999999999999</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>0.0842</v>
+        <v>0.2452</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>0.0101</v>
+        <v>0.0123</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>0.132691</v>
+        <v>0.15993</v>
       </c>
       <c r="K15" s="35" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L15" s="34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M15" s="34" t="inlineStr">
@@ -2646,42 +2650,42 @@
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>SOL 미국30년국채커버드콜(합성)</t>
+          <t>TIGER 미국30년국채커버드콜액티브(H)</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
         <is>
-          <t>473330</t>
+          <t>476550</t>
         </is>
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="D16" s="35" t="n">
-        <v>7780</v>
+        <v>6690</v>
       </c>
       <c r="E16" s="35" t="n">
-        <v>272513750000</v>
+        <v>756407750000</v>
       </c>
       <c r="F16" s="35" t="n">
-        <v>2163579550</v>
+        <v>7955569118</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>0.0035</v>
+        <v>0.007784</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>0.135</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>0.0074</v>
+        <v>0.01</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>0.13072</v>
+        <v>0.135426</v>
       </c>
       <c r="K16" s="35" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L16" s="34" t="inlineStr">
         <is>
@@ -2698,46 +2702,46 @@
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국나스닥100커버드콜(합성)</t>
+          <t>KODEX 미국30년국채타겟커버드콜(합성 H)</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>441680</t>
+          <t>481060</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D17" s="35" t="n">
-        <v>10615</v>
+        <v>7265</v>
       </c>
       <c r="E17" s="35" t="n">
-        <v>279306000000</v>
+        <v>740576850000</v>
       </c>
       <c r="F17" s="35" t="n">
-        <v>960115974</v>
+        <v>4086823114</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>0.004923</v>
+        <v>0.003244</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>0.146</v>
+        <v>0.0842</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>0.01</v>
+        <v>0.0101</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>0.126236</v>
+        <v>0.132691</v>
       </c>
       <c r="K17" s="35" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="L17" s="34" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M17" s="34" t="inlineStr">
@@ -2750,42 +2754,42 @@
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국배당다우존스타겟커버드콜</t>
+          <t>SOL 미국30년국채커버드콜(합성)</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>483290</t>
+          <t>473330</t>
         </is>
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="D18" s="35" t="n">
-        <v>10230</v>
+        <v>7785</v>
       </c>
       <c r="E18" s="35" t="n">
-        <v>177915000000</v>
+        <v>272513750000</v>
       </c>
       <c r="F18" s="35" t="n">
-        <v>2277591278</v>
+        <v>2163923045</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>0.005798</v>
+        <v>0.0035</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>0.1572</v>
+        <v>0.135</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>0.0098</v>
+        <v>0.0074</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>0.121799</v>
+        <v>0.130636</v>
       </c>
       <c r="K18" s="35" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L18" s="34" t="inlineStr">
         <is>
@@ -2802,12 +2806,12 @@
     <row r="19">
       <c r="A19" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국배당다우존스타겟데일리커버드콜</t>
+          <t>TIGER 미국나스닥100커버드콜(합성)</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>0008S0</t>
+          <t>441680</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
@@ -2816,32 +2820,32 @@
         </is>
       </c>
       <c r="D19" s="35" t="n">
-        <v>9770</v>
+        <v>10610</v>
       </c>
       <c r="E19" s="35" t="n">
-        <v>315077000000</v>
+        <v>279306000000</v>
       </c>
       <c r="F19" s="35" t="n">
-        <v>3345510671</v>
+        <v>960130678</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>0.004797</v>
+        <v>0.004923</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>0.1437</v>
+        <v>0.146</v>
       </c>
       <c r="I19" s="36" t="n">
         <v>0.01</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>0.120471</v>
+        <v>0.126296</v>
       </c>
       <c r="K19" s="35" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="L19" s="34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M19" s="34" t="inlineStr">
@@ -2854,46 +2858,46 @@
     <row r="20">
       <c r="A20" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국S&amp;P500타겟데일리커버드콜</t>
+          <t>KODEX 미국배당다우존스타겟커버드콜</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
         <is>
-          <t>482730</t>
+          <t>483290</t>
         </is>
       </c>
       <c r="C20" s="34" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D20" s="35" t="n">
-        <v>11445</v>
+        <v>10230</v>
       </c>
       <c r="E20" s="35" t="n">
-        <v>657225000000</v>
+        <v>177915000000</v>
       </c>
       <c r="F20" s="35" t="n">
-        <v>4930903583</v>
+        <v>2277594518</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>0.004313</v>
+        <v>0.005798</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>0.148</v>
+        <v>0.1572</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>0.01</v>
+        <v>0.0098</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>0.107034</v>
+        <v>0.121799</v>
       </c>
       <c r="K20" s="35" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L20" s="34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M20" s="34" t="inlineStr">
@@ -2906,12 +2910,12 @@
     <row r="21">
       <c r="A21" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국테크TOP10타겟커버드콜</t>
+          <t>TIGER 미국배당다우존스타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>474220</t>
+          <t>0008S0</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
@@ -2920,28 +2924,28 @@
         </is>
       </c>
       <c r="D21" s="35" t="n">
-        <v>14695</v>
+        <v>9785</v>
       </c>
       <c r="E21" s="35" t="n">
-        <v>413976000000</v>
+        <v>315077000000</v>
       </c>
       <c r="F21" s="35" t="n">
-        <v>1732040955</v>
+        <v>3345859260</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>0.006686</v>
+        <v>0.004797</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>0.1938</v>
+        <v>0.1437</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>0.0083</v>
+        <v>0.01</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>0.106703</v>
+        <v>0.120286</v>
       </c>
       <c r="K21" s="35" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="L21" s="34" t="inlineStr">
         <is>
@@ -2958,12 +2962,12 @@
     <row r="22">
       <c r="A22" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국배당다우존스타겟커버드콜2호</t>
+          <t>TIGER 미국S&amp;P500타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>458760</t>
+          <t>482730</t>
         </is>
       </c>
       <c r="C22" s="34" t="inlineStr">
@@ -2972,32 +2976,32 @@
         </is>
       </c>
       <c r="D22" s="35" t="n">
-        <v>10880</v>
+        <v>11440</v>
       </c>
       <c r="E22" s="35" t="n">
-        <v>699584000000</v>
+        <v>657225000000</v>
       </c>
       <c r="F22" s="35" t="n">
-        <v>3403357256</v>
+        <v>4931810730</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>0.005643</v>
+        <v>0.004313</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>0.1504</v>
+        <v>0.148</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>0.1</v>
+        <v>0.10708</v>
       </c>
       <c r="K22" s="35" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="L22" s="34" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M22" s="34" t="inlineStr">
@@ -3010,174 +3014,168 @@
     <row r="23">
       <c r="A23" s="34" t="inlineStr">
         <is>
+          <t>TIGER 미국테크TOP10타겟커버드콜</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>474220</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="n">
+        <v>14695</v>
+      </c>
+      <c r="E23" s="35" t="n">
+        <v>413976000000</v>
+      </c>
+      <c r="F23" s="35" t="n">
+        <v>1732176149</v>
+      </c>
+      <c r="G23" s="36" t="n">
+        <v>0.006686</v>
+      </c>
+      <c r="H23" s="36" t="n">
+        <v>0.1938</v>
+      </c>
+      <c r="I23" s="36" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="J23" s="36" t="n">
+        <v>0.106703</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="L23" s="34" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M23" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N23" s="34" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>TIGER 미국배당다우존스타겟커버드콜2호</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>458760</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="n">
+        <v>10885</v>
+      </c>
+      <c r="E24" s="35" t="n">
+        <v>699584000000</v>
+      </c>
+      <c r="F24" s="35" t="n">
+        <v>3403419023</v>
+      </c>
+      <c r="G24" s="36" t="n">
+        <v>0.005643</v>
+      </c>
+      <c r="H24" s="36" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="I24" s="36" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J24" s="36" t="n">
+        <v>0.099954</v>
+      </c>
+      <c r="K24" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="L24" s="34" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M24" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N24" s="34" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
           <t>KODEX 미국배당커버드콜액티브</t>
         </is>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>441640</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="D23" s="35" t="n">
-        <v>12340</v>
-      </c>
-      <c r="E23" s="35" t="n">
+      <c r="D25" s="35" t="n">
+        <v>12335</v>
+      </c>
+      <c r="E25" s="35" t="n">
         <v>1701540000000</v>
       </c>
-      <c r="F23" s="35" t="n">
-        <v>12378618519</v>
-      </c>
-      <c r="G23" s="36" t="n">
+      <c r="F25" s="35" t="n">
+        <v>12379074849</v>
+      </c>
+      <c r="G25" s="36" t="n">
         <v>0.003631</v>
       </c>
-      <c r="H23" s="36" t="n">
+      <c r="H25" s="36" t="n">
         <v>0.1233</v>
       </c>
-      <c r="I23" s="36" t="n">
+      <c r="I25" s="36" t="n">
         <v>0.007800000000000001</v>
       </c>
-      <c r="J23" s="36" t="n">
-        <v>0.09594799999999999</v>
-      </c>
-      <c r="K23" s="35" t="n">
+      <c r="J25" s="36" t="n">
+        <v>0.09598699999999999</v>
+      </c>
+      <c r="K25" s="35" t="n">
         <v>48</v>
       </c>
-      <c r="L23" s="34" t="inlineStr">
+      <c r="L25" s="34" t="inlineStr">
         <is>
           <t>20260914</t>
         </is>
       </c>
-      <c r="M23" s="34" t="inlineStr">
+      <c r="M25" s="34" t="inlineStr">
         <is>
           <t>채택</t>
         </is>
       </c>
-      <c r="N23" s="34" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="37" t="inlineStr">
-        <is>
-          <t>ACE 고배당주Plus커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B24" s="37" t="inlineStr">
-        <is>
-          <t>0199C0</t>
-        </is>
-      </c>
-      <c r="C24" s="37" t="inlineStr">
-        <is>
-          <t>한국투신운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D24" s="38" t="n">
-        <v>9230</v>
-      </c>
-      <c r="E24" s="38" t="n">
-        <v>138375000000</v>
-      </c>
-      <c r="F24" s="38" t="n">
-        <v>6507497157</v>
-      </c>
-      <c r="G24" s="39" t="n">
-        <v>0.004522</v>
-      </c>
-      <c r="H24" s="39" t="n">
-        <v>0.3598</v>
-      </c>
-      <c r="I24" s="39" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="J24" s="39" t="n"/>
-      <c r="K24" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M24" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N24" s="37" t="inlineStr">
-        <is>
-          <t>변동성 36.0%(기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="37" t="inlineStr">
-        <is>
-          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
-        </is>
-      </c>
-      <c r="B25" s="37" t="inlineStr">
-        <is>
-          <t>480040</t>
-        </is>
-      </c>
-      <c r="C25" s="37" t="inlineStr">
-        <is>
-          <t>한국투신운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D25" s="38" t="n">
-        <v>13350</v>
-      </c>
-      <c r="E25" s="38" t="n">
-        <v>181016000000</v>
-      </c>
-      <c r="F25" s="38" t="n">
-        <v>3487093680</v>
-      </c>
-      <c r="G25" s="39" t="n">
-        <v>0.005406999999999999</v>
-      </c>
-      <c r="H25" s="39" t="n">
-        <v>0.4411</v>
-      </c>
-      <c r="I25" s="39" t="n">
-        <v>0.0303</v>
-      </c>
-      <c r="J25" s="39" t="n">
-        <v>0.260824</v>
-      </c>
-      <c r="K25" s="38" t="n">
-        <v>29</v>
-      </c>
-      <c r="L25" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M25" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N25" s="37" t="inlineStr">
-        <is>
-          <t>변동성 44.1%(기준 25% 초과)</t>
-        </is>
-      </c>
+      <c r="N25" s="34" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="37" t="inlineStr">
         <is>
-          <t>ACE 미국배당퀄리티+커버드콜액티브</t>
+          <t>ACE 고배당주Plus커버드콜액티브</t>
         </is>
       </c>
       <c r="B26" s="37" t="inlineStr">
         <is>
-          <t>0049M0</t>
+          <t>0199C0</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
@@ -3186,28 +3184,26 @@
         </is>
       </c>
       <c r="D26" s="38" t="n">
-        <v>11015</v>
+        <v>9215</v>
       </c>
       <c r="E26" s="38" t="n">
-        <v>78171000000</v>
+        <v>138375000000</v>
       </c>
       <c r="F26" s="38" t="n">
-        <v>379512001</v>
+        <v>6508557052</v>
       </c>
       <c r="G26" s="39" t="n">
-        <v>0.005323</v>
+        <v>0.004522</v>
       </c>
       <c r="H26" s="39" t="n">
-        <v>0.1288</v>
+        <v>0.3598</v>
       </c>
       <c r="I26" s="39" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="J26" s="39" t="n">
-        <v>0.075624</v>
-      </c>
+        <v>0.0179</v>
+      </c>
+      <c r="J26" s="39" t="n"/>
       <c r="K26" s="38" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L26" s="37" t="inlineStr">
         <is>
@@ -3221,51 +3217,53 @@
       </c>
       <c r="N26" s="37" t="inlineStr">
         <is>
-          <t>60일 거래대금 3.8억(기준 5억 미만)</t>
+          <t>변동성 36.0%(기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="37" t="inlineStr">
         <is>
-          <t>FOCUS AI반도체위클리고정커버드콜</t>
+          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
         </is>
       </c>
       <c r="B27" s="37" t="inlineStr">
         <is>
-          <t>0176P0</t>
+          <t>480040</t>
         </is>
       </c>
       <c r="C27" s="37" t="inlineStr">
         <is>
-          <t>브이아이자산운용</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D27" s="38" t="n">
-        <v>12650</v>
+        <v>13340</v>
       </c>
       <c r="E27" s="38" t="n">
-        <v>6864000000</v>
+        <v>181016000000</v>
       </c>
       <c r="F27" s="38" t="n">
-        <v>168941906</v>
+        <v>3487605490</v>
       </c>
       <c r="G27" s="39" t="n">
-        <v>0.003711</v>
+        <v>0.005406999999999999</v>
       </c>
       <c r="H27" s="39" t="n">
-        <v>0.7998999999999999</v>
+        <v>0.4411</v>
       </c>
       <c r="I27" s="39" t="n">
-        <v>0.0143</v>
-      </c>
-      <c r="J27" s="39" t="n"/>
+        <v>0.0303</v>
+      </c>
+      <c r="J27" s="39" t="n">
+        <v>0.261019</v>
+      </c>
       <c r="K27" s="38" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="L27" s="37" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M27" s="37" t="inlineStr">
@@ -3275,49 +3273,49 @@
       </c>
       <c r="N27" s="37" t="inlineStr">
         <is>
-          <t>순자산 69억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 80.0%(기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 44.1%(기준 25% 초과)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="37" t="inlineStr">
         <is>
-          <t>FOCUS 알리바바미국채커버드콜혼합</t>
+          <t>ACE 미국배당퀄리티+커버드콜액티브</t>
         </is>
       </c>
       <c r="B28" s="37" t="inlineStr">
         <is>
-          <t>0073X0</t>
+          <t>0049M0</t>
         </is>
       </c>
       <c r="C28" s="37" t="inlineStr">
         <is>
-          <t>브이아이자산운용</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D28" s="38" t="n">
-        <v>8655</v>
+        <v>11015</v>
       </c>
       <c r="E28" s="38" t="n">
-        <v>4760250000</v>
+        <v>78171000000</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>30593823</v>
+        <v>379512735</v>
       </c>
       <c r="G28" s="39" t="n">
-        <v>0.01601</v>
+        <v>0.005323</v>
       </c>
       <c r="H28" s="39" t="n">
-        <v>0.165</v>
+        <v>0.1288</v>
       </c>
       <c r="I28" s="39" t="n">
-        <v>0.0091</v>
+        <v>0.006</v>
       </c>
       <c r="J28" s="39" t="n">
-        <v>0.148469</v>
+        <v>0.075624</v>
       </c>
       <c r="K28" s="38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L28" s="37" t="inlineStr">
         <is>
@@ -3331,45 +3329,47 @@
       </c>
       <c r="N28" s="37" t="inlineStr">
         <is>
-          <t>순자산 48억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만)</t>
+          <t>60일 거래대금 3.8억(기준 5억 미만)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="37" t="inlineStr">
         <is>
-          <t>KIWOOM 코스닥150커버드콜액티브</t>
+          <t>FOCUS AI반도체위클리고정커버드콜</t>
         </is>
       </c>
       <c r="B29" s="37" t="inlineStr">
         <is>
-          <t>0198A0</t>
+          <t>0176P0</t>
         </is>
       </c>
       <c r="C29" s="37" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>브이아이자산운용</t>
         </is>
       </c>
       <c r="D29" s="38" t="n">
-        <v>8390</v>
+        <v>12650</v>
       </c>
       <c r="E29" s="38" t="n">
-        <v>72688500000</v>
+        <v>6864000000</v>
       </c>
       <c r="F29" s="38" t="n">
-        <v>4940619075</v>
+        <v>168942749</v>
       </c>
       <c r="G29" s="39" t="n">
-        <v>0.006657</v>
-      </c>
-      <c r="H29" s="39" t="n"/>
+        <v>0.003711</v>
+      </c>
+      <c r="H29" s="39" t="n">
+        <v>0.7998999999999999</v>
+      </c>
       <c r="I29" s="39" t="n">
-        <v>0.0243</v>
+        <v>0.0143</v>
       </c>
       <c r="J29" s="39" t="n"/>
       <c r="K29" s="38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L29" s="37" t="inlineStr">
         <is>
@@ -3383,45 +3383,49 @@
       </c>
       <c r="N29" s="37" t="inlineStr">
         <is>
-          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>순자산 69억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 80.0%(기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="37" t="inlineStr">
         <is>
-          <t>KODEX 200커버드콜액티브</t>
+          <t>FOCUS 알리바바미국채커버드콜혼합</t>
         </is>
       </c>
       <c r="B30" s="37" t="inlineStr">
         <is>
-          <t>0219E0</t>
+          <t>0073X0</t>
         </is>
       </c>
       <c r="C30" s="37" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>브이아이자산운용</t>
         </is>
       </c>
       <c r="D30" s="38" t="n">
-        <v>8155</v>
+        <v>8650</v>
       </c>
       <c r="E30" s="38" t="n">
-        <v>726902000000</v>
+        <v>4760250000</v>
       </c>
       <c r="F30" s="38" t="n">
-        <v>46375278871</v>
+        <v>30593963</v>
       </c>
       <c r="G30" s="39" t="n">
-        <v>0.005278000000000001</v>
-      </c>
-      <c r="H30" s="39" t="n"/>
+        <v>0.01601</v>
+      </c>
+      <c r="H30" s="39" t="n">
+        <v>0.165</v>
+      </c>
       <c r="I30" s="39" t="n">
-        <v>0.0193</v>
-      </c>
-      <c r="J30" s="39" t="n"/>
+        <v>0.0091</v>
+      </c>
+      <c r="J30" s="39" t="n">
+        <v>0.148555</v>
+      </c>
       <c r="K30" s="38" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L30" s="37" t="inlineStr">
         <is>
@@ -3435,53 +3439,49 @@
       </c>
       <c r="N30" s="37" t="inlineStr">
         <is>
-          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>순자산 48억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="37" t="inlineStr">
         <is>
-          <t>KODEX 200타겟위클리커버드콜</t>
+          <t>KIWOOM 코스닥150커버드콜액티브</t>
         </is>
       </c>
       <c r="B31" s="37" t="inlineStr">
         <is>
-          <t>498400</t>
+          <t>0198A0</t>
         </is>
       </c>
       <c r="C31" s="37" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="D31" s="38" t="n">
-        <v>19720</v>
+        <v>8390</v>
       </c>
       <c r="E31" s="38" t="n">
-        <v>5759831000000</v>
+        <v>72688500000</v>
       </c>
       <c r="F31" s="38" t="n">
-        <v>176401662492</v>
+        <v>4940765671</v>
       </c>
       <c r="G31" s="39" t="n">
-        <v>0.005095</v>
-      </c>
-      <c r="H31" s="39" t="n">
-        <v>0.5655</v>
-      </c>
+        <v>0.006657</v>
+      </c>
+      <c r="H31" s="39" t="n"/>
       <c r="I31" s="39" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="J31" s="39" t="n">
-        <v>0.158519</v>
-      </c>
+        <v>0.0243</v>
+      </c>
+      <c r="J31" s="39" t="n"/>
       <c r="K31" s="38" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="L31" s="37" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M31" s="37" t="inlineStr">
@@ -3491,19 +3491,19 @@
       </c>
       <c r="N31" s="37" t="inlineStr">
         <is>
-          <t>변동성 56.6%(기준 25% 초과)</t>
+          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="37" t="inlineStr">
         <is>
-          <t>KODEX 금융고배당TOP10타겟위클리커버드콜</t>
+          <t>KODEX 200커버드콜액티브</t>
         </is>
       </c>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>498410</t>
+          <t>0219E0</t>
         </is>
       </c>
       <c r="C32" s="37" t="inlineStr">
@@ -3512,28 +3512,24 @@
         </is>
       </c>
       <c r="D32" s="38" t="n">
-        <v>11965</v>
+        <v>8165</v>
       </c>
       <c r="E32" s="38" t="n">
-        <v>843040000000</v>
+        <v>726902000000</v>
       </c>
       <c r="F32" s="38" t="n">
-        <v>22961390586</v>
+        <v>46383634315</v>
       </c>
       <c r="G32" s="39" t="n">
-        <v>0.006697</v>
-      </c>
-      <c r="H32" s="39" t="n">
-        <v>0.3274</v>
-      </c>
+        <v>0.005278000000000001</v>
+      </c>
+      <c r="H32" s="39" t="n"/>
       <c r="I32" s="39" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="J32" s="39" t="n">
-        <v>0.157292</v>
-      </c>
+        <v>0.0193</v>
+      </c>
+      <c r="J32" s="39" t="n"/>
       <c r="K32" s="38" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L32" s="37" t="inlineStr">
         <is>
@@ -3547,19 +3543,19 @@
       </c>
       <c r="N32" s="37" t="inlineStr">
         <is>
-          <t>변동성 32.7%(기준 25% 초과)</t>
+          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="37" t="inlineStr">
         <is>
-          <t>KODEX 미국S&amp;P500변동성확대시커버드콜</t>
+          <t>KODEX 200타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B33" s="37" t="inlineStr">
         <is>
-          <t>0089C0</t>
+          <t>498400</t>
         </is>
       </c>
       <c r="C33" s="37" t="inlineStr">
@@ -3568,32 +3564,32 @@
         </is>
       </c>
       <c r="D33" s="38" t="n">
-        <v>11170</v>
+        <v>19740</v>
       </c>
       <c r="E33" s="38" t="n">
-        <v>42541000000</v>
+        <v>5759831000000</v>
       </c>
       <c r="F33" s="38" t="n">
-        <v>369289199</v>
+        <v>176412063439</v>
       </c>
       <c r="G33" s="39" t="n">
-        <v>0.006338</v>
+        <v>0.005095</v>
       </c>
       <c r="H33" s="39" t="n">
-        <v>0.1398</v>
+        <v>0.5655</v>
       </c>
       <c r="I33" s="39" t="n">
-        <v>0.0009</v>
+        <v>0.0145</v>
       </c>
       <c r="J33" s="39" t="n">
-        <v>0.022292</v>
+        <v>0.158359</v>
       </c>
       <c r="K33" s="38" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L33" s="37" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M33" s="37" t="inlineStr">
@@ -3603,19 +3599,19 @@
       </c>
       <c r="N33" s="37" t="inlineStr">
         <is>
-          <t>60일 거래대금 3.7억(기준 5억 미만)</t>
+          <t>변동성 56.6%(기준 25% 초과)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="37" t="inlineStr">
         <is>
-          <t>KODEX 미국성장커버드콜액티브</t>
+          <t>KODEX 금융고배당TOP10타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>0144L0</t>
+          <t>498410</t>
         </is>
       </c>
       <c r="C34" s="37" t="inlineStr">
@@ -3624,26 +3620,28 @@
         </is>
       </c>
       <c r="D34" s="38" t="n">
-        <v>9305</v>
+        <v>11947</v>
       </c>
       <c r="E34" s="38" t="n">
-        <v>339450000000</v>
+        <v>843040000000</v>
       </c>
       <c r="F34" s="38" t="n">
-        <v>2519327575</v>
+        <v>22964822749</v>
       </c>
       <c r="G34" s="39" t="n">
-        <v>0.006395</v>
+        <v>0.006697</v>
       </c>
       <c r="H34" s="39" t="n">
-        <v>0.1816</v>
+        <v>0.3274</v>
       </c>
       <c r="I34" s="39" t="n">
-        <v>0.009899999999999999</v>
-      </c>
-      <c r="J34" s="39" t="n"/>
+        <v>0.0121</v>
+      </c>
+      <c r="J34" s="39" t="n">
+        <v>0.157529</v>
+      </c>
       <c r="K34" s="38" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L34" s="37" t="inlineStr">
         <is>
@@ -3657,19 +3655,19 @@
       </c>
       <c r="N34" s="37" t="inlineStr">
         <is>
-          <t>분배 이력 8개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 32.7%(기준 25% 초과)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="37" t="inlineStr">
         <is>
-          <t>KODEX 반도체타겟위클리커버드콜</t>
+          <t>KODEX 미국S&amp;P500변동성확대시커버드콜</t>
         </is>
       </c>
       <c r="B35" s="37" t="inlineStr">
         <is>
-          <t>0190G0</t>
+          <t>0089C0</t>
         </is>
       </c>
       <c r="C35" s="37" t="inlineStr">
@@ -3678,26 +3676,28 @@
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>8670</v>
+        <v>11170</v>
       </c>
       <c r="E35" s="38" t="n">
-        <v>166945000000</v>
+        <v>42541000000</v>
       </c>
       <c r="F35" s="38" t="n">
-        <v>8916724632</v>
+        <v>369289199</v>
       </c>
       <c r="G35" s="39" t="n">
-        <v>0.006131</v>
+        <v>0.006338</v>
       </c>
       <c r="H35" s="39" t="n">
-        <v>0.8571</v>
+        <v>0.1398</v>
       </c>
       <c r="I35" s="39" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="J35" s="39" t="n"/>
+        <v>0.0009</v>
+      </c>
+      <c r="J35" s="39" t="n">
+        <v>0.022292</v>
+      </c>
       <c r="K35" s="38" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L35" s="37" t="inlineStr">
         <is>
@@ -3711,47 +3711,47 @@
       </c>
       <c r="N35" s="37" t="inlineStr">
         <is>
-          <t>변동성 85.7%(기준 25% 초과), 분배 이력 4개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>60일 거래대금 3.7억(기준 5억 미만)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="37" t="inlineStr">
         <is>
-          <t>PLUS 200위클리커버드콜채권혼합</t>
+          <t>KODEX 미국성장커버드콜액티브</t>
         </is>
       </c>
       <c r="B36" s="37" t="inlineStr">
         <is>
-          <t>0203D0</t>
+          <t>0144L0</t>
         </is>
       </c>
       <c r="C36" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D36" s="38" t="n">
-        <v>8805</v>
+        <v>9300</v>
       </c>
       <c r="E36" s="38" t="n">
-        <v>10560000000</v>
+        <v>339450000000</v>
       </c>
       <c r="F36" s="38" t="n">
-        <v>272946448</v>
+        <v>2519368175</v>
       </c>
       <c r="G36" s="39" t="n">
-        <v>0.004914</v>
+        <v>0.006395</v>
       </c>
       <c r="H36" s="39" t="n">
-        <v>0.3808</v>
+        <v>0.1816</v>
       </c>
       <c r="I36" s="39" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="J36" s="39" t="n"/>
       <c r="K36" s="38" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L36" s="37" t="inlineStr">
         <is>
@@ -3765,45 +3765,47 @@
       </c>
       <c r="N36" s="37" t="inlineStr">
         <is>
-          <t>순자산 106억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 38.1%(기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>분배 이력 8개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="37" t="inlineStr">
         <is>
-          <t>PLUS 200커버드콜액티브</t>
+          <t>KODEX 반도체타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B37" s="37" t="inlineStr">
         <is>
-          <t>0210E0</t>
+          <t>0190G0</t>
         </is>
       </c>
       <c r="C37" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>7135</v>
+        <v>8670</v>
       </c>
       <c r="E37" s="38" t="n">
-        <v>66881000000</v>
+        <v>166945000000</v>
       </c>
       <c r="F37" s="38" t="n">
-        <v>3119230075</v>
+        <v>8916779253</v>
       </c>
       <c r="G37" s="39" t="n">
-        <v>0.006020999999999999</v>
-      </c>
-      <c r="H37" s="39" t="n"/>
+        <v>0.006131</v>
+      </c>
+      <c r="H37" s="39" t="n">
+        <v>0.8571</v>
+      </c>
       <c r="I37" s="39" t="n">
-        <v>0.0194</v>
+        <v>0.0074</v>
       </c>
       <c r="J37" s="39" t="n"/>
       <c r="K37" s="38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L37" s="37" t="inlineStr">
         <is>
@@ -3817,19 +3819,19 @@
       </c>
       <c r="N37" s="37" t="inlineStr">
         <is>
-          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 85.7%(기준 25% 초과), 분배 이력 4개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="37" t="inlineStr">
         <is>
-          <t>PLUS 고배당주위클리고정커버드콜</t>
+          <t>PLUS 200위클리커버드콜채권혼합</t>
         </is>
       </c>
       <c r="B38" s="37" t="inlineStr">
         <is>
-          <t>0018C0</t>
+          <t>0203D0</t>
         </is>
       </c>
       <c r="C38" s="37" t="inlineStr">
@@ -3838,32 +3840,30 @@
         </is>
       </c>
       <c r="D38" s="38" t="n">
-        <v>10575</v>
+        <v>8815</v>
       </c>
       <c r="E38" s="38" t="n">
-        <v>80370000000</v>
+        <v>10560000000</v>
       </c>
       <c r="F38" s="38" t="n">
-        <v>1033449479</v>
+        <v>272987049</v>
       </c>
       <c r="G38" s="39" t="n">
-        <v>0.005958</v>
+        <v>0.004914</v>
       </c>
       <c r="H38" s="39" t="n">
-        <v>0.2667</v>
+        <v>0.3808</v>
       </c>
       <c r="I38" s="39" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="J38" s="39" t="n">
-        <v>0.168983</v>
-      </c>
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="J38" s="39" t="n"/>
       <c r="K38" s="38" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L38" s="37" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M38" s="37" t="inlineStr">
@@ -3873,19 +3873,19 @@
       </c>
       <c r="N38" s="37" t="inlineStr">
         <is>
-          <t>변동성 26.7%(기준 25% 초과)</t>
+          <t>순자산 106억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 38.1%(기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="37" t="inlineStr">
         <is>
-          <t>PLUS 고배당주위클리커버드콜</t>
+          <t>PLUS 200커버드콜액티브</t>
         </is>
       </c>
       <c r="B39" s="37" t="inlineStr">
         <is>
-          <t>489030</t>
+          <t>0210E0</t>
         </is>
       </c>
       <c r="C39" s="37" t="inlineStr">
@@ -3894,28 +3894,24 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>6470</v>
+        <v>7135</v>
       </c>
       <c r="E39" s="38" t="n">
-        <v>303208500000</v>
+        <v>66881000000</v>
       </c>
       <c r="F39" s="38" t="n">
-        <v>4300148374</v>
+        <v>3119898268</v>
       </c>
       <c r="G39" s="39" t="n">
-        <v>0.008243</v>
-      </c>
-      <c r="H39" s="39" t="n">
-        <v>0.3069</v>
-      </c>
+        <v>0.006020999999999999</v>
+      </c>
+      <c r="H39" s="39" t="n"/>
       <c r="I39" s="39" t="n">
-        <v>0.0148</v>
-      </c>
-      <c r="J39" s="39" t="n">
-        <v>0.234621</v>
-      </c>
+        <v>0.0194</v>
+      </c>
+      <c r="J39" s="39" t="n"/>
       <c r="K39" s="38" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L39" s="37" t="inlineStr">
         <is>
@@ -3929,19 +3925,19 @@
       </c>
       <c r="N39" s="37" t="inlineStr">
         <is>
-          <t>변동성 30.7%(기준 25% 초과)</t>
+          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="37" t="inlineStr">
         <is>
-          <t>PLUS 미국배당증가성장주데일리커버드콜</t>
+          <t>PLUS 고배당주위클리고정커버드콜</t>
         </is>
       </c>
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>494420</t>
+          <t>0018C0</t>
         </is>
       </c>
       <c r="C40" s="37" t="inlineStr">
@@ -3950,28 +3946,28 @@
         </is>
       </c>
       <c r="D40" s="38" t="n">
-        <v>8670</v>
+        <v>10570</v>
       </c>
       <c r="E40" s="38" t="n">
-        <v>15588000000</v>
+        <v>80370000000</v>
       </c>
       <c r="F40" s="38" t="n">
-        <v>115236450</v>
+        <v>1033597951</v>
       </c>
       <c r="G40" s="39" t="n">
-        <v>0.007707</v>
+        <v>0.005958</v>
       </c>
       <c r="H40" s="39" t="n">
-        <v>0.1439</v>
+        <v>0.2667</v>
       </c>
       <c r="I40" s="39" t="n">
-        <v>0.0119</v>
+        <v>0.0124</v>
       </c>
       <c r="J40" s="39" t="n">
-        <v>0.14925</v>
+        <v>0.169063</v>
       </c>
       <c r="K40" s="38" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L40" s="37" t="inlineStr">
         <is>
@@ -3985,19 +3981,19 @@
       </c>
       <c r="N40" s="37" t="inlineStr">
         <is>
-          <t>순자산 156억(기준 300억 미만), 60일 거래대금 1.2억(기준 5억 미만)</t>
+          <t>변동성 26.7%(기준 25% 초과)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="37" t="inlineStr">
         <is>
-          <t>PLUS 차이나항셍테크위클리타겟커버드콜</t>
+          <t>PLUS 고배당주위클리커버드콜</t>
         </is>
       </c>
       <c r="B41" s="37" t="inlineStr">
         <is>
-          <t>0128D0</t>
+          <t>489030</t>
         </is>
       </c>
       <c r="C41" s="37" t="inlineStr">
@@ -4006,26 +4002,28 @@
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>6395</v>
+        <v>6460</v>
       </c>
       <c r="E41" s="38" t="n">
-        <v>4476500000</v>
+        <v>303208500000</v>
       </c>
       <c r="F41" s="38" t="n">
-        <v>29887189</v>
+        <v>4301071496</v>
       </c>
       <c r="G41" s="39" t="n">
-        <v>0.01153</v>
+        <v>0.008243</v>
       </c>
       <c r="H41" s="39" t="n">
-        <v>0.2721</v>
+        <v>0.3069</v>
       </c>
       <c r="I41" s="39" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="J41" s="39" t="n"/>
+        <v>0.0148</v>
+      </c>
+      <c r="J41" s="39" t="n">
+        <v>0.234985</v>
+      </c>
       <c r="K41" s="38" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="L41" s="37" t="inlineStr">
         <is>
@@ -4039,19 +4037,19 @@
       </c>
       <c r="N41" s="37" t="inlineStr">
         <is>
-          <t>순자산 45억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만), 변동성 27.2%(기준 25% 초과), 분배 이력 9개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 30.7%(기준 25% 초과)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="37" t="inlineStr">
         <is>
-          <t>PLUS 테슬라위클리커버드콜채권혼합</t>
+          <t>PLUS 미국배당증가성장주데일리커버드콜</t>
         </is>
       </c>
       <c r="B42" s="37" t="inlineStr">
         <is>
-          <t>0132K0</t>
+          <t>494420</t>
         </is>
       </c>
       <c r="C42" s="37" t="inlineStr">
@@ -4059,33 +4057,15 @@
           <t>한화자산운용</t>
         </is>
       </c>
-      <c r="D42" s="38" t="n">
-        <v>7817</v>
-      </c>
-      <c r="E42" s="38" t="n">
-        <v>108307000000</v>
-      </c>
-      <c r="F42" s="38" t="n">
-        <v>1315637734</v>
-      </c>
-      <c r="G42" s="39" t="n">
-        <v>0.006500000000000001</v>
-      </c>
-      <c r="H42" s="39" t="n">
-        <v>0.1302</v>
-      </c>
-      <c r="I42" s="39" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="D42" s="38" t="n"/>
+      <c r="E42" s="38" t="n"/>
+      <c r="F42" s="38" t="n"/>
+      <c r="G42" s="39" t="n"/>
+      <c r="H42" s="39" t="n"/>
+      <c r="I42" s="39" t="n"/>
       <c r="J42" s="39" t="n"/>
-      <c r="K42" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="L42" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
+      <c r="K42" s="38" t="n"/>
+      <c r="L42" s="37" t="n"/>
       <c r="M42" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -4093,703 +4073,41 @@
       </c>
       <c r="N42" s="37" t="inlineStr">
         <is>
-          <t>분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 403)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="37" t="inlineStr">
         <is>
-          <t>RISE 200고배당커버드콜ATM</t>
+          <t>PLUS 차이나항셍테크위클리타겟커버드콜</t>
         </is>
       </c>
       <c r="B43" s="37" t="inlineStr">
         <is>
-          <t>290080</t>
+          <t>0128D0</t>
         </is>
       </c>
       <c r="C43" s="37" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D43" s="38" t="n">
-        <v>7355</v>
-      </c>
-      <c r="E43" s="38" t="n">
-        <v>12614000000</v>
-      </c>
-      <c r="F43" s="38" t="n">
-        <v>168554500</v>
-      </c>
-      <c r="G43" s="39" t="n">
-        <v>0.00636</v>
-      </c>
-      <c r="H43" s="39" t="n">
-        <v>0.3097</v>
-      </c>
-      <c r="I43" s="39" t="n">
-        <v>0.008100000000000001</v>
-      </c>
-      <c r="J43" s="39" t="n">
-        <v>0.107682</v>
-      </c>
-      <c r="K43" s="38" t="n">
-        <v>49</v>
-      </c>
-      <c r="L43" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D43" s="38" t="n"/>
+      <c r="E43" s="38" t="n"/>
+      <c r="F43" s="38" t="n"/>
+      <c r="G43" s="39" t="n"/>
+      <c r="H43" s="39" t="n"/>
+      <c r="I43" s="39" t="n"/>
+      <c r="J43" s="39" t="n"/>
+      <c r="K43" s="38" t="n"/>
+      <c r="L43" s="37" t="n"/>
       <c r="M43" s="37" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
       <c r="N43" s="37" t="inlineStr">
-        <is>
-          <t>순자산 126억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 31.0%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="37" t="inlineStr">
-        <is>
-          <t>RISE 200위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B44" s="37" t="inlineStr">
-        <is>
-          <t>475720</t>
-        </is>
-      </c>
-      <c r="C44" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D44" s="38" t="n">
-        <v>12380</v>
-      </c>
-      <c r="E44" s="38" t="n">
-        <v>821275000000</v>
-      </c>
-      <c r="F44" s="38" t="n">
-        <v>12908999692</v>
-      </c>
-      <c r="G44" s="39" t="n">
-        <v>0.006305</v>
-      </c>
-      <c r="H44" s="39" t="n">
-        <v>0.4327</v>
-      </c>
-      <c r="I44" s="39" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="J44" s="39" t="n">
-        <v>0.199515</v>
-      </c>
-      <c r="K44" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="L44" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M44" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N44" s="37" t="inlineStr">
-        <is>
-          <t>변동성 43.3%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="37" t="inlineStr">
-        <is>
-          <t>RISE 미국30년국채커버드콜(합성)</t>
-        </is>
-      </c>
-      <c r="B45" s="37" t="inlineStr">
-        <is>
-          <t>472830</t>
-        </is>
-      </c>
-      <c r="C45" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D45" s="38" t="n">
-        <v>7705</v>
-      </c>
-      <c r="E45" s="38" t="n">
-        <v>42707250000</v>
-      </c>
-      <c r="F45" s="38" t="n">
-        <v>286004344</v>
-      </c>
-      <c r="G45" s="39" t="n">
-        <v>0.003419</v>
-      </c>
-      <c r="H45" s="39" t="n">
-        <v>0.1409</v>
-      </c>
-      <c r="I45" s="39" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="J45" s="39" t="n">
-        <v>0.11499</v>
-      </c>
-      <c r="K45" s="38" t="n">
-        <v>32</v>
-      </c>
-      <c r="L45" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M45" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N45" s="37" t="inlineStr">
-        <is>
-          <t>60일 거래대금 2.9억(기준 5억 미만)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="37" t="inlineStr">
-        <is>
-          <t>RISE 미국AI밸류체인데일리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B46" s="37" t="inlineStr">
-        <is>
-          <t>490590</t>
-        </is>
-      </c>
-      <c r="C46" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D46" s="38" t="n">
-        <v>13615</v>
-      </c>
-      <c r="E46" s="38" t="n">
-        <v>760760000000</v>
-      </c>
-      <c r="F46" s="38" t="n">
-        <v>10122233904</v>
-      </c>
-      <c r="G46" s="39" t="n">
-        <v>0.00578</v>
-      </c>
-      <c r="H46" s="39" t="n">
-        <v>0.3307</v>
-      </c>
-      <c r="I46" s="39" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="J46" s="39" t="n">
-        <v>0.213147</v>
-      </c>
-      <c r="K46" s="38" t="n">
-        <v>23</v>
-      </c>
-      <c r="L46" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M46" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N46" s="37" t="inlineStr">
-        <is>
-          <t>변동성 33.1%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="37" t="inlineStr">
-        <is>
-          <t>RISE 미국S&amp;P500데일리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B47" s="37" t="inlineStr">
-        <is>
-          <t>0138T0</t>
-        </is>
-      </c>
-      <c r="C47" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D47" s="38" t="n">
-        <v>9260</v>
-      </c>
-      <c r="E47" s="38" t="n">
-        <v>32305000000</v>
-      </c>
-      <c r="F47" s="38" t="n">
-        <v>320379491</v>
-      </c>
-      <c r="G47" s="39" t="n">
-        <v>0.006153</v>
-      </c>
-      <c r="H47" s="39" t="n">
-        <v>0.1559</v>
-      </c>
-      <c r="I47" s="39" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J47" s="39" t="n"/>
-      <c r="K47" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="L47" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M47" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N47" s="37" t="inlineStr">
-        <is>
-          <t>60일 거래대금 3.2억(기준 5억 미만), 분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="37" t="inlineStr">
-        <is>
-          <t>RISE 차이나테크TOP10위클리타겟커버드콜</t>
-        </is>
-      </c>
-      <c r="B48" s="37" t="inlineStr">
-        <is>
-          <t>0094L0</t>
-        </is>
-      </c>
-      <c r="C48" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D48" s="38" t="n">
-        <v>7055</v>
-      </c>
-      <c r="E48" s="38" t="n">
-        <v>9870000000</v>
-      </c>
-      <c r="F48" s="38" t="n">
-        <v>60749389</v>
-      </c>
-      <c r="G48" s="39" t="n">
-        <v>0.011533</v>
-      </c>
-      <c r="H48" s="39" t="n">
-        <v>0.2793</v>
-      </c>
-      <c r="I48" s="39" t="n">
-        <v>0.0097</v>
-      </c>
-      <c r="J48" s="39" t="n">
-        <v>0.1545</v>
-      </c>
-      <c r="K48" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="L48" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M48" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N48" s="37" t="inlineStr">
-        <is>
-          <t>순자산 99억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만), 변동성 27.9%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="37" t="inlineStr">
-        <is>
-          <t>RISE 코리아밸류업위클리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B49" s="37" t="inlineStr">
-        <is>
-          <t>0094M0</t>
-        </is>
-      </c>
-      <c r="C49" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D49" s="38" t="n">
-        <v>16870</v>
-      </c>
-      <c r="E49" s="38" t="n">
-        <v>343230000000</v>
-      </c>
-      <c r="F49" s="38" t="n">
-        <v>9599979617</v>
-      </c>
-      <c r="G49" s="39" t="n">
-        <v>0.005637</v>
-      </c>
-      <c r="H49" s="39" t="n">
-        <v>0.4584</v>
-      </c>
-      <c r="I49" s="39" t="n">
-        <v>0.0299</v>
-      </c>
-      <c r="J49" s="39" t="n">
-        <v>0.248963</v>
-      </c>
-      <c r="K49" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="L49" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M49" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N49" s="37" t="inlineStr">
-        <is>
-          <t>변동성 45.8%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="37" t="inlineStr">
-        <is>
-          <t>RISE 코스닥커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B50" s="37" t="inlineStr">
-        <is>
-          <t>0223A0</t>
-        </is>
-      </c>
-      <c r="C50" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D50" s="38" t="n">
-        <v>10435</v>
-      </c>
-      <c r="E50" s="38" t="n">
-        <v>16624000000</v>
-      </c>
-      <c r="F50" s="38" t="n"/>
-      <c r="G50" s="39" t="n">
-        <v>0.003264</v>
-      </c>
-      <c r="H50" s="39" t="n"/>
-      <c r="I50" s="39" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J50" s="39" t="n"/>
-      <c r="K50" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M50" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N50" s="37" t="inlineStr">
-        <is>
-          <t>순자산 166억(기준 300억 미만), 거래대금 미확인, 변동성 산출 불가(시세 이력 부족), 분배 이력 1개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="37" t="inlineStr">
-        <is>
-          <t>RISE 테슬라미국채타겟커버드콜혼합(합성)</t>
-        </is>
-      </c>
-      <c r="B51" s="37" t="inlineStr">
-        <is>
-          <t>0013R0</t>
-        </is>
-      </c>
-      <c r="C51" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D51" s="38" t="n">
-        <v>7620</v>
-      </c>
-      <c r="E51" s="38" t="n">
-        <v>27432000000</v>
-      </c>
-      <c r="F51" s="38" t="n">
-        <v>162123325</v>
-      </c>
-      <c r="G51" s="39" t="n">
-        <v>0.003495</v>
-      </c>
-      <c r="H51" s="39" t="n">
-        <v>0.1853</v>
-      </c>
-      <c r="I51" s="39" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="J51" s="39" t="n">
-        <v>0.183727</v>
-      </c>
-      <c r="K51" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="L51" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M51" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N51" s="37" t="inlineStr">
-        <is>
-          <t>순자산 274억(기준 300억 미만), 60일 거래대금 1.6억(기준 5억 미만)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="37" t="inlineStr">
-        <is>
-          <t>SOL 200타겟위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B52" s="37" t="inlineStr">
-        <is>
-          <t>0167B0</t>
-        </is>
-      </c>
-      <c r="C52" s="37" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D52" s="38" t="n">
-        <v>11450</v>
-      </c>
-      <c r="E52" s="38" t="n">
-        <v>627507000000</v>
-      </c>
-      <c r="F52" s="38" t="n">
-        <v>21319332425</v>
-      </c>
-      <c r="G52" s="39" t="n">
-        <v>0.00345</v>
-      </c>
-      <c r="H52" s="39" t="n">
-        <v>0.6943</v>
-      </c>
-      <c r="I52" s="39" t="n">
-        <v>0.0139</v>
-      </c>
-      <c r="J52" s="39" t="n"/>
-      <c r="K52" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L52" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M52" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N52" s="37" t="inlineStr">
-        <is>
-          <t>변동성 69.4%(기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="37" t="inlineStr">
-        <is>
-          <t>SOL 국제금커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B53" s="37" t="inlineStr">
-        <is>
-          <t>0022T0</t>
-        </is>
-      </c>
-      <c r="C53" s="37" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D53" s="38" t="n">
-        <v>12835</v>
-      </c>
-      <c r="E53" s="38" t="n">
-        <v>73074000000</v>
-      </c>
-      <c r="F53" s="38" t="n">
-        <v>1007373121</v>
-      </c>
-      <c r="G53" s="39" t="n">
-        <v>0.006737999999999999</v>
-      </c>
-      <c r="H53" s="39" t="n">
-        <v>0.2874</v>
-      </c>
-      <c r="I53" s="39" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="J53" s="39" t="n">
-        <v>0.04495499999999999</v>
-      </c>
-      <c r="K53" s="38" t="n">
-        <v>17</v>
-      </c>
-      <c r="L53" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M53" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N53" s="37" t="inlineStr">
-        <is>
-          <t>변동성 28.7%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="37" t="inlineStr">
-        <is>
-          <t>SOL 미국500타겟데일리커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B54" s="37" t="inlineStr">
-        <is>
-          <t>494210</t>
-        </is>
-      </c>
-      <c r="C54" s="37" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D54" s="38" t="n">
-        <v>10630</v>
-      </c>
-      <c r="E54" s="38" t="n">
-        <v>7423500000</v>
-      </c>
-      <c r="F54" s="38" t="n">
-        <v>64447485</v>
-      </c>
-      <c r="G54" s="39" t="n">
-        <v>0.00621</v>
-      </c>
-      <c r="H54" s="39" t="n">
-        <v>0.1571</v>
-      </c>
-      <c r="I54" s="39" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J54" s="39" t="n">
-        <v>0.126341</v>
-      </c>
-      <c r="K54" s="38" t="n">
-        <v>22</v>
-      </c>
-      <c r="L54" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M54" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N54" s="37" t="inlineStr">
-        <is>
-          <t>순자산 74억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="37" t="inlineStr">
-        <is>
-          <t>SOL 팔란티어미국채커버드콜혼합</t>
-        </is>
-      </c>
-      <c r="B55" s="37" t="inlineStr">
-        <is>
-          <t>0040X0</t>
-        </is>
-      </c>
-      <c r="C55" s="37" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D55" s="38" t="n"/>
-      <c r="E55" s="38" t="n"/>
-      <c r="F55" s="38" t="n"/>
-      <c r="G55" s="39" t="n"/>
-      <c r="H55" s="39" t="n"/>
-      <c r="I55" s="39" t="n"/>
-      <c r="J55" s="39" t="n"/>
-      <c r="K55" s="38" t="n"/>
-      <c r="L55" s="37" t="n"/>
-      <c r="M55" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N55" s="37" t="inlineStr">
         <is>
           <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
 Call log:
@@ -4797,15 +4115,639 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 테슬라위클리커버드콜채권혼합</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>0132K0</t>
+        </is>
+      </c>
+      <c r="C44" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D44" s="38" t="n"/>
+      <c r="E44" s="38" t="n"/>
+      <c r="F44" s="38" t="n"/>
+      <c r="G44" s="39" t="n"/>
+      <c r="H44" s="39" t="n"/>
+      <c r="I44" s="39" t="n"/>
+      <c r="J44" s="39" t="n"/>
+      <c r="K44" s="38" t="n"/>
+      <c r="L44" s="37" t="n"/>
+      <c r="M44" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N44" s="37" t="inlineStr">
+        <is>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
+Call log:
+  - )</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t>RISE 200고배당커버드콜ATM</t>
+        </is>
+      </c>
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>290080</t>
+        </is>
+      </c>
+      <c r="C45" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D45" s="38" t="n"/>
+      <c r="E45" s="38" t="n"/>
+      <c r="F45" s="38" t="n"/>
+      <c r="G45" s="39" t="n"/>
+      <c r="H45" s="39" t="n"/>
+      <c r="I45" s="39" t="n"/>
+      <c r="J45" s="39" t="n"/>
+      <c r="K45" s="38" t="n"/>
+      <c r="L45" s="37" t="n"/>
+      <c r="M45" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N45" s="37" t="inlineStr">
+        <is>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="37" t="inlineStr">
+        <is>
+          <t>RISE 200위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B46" s="37" t="inlineStr">
+        <is>
+          <t>475720</t>
+        </is>
+      </c>
+      <c r="C46" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D46" s="38" t="n">
+        <v>12385</v>
+      </c>
+      <c r="E46" s="38" t="n">
+        <v>821275000000</v>
+      </c>
+      <c r="F46" s="38" t="n">
+        <v>12909142288</v>
+      </c>
+      <c r="G46" s="39" t="n">
+        <v>0.006305</v>
+      </c>
+      <c r="H46" s="39" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="I46" s="39" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="J46" s="39" t="n">
+        <v>0.199435</v>
+      </c>
+      <c r="K46" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="L46" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M46" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N46" s="37" t="inlineStr">
+        <is>
+          <t>변동성 43.3%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="37" t="inlineStr">
+        <is>
+          <t>RISE 미국30년국채커버드콜(합성)</t>
+        </is>
+      </c>
+      <c r="B47" s="37" t="inlineStr">
+        <is>
+          <t>472830</t>
+        </is>
+      </c>
+      <c r="C47" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="n">
+        <v>7700</v>
+      </c>
+      <c r="E47" s="38" t="n">
+        <v>42707250000</v>
+      </c>
+      <c r="F47" s="38" t="n">
+        <v>286133353</v>
+      </c>
+      <c r="G47" s="39" t="n">
+        <v>0.003419</v>
+      </c>
+      <c r="H47" s="39" t="n">
+        <v>0.1409</v>
+      </c>
+      <c r="I47" s="39" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="J47" s="39" t="n">
+        <v>0.115065</v>
+      </c>
+      <c r="K47" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="L47" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M47" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N47" s="37" t="inlineStr">
+        <is>
+          <t>60일 거래대금 2.9억(기준 5억 미만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="37" t="inlineStr">
+        <is>
+          <t>RISE 미국AI밸류체인데일리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>490590</t>
+        </is>
+      </c>
+      <c r="C48" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D48" s="38" t="n">
+        <v>13620</v>
+      </c>
+      <c r="E48" s="38" t="n">
+        <v>760760000000</v>
+      </c>
+      <c r="F48" s="38" t="n">
+        <v>10122960865</v>
+      </c>
+      <c r="G48" s="39" t="n">
+        <v>0.00578</v>
+      </c>
+      <c r="H48" s="39" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="I48" s="39" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="J48" s="39" t="n">
+        <v>0.213069</v>
+      </c>
+      <c r="K48" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="L48" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M48" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N48" s="37" t="inlineStr">
+        <is>
+          <t>변동성 33.1%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="37" t="inlineStr">
+        <is>
+          <t>RISE 미국S&amp;P500데일리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>0138T0</t>
+        </is>
+      </c>
+      <c r="C49" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D49" s="38" t="n">
+        <v>9255</v>
+      </c>
+      <c r="E49" s="38" t="n">
+        <v>32305000000</v>
+      </c>
+      <c r="F49" s="38" t="n">
+        <v>320379724</v>
+      </c>
+      <c r="G49" s="39" t="n">
+        <v>0.006153</v>
+      </c>
+      <c r="H49" s="39" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="I49" s="39" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J49" s="39" t="n"/>
+      <c r="K49" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="L49" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M49" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N49" s="37" t="inlineStr">
+        <is>
+          <t>60일 거래대금 3.2억(기준 5억 미만), 분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="37" t="inlineStr">
+        <is>
+          <t>RISE 차이나테크TOP10위클리타겟커버드콜</t>
+        </is>
+      </c>
+      <c r="B50" s="37" t="inlineStr">
+        <is>
+          <t>0094L0</t>
+        </is>
+      </c>
+      <c r="C50" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D50" s="38" t="n">
+        <v>7060</v>
+      </c>
+      <c r="E50" s="38" t="n">
+        <v>9870000000</v>
+      </c>
+      <c r="F50" s="38" t="n">
+        <v>60751544</v>
+      </c>
+      <c r="G50" s="39" t="n">
+        <v>0.011533</v>
+      </c>
+      <c r="H50" s="39" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="I50" s="39" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="J50" s="39" t="n">
+        <v>0.154391</v>
+      </c>
+      <c r="K50" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="L50" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M50" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N50" s="37" t="inlineStr">
+        <is>
+          <t>순자산 99억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만), 변동성 27.9%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="37" t="inlineStr">
+        <is>
+          <t>RISE 코리아밸류업위클리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B51" s="37" t="inlineStr">
+        <is>
+          <t>0094M0</t>
+        </is>
+      </c>
+      <c r="C51" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D51" s="38" t="n">
+        <v>16850</v>
+      </c>
+      <c r="E51" s="38" t="n">
+        <v>343230000000</v>
+      </c>
+      <c r="F51" s="38" t="n">
+        <v>9600216582</v>
+      </c>
+      <c r="G51" s="39" t="n">
+        <v>0.005637</v>
+      </c>
+      <c r="H51" s="39" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="I51" s="39" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="J51" s="39" t="n">
+        <v>0.249258</v>
+      </c>
+      <c r="K51" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="L51" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M51" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N51" s="37" t="inlineStr">
+        <is>
+          <t>변동성 45.8%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="37" t="inlineStr">
+        <is>
+          <t>RISE 코스닥커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B52" s="37" t="inlineStr">
+        <is>
+          <t>0223A0</t>
+        </is>
+      </c>
+      <c r="C52" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D52" s="38" t="n">
+        <v>10440</v>
+      </c>
+      <c r="E52" s="38" t="n">
+        <v>16624000000</v>
+      </c>
+      <c r="F52" s="38" t="n"/>
+      <c r="G52" s="39" t="n">
+        <v>0.003264</v>
+      </c>
+      <c r="H52" s="39" t="n"/>
+      <c r="I52" s="39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J52" s="39" t="n"/>
+      <c r="K52" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M52" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N52" s="37" t="inlineStr">
+        <is>
+          <t>순자산 166억(기준 300억 미만), 거래대금 미확인, 변동성 산출 불가(시세 이력 부족), 분배 이력 1개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>RISE 테슬라미국채타겟커버드콜혼합(합성)</t>
+        </is>
+      </c>
+      <c r="B53" s="37" t="inlineStr">
+        <is>
+          <t>0013R0</t>
+        </is>
+      </c>
+      <c r="C53" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D53" s="38" t="n">
+        <v>7620</v>
+      </c>
+      <c r="E53" s="38" t="n">
+        <v>27432000000</v>
+      </c>
+      <c r="F53" s="38" t="n">
+        <v>162123452</v>
+      </c>
+      <c r="G53" s="39" t="n">
+        <v>0.003495</v>
+      </c>
+      <c r="H53" s="39" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="I53" s="39" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="J53" s="39" t="n">
+        <v>0.183727</v>
+      </c>
+      <c r="K53" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="L53" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M53" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N53" s="37" t="inlineStr">
+        <is>
+          <t>순자산 274억(기준 300억 미만), 60일 거래대금 1.6억(기준 5억 미만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t>SOL 200타겟위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B54" s="37" t="inlineStr">
+        <is>
+          <t>0167B0</t>
+        </is>
+      </c>
+      <c r="C54" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D54" s="38" t="n">
+        <v>11470</v>
+      </c>
+      <c r="E54" s="38" t="n">
+        <v>627507000000</v>
+      </c>
+      <c r="F54" s="38" t="n">
+        <v>21320154168</v>
+      </c>
+      <c r="G54" s="39" t="n">
+        <v>0.00345</v>
+      </c>
+      <c r="H54" s="39" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="I54" s="39" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="J54" s="39" t="n"/>
+      <c r="K54" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="L54" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M54" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N54" s="37" t="inlineStr">
+        <is>
+          <t>변동성 69.4%(기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="37" t="inlineStr">
+        <is>
+          <t>SOL 국제금커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B55" s="37" t="inlineStr">
+        <is>
+          <t>0022T0</t>
+        </is>
+      </c>
+      <c r="C55" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D55" s="38" t="n">
+        <v>12835</v>
+      </c>
+      <c r="E55" s="38" t="n">
+        <v>73074000000</v>
+      </c>
+      <c r="F55" s="38" t="n">
+        <v>1007376543</v>
+      </c>
+      <c r="G55" s="39" t="n">
+        <v>0.006737999999999999</v>
+      </c>
+      <c r="H55" s="39" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="I55" s="39" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="J55" s="39" t="n">
+        <v>0.04495499999999999</v>
+      </c>
+      <c r="K55" s="38" t="n">
+        <v>17</v>
+      </c>
+      <c r="L55" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M55" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N55" s="37" t="inlineStr">
+        <is>
+          <t>변동성 28.7%(기준 25% 초과)</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
       <c r="A56" s="37" t="inlineStr">
         <is>
-          <t>SOL 팔란티어커버드콜OTM채권혼합</t>
+          <t>SOL 미국500타겟데일리커버드콜액티브</t>
         </is>
       </c>
       <c r="B56" s="37" t="inlineStr">
         <is>
-          <t>0040Y0</t>
+          <t>494210</t>
         </is>
       </c>
       <c r="C56" s="37" t="inlineStr">
@@ -4813,15 +4755,35 @@
           <t>신한자산운용</t>
         </is>
       </c>
-      <c r="D56" s="38" t="n"/>
-      <c r="E56" s="38" t="n"/>
-      <c r="F56" s="38" t="n"/>
-      <c r="G56" s="39" t="n"/>
-      <c r="H56" s="39" t="n"/>
-      <c r="I56" s="39" t="n"/>
-      <c r="J56" s="39" t="n"/>
-      <c r="K56" s="38" t="n"/>
-      <c r="L56" s="37" t="n"/>
+      <c r="D56" s="38" t="n">
+        <v>10605</v>
+      </c>
+      <c r="E56" s="38" t="n">
+        <v>7423500000</v>
+      </c>
+      <c r="F56" s="38" t="n">
+        <v>64446271</v>
+      </c>
+      <c r="G56" s="39" t="n">
+        <v>0.00621</v>
+      </c>
+      <c r="H56" s="39" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="I56" s="39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J56" s="39" t="n">
+        <v>0.126638</v>
+      </c>
+      <c r="K56" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="L56" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
       <c r="M56" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -4829,7 +4791,7 @@
       </c>
       <c r="N56" s="37" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
+          <t>순자산 74억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만)</t>
         </is>
       </c>
     </row>
@@ -4962,13 +4924,13 @@
         </is>
       </c>
       <c r="D59" s="38" t="n">
-        <v>20277</v>
+        <v>20320</v>
       </c>
       <c r="E59" s="38" t="n">
         <v>208472000000</v>
       </c>
       <c r="F59" s="38" t="n">
-        <v>3412380553</v>
+        <v>3412420947</v>
       </c>
       <c r="G59" s="39" t="n">
         <v>0.003325</v>
@@ -4980,7 +4942,7 @@
         <v>0.0059</v>
       </c>
       <c r="J59" s="39" t="n">
-        <v>0.06066</v>
+        <v>0.06053099999999999</v>
       </c>
       <c r="K59" s="38" t="n">
         <v>12</v>
@@ -5018,13 +4980,13 @@
         </is>
       </c>
       <c r="D60" s="38" t="n">
-        <v>12835</v>
+        <v>12825</v>
       </c>
       <c r="E60" s="38" t="n">
         <v>66690000000</v>
       </c>
       <c r="F60" s="38" t="n">
-        <v>411171632</v>
+        <v>411176413</v>
       </c>
       <c r="G60" s="39" t="n">
         <v>0.005842000000000001</v>
@@ -5036,7 +4998,7 @@
         <v>0.0052</v>
       </c>
       <c r="J60" s="39" t="n">
-        <v>0.059758</v>
+        <v>0.059805</v>
       </c>
       <c r="K60" s="38" t="n">
         <v>39</v>
@@ -5074,19 +5036,19 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>10810</v>
+        <v>10840</v>
       </c>
       <c r="E61" s="38" t="n">
         <v>818900000000</v>
       </c>
       <c r="F61" s="38" t="n">
-        <v>33027634212</v>
+        <v>33031128122</v>
       </c>
       <c r="G61" s="39" t="n">
         <v>0.005719999999999999</v>
       </c>
       <c r="H61" s="39" t="n">
-        <v>0.9128000000000001</v>
+        <v>0.9129</v>
       </c>
       <c r="I61" s="39" t="n">
         <v>0.0155</v>
@@ -5128,13 +5090,13 @@
         </is>
       </c>
       <c r="D62" s="38" t="n">
-        <v>19835</v>
+        <v>19885</v>
       </c>
       <c r="E62" s="38" t="n">
         <v>2396790000000</v>
       </c>
       <c r="F62" s="38" t="n">
-        <v>103328325983</v>
+        <v>103343413229</v>
       </c>
       <c r="G62" s="39" t="n">
         <v>0.006008</v>
@@ -5146,7 +5108,7 @@
         <v>0.0197</v>
       </c>
       <c r="J62" s="39" t="n">
-        <v>0.221074</v>
+        <v>0.220518</v>
       </c>
       <c r="K62" s="38" t="n">
         <v>33</v>
@@ -5240,13 +5202,13 @@
         </is>
       </c>
       <c r="D64" s="38" t="n">
-        <v>10995</v>
+        <v>10985</v>
       </c>
       <c r="E64" s="38" t="n">
         <v>18742500000</v>
       </c>
       <c r="F64" s="38" t="n">
-        <v>267091677</v>
+        <v>267092197</v>
       </c>
       <c r="G64" s="39" t="n">
         <v>0.004345</v>
@@ -5363,14 +5325,14 @@
     <row r="12" ht="19" customHeight="1">
       <c r="B12" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 채택 20종목 — 유동성·변동성 기준을 통과한 월배당 커버드콜 ETF</t>
+          <t xml:space="preserve">     · 채택 22종목 — 유동성·변동성 기준을 통과한 월배당 커버드콜 ETF</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="B13" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 제외 41종목 — 사유는 [ETF데이터] 장 맨 오른쪽 칸에 적혀 있습니다.</t>
+          <t xml:space="preserve">     · 제외 39종목 — 사유는 [ETF데이터] 장 맨 오른쪽 칸에 적혀 있습니다.</t>
         </is>
       </c>
     </row>

--- a/고객제안서_월배당ETF.xlsx
+++ b/고객제안서_월배당ETF.xlsx
@@ -12,7 +12,7 @@
     <sheet name="사용법" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="채택종목">'ETF데이터'!$A$4:$A$25</definedName>
+    <definedName name="채택종목">'ETF데이터'!$A$4:$A$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'제안서'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'제안서'!$A$1:$H$73</definedName>
   </definedNames>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="K2" s="3">
-        <f>IFERROR(MATCH($C$9,'ETF데이터'!$A$4:$A$25,0),0)</f>
+        <f>IFERROR(MATCH($C$9,'ETF데이터'!$A$4:$A$20,0),0)</f>
         <v/>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
+          <t>KODEX 미국배당커버드콜액티브</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="C14" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$B$4:$B$25,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$B$4:$B$20,$K$2))</f>
         <v/>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="F14" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$G$4:$G$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$G$4:$G$20,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -836,16 +836,16 @@
         </is>
       </c>
       <c r="C15" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$C$4:$C$25,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$C$4:$C$20,$K$2))</f>
         <v/>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>변동성 (1년)</t>
+          <t>변동성 (1년, 연환산)</t>
         </is>
       </c>
       <c r="F15" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$H$4:$H$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$H$4:$H$20,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C16" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$D$4:$D$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$D$4:$D$20,$K$2))</f>
         <v/>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F16" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$I$4:$I$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$I$4:$I$20,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C17" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$E$4:$E$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$E$4:$E$20,$K$2))</f>
         <v/>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F17" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$J$4:$J$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$J$4:$J$20,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -896,7 +896,16 @@
         </is>
       </c>
       <c r="C18" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$F$4:$F$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$F$4:$F$20,$K$2))</f>
+        <v/>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>기초지수</t>
+        </is>
+      </c>
+      <c r="F18" s="12">
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$O$4:$O$20,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -1352,7 +1361,7 @@
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>5. 채택 ETF 비교 (1억원 투자 기준) — 연 분배율 상위 12종목 / 전체 22종목</t>
+          <t>5. 채택 ETF 비교 (1억원 투자 기준) — 연 분배율 상위 12종목 / 전체 17종목</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1898,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T03:46:41.846Z · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 1년 변동성 25% 이하, 분배 이력 12개월 이상</t>
+          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T03:52:32.909Z · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 연환산 변동성 25% 이하, 분배 이력 12개월 이상</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1935,13 +1944,14 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2022,6 +2032,11 @@
           <t>제외 사유</t>
         </is>
       </c>
+      <c r="O3" s="19" t="inlineStr">
+        <is>
+          <t>기초지수</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
@@ -2040,13 +2055,13 @@
         </is>
       </c>
       <c r="D4" s="35" t="n">
-        <v>7930</v>
+        <v>7925</v>
       </c>
       <c r="E4" s="35" t="n">
         <v>357021250000</v>
       </c>
       <c r="F4" s="35" t="n">
-        <v>2991827697</v>
+        <v>2991918624</v>
       </c>
       <c r="G4" s="36" t="n">
         <v>0.007532</v>
@@ -2058,7 +2073,7 @@
         <v>0.0194</v>
       </c>
       <c r="J4" s="36" t="n">
-        <v>0.281841</v>
+        <v>0.282019</v>
       </c>
       <c r="K4" s="35" t="n">
         <v>16</v>
@@ -2074,6 +2089,11 @@
         </is>
       </c>
       <c r="N4" s="34" t="inlineStr"/>
+      <c r="O4" s="34" t="inlineStr">
+        <is>
+          <t>KEDI Palantir Covered Call OTM Treasury Balanced Index NTR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
@@ -2092,13 +2112,13 @@
         </is>
       </c>
       <c r="D5" s="35" t="n">
-        <v>9895</v>
+        <v>9890</v>
       </c>
       <c r="E5" s="35" t="n">
         <v>176941500000</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>2871808688</v>
+        <v>2871904454</v>
       </c>
       <c r="G5" s="36" t="n">
         <v>0.005384</v>
@@ -2110,7 +2130,7 @@
         <v>0.0297</v>
       </c>
       <c r="J5" s="36" t="n">
-        <v>0.267812</v>
+        <v>0.267947</v>
       </c>
       <c r="K5" s="35" t="n">
         <v>29</v>
@@ -2126,6 +2146,11 @@
         </is>
       </c>
       <c r="N5" s="34" t="inlineStr"/>
+      <c r="O5" s="34" t="inlineStr">
+        <is>
+          <t>Bloomberg US Big Tech Top 7 Plus Premium(QQQ) Decrement 15%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
@@ -2178,6 +2203,11 @@
         </is>
       </c>
       <c r="N6" s="34" t="inlineStr"/>
+      <c r="O6" s="34" t="inlineStr">
+        <is>
+          <t>KEDI Palantir U.S. Treasury Covered Call Balanced Index NTR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="34" t="inlineStr">
@@ -2196,13 +2226,13 @@
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>8775</v>
+        <v>8785</v>
       </c>
       <c r="E7" s="35" t="n">
         <v>1002716000000</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>13538746518</v>
+        <v>13541085082</v>
       </c>
       <c r="G7" s="36" t="n">
         <v>0.005108000000000001</v>
@@ -2214,7 +2244,7 @@
         <v>0.0166</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>0.230199</v>
+        <v>0.229937</v>
       </c>
       <c r="K7" s="35" t="n">
         <v>22</v>
@@ -2230,6 +2260,11 @@
         </is>
       </c>
       <c r="N7" s="34" t="inlineStr"/>
+      <c r="O7" s="34" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 Daily Covered Call 101 Index TR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="34" t="inlineStr">
@@ -2248,13 +2283,13 @@
         </is>
       </c>
       <c r="D8" s="35" t="n">
-        <v>10235</v>
+        <v>10230</v>
       </c>
       <c r="E8" s="35" t="n">
         <v>560567000000</v>
       </c>
       <c r="F8" s="35" t="n">
-        <v>7569909350</v>
+        <v>7570448667</v>
       </c>
       <c r="G8" s="36" t="n">
         <v>0.005748</v>
@@ -2266,7 +2301,7 @@
         <v>0.0166</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>0.219834</v>
+        <v>0.219941</v>
       </c>
       <c r="K8" s="35" t="n">
         <v>23</v>
@@ -2282,6 +2317,11 @@
         </is>
       </c>
       <c r="N8" s="34" t="inlineStr"/>
+      <c r="O8" s="34" t="inlineStr">
+        <is>
+          <t>KEDI U.S. Tech100 90% Participation + Daily Options Premium</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
@@ -2306,7 +2346,7 @@
         <v>160608000000</v>
       </c>
       <c r="F9" s="35" t="n">
-        <v>1353456781</v>
+        <v>1353459169</v>
       </c>
       <c r="G9" s="36" t="n">
         <v>0.005391</v>
@@ -2334,6 +2374,11 @@
         </is>
       </c>
       <c r="N9" s="34" t="inlineStr"/>
+      <c r="O9" s="34" t="inlineStr">
+        <is>
+          <t>Bloomberg US 500 Large Cap Premium(SPY) Decrement 15% Distri</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="34" t="inlineStr">
@@ -2358,7 +2403,7 @@
         <v>168973500000</v>
       </c>
       <c r="F10" s="35" t="n">
-        <v>2335576978</v>
+        <v>2335600914</v>
       </c>
       <c r="G10" s="36" t="n">
         <v>0.005953000000000001</v>
@@ -2386,6 +2431,11 @@
         </is>
       </c>
       <c r="N10" s="34" t="inlineStr"/>
+      <c r="O10" s="34" t="inlineStr">
+        <is>
+          <t>KEDI U.S. Dividend100 90% Participation + Daily Options Prem</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
@@ -2404,13 +2454,13 @@
         </is>
       </c>
       <c r="D11" s="35" t="n">
-        <v>7830</v>
+        <v>7835</v>
       </c>
       <c r="E11" s="35" t="n">
         <v>285403500000</v>
       </c>
       <c r="F11" s="35" t="n">
-        <v>1454588648</v>
+        <v>1454665215</v>
       </c>
       <c r="G11" s="36" t="n">
         <v>0.005215</v>
@@ -2422,7 +2472,7 @@
         <v>0.0125</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>0.16424</v>
+        <v>0.164135</v>
       </c>
       <c r="K11" s="35" t="n">
         <v>31</v>
@@ -2438,6 +2488,11 @@
         </is>
       </c>
       <c r="N11" s="34" t="inlineStr"/>
+      <c r="O11" s="34" t="inlineStr">
+        <is>
+          <t>KEDI Tesla Income Premium Balanced Index</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
@@ -2456,13 +2511,13 @@
         </is>
       </c>
       <c r="D12" s="35" t="n">
-        <v>11110</v>
+        <v>11115</v>
       </c>
       <c r="E12" s="35" t="n">
         <v>240761500000</v>
       </c>
       <c r="F12" s="35" t="n">
-        <v>1833485783</v>
+        <v>1833496002</v>
       </c>
       <c r="G12" s="36" t="n">
         <v>0.004813</v>
@@ -2474,7 +2529,7 @@
         <v>0.0124</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>0.163456</v>
+        <v>0.163383</v>
       </c>
       <c r="K12" s="35" t="n">
         <v>23</v>
@@ -2490,6 +2545,11 @@
         </is>
       </c>
       <c r="N12" s="34" t="inlineStr"/>
+      <c r="O12" s="34" t="inlineStr">
+        <is>
+          <t>KEDI US AI Big Tech 10+15% Daily Premium Index TR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
@@ -2514,7 +2574,7 @@
         <v>198660000000</v>
       </c>
       <c r="F13" s="35" t="n">
-        <v>1973258151</v>
+        <v>1973293327</v>
       </c>
       <c r="G13" s="36" t="n">
         <v>0.005639999999999999</v>
@@ -2542,46 +2602,51 @@
         </is>
       </c>
       <c r="N13" s="34" t="inlineStr"/>
+      <c r="O13" s="34" t="inlineStr">
+        <is>
+          <t>S&amp;P500 Covered Call 1% OTM Daily Index(TR)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
+          <t>KODEX 미국AI테크TOP10타겟커버드콜</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>486290</t>
+          <t>483280</t>
         </is>
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D14" s="35" t="n">
-        <v>10230</v>
+        <v>11510</v>
       </c>
       <c r="E14" s="35" t="n">
-        <v>2435426000000</v>
+        <v>451950000000</v>
       </c>
       <c r="F14" s="35" t="n">
-        <v>29766958577</v>
+        <v>2928636655</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>0.004563</v>
+        <v>0.005830999999999999</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>0.2068</v>
+        <v>0.2452</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>0.0124</v>
+        <v>0.0123</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>0.160117</v>
+        <v>0.159861</v>
       </c>
       <c r="K14" s="35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L14" s="34" t="inlineStr">
         <is>
@@ -2594,46 +2659,51 @@
         </is>
       </c>
       <c r="N14" s="34" t="inlineStr"/>
+      <c r="O14" s="34" t="inlineStr">
+        <is>
+          <t>KEDI US AI Tech Top 10+15% Premium Index</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국AI테크TOP10타겟커버드콜</t>
+          <t>TIGER 미국30년국채커버드콜액티브(H)</t>
         </is>
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>483280</t>
+          <t>476550</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="D15" s="35" t="n">
-        <v>11505</v>
+        <v>6690</v>
       </c>
       <c r="E15" s="35" t="n">
-        <v>451950000000</v>
+        <v>756407750000</v>
       </c>
       <c r="F15" s="35" t="n">
-        <v>2928583908</v>
+        <v>7956706084</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>0.005830999999999999</v>
+        <v>0.007784</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>0.2452</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>0.0123</v>
+        <v>0.01</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>0.15993</v>
+        <v>0.135426</v>
       </c>
       <c r="K15" s="35" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L15" s="34" t="inlineStr">
         <is>
@@ -2646,50 +2716,55 @@
         </is>
       </c>
       <c r="N15" s="34" t="inlineStr"/>
+      <c r="O15" s="34" t="inlineStr">
+        <is>
+          <t>KEDI US Treasury 30Y Weekly Covered Call 30 Index</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국30년국채커버드콜액티브(H)</t>
+          <t>KODEX 미국30년국채타겟커버드콜(합성 H)</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
         <is>
-          <t>476550</t>
+          <t>481060</t>
         </is>
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D16" s="35" t="n">
-        <v>6690</v>
+        <v>7265</v>
       </c>
       <c r="E16" s="35" t="n">
-        <v>756407750000</v>
+        <v>740576850000</v>
       </c>
       <c r="F16" s="35" t="n">
-        <v>7955569118</v>
+        <v>4086859803</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>0.007784</v>
+        <v>0.003244</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0842</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>0.01</v>
+        <v>0.0101</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>0.135426</v>
+        <v>0.132691</v>
       </c>
       <c r="K16" s="35" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L16" s="34" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M16" s="34" t="inlineStr">
@@ -2698,50 +2773,55 @@
         </is>
       </c>
       <c r="N16" s="34" t="inlineStr"/>
+      <c r="O16" s="34" t="inlineStr">
+        <is>
+          <t>Bloomberg U.S. Treasury 20+ Year + 12% Premium (TLT) Covered</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국30년국채타겟커버드콜(합성 H)</t>
+          <t>SOL 미국30년국채커버드콜(합성)</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>481060</t>
+          <t>473330</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="D17" s="35" t="n">
-        <v>7265</v>
+        <v>7780</v>
       </c>
       <c r="E17" s="35" t="n">
-        <v>740576850000</v>
+        <v>272513750000</v>
       </c>
       <c r="F17" s="35" t="n">
-        <v>4086823114</v>
+        <v>2164088880</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>0.003244</v>
+        <v>0.0035</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>0.0842</v>
+        <v>0.135</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>0.0101</v>
+        <v>0.0074</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>0.132691</v>
+        <v>0.13072</v>
       </c>
       <c r="K17" s="35" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L17" s="34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M17" s="34" t="inlineStr">
@@ -2750,46 +2830,51 @@
         </is>
       </c>
       <c r="N17" s="34" t="inlineStr"/>
+      <c r="O17" s="34" t="inlineStr">
+        <is>
+          <t>KEDI US Treasury 20Y+ 2% OTM BuyWrite Index</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
         <is>
-          <t>SOL 미국30년국채커버드콜(합성)</t>
+          <t>KODEX 미국배당다우존스타겟커버드콜</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>473330</t>
+          <t>483290</t>
         </is>
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D18" s="35" t="n">
-        <v>7785</v>
+        <v>10230</v>
       </c>
       <c r="E18" s="35" t="n">
-        <v>272513750000</v>
+        <v>177915000000</v>
       </c>
       <c r="F18" s="35" t="n">
-        <v>2163923045</v>
+        <v>2277739954</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>0.0035</v>
+        <v>0.005798</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>0.135</v>
+        <v>0.1572</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>0.0074</v>
+        <v>0.0098</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>0.130636</v>
+        <v>0.121799</v>
       </c>
       <c r="K18" s="35" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L18" s="34" t="inlineStr">
         <is>
@@ -2802,16 +2887,21 @@
         </is>
       </c>
       <c r="N18" s="34" t="inlineStr"/>
+      <c r="O18" s="34" t="inlineStr">
+        <is>
+          <t>Dow Jones US Dividend 100 10% Premium Covered Call Index(PR)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국나스닥100커버드콜(합성)</t>
+          <t>TIGER 미국S&amp;P500타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>441680</t>
+          <t>482730</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
@@ -2820,32 +2910,32 @@
         </is>
       </c>
       <c r="D19" s="35" t="n">
-        <v>10610</v>
+        <v>11445</v>
       </c>
       <c r="E19" s="35" t="n">
-        <v>279306000000</v>
+        <v>657225000000</v>
       </c>
       <c r="F19" s="35" t="n">
-        <v>960130678</v>
+        <v>4931971020</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>0.004923</v>
+        <v>0.004313</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>0.146</v>
+        <v>0.148</v>
       </c>
       <c r="I19" s="36" t="n">
         <v>0.01</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>0.126296</v>
+        <v>0.107034</v>
       </c>
       <c r="K19" s="35" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="L19" s="34" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M19" s="34" t="inlineStr">
@@ -2854,16 +2944,21 @@
         </is>
       </c>
       <c r="N19" s="34" t="inlineStr"/>
+      <c r="O19" s="34" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 10% Daily Premium Covered Call Index (USD) PR</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국배당다우존스타겟커버드콜</t>
+          <t>KODEX 미국배당커버드콜액티브</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
         <is>
-          <t>483290</t>
+          <t>441640</t>
         </is>
       </c>
       <c r="C20" s="34" t="inlineStr">
@@ -2872,338 +2967,360 @@
         </is>
       </c>
       <c r="D20" s="35" t="n">
-        <v>10230</v>
+        <v>12340</v>
       </c>
       <c r="E20" s="35" t="n">
-        <v>177915000000</v>
+        <v>1701540000000</v>
       </c>
       <c r="F20" s="35" t="n">
-        <v>2277594518</v>
+        <v>12379897766</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>0.005798</v>
+        <v>0.003631</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>0.1572</v>
+        <v>0.1233</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>0.0098</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>0.121799</v>
+        <v>0.09594799999999999</v>
       </c>
       <c r="K20" s="35" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="L20" s="34" t="inlineStr">
         <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M20" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N20" s="34" t="inlineStr"/>
+      <c r="O20" s="34" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="37" t="inlineStr">
+        <is>
+          <t>ACE 고배당주Plus커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B21" s="37" t="inlineStr">
+        <is>
+          <t>0199C0</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
+        <is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D21" s="38" t="n"/>
+      <c r="E21" s="38" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
+      <c r="H21" s="39" t="n"/>
+      <c r="I21" s="39" t="n"/>
+      <c r="J21" s="39" t="n"/>
+      <c r="K21" s="38" t="n"/>
+      <c r="L21" s="37" t="n"/>
+      <c r="M21" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N21" s="37" t="inlineStr">
+        <is>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
+        </is>
+      </c>
+      <c r="O21" s="37" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
+        </is>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>480040</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
+        <is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D22" s="38" t="n">
+        <v>13340</v>
+      </c>
+      <c r="E22" s="38" t="n">
+        <v>181016000000</v>
+      </c>
+      <c r="F22" s="38" t="n">
+        <v>3487753342</v>
+      </c>
+      <c r="G22" s="39" t="n">
+        <v>0.005406999999999999</v>
+      </c>
+      <c r="H22" s="39" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="I22" s="39" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="J22" s="39" t="n">
+        <v>0.261019</v>
+      </c>
+      <c r="K22" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="L22" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M22" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N22" s="37" t="inlineStr">
+        <is>
+          <t>변동성 44.1%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O22" s="37" t="inlineStr">
+        <is>
+          <t>Bloomberg US Listed Semiconductor Premium(QQQ) Decrement 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t>ACE 미국배당퀄리티+커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>0049M0</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D23" s="38" t="n">
+        <v>11010</v>
+      </c>
+      <c r="E23" s="38" t="n">
+        <v>78171000000</v>
+      </c>
+      <c r="F23" s="38" t="n">
+        <v>379517920</v>
+      </c>
+      <c r="G23" s="39" t="n">
+        <v>0.005323</v>
+      </c>
+      <c r="H23" s="39" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="I23" s="39" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J23" s="39" t="n">
+        <v>0.075658</v>
+      </c>
+      <c r="K23" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="L23" s="37" t="inlineStr">
+        <is>
           <t>20260828</t>
         </is>
       </c>
-      <c r="M20" s="34" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N20" s="34" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>TIGER 미국배당다우존스타겟데일리커버드콜</t>
-        </is>
-      </c>
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>0008S0</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="n">
-        <v>9785</v>
-      </c>
-      <c r="E21" s="35" t="n">
-        <v>315077000000</v>
-      </c>
-      <c r="F21" s="35" t="n">
-        <v>3345859260</v>
-      </c>
-      <c r="G21" s="36" t="n">
-        <v>0.004797</v>
-      </c>
-      <c r="H21" s="36" t="n">
-        <v>0.1437</v>
-      </c>
-      <c r="I21" s="36" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J21" s="36" t="n">
-        <v>0.120286</v>
-      </c>
-      <c r="K21" s="35" t="n">
-        <v>20</v>
-      </c>
-      <c r="L21" s="34" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M21" s="34" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N21" s="34" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="34" t="inlineStr">
-        <is>
-          <t>TIGER 미국S&amp;P500타겟데일리커버드콜</t>
-        </is>
-      </c>
-      <c r="B22" s="34" t="inlineStr">
-        <is>
-          <t>482730</t>
-        </is>
-      </c>
-      <c r="C22" s="34" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="n">
-        <v>11440</v>
-      </c>
-      <c r="E22" s="35" t="n">
-        <v>657225000000</v>
-      </c>
-      <c r="F22" s="35" t="n">
-        <v>4931810730</v>
-      </c>
-      <c r="G22" s="36" t="n">
-        <v>0.004313</v>
-      </c>
-      <c r="H22" s="36" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="I22" s="36" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J22" s="36" t="n">
-        <v>0.10708</v>
-      </c>
-      <c r="K22" s="35" t="n">
-        <v>28</v>
-      </c>
-      <c r="L22" s="34" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M22" s="34" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N22" s="34" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="34" t="inlineStr">
-        <is>
-          <t>TIGER 미국테크TOP10타겟커버드콜</t>
-        </is>
-      </c>
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>474220</t>
-        </is>
-      </c>
-      <c r="C23" s="34" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>14695</v>
-      </c>
-      <c r="E23" s="35" t="n">
-        <v>413976000000</v>
-      </c>
-      <c r="F23" s="35" t="n">
-        <v>1732176149</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>0.006686</v>
-      </c>
-      <c r="H23" s="36" t="n">
-        <v>0.1938</v>
-      </c>
-      <c r="I23" s="36" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="J23" s="36" t="n">
-        <v>0.106703</v>
-      </c>
-      <c r="K23" s="35" t="n">
-        <v>32</v>
-      </c>
-      <c r="L23" s="34" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M23" s="34" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N23" s="34" t="inlineStr"/>
+      <c r="M23" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N23" s="37" t="inlineStr">
+        <is>
+          <t>60일 거래대금 3.8억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O23" s="37" t="inlineStr">
+        <is>
+          <t>Bloomberg WisdomTree U.S. Quality Dividend &amp; B500 Premium De</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
-        <is>
-          <t>TIGER 미국배당다우존스타겟커버드콜2호</t>
-        </is>
-      </c>
-      <c r="B24" s="34" t="inlineStr">
-        <is>
-          <t>458760</t>
-        </is>
-      </c>
-      <c r="C24" s="34" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D24" s="35" t="n">
-        <v>10885</v>
-      </c>
-      <c r="E24" s="35" t="n">
-        <v>699584000000</v>
-      </c>
-      <c r="F24" s="35" t="n">
-        <v>3403419023</v>
-      </c>
-      <c r="G24" s="36" t="n">
-        <v>0.005643</v>
-      </c>
-      <c r="H24" s="36" t="n">
-        <v>0.1504</v>
-      </c>
-      <c r="I24" s="36" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J24" s="36" t="n">
-        <v>0.099954</v>
-      </c>
-      <c r="K24" s="35" t="n">
-        <v>38</v>
-      </c>
-      <c r="L24" s="34" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>FOCUS AI반도체위클리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>0176P0</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
+        <is>
+          <t>브이아이자산운용</t>
+        </is>
+      </c>
+      <c r="D24" s="38" t="n">
+        <v>12650</v>
+      </c>
+      <c r="E24" s="38" t="n">
+        <v>6864000000</v>
+      </c>
+      <c r="F24" s="38" t="n">
+        <v>168942749</v>
+      </c>
+      <c r="G24" s="39" t="n">
+        <v>0.003711</v>
+      </c>
+      <c r="H24" s="39" t="n">
+        <v>0.7998999999999999</v>
+      </c>
+      <c r="I24" s="39" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="J24" s="39" t="n"/>
+      <c r="K24" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" s="37" t="inlineStr">
         <is>
           <t>20260828</t>
         </is>
       </c>
-      <c r="M24" s="34" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N24" s="34" t="inlineStr"/>
+      <c r="M24" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N24" s="37" t="inlineStr">
+        <is>
+          <t>순자산 69억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 80.0%(111거래일 기준, 기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O24" s="37" t="inlineStr">
+        <is>
+          <t>AI 반도체 위클리 고정 30% 커버드콜 지수</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
-        <is>
-          <t>KODEX 미국배당커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B25" s="34" t="inlineStr">
-        <is>
-          <t>441640</t>
-        </is>
-      </c>
-      <c r="C25" s="34" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="n">
-        <v>12335</v>
-      </c>
-      <c r="E25" s="35" t="n">
-        <v>1701540000000</v>
-      </c>
-      <c r="F25" s="35" t="n">
-        <v>12379074849</v>
-      </c>
-      <c r="G25" s="36" t="n">
-        <v>0.003631</v>
-      </c>
-      <c r="H25" s="36" t="n">
-        <v>0.1233</v>
-      </c>
-      <c r="I25" s="36" t="n">
-        <v>0.007800000000000001</v>
-      </c>
-      <c r="J25" s="36" t="n">
-        <v>0.09598699999999999</v>
-      </c>
-      <c r="K25" s="35" t="n">
-        <v>48</v>
-      </c>
-      <c r="L25" s="34" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M25" s="34" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N25" s="34" t="inlineStr"/>
+      <c r="A25" s="37" t="inlineStr">
+        <is>
+          <t>FOCUS 알리바바미국채커버드콜혼합</t>
+        </is>
+      </c>
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t>0073X0</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>브이아이자산운용</t>
+        </is>
+      </c>
+      <c r="D25" s="38" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E25" s="38" t="n">
+        <v>4760250000</v>
+      </c>
+      <c r="F25" s="38" t="n">
+        <v>30623084</v>
+      </c>
+      <c r="G25" s="39" t="n">
+        <v>0.01601</v>
+      </c>
+      <c r="H25" s="39" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="I25" s="39" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="J25" s="39" t="n">
+        <v>0.148555</v>
+      </c>
+      <c r="K25" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="L25" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M25" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N25" s="37" t="inlineStr">
+        <is>
+          <t>순자산 48억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O25" s="37" t="inlineStr">
+        <is>
+          <t>KEDI 알리바바 미국채커버드콜혼합지수(TR)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="37" t="inlineStr">
         <is>
-          <t>ACE 고배당주Plus커버드콜액티브</t>
+          <t>KIWOOM 코스닥150커버드콜액티브</t>
         </is>
       </c>
       <c r="B26" s="37" t="inlineStr">
         <is>
-          <t>0199C0</t>
+          <t>0198A0</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="D26" s="38" t="n">
-        <v>9215</v>
+        <v>8390</v>
       </c>
       <c r="E26" s="38" t="n">
-        <v>138375000000</v>
+        <v>72688500000</v>
       </c>
       <c r="F26" s="38" t="n">
-        <v>6508557052</v>
+        <v>4941048490</v>
       </c>
       <c r="G26" s="39" t="n">
-        <v>0.004522</v>
-      </c>
-      <c r="H26" s="39" t="n">
-        <v>0.3598</v>
-      </c>
+        <v>0.006657</v>
+      </c>
+      <c r="H26" s="39" t="n"/>
       <c r="I26" s="39" t="n">
-        <v>0.0179</v>
+        <v>0.0243</v>
       </c>
       <c r="J26" s="39" t="n"/>
       <c r="K26" s="38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" s="37" t="inlineStr">
         <is>
@@ -3217,53 +3334,54 @@
       </c>
       <c r="N26" s="37" t="inlineStr">
         <is>
-          <t>변동성 36.0%(기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 산출 불가(시세 55일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O26" s="37" t="inlineStr">
+        <is>
+          <t>코스닥 150 위클리 고정 30% 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="37" t="inlineStr">
         <is>
-          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
+          <t>KODEX 200커버드콜액티브</t>
         </is>
       </c>
       <c r="B27" s="37" t="inlineStr">
         <is>
-          <t>480040</t>
+          <t>0219E0</t>
         </is>
       </c>
       <c r="C27" s="37" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D27" s="38" t="n">
-        <v>13340</v>
+        <v>8180</v>
       </c>
       <c r="E27" s="38" t="n">
-        <v>181016000000</v>
+        <v>726902000000</v>
       </c>
       <c r="F27" s="38" t="n">
-        <v>3487605490</v>
+        <v>46393698652</v>
       </c>
       <c r="G27" s="39" t="n">
-        <v>0.005406999999999999</v>
-      </c>
-      <c r="H27" s="39" t="n">
-        <v>0.4411</v>
-      </c>
+        <v>0.005278000000000001</v>
+      </c>
+      <c r="H27" s="39" t="n"/>
       <c r="I27" s="39" t="n">
-        <v>0.0303</v>
-      </c>
-      <c r="J27" s="39" t="n">
-        <v>0.261019</v>
-      </c>
+        <v>0.0193</v>
+      </c>
+      <c r="J27" s="39" t="n"/>
       <c r="K27" s="38" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="L27" s="37" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M27" s="37" t="inlineStr">
@@ -3273,53 +3391,58 @@
       </c>
       <c r="N27" s="37" t="inlineStr">
         <is>
-          <t>변동성 44.1%(기준 25% 초과)</t>
+          <t>변동성 산출 불가(시세 45일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O27" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 커버드콜 5% OTM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="37" t="inlineStr">
         <is>
-          <t>ACE 미국배당퀄리티+커버드콜액티브</t>
+          <t>KODEX 200타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B28" s="37" t="inlineStr">
         <is>
-          <t>0049M0</t>
+          <t>498400</t>
         </is>
       </c>
       <c r="C28" s="37" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D28" s="38" t="n">
-        <v>11015</v>
+        <v>19775</v>
       </c>
       <c r="E28" s="38" t="n">
-        <v>78171000000</v>
+        <v>5759831000000</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>379512735</v>
+        <v>176445783223</v>
       </c>
       <c r="G28" s="39" t="n">
-        <v>0.005323</v>
+        <v>0.005095</v>
       </c>
       <c r="H28" s="39" t="n">
-        <v>0.1288</v>
+        <v>0.5655</v>
       </c>
       <c r="I28" s="39" t="n">
-        <v>0.006</v>
+        <v>0.0145</v>
       </c>
       <c r="J28" s="39" t="n">
-        <v>0.075624</v>
+        <v>0.158078</v>
       </c>
       <c r="K28" s="38" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L28" s="37" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M28" s="37" t="inlineStr">
@@ -3329,47 +3452,54 @@
       </c>
       <c r="N28" s="37" t="inlineStr">
         <is>
-          <t>60일 거래대금 3.8억(기준 5억 미만)</t>
+          <t>변동성 56.6%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O28" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 타겟 15% 위클리 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="37" t="inlineStr">
         <is>
-          <t>FOCUS AI반도체위클리고정커버드콜</t>
+          <t>KODEX 금융고배당TOP10타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B29" s="37" t="inlineStr">
         <is>
-          <t>0176P0</t>
+          <t>498410</t>
         </is>
       </c>
       <c r="C29" s="37" t="inlineStr">
         <is>
-          <t>브이아이자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D29" s="38" t="n">
-        <v>12650</v>
+        <v>11965</v>
       </c>
       <c r="E29" s="38" t="n">
-        <v>6864000000</v>
+        <v>843040000000</v>
       </c>
       <c r="F29" s="38" t="n">
-        <v>168942749</v>
+        <v>22965862505</v>
       </c>
       <c r="G29" s="39" t="n">
-        <v>0.003711</v>
+        <v>0.006697</v>
       </c>
       <c r="H29" s="39" t="n">
-        <v>0.7998999999999999</v>
+        <v>0.3274</v>
       </c>
       <c r="I29" s="39" t="n">
-        <v>0.0143</v>
-      </c>
-      <c r="J29" s="39" t="n"/>
+        <v>0.0121</v>
+      </c>
+      <c r="J29" s="39" t="n">
+        <v>0.157292</v>
+      </c>
       <c r="K29" s="38" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L29" s="37" t="inlineStr">
         <is>
@@ -3383,49 +3513,54 @@
       </c>
       <c r="N29" s="37" t="inlineStr">
         <is>
-          <t>순자산 69억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 80.0%(기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 32.7%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O29" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 금융 고배당 TOP 10 타겟 15% 분배 위클리 커버드콜</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="37" t="inlineStr">
         <is>
-          <t>FOCUS 알리바바미국채커버드콜혼합</t>
+          <t>KODEX 미국S&amp;P500변동성확대시커버드콜</t>
         </is>
       </c>
       <c r="B30" s="37" t="inlineStr">
         <is>
-          <t>0073X0</t>
+          <t>0089C0</t>
         </is>
       </c>
       <c r="C30" s="37" t="inlineStr">
         <is>
-          <t>브이아이자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D30" s="38" t="n">
-        <v>8650</v>
+        <v>11170</v>
       </c>
       <c r="E30" s="38" t="n">
-        <v>4760250000</v>
+        <v>42541000000</v>
       </c>
       <c r="F30" s="38" t="n">
-        <v>30593963</v>
+        <v>369289199</v>
       </c>
       <c r="G30" s="39" t="n">
-        <v>0.01601</v>
+        <v>0.006338</v>
       </c>
       <c r="H30" s="39" t="n">
-        <v>0.165</v>
+        <v>0.1398</v>
       </c>
       <c r="I30" s="39" t="n">
-        <v>0.0091</v>
+        <v>0.0009</v>
       </c>
       <c r="J30" s="39" t="n">
-        <v>0.148555</v>
+        <v>0.022292</v>
       </c>
       <c r="K30" s="38" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L30" s="37" t="inlineStr">
         <is>
@@ -3439,45 +3574,52 @@
       </c>
       <c r="N30" s="37" t="inlineStr">
         <is>
-          <t>순자산 48억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만)</t>
+          <t>60일 거래대금 3.7억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O30" s="37" t="inlineStr">
+        <is>
+          <t>Cboe S&amp;P 500 Volatility Contingent Daily Covered Call Index</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="37" t="inlineStr">
         <is>
-          <t>KIWOOM 코스닥150커버드콜액티브</t>
+          <t>KODEX 미국성장커버드콜액티브</t>
         </is>
       </c>
       <c r="B31" s="37" t="inlineStr">
         <is>
-          <t>0198A0</t>
+          <t>0144L0</t>
         </is>
       </c>
       <c r="C31" s="37" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D31" s="38" t="n">
-        <v>8390</v>
+        <v>9305</v>
       </c>
       <c r="E31" s="38" t="n">
-        <v>72688500000</v>
+        <v>339450000000</v>
       </c>
       <c r="F31" s="38" t="n">
-        <v>4940765671</v>
+        <v>2519924801</v>
       </c>
       <c r="G31" s="39" t="n">
-        <v>0.006657</v>
-      </c>
-      <c r="H31" s="39" t="n"/>
+        <v>0.006395</v>
+      </c>
+      <c r="H31" s="39" t="n">
+        <v>0.1816</v>
+      </c>
       <c r="I31" s="39" t="n">
-        <v>0.0243</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="J31" s="39" t="n"/>
       <c r="K31" s="38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L31" s="37" t="inlineStr">
         <is>
@@ -3491,19 +3633,24 @@
       </c>
       <c r="N31" s="37" t="inlineStr">
         <is>
-          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>분배 이력 8개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O31" s="37" t="inlineStr">
+        <is>
+          <t>나스닥 100</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="37" t="inlineStr">
         <is>
-          <t>KODEX 200커버드콜액티브</t>
+          <t>KODEX 반도체타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>0219E0</t>
+          <t>0190G0</t>
         </is>
       </c>
       <c r="C32" s="37" t="inlineStr">
@@ -3512,24 +3659,26 @@
         </is>
       </c>
       <c r="D32" s="38" t="n">
-        <v>8165</v>
+        <v>8685</v>
       </c>
       <c r="E32" s="38" t="n">
-        <v>726902000000</v>
+        <v>166945000000</v>
       </c>
       <c r="F32" s="38" t="n">
-        <v>46383634315</v>
+        <v>8917001863</v>
       </c>
       <c r="G32" s="39" t="n">
-        <v>0.005278000000000001</v>
-      </c>
-      <c r="H32" s="39" t="n"/>
+        <v>0.006131</v>
+      </c>
+      <c r="H32" s="39" t="n">
+        <v>0.8571</v>
+      </c>
       <c r="I32" s="39" t="n">
-        <v>0.0193</v>
+        <v>0.0074</v>
       </c>
       <c r="J32" s="39" t="n"/>
       <c r="K32" s="38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L32" s="37" t="inlineStr">
         <is>
@@ -3543,53 +3692,56 @@
       </c>
       <c r="N32" s="37" t="inlineStr">
         <is>
-          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 85.7%(88거래일 기준, 기준 25% 초과), 분배 이력 4개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O32" s="37" t="inlineStr">
+        <is>
+          <t>KRX 반도체 타겟 9% 분배 위클리 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="37" t="inlineStr">
         <is>
-          <t>KODEX 200타겟위클리커버드콜</t>
+          <t>PLUS 200위클리커버드콜채권혼합</t>
         </is>
       </c>
       <c r="B33" s="37" t="inlineStr">
         <is>
-          <t>498400</t>
+          <t>0203D0</t>
         </is>
       </c>
       <c r="C33" s="37" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="D33" s="38" t="n">
-        <v>19740</v>
+        <v>8820</v>
       </c>
       <c r="E33" s="38" t="n">
-        <v>5759831000000</v>
+        <v>10560000000</v>
       </c>
       <c r="F33" s="38" t="n">
-        <v>176412063439</v>
+        <v>273040602</v>
       </c>
       <c r="G33" s="39" t="n">
-        <v>0.005095</v>
+        <v>0.004914</v>
       </c>
       <c r="H33" s="39" t="n">
-        <v>0.5655</v>
+        <v>0.3808</v>
       </c>
       <c r="I33" s="39" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="J33" s="39" t="n">
-        <v>0.158359</v>
-      </c>
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="J33" s="39" t="n"/>
       <c r="K33" s="38" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="L33" s="37" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M33" s="37" t="inlineStr">
@@ -3599,49 +3751,50 @@
       </c>
       <c r="N33" s="37" t="inlineStr">
         <is>
-          <t>변동성 56.6%(기준 25% 초과)</t>
+          <t>순자산 106억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 38.1%(74거래일 기준, 기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O33" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 KTB 혼합 위클리 고정 10% 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="37" t="inlineStr">
         <is>
-          <t>KODEX 금융고배당TOP10타겟위클리커버드콜</t>
+          <t>PLUS 200커버드콜액티브</t>
         </is>
       </c>
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>498410</t>
+          <t>0210E0</t>
         </is>
       </c>
       <c r="C34" s="37" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="D34" s="38" t="n">
-        <v>11947</v>
+        <v>7160</v>
       </c>
       <c r="E34" s="38" t="n">
-        <v>843040000000</v>
+        <v>66881000000</v>
       </c>
       <c r="F34" s="38" t="n">
-        <v>22964822749</v>
+        <v>3120007789</v>
       </c>
       <c r="G34" s="39" t="n">
-        <v>0.006697</v>
-      </c>
-      <c r="H34" s="39" t="n">
-        <v>0.3274</v>
-      </c>
+        <v>0.006020999999999999</v>
+      </c>
+      <c r="H34" s="39" t="n"/>
       <c r="I34" s="39" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="J34" s="39" t="n">
-        <v>0.157529</v>
-      </c>
+        <v>0.0194</v>
+      </c>
+      <c r="J34" s="39" t="n"/>
       <c r="K34" s="38" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L34" s="37" t="inlineStr">
         <is>
@@ -3655,53 +3808,58 @@
       </c>
       <c r="N34" s="37" t="inlineStr">
         <is>
-          <t>변동성 32.7%(기준 25% 초과)</t>
+          <t>변동성 산출 불가(시세 60일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O34" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 위클리 고정 30% 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="37" t="inlineStr">
         <is>
-          <t>KODEX 미국S&amp;P500변동성확대시커버드콜</t>
+          <t>PLUS 고배당주위클리고정커버드콜</t>
         </is>
       </c>
       <c r="B35" s="37" t="inlineStr">
         <is>
-          <t>0089C0</t>
+          <t>0018C0</t>
         </is>
       </c>
       <c r="C35" s="37" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="D35" s="38" t="n">
-        <v>11170</v>
+        <v>10575</v>
       </c>
       <c r="E35" s="38" t="n">
-        <v>42541000000</v>
+        <v>80370000000</v>
       </c>
       <c r="F35" s="38" t="n">
-        <v>369289199</v>
+        <v>1033603521</v>
       </c>
       <c r="G35" s="39" t="n">
-        <v>0.006338</v>
+        <v>0.005958</v>
       </c>
       <c r="H35" s="39" t="n">
-        <v>0.1398</v>
+        <v>0.2667</v>
       </c>
       <c r="I35" s="39" t="n">
-        <v>0.0009</v>
+        <v>0.0124</v>
       </c>
       <c r="J35" s="39" t="n">
-        <v>0.022292</v>
+        <v>0.168983</v>
       </c>
       <c r="K35" s="38" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L35" s="37" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M35" s="37" t="inlineStr">
@@ -3711,47 +3869,54 @@
       </c>
       <c r="N35" s="37" t="inlineStr">
         <is>
-          <t>60일 거래대금 3.7억(기준 5억 미만)</t>
+          <t>변동성 26.7%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O35" s="37" t="inlineStr">
+        <is>
+          <t>코스피 고배당 위클리 고정 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="37" t="inlineStr">
         <is>
-          <t>KODEX 미국성장커버드콜액티브</t>
+          <t>PLUS 고배당주위클리커버드콜</t>
         </is>
       </c>
       <c r="B36" s="37" t="inlineStr">
         <is>
-          <t>0144L0</t>
+          <t>489030</t>
         </is>
       </c>
       <c r="C36" s="37" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="D36" s="38" t="n">
-        <v>9300</v>
+        <v>6460</v>
       </c>
       <c r="E36" s="38" t="n">
-        <v>339450000000</v>
+        <v>303208500000</v>
       </c>
       <c r="F36" s="38" t="n">
-        <v>2519368175</v>
+        <v>4301390728</v>
       </c>
       <c r="G36" s="39" t="n">
-        <v>0.006395</v>
+        <v>0.008243</v>
       </c>
       <c r="H36" s="39" t="n">
-        <v>0.1816</v>
+        <v>0.3069</v>
       </c>
       <c r="I36" s="39" t="n">
-        <v>0.009899999999999999</v>
-      </c>
-      <c r="J36" s="39" t="n"/>
+        <v>0.0148</v>
+      </c>
+      <c r="J36" s="39" t="n">
+        <v>0.234985</v>
+      </c>
       <c r="K36" s="38" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="L36" s="37" t="inlineStr">
         <is>
@@ -3765,51 +3930,58 @@
       </c>
       <c r="N36" s="37" t="inlineStr">
         <is>
-          <t>분배 이력 8개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 30.7%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O36" s="37" t="inlineStr">
+        <is>
+          <t>코스피 고배당 위클리 콜매도 ATM 지수</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="37" t="inlineStr">
         <is>
-          <t>KODEX 반도체타겟위클리커버드콜</t>
+          <t>PLUS 미국배당증가성장주데일리커버드콜</t>
         </is>
       </c>
       <c r="B37" s="37" t="inlineStr">
         <is>
-          <t>0190G0</t>
+          <t>494420</t>
         </is>
       </c>
       <c r="C37" s="37" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="D37" s="38" t="n">
-        <v>8670</v>
+        <v>8665</v>
       </c>
       <c r="E37" s="38" t="n">
-        <v>166945000000</v>
+        <v>15588000000</v>
       </c>
       <c r="F37" s="38" t="n">
-        <v>8916779253</v>
+        <v>115241283</v>
       </c>
       <c r="G37" s="39" t="n">
-        <v>0.006131</v>
+        <v>0.007707</v>
       </c>
       <c r="H37" s="39" t="n">
-        <v>0.8571</v>
+        <v>0.1439</v>
       </c>
       <c r="I37" s="39" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="J37" s="39" t="n"/>
+        <v>0.0119</v>
+      </c>
+      <c r="J37" s="39" t="n">
+        <v>0.149336</v>
+      </c>
       <c r="K37" s="38" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="L37" s="37" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M37" s="37" t="inlineStr">
@@ -3819,19 +3991,24 @@
       </c>
       <c r="N37" s="37" t="inlineStr">
         <is>
-          <t>변동성 85.7%(기준 25% 초과), 분배 이력 4개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>순자산 156억(기준 300억 미만), 60일 거래대금 1.2억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O37" s="37" t="inlineStr">
+        <is>
+          <t>Bloomberg U.S. Dividend Growth Partial Covered Call Index</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="37" t="inlineStr">
         <is>
-          <t>PLUS 200위클리커버드콜채권혼합</t>
+          <t>PLUS 차이나항셍테크위클리타겟커버드콜</t>
         </is>
       </c>
       <c r="B38" s="37" t="inlineStr">
         <is>
-          <t>0203D0</t>
+          <t>0128D0</t>
         </is>
       </c>
       <c r="C38" s="37" t="inlineStr">
@@ -3840,26 +4017,26 @@
         </is>
       </c>
       <c r="D38" s="38" t="n">
-        <v>8815</v>
+        <v>6410</v>
       </c>
       <c r="E38" s="38" t="n">
-        <v>10560000000</v>
+        <v>4476500000</v>
       </c>
       <c r="F38" s="38" t="n">
-        <v>272987049</v>
+        <v>29889499</v>
       </c>
       <c r="G38" s="39" t="n">
-        <v>0.004914</v>
+        <v>0.01153</v>
       </c>
       <c r="H38" s="39" t="n">
-        <v>0.3808</v>
+        <v>0.2722</v>
       </c>
       <c r="I38" s="39" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0125</v>
       </c>
       <c r="J38" s="39" t="n"/>
       <c r="K38" s="38" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L38" s="37" t="inlineStr">
         <is>
@@ -3873,19 +4050,24 @@
       </c>
       <c r="N38" s="37" t="inlineStr">
         <is>
-          <t>순자산 106억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 38.1%(기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>순자산 45억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만), 변동성 27.2%(1년 기준, 기준 25% 초과), 분배 이력 9개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O38" s="37" t="inlineStr">
+        <is>
+          <t>HSTECH 15% Target Premium Weekly Covered Call Index</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="37" t="inlineStr">
         <is>
-          <t>PLUS 200커버드콜액티브</t>
+          <t>PLUS 테슬라위클리커버드콜채권혼합</t>
         </is>
       </c>
       <c r="B39" s="37" t="inlineStr">
         <is>
-          <t>0210E0</t>
+          <t>0132K0</t>
         </is>
       </c>
       <c r="C39" s="37" t="inlineStr">
@@ -3894,28 +4076,30 @@
         </is>
       </c>
       <c r="D39" s="38" t="n">
-        <v>7135</v>
+        <v>7835</v>
       </c>
       <c r="E39" s="38" t="n">
-        <v>66881000000</v>
+        <v>108307000000</v>
       </c>
       <c r="F39" s="38" t="n">
-        <v>3119898268</v>
+        <v>1317359602</v>
       </c>
       <c r="G39" s="39" t="n">
-        <v>0.006020999999999999</v>
-      </c>
-      <c r="H39" s="39" t="n"/>
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="H39" s="39" t="n">
+        <v>0.1302</v>
+      </c>
       <c r="I39" s="39" t="n">
-        <v>0.0194</v>
+        <v>0.02</v>
       </c>
       <c r="J39" s="39" t="n"/>
       <c r="K39" s="38" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L39" s="37" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M39" s="37" t="inlineStr">
@@ -3925,53 +4109,58 @@
       </c>
       <c r="N39" s="37" t="inlineStr">
         <is>
-          <t>변동성 산출 불가(시세 이력 부족), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O39" s="37" t="inlineStr">
+        <is>
+          <t>Akros Tesla Weekly Covered Call Treasury Balanced Index</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="37" t="inlineStr">
         <is>
-          <t>PLUS 고배당주위클리고정커버드콜</t>
+          <t>RISE 200고배당커버드콜ATM</t>
         </is>
       </c>
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>0018C0</t>
+          <t>290080</t>
         </is>
       </c>
       <c r="C40" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>KB자산운용</t>
         </is>
       </c>
       <c r="D40" s="38" t="n">
-        <v>10570</v>
+        <v>7355</v>
       </c>
       <c r="E40" s="38" t="n">
-        <v>80370000000</v>
+        <v>12614000000</v>
       </c>
       <c r="F40" s="38" t="n">
-        <v>1033597951</v>
+        <v>168593114</v>
       </c>
       <c r="G40" s="39" t="n">
-        <v>0.005958</v>
+        <v>0.00636</v>
       </c>
       <c r="H40" s="39" t="n">
-        <v>0.2667</v>
+        <v>0.3097</v>
       </c>
       <c r="I40" s="39" t="n">
-        <v>0.0124</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="J40" s="39" t="n">
-        <v>0.169063</v>
+        <v>0.107682</v>
       </c>
       <c r="K40" s="38" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="L40" s="37" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M40" s="37" t="inlineStr">
@@ -3981,49 +4170,54 @@
       </c>
       <c r="N40" s="37" t="inlineStr">
         <is>
-          <t>변동성 26.7%(기준 25% 초과)</t>
+          <t>순자산 126억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 31.0%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O40" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 고배당 커버드콜 ATM</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="37" t="inlineStr">
         <is>
-          <t>PLUS 고배당주위클리커버드콜</t>
+          <t>RISE 200위클리커버드콜</t>
         </is>
       </c>
       <c r="B41" s="37" t="inlineStr">
         <is>
-          <t>489030</t>
+          <t>475720</t>
         </is>
       </c>
       <c r="C41" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>KB자산운용</t>
         </is>
       </c>
       <c r="D41" s="38" t="n">
-        <v>6460</v>
+        <v>12395</v>
       </c>
       <c r="E41" s="38" t="n">
-        <v>303208500000</v>
+        <v>821275000000</v>
       </c>
       <c r="F41" s="38" t="n">
-        <v>4301071496</v>
+        <v>12909513810</v>
       </c>
       <c r="G41" s="39" t="n">
-        <v>0.008243</v>
+        <v>0.006305</v>
       </c>
       <c r="H41" s="39" t="n">
-        <v>0.3069</v>
+        <v>0.4327</v>
       </c>
       <c r="I41" s="39" t="n">
-        <v>0.0148</v>
+        <v>0.0185</v>
       </c>
       <c r="J41" s="39" t="n">
-        <v>0.234985</v>
+        <v>0.199274</v>
       </c>
       <c r="K41" s="38" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L41" s="37" t="inlineStr">
         <is>
@@ -4037,35 +4231,60 @@
       </c>
       <c r="N41" s="37" t="inlineStr">
         <is>
-          <t>변동성 30.7%(기준 25% 초과)</t>
+          <t>변동성 43.3%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O41" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 위클리 커버드콜 ATM 지수</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="37" t="inlineStr">
         <is>
-          <t>PLUS 미국배당증가성장주데일리커버드콜</t>
+          <t>RISE 미국30년국채커버드콜(합성)</t>
         </is>
       </c>
       <c r="B42" s="37" t="inlineStr">
         <is>
-          <t>494420</t>
+          <t>472830</t>
         </is>
       </c>
       <c r="C42" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D42" s="38" t="n"/>
-      <c r="E42" s="38" t="n"/>
-      <c r="F42" s="38" t="n"/>
-      <c r="G42" s="39" t="n"/>
-      <c r="H42" s="39" t="n"/>
-      <c r="I42" s="39" t="n"/>
-      <c r="J42" s="39" t="n"/>
-      <c r="K42" s="38" t="n"/>
-      <c r="L42" s="37" t="n"/>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D42" s="38" t="n">
+        <v>7700</v>
+      </c>
+      <c r="E42" s="38" t="n">
+        <v>42707250000</v>
+      </c>
+      <c r="F42" s="38" t="n">
+        <v>286133353</v>
+      </c>
+      <c r="G42" s="39" t="n">
+        <v>0.003419</v>
+      </c>
+      <c r="H42" s="39" t="n">
+        <v>0.1409</v>
+      </c>
+      <c r="I42" s="39" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="J42" s="39" t="n">
+        <v>0.115065</v>
+      </c>
+      <c r="K42" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="L42" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
       <c r="M42" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -4073,35 +4292,60 @@
       </c>
       <c r="N42" s="37" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 403)</t>
+          <t>60일 거래대금 2.9억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O42" s="37" t="inlineStr">
+        <is>
+          <t>Bloomberg U.S. Treasury 20+ Year(TLT) 2% OTM Covered Call In</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="37" t="inlineStr">
         <is>
-          <t>PLUS 차이나항셍테크위클리타겟커버드콜</t>
+          <t>RISE 미국AI밸류체인데일리고정커버드콜</t>
         </is>
       </c>
       <c r="B43" s="37" t="inlineStr">
         <is>
-          <t>0128D0</t>
+          <t>490590</t>
         </is>
       </c>
       <c r="C43" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D43" s="38" t="n"/>
-      <c r="E43" s="38" t="n"/>
-      <c r="F43" s="38" t="n"/>
-      <c r="G43" s="39" t="n"/>
-      <c r="H43" s="39" t="n"/>
-      <c r="I43" s="39" t="n"/>
-      <c r="J43" s="39" t="n"/>
-      <c r="K43" s="38" t="n"/>
-      <c r="L43" s="37" t="n"/>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D43" s="38" t="n">
+        <v>13625</v>
+      </c>
+      <c r="E43" s="38" t="n">
+        <v>760760000000</v>
+      </c>
+      <c r="F43" s="38" t="n">
+        <v>10123027992</v>
+      </c>
+      <c r="G43" s="39" t="n">
+        <v>0.00578</v>
+      </c>
+      <c r="H43" s="39" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="I43" s="39" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="J43" s="39" t="n">
+        <v>0.212991</v>
+      </c>
+      <c r="K43" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="L43" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
       <c r="M43" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -4109,26 +4353,29 @@
       </c>
       <c r="N43" s="37" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
-Call log:
-  - )</t>
+          <t>변동성 33.1%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O43" s="37" t="inlineStr">
+        <is>
+          <t>KEDI U.S. AI Value Chain 90% Participation + Daily Options P</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="37" t="inlineStr">
         <is>
-          <t>PLUS 테슬라위클리커버드콜채권혼합</t>
+          <t>RISE 미국S&amp;P500데일리고정커버드콜</t>
         </is>
       </c>
       <c r="B44" s="37" t="inlineStr">
         <is>
-          <t>0132K0</t>
+          <t>0138T0</t>
         </is>
       </c>
       <c r="C44" s="37" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>KB자산운용</t>
         </is>
       </c>
       <c r="D44" s="38" t="n"/>
@@ -4147,643 +4394,677 @@
       </c>
       <c r="N44" s="37" t="inlineStr">
         <is>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
+        </is>
+      </c>
+      <c r="O44" s="37" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t>RISE 차이나테크TOP10위클리타겟커버드콜</t>
+        </is>
+      </c>
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>0094L0</t>
+        </is>
+      </c>
+      <c r="C45" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D45" s="38" t="n">
+        <v>7065</v>
+      </c>
+      <c r="E45" s="38" t="n">
+        <v>9870000000</v>
+      </c>
+      <c r="F45" s="38" t="n">
+        <v>60752172</v>
+      </c>
+      <c r="G45" s="39" t="n">
+        <v>0.011533</v>
+      </c>
+      <c r="H45" s="39" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="I45" s="39" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="J45" s="39" t="n">
+        <v>0.154282</v>
+      </c>
+      <c r="K45" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="L45" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M45" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N45" s="37" t="inlineStr">
+        <is>
+          <t>순자산 99억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만), 변동성 27.9%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O45" s="37" t="inlineStr">
+        <is>
+          <t>Bloomberg China Tech Select Top 10 + 12% Target Premium Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="37" t="inlineStr">
+        <is>
+          <t>RISE 코리아밸류업위클리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B46" s="37" t="inlineStr">
+        <is>
+          <t>0094M0</t>
+        </is>
+      </c>
+      <c r="C46" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D46" s="38" t="n">
+        <v>16880</v>
+      </c>
+      <c r="E46" s="38" t="n">
+        <v>343230000000</v>
+      </c>
+      <c r="F46" s="38" t="n">
+        <v>9600787404</v>
+      </c>
+      <c r="G46" s="39" t="n">
+        <v>0.005637</v>
+      </c>
+      <c r="H46" s="39" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="I46" s="39" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="J46" s="39" t="n">
+        <v>0.248815</v>
+      </c>
+      <c r="K46" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="L46" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M46" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N46" s="37" t="inlineStr">
+        <is>
+          <t>변동성 45.8%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O46" s="37" t="inlineStr">
+        <is>
+          <t>코리아 밸류업 위클리 커버드콜 30% 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="37" t="inlineStr">
+        <is>
+          <t>RISE 코스닥커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B47" s="37" t="inlineStr">
+        <is>
+          <t>0223A0</t>
+        </is>
+      </c>
+      <c r="C47" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="n">
+        <v>10440</v>
+      </c>
+      <c r="E47" s="38" t="n">
+        <v>16624000000</v>
+      </c>
+      <c r="F47" s="38" t="n"/>
+      <c r="G47" s="39" t="n">
+        <v>0.003264</v>
+      </c>
+      <c r="H47" s="39" t="n"/>
+      <c r="I47" s="39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J47" s="39" t="n"/>
+      <c r="K47" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M47" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N47" s="37" t="inlineStr">
+        <is>
+          <t>순자산 166억(기준 300억 미만), 거래대금 미확인, 변동성 산출 불가(시세 36일치뿐), 분배 이력 1개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O47" s="37" t="inlineStr">
+        <is>
+          <t>코스닥 150 타겟 15% 위클리 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="37" t="inlineStr">
+        <is>
+          <t>RISE 테슬라미국채타겟커버드콜혼합(합성)</t>
+        </is>
+      </c>
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>0013R0</t>
+        </is>
+      </c>
+      <c r="C48" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D48" s="38" t="n">
+        <v>7620</v>
+      </c>
+      <c r="E48" s="38" t="n">
+        <v>27432000000</v>
+      </c>
+      <c r="F48" s="38" t="n">
+        <v>162123452</v>
+      </c>
+      <c r="G48" s="39" t="n">
+        <v>0.003495</v>
+      </c>
+      <c r="H48" s="39" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="I48" s="39" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="J48" s="39" t="n">
+        <v>0.183727</v>
+      </c>
+      <c r="K48" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="L48" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M48" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N48" s="37" t="inlineStr">
+        <is>
+          <t>순자산 274억(기준 300억 미만), 60일 거래대금 1.6억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O48" s="37" t="inlineStr">
+        <is>
+          <t>KEDI Tesla U.S. 30Y Treasury 15% Target Premium Balanced Ind</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="37" t="inlineStr">
+        <is>
+          <t>SOL 200타겟위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>0167B0</t>
+        </is>
+      </c>
+      <c r="C49" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D49" s="38" t="n">
+        <v>11485</v>
+      </c>
+      <c r="E49" s="38" t="n">
+        <v>627507000000</v>
+      </c>
+      <c r="F49" s="38" t="n">
+        <v>21321082573</v>
+      </c>
+      <c r="G49" s="39" t="n">
+        <v>0.00345</v>
+      </c>
+      <c r="H49" s="39" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="I49" s="39" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="J49" s="39" t="n"/>
+      <c r="K49" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="L49" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M49" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N49" s="37" t="inlineStr">
+        <is>
+          <t>변동성 69.4%(126거래일 기준, 기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O49" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 타겟 15% 위클리 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="37" t="inlineStr">
+        <is>
+          <t>SOL 국제금커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B50" s="37" t="inlineStr">
+        <is>
+          <t>0022T0</t>
+        </is>
+      </c>
+      <c r="C50" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D50" s="38" t="n">
+        <v>12830</v>
+      </c>
+      <c r="E50" s="38" t="n">
+        <v>73074000000</v>
+      </c>
+      <c r="F50" s="38" t="n">
+        <v>1007418276</v>
+      </c>
+      <c r="G50" s="39" t="n">
+        <v>0.006737999999999999</v>
+      </c>
+      <c r="H50" s="39" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="I50" s="39" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="J50" s="39" t="n">
+        <v>0.044973</v>
+      </c>
+      <c r="K50" s="38" t="n">
+        <v>17</v>
+      </c>
+      <c r="L50" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M50" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N50" s="37" t="inlineStr">
+        <is>
+          <t>변동성 28.7%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O50" s="37" t="inlineStr">
+        <is>
+          <t>KEDI Gold Income Premium Index (Net Total Return)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="37" t="inlineStr">
+        <is>
+          <t>SOL 미국500타겟데일리커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B51" s="37" t="inlineStr">
+        <is>
+          <t>494210</t>
+        </is>
+      </c>
+      <c r="C51" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D51" s="38" t="n">
+        <v>10605</v>
+      </c>
+      <c r="E51" s="38" t="n">
+        <v>7423500000</v>
+      </c>
+      <c r="F51" s="38" t="n">
+        <v>64446271</v>
+      </c>
+      <c r="G51" s="39" t="n">
+        <v>0.00621</v>
+      </c>
+      <c r="H51" s="39" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="I51" s="39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J51" s="39" t="n">
+        <v>0.126638</v>
+      </c>
+      <c r="K51" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="L51" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M51" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N51" s="37" t="inlineStr">
+        <is>
+          <t>순자산 74억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O51" s="37" t="inlineStr">
+        <is>
+          <t>KEDI U.S. Quality500 + Monthly 1% Premium Index NTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 200커버드콜</t>
+        </is>
+      </c>
+      <c r="B52" s="37" t="inlineStr">
+        <is>
+          <t>289480</t>
+        </is>
+      </c>
+      <c r="C52" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D52" s="38" t="n">
+        <v>12695</v>
+      </c>
+      <c r="E52" s="38" t="n">
+        <v>26512500000</v>
+      </c>
+      <c r="F52" s="38" t="n">
+        <v>429004958</v>
+      </c>
+      <c r="G52" s="39" t="n">
+        <v>0.007145</v>
+      </c>
+      <c r="H52" s="39" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="I52" s="39" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="J52" s="39" t="n">
+        <v>0.07026399999999999</v>
+      </c>
+      <c r="K52" s="38" t="n">
+        <v>51</v>
+      </c>
+      <c r="L52" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M52" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N52" s="37" t="inlineStr">
+        <is>
+          <t>순자산 265억(기준 300억 미만), 60일 거래대금 4.3억(기준 5억 미만), 변동성 38.3%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O52" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 커버드콜 ATM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 200커버드콜OTM</t>
+        </is>
+      </c>
+      <c r="B53" s="37" t="inlineStr">
+        <is>
+          <t>166400</t>
+        </is>
+      </c>
+      <c r="C53" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D53" s="38" t="n">
+        <v>24020</v>
+      </c>
+      <c r="E53" s="38" t="n">
+        <v>11965000000</v>
+      </c>
+      <c r="F53" s="38" t="n">
+        <v>48230202</v>
+      </c>
+      <c r="G53" s="39" t="n">
+        <v>0.006403</v>
+      </c>
+      <c r="H53" s="39" t="n">
+        <v>0.4264</v>
+      </c>
+      <c r="I53" s="39" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="J53" s="39" t="n">
+        <v>0.039592</v>
+      </c>
+      <c r="K53" s="38" t="n">
+        <v>51</v>
+      </c>
+      <c r="L53" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M53" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N53" s="37" t="inlineStr">
+        <is>
+          <t>순자산 120억(기준 300억 미만), 60일 거래대금 0.5억(기준 5억 미만), 변동성 42.6%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O53" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 커버드콜 5% OTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 200타겟위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B54" s="37" t="inlineStr">
+        <is>
+          <t>0104N0</t>
+        </is>
+      </c>
+      <c r="C54" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D54" s="38" t="n">
+        <v>20340</v>
+      </c>
+      <c r="E54" s="38" t="n">
+        <v>208472000000</v>
+      </c>
+      <c r="F54" s="38" t="n">
+        <v>3412458770</v>
+      </c>
+      <c r="G54" s="39" t="n">
+        <v>0.003325</v>
+      </c>
+      <c r="H54" s="39" t="n">
+        <v>0.5913</v>
+      </c>
+      <c r="I54" s="39" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="J54" s="39" t="n">
+        <v>0.060472</v>
+      </c>
+      <c r="K54" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="L54" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M54" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N54" s="37" t="inlineStr">
+        <is>
+          <t>변동성 59.1%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O54" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 타겟 7% 위클리 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="37" t="inlineStr">
+        <is>
+          <t>TIGER 미국나스닥100커버드콜(합성)</t>
+        </is>
+      </c>
+      <c r="B55" s="37" t="inlineStr">
+        <is>
+          <t>441680</t>
+        </is>
+      </c>
+      <c r="C55" s="37" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D55" s="38" t="n"/>
+      <c r="E55" s="38" t="n"/>
+      <c r="F55" s="38" t="n"/>
+      <c r="G55" s="39" t="n"/>
+      <c r="H55" s="39" t="n"/>
+      <c r="I55" s="39" t="n"/>
+      <c r="J55" s="39" t="n"/>
+      <c r="K55" s="38" t="n"/>
+      <c r="L55" s="37" t="n"/>
+      <c r="M55" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N55" s="37" t="inlineStr">
+        <is>
           <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
 Call log:
   - )</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="37" t="inlineStr">
-        <is>
-          <t>RISE 200고배당커버드콜ATM</t>
-        </is>
-      </c>
-      <c r="B45" s="37" t="inlineStr">
-        <is>
-          <t>290080</t>
-        </is>
-      </c>
-      <c r="C45" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D45" s="38" t="n"/>
-      <c r="E45" s="38" t="n"/>
-      <c r="F45" s="38" t="n"/>
-      <c r="G45" s="39" t="n"/>
-      <c r="H45" s="39" t="n"/>
-      <c r="I45" s="39" t="n"/>
-      <c r="J45" s="39" t="n"/>
-      <c r="K45" s="38" t="n"/>
-      <c r="L45" s="37" t="n"/>
-      <c r="M45" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N45" s="37" t="inlineStr">
-        <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="37" t="inlineStr">
-        <is>
-          <t>RISE 200위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B46" s="37" t="inlineStr">
-        <is>
-          <t>475720</t>
-        </is>
-      </c>
-      <c r="C46" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D46" s="38" t="n">
-        <v>12385</v>
-      </c>
-      <c r="E46" s="38" t="n">
-        <v>821275000000</v>
-      </c>
-      <c r="F46" s="38" t="n">
-        <v>12909142288</v>
-      </c>
-      <c r="G46" s="39" t="n">
-        <v>0.006305</v>
-      </c>
-      <c r="H46" s="39" t="n">
-        <v>0.4327</v>
-      </c>
-      <c r="I46" s="39" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="J46" s="39" t="n">
-        <v>0.199435</v>
-      </c>
-      <c r="K46" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="L46" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M46" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N46" s="37" t="inlineStr">
-        <is>
-          <t>변동성 43.3%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="37" t="inlineStr">
-        <is>
-          <t>RISE 미국30년국채커버드콜(합성)</t>
-        </is>
-      </c>
-      <c r="B47" s="37" t="inlineStr">
-        <is>
-          <t>472830</t>
-        </is>
-      </c>
-      <c r="C47" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D47" s="38" t="n">
-        <v>7700</v>
-      </c>
-      <c r="E47" s="38" t="n">
-        <v>42707250000</v>
-      </c>
-      <c r="F47" s="38" t="n">
-        <v>286133353</v>
-      </c>
-      <c r="G47" s="39" t="n">
-        <v>0.003419</v>
-      </c>
-      <c r="H47" s="39" t="n">
-        <v>0.1409</v>
-      </c>
-      <c r="I47" s="39" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="J47" s="39" t="n">
-        <v>0.115065</v>
-      </c>
-      <c r="K47" s="38" t="n">
-        <v>32</v>
-      </c>
-      <c r="L47" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M47" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N47" s="37" t="inlineStr">
-        <is>
-          <t>60일 거래대금 2.9억(기준 5억 미만)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="37" t="inlineStr">
-        <is>
-          <t>RISE 미국AI밸류체인데일리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B48" s="37" t="inlineStr">
-        <is>
-          <t>490590</t>
-        </is>
-      </c>
-      <c r="C48" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D48" s="38" t="n">
-        <v>13620</v>
-      </c>
-      <c r="E48" s="38" t="n">
-        <v>760760000000</v>
-      </c>
-      <c r="F48" s="38" t="n">
-        <v>10122960865</v>
-      </c>
-      <c r="G48" s="39" t="n">
-        <v>0.00578</v>
-      </c>
-      <c r="H48" s="39" t="n">
-        <v>0.3307</v>
-      </c>
-      <c r="I48" s="39" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="J48" s="39" t="n">
-        <v>0.213069</v>
-      </c>
-      <c r="K48" s="38" t="n">
-        <v>23</v>
-      </c>
-      <c r="L48" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M48" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N48" s="37" t="inlineStr">
-        <is>
-          <t>변동성 33.1%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="37" t="inlineStr">
-        <is>
-          <t>RISE 미국S&amp;P500데일리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B49" s="37" t="inlineStr">
-        <is>
-          <t>0138T0</t>
-        </is>
-      </c>
-      <c r="C49" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D49" s="38" t="n">
-        <v>9255</v>
-      </c>
-      <c r="E49" s="38" t="n">
-        <v>32305000000</v>
-      </c>
-      <c r="F49" s="38" t="n">
-        <v>320379724</v>
-      </c>
-      <c r="G49" s="39" t="n">
-        <v>0.006153</v>
-      </c>
-      <c r="H49" s="39" t="n">
-        <v>0.1559</v>
-      </c>
-      <c r="I49" s="39" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J49" s="39" t="n"/>
-      <c r="K49" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="L49" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M49" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N49" s="37" t="inlineStr">
-        <is>
-          <t>60일 거래대금 3.2억(기준 5억 미만), 분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="37" t="inlineStr">
-        <is>
-          <t>RISE 차이나테크TOP10위클리타겟커버드콜</t>
-        </is>
-      </c>
-      <c r="B50" s="37" t="inlineStr">
-        <is>
-          <t>0094L0</t>
-        </is>
-      </c>
-      <c r="C50" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D50" s="38" t="n">
-        <v>7060</v>
-      </c>
-      <c r="E50" s="38" t="n">
-        <v>9870000000</v>
-      </c>
-      <c r="F50" s="38" t="n">
-        <v>60751544</v>
-      </c>
-      <c r="G50" s="39" t="n">
-        <v>0.011533</v>
-      </c>
-      <c r="H50" s="39" t="n">
-        <v>0.2793</v>
-      </c>
-      <c r="I50" s="39" t="n">
-        <v>0.0097</v>
-      </c>
-      <c r="J50" s="39" t="n">
-        <v>0.154391</v>
-      </c>
-      <c r="K50" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="L50" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M50" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N50" s="37" t="inlineStr">
-        <is>
-          <t>순자산 99억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만), 변동성 27.9%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="37" t="inlineStr">
-        <is>
-          <t>RISE 코리아밸류업위클리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B51" s="37" t="inlineStr">
-        <is>
-          <t>0094M0</t>
-        </is>
-      </c>
-      <c r="C51" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D51" s="38" t="n">
-        <v>16850</v>
-      </c>
-      <c r="E51" s="38" t="n">
-        <v>343230000000</v>
-      </c>
-      <c r="F51" s="38" t="n">
-        <v>9600216582</v>
-      </c>
-      <c r="G51" s="39" t="n">
-        <v>0.005637</v>
-      </c>
-      <c r="H51" s="39" t="n">
-        <v>0.4584</v>
-      </c>
-      <c r="I51" s="39" t="n">
-        <v>0.0299</v>
-      </c>
-      <c r="J51" s="39" t="n">
-        <v>0.249258</v>
-      </c>
-      <c r="K51" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="L51" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M51" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N51" s="37" t="inlineStr">
-        <is>
-          <t>변동성 45.8%(기준 25% 초과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="37" t="inlineStr">
-        <is>
-          <t>RISE 코스닥커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B52" s="37" t="inlineStr">
-        <is>
-          <t>0223A0</t>
-        </is>
-      </c>
-      <c r="C52" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D52" s="38" t="n">
-        <v>10440</v>
-      </c>
-      <c r="E52" s="38" t="n">
-        <v>16624000000</v>
-      </c>
-      <c r="F52" s="38" t="n"/>
-      <c r="G52" s="39" t="n">
-        <v>0.003264</v>
-      </c>
-      <c r="H52" s="39" t="n"/>
-      <c r="I52" s="39" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J52" s="39" t="n"/>
-      <c r="K52" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M52" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N52" s="37" t="inlineStr">
-        <is>
-          <t>순자산 166억(기준 300억 미만), 거래대금 미확인, 변동성 산출 불가(시세 이력 부족), 분배 이력 1개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="37" t="inlineStr">
-        <is>
-          <t>RISE 테슬라미국채타겟커버드콜혼합(합성)</t>
-        </is>
-      </c>
-      <c r="B53" s="37" t="inlineStr">
-        <is>
-          <t>0013R0</t>
-        </is>
-      </c>
-      <c r="C53" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D53" s="38" t="n">
-        <v>7620</v>
-      </c>
-      <c r="E53" s="38" t="n">
-        <v>27432000000</v>
-      </c>
-      <c r="F53" s="38" t="n">
-        <v>162123452</v>
-      </c>
-      <c r="G53" s="39" t="n">
-        <v>0.003495</v>
-      </c>
-      <c r="H53" s="39" t="n">
-        <v>0.1854</v>
-      </c>
-      <c r="I53" s="39" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="J53" s="39" t="n">
-        <v>0.183727</v>
-      </c>
-      <c r="K53" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="L53" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M53" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N53" s="37" t="inlineStr">
-        <is>
-          <t>순자산 274억(기준 300억 미만), 60일 거래대금 1.6억(기준 5억 미만)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="37" t="inlineStr">
-        <is>
-          <t>SOL 200타겟위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B54" s="37" t="inlineStr">
-        <is>
-          <t>0167B0</t>
-        </is>
-      </c>
-      <c r="C54" s="37" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D54" s="38" t="n">
-        <v>11470</v>
-      </c>
-      <c r="E54" s="38" t="n">
-        <v>627507000000</v>
-      </c>
-      <c r="F54" s="38" t="n">
-        <v>21320154168</v>
-      </c>
-      <c r="G54" s="39" t="n">
-        <v>0.00345</v>
-      </c>
-      <c r="H54" s="39" t="n">
-        <v>0.6944</v>
-      </c>
-      <c r="I54" s="39" t="n">
-        <v>0.0139</v>
-      </c>
-      <c r="J54" s="39" t="n"/>
-      <c r="K54" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L54" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M54" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N54" s="37" t="inlineStr">
-        <is>
-          <t>변동성 69.4%(기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="37" t="inlineStr">
-        <is>
-          <t>SOL 국제금커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B55" s="37" t="inlineStr">
-        <is>
-          <t>0022T0</t>
-        </is>
-      </c>
-      <c r="C55" s="37" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D55" s="38" t="n">
-        <v>12835</v>
-      </c>
-      <c r="E55" s="38" t="n">
-        <v>73074000000</v>
-      </c>
-      <c r="F55" s="38" t="n">
-        <v>1007376543</v>
-      </c>
-      <c r="G55" s="39" t="n">
-        <v>0.006737999999999999</v>
-      </c>
-      <c r="H55" s="39" t="n">
-        <v>0.2874</v>
-      </c>
-      <c r="I55" s="39" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="J55" s="39" t="n">
-        <v>0.04495499999999999</v>
-      </c>
-      <c r="K55" s="38" t="n">
-        <v>17</v>
-      </c>
-      <c r="L55" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M55" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N55" s="37" t="inlineStr">
-        <is>
-          <t>변동성 28.7%(기준 25% 초과)</t>
-        </is>
-      </c>
+      <c r="O55" s="37" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="37" t="inlineStr">
         <is>
-          <t>SOL 미국500타겟데일리커버드콜액티브</t>
+          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B56" s="37" t="inlineStr">
         <is>
-          <t>494210</t>
+          <t>486290</t>
         </is>
       </c>
       <c r="C56" s="37" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D56" s="38" t="n">
-        <v>10605</v>
-      </c>
-      <c r="E56" s="38" t="n">
-        <v>7423500000</v>
-      </c>
-      <c r="F56" s="38" t="n">
-        <v>64446271</v>
-      </c>
-      <c r="G56" s="39" t="n">
-        <v>0.00621</v>
-      </c>
-      <c r="H56" s="39" t="n">
-        <v>0.1571</v>
-      </c>
-      <c r="I56" s="39" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J56" s="39" t="n">
-        <v>0.126638</v>
-      </c>
-      <c r="K56" s="38" t="n">
-        <v>22</v>
-      </c>
-      <c r="L56" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D56" s="38" t="n"/>
+      <c r="E56" s="38" t="n"/>
+      <c r="F56" s="38" t="n"/>
+      <c r="G56" s="39" t="n"/>
+      <c r="H56" s="39" t="n"/>
+      <c r="I56" s="39" t="n"/>
+      <c r="J56" s="39" t="n"/>
+      <c r="K56" s="38" t="n"/>
+      <c r="L56" s="37" t="n"/>
       <c r="M56" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -4791,19 +5072,20 @@
       </c>
       <c r="N56" s="37" t="inlineStr">
         <is>
-          <t>순자산 74억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만)</t>
-        </is>
-      </c>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 403)</t>
+        </is>
+      </c>
+      <c r="O56" s="37" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="37" t="inlineStr">
         <is>
-          <t>TIGER 200커버드콜</t>
+          <t>TIGER 미국배당다우존스타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B57" s="37" t="inlineStr">
         <is>
-          <t>289480</t>
+          <t>0008S0</t>
         </is>
       </c>
       <c r="C57" s="37" t="inlineStr">
@@ -4811,35 +5093,15 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D57" s="38" t="n">
-        <v>12667</v>
-      </c>
-      <c r="E57" s="38" t="n">
-        <v>26512500000</v>
-      </c>
-      <c r="F57" s="38" t="n">
-        <v>429000383</v>
-      </c>
-      <c r="G57" s="39" t="n">
-        <v>0.007145</v>
-      </c>
-      <c r="H57" s="39" t="n">
-        <v>0.3832</v>
-      </c>
-      <c r="I57" s="39" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="J57" s="39" t="n">
-        <v>0.070419</v>
-      </c>
-      <c r="K57" s="38" t="n">
-        <v>51</v>
-      </c>
-      <c r="L57" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
+      <c r="D57" s="38" t="n"/>
+      <c r="E57" s="38" t="n"/>
+      <c r="F57" s="38" t="n"/>
+      <c r="G57" s="39" t="n"/>
+      <c r="H57" s="39" t="n"/>
+      <c r="I57" s="39" t="n"/>
+      <c r="J57" s="39" t="n"/>
+      <c r="K57" s="38" t="n"/>
+      <c r="L57" s="37" t="n"/>
       <c r="M57" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -4847,19 +5109,20 @@
       </c>
       <c r="N57" s="37" t="inlineStr">
         <is>
-          <t>순자산 265억(기준 300억 미만), 60일 거래대금 4.3억(기준 5억 미만), 변동성 38.3%(기준 25% 초과)</t>
-        </is>
-      </c>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 403)</t>
+        </is>
+      </c>
+      <c r="O57" s="37" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="37" t="inlineStr">
         <is>
-          <t>TIGER 200커버드콜OTM</t>
+          <t>TIGER 미국배당다우존스타겟커버드콜1호</t>
         </is>
       </c>
       <c r="B58" s="37" t="inlineStr">
         <is>
-          <t>166400</t>
+          <t>458750</t>
         </is>
       </c>
       <c r="C58" s="37" t="inlineStr">
@@ -4867,35 +5130,15 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D58" s="38" t="n">
-        <v>24020</v>
-      </c>
-      <c r="E58" s="38" t="n">
-        <v>11965000000</v>
-      </c>
-      <c r="F58" s="38" t="n">
-        <v>48230202</v>
-      </c>
-      <c r="G58" s="39" t="n">
-        <v>0.006403</v>
-      </c>
-      <c r="H58" s="39" t="n">
-        <v>0.4264</v>
-      </c>
-      <c r="I58" s="39" t="n">
-        <v>0.0039</v>
-      </c>
-      <c r="J58" s="39" t="n">
-        <v>0.039592</v>
-      </c>
-      <c r="K58" s="38" t="n">
-        <v>51</v>
-      </c>
-      <c r="L58" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
+      <c r="D58" s="38" t="n"/>
+      <c r="E58" s="38" t="n"/>
+      <c r="F58" s="38" t="n"/>
+      <c r="G58" s="39" t="n"/>
+      <c r="H58" s="39" t="n"/>
+      <c r="I58" s="39" t="n"/>
+      <c r="J58" s="39" t="n"/>
+      <c r="K58" s="38" t="n"/>
+      <c r="L58" s="37" t="n"/>
       <c r="M58" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -4903,19 +5146,22 @@
       </c>
       <c r="N58" s="37" t="inlineStr">
         <is>
-          <t>순자산 120억(기준 300억 미만), 60일 거래대금 0.5억(기준 5억 미만), 변동성 42.6%(기준 25% 초과)</t>
-        </is>
-      </c>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
+Call log:
+  - )</t>
+        </is>
+      </c>
+      <c r="O58" s="37" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="37" t="inlineStr">
         <is>
-          <t>TIGER 200타겟위클리커버드콜</t>
+          <t>TIGER 미국배당다우존스타겟커버드콜2호</t>
         </is>
       </c>
       <c r="B59" s="37" t="inlineStr">
         <is>
-          <t>0104N0</t>
+          <t>458760</t>
         </is>
       </c>
       <c r="C59" s="37" t="inlineStr">
@@ -4923,35 +5169,15 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D59" s="38" t="n">
-        <v>20320</v>
-      </c>
-      <c r="E59" s="38" t="n">
-        <v>208472000000</v>
-      </c>
-      <c r="F59" s="38" t="n">
-        <v>3412420947</v>
-      </c>
-      <c r="G59" s="39" t="n">
-        <v>0.003325</v>
-      </c>
-      <c r="H59" s="39" t="n">
-        <v>0.5911999999999999</v>
-      </c>
-      <c r="I59" s="39" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="J59" s="39" t="n">
-        <v>0.06053099999999999</v>
-      </c>
-      <c r="K59" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="L59" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
+      <c r="D59" s="38" t="n"/>
+      <c r="E59" s="38" t="n"/>
+      <c r="F59" s="38" t="n"/>
+      <c r="G59" s="39" t="n"/>
+      <c r="H59" s="39" t="n"/>
+      <c r="I59" s="39" t="n"/>
+      <c r="J59" s="39" t="n"/>
+      <c r="K59" s="38" t="n"/>
+      <c r="L59" s="37" t="n"/>
       <c r="M59" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -4959,19 +5185,22 @@
       </c>
       <c r="N59" s="37" t="inlineStr">
         <is>
-          <t>변동성 59.1%(기준 25% 초과)</t>
-        </is>
-      </c>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
+Call log:
+  - )</t>
+        </is>
+      </c>
+      <c r="O59" s="37" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="37" t="inlineStr">
         <is>
-          <t>TIGER 미국배당다우존스타겟커버드콜1호</t>
+          <t>TIGER 미국테크TOP10타겟커버드콜</t>
         </is>
       </c>
       <c r="B60" s="37" t="inlineStr">
         <is>
-          <t>458750</t>
+          <t>474220</t>
         </is>
       </c>
       <c r="C60" s="37" t="inlineStr">
@@ -4979,35 +5208,15 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D60" s="38" t="n">
-        <v>12825</v>
-      </c>
-      <c r="E60" s="38" t="n">
-        <v>66690000000</v>
-      </c>
-      <c r="F60" s="38" t="n">
-        <v>411176413</v>
-      </c>
-      <c r="G60" s="39" t="n">
-        <v>0.005842000000000001</v>
-      </c>
-      <c r="H60" s="39" t="n">
-        <v>0.1448</v>
-      </c>
-      <c r="I60" s="39" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="J60" s="39" t="n">
-        <v>0.059805</v>
-      </c>
-      <c r="K60" s="38" t="n">
-        <v>39</v>
-      </c>
-      <c r="L60" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
+      <c r="D60" s="38" t="n"/>
+      <c r="E60" s="38" t="n"/>
+      <c r="F60" s="38" t="n"/>
+      <c r="G60" s="39" t="n"/>
+      <c r="H60" s="39" t="n"/>
+      <c r="I60" s="39" t="n"/>
+      <c r="J60" s="39" t="n"/>
+      <c r="K60" s="38" t="n"/>
+      <c r="L60" s="37" t="n"/>
       <c r="M60" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -5015,9 +5224,10 @@
       </c>
       <c r="N60" s="37" t="inlineStr">
         <is>
-          <t>60일 거래대금 4.1억(기준 5억 미만)</t>
-        </is>
-      </c>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
+        </is>
+      </c>
+      <c r="O60" s="37" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="37" t="inlineStr">
@@ -5036,19 +5246,19 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>10840</v>
+        <v>10845</v>
       </c>
       <c r="E61" s="38" t="n">
         <v>818900000000</v>
       </c>
       <c r="F61" s="38" t="n">
-        <v>33031128122</v>
+        <v>33032465908</v>
       </c>
       <c r="G61" s="39" t="n">
         <v>0.005719999999999999</v>
       </c>
       <c r="H61" s="39" t="n">
-        <v>0.9129</v>
+        <v>0.9129999999999999</v>
       </c>
       <c r="I61" s="39" t="n">
         <v>0.0155</v>
@@ -5069,7 +5279,12 @@
       </c>
       <c r="N61" s="37" t="inlineStr">
         <is>
-          <t>변동성 91.3%(기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 91.3%(101거래일 기준, 기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O61" s="37" t="inlineStr">
+        <is>
+          <t>FnGuide 반도체 TOP10 Capped 지수</t>
         </is>
       </c>
     </row>
@@ -5090,25 +5305,25 @@
         </is>
       </c>
       <c r="D62" s="38" t="n">
-        <v>19885</v>
+        <v>19890</v>
       </c>
       <c r="E62" s="38" t="n">
         <v>2396790000000</v>
       </c>
       <c r="F62" s="38" t="n">
-        <v>103343413229</v>
+        <v>103354864477</v>
       </c>
       <c r="G62" s="39" t="n">
         <v>0.006008</v>
       </c>
       <c r="H62" s="39" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5732</v>
       </c>
       <c r="I62" s="39" t="n">
         <v>0.0197</v>
       </c>
       <c r="J62" s="39" t="n">
-        <v>0.220518</v>
+        <v>0.220463</v>
       </c>
       <c r="K62" s="38" t="n">
         <v>33</v>
@@ -5125,7 +5340,12 @@
       </c>
       <c r="N62" s="37" t="inlineStr">
         <is>
-          <t>변동성 57.3%(기준 25% 초과)</t>
+          <t>변동성 57.3%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O62" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 커버드콜 5% OTM</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5372,7 @@
         <v>60375000000</v>
       </c>
       <c r="F63" s="38" t="n">
-        <v>357325594</v>
+        <v>357388632</v>
       </c>
       <c r="G63" s="39" t="n">
         <v>0.004741</v>
@@ -5182,6 +5402,11 @@
       <c r="N63" s="37" t="inlineStr">
         <is>
           <t>60일 거래대금 3.6억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O63" s="37" t="inlineStr">
+        <is>
+          <t>KEDI Nvidia U.S. 30Y Treasury Target Covered Call Balanced I</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5460,12 @@
       </c>
       <c r="N64" s="37" t="inlineStr">
         <is>
-          <t>순자산 187억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 31.1%(기준 25% 초과), 분배 이력 11개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>순자산 187억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 31.1%(1년 기준, 기준 25% 초과), 분배 이력 11개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O64" s="37" t="inlineStr">
+        <is>
+          <t>KRX 다우존스 코리아 배당 30 타겟 7% 위클리 커버드콜 지수</t>
         </is>
       </c>
     </row>
@@ -5325,14 +5555,14 @@
     <row r="12" ht="19" customHeight="1">
       <c r="B12" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 채택 22종목 — 유동성·변동성 기준을 통과한 월배당 커버드콜 ETF</t>
+          <t xml:space="preserve">     · 채택 17종목 — 유동성·변동성 기준을 통과한 월배당 커버드콜 ETF</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="B13" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 제외 39종목 — 사유는 [ETF데이터] 장 맨 오른쪽 칸에 적혀 있습니다.</t>
+          <t xml:space="preserve">     · 제외 44종목 — 사유는 [ETF데이터] 장 맨 오른쪽 칸에 적혀 있습니다.</t>
         </is>
       </c>
     </row>

--- a/고객제안서_월배당ETF.xlsx
+++ b/고객제안서_월배당ETF.xlsx
@@ -12,7 +12,7 @@
     <sheet name="사용법" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="채택종목">'ETF데이터'!$A$4:$A$20</definedName>
+    <definedName name="채택종목">'ETF데이터'!$A$4:$A$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'제안서'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'제안서'!$A$1:$H$73</definedName>
   </definedNames>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="K2" s="3">
-        <f>IFERROR(MATCH($C$9,'ETF데이터'!$A$4:$A$20,0),0)</f>
+        <f>IFERROR(MATCH($C$9,'ETF데이터'!$A$4:$A$24,0),0)</f>
         <v/>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>KODEX 미국배당커버드콜액티브</t>
+          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="C14" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$B$4:$B$20,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$B$4:$B$24,$K$2))</f>
         <v/>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="F14" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$G$4:$G$20,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$G$4:$G$24,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="C15" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$C$4:$C$20,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$C$4:$C$24,$K$2))</f>
         <v/>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="F15" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$H$4:$H$20,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$H$4:$H$24,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C16" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$D$4:$D$20,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$D$4:$D$24,$K$2))</f>
         <v/>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="F16" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$I$4:$I$20,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$I$4:$I$24,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C17" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$E$4:$E$20,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$E$4:$E$24,$K$2))</f>
         <v/>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="F17" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$J$4:$J$20,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$J$4:$J$24,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="C18" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$F$4:$F$20,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$F$4:$F$24,$K$2))</f>
         <v/>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="F18" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$O$4:$O$20,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$O$4:$O$24,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>5. 채택 ETF 비교 (1억원 투자 기준) — 연 분배율 상위 12종목 / 전체 17종목</t>
+          <t>5. 채택 ETF 비교 (1억원 투자 기준) — 연 분배율 상위 12종목 / 전체 21종목</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T03:52:32.909Z · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 연환산 변동성 25% 이하, 분배 이력 12개월 이상</t>
+          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T03:57:18.135Z · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 연환산 변동성 25% 이하, 분배 이력 12개월 이상</t>
         </is>
       </c>
     </row>
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="D4" s="35" t="n">
-        <v>7925</v>
+        <v>7930</v>
       </c>
       <c r="E4" s="35" t="n">
         <v>357021250000</v>
       </c>
       <c r="F4" s="35" t="n">
-        <v>2991918624</v>
+        <v>2991929201</v>
       </c>
       <c r="G4" s="36" t="n">
         <v>0.007532</v>
@@ -2073,7 +2073,7 @@
         <v>0.0194</v>
       </c>
       <c r="J4" s="36" t="n">
-        <v>0.282019</v>
+        <v>0.281841</v>
       </c>
       <c r="K4" s="35" t="n">
         <v>16</v>
@@ -2112,13 +2112,13 @@
         </is>
       </c>
       <c r="D5" s="35" t="n">
-        <v>9890</v>
+        <v>9895</v>
       </c>
       <c r="E5" s="35" t="n">
         <v>176941500000</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>2871904454</v>
+        <v>2871968492</v>
       </c>
       <c r="G5" s="36" t="n">
         <v>0.005384</v>
@@ -2130,7 +2130,7 @@
         <v>0.0297</v>
       </c>
       <c r="J5" s="36" t="n">
-        <v>0.267947</v>
+        <v>0.267812</v>
       </c>
       <c r="K5" s="35" t="n">
         <v>29</v>
@@ -2226,13 +2226,13 @@
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>8785</v>
+        <v>8782</v>
       </c>
       <c r="E7" s="35" t="n">
         <v>1002716000000</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>13541085082</v>
+        <v>13541972736</v>
       </c>
       <c r="G7" s="36" t="n">
         <v>0.005108000000000001</v>
@@ -2244,7 +2244,7 @@
         <v>0.0166</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>0.229937</v>
+        <v>0.230016</v>
       </c>
       <c r="K7" s="35" t="n">
         <v>22</v>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="D8" s="35" t="n">
-        <v>10230</v>
+        <v>10240</v>
       </c>
       <c r="E8" s="35" t="n">
         <v>560567000000</v>
       </c>
       <c r="F8" s="35" t="n">
-        <v>7570448667</v>
+        <v>7570551013</v>
       </c>
       <c r="G8" s="36" t="n">
         <v>0.005748</v>
@@ -2301,7 +2301,7 @@
         <v>0.0166</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>0.219941</v>
+        <v>0.219727</v>
       </c>
       <c r="K8" s="35" t="n">
         <v>23</v>
@@ -2326,42 +2326,42 @@
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
         <is>
-          <t>ACE 미국500데일리타겟커버드콜(합성)</t>
+          <t>RISE 미국배당100데일리고정커버드콜</t>
         </is>
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>480030</t>
+          <t>490600</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>KB자산운용</t>
         </is>
       </c>
       <c r="D9" s="35" t="n">
-        <v>9555</v>
+        <v>8860</v>
       </c>
       <c r="E9" s="35" t="n">
-        <v>160608000000</v>
+        <v>168973500000</v>
       </c>
       <c r="F9" s="35" t="n">
-        <v>1353459169</v>
+        <v>2335736853</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>0.005391</v>
+        <v>0.005953000000000001</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>0.1502</v>
+        <v>0.1459</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>0.0199</v>
+        <v>0.01</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>0.203349</v>
+        <v>0.164447</v>
       </c>
       <c r="K9" s="35" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="L9" s="34" t="inlineStr">
         <is>
@@ -2376,53 +2376,53 @@
       <c r="N9" s="34" t="inlineStr"/>
       <c r="O9" s="34" t="inlineStr">
         <is>
-          <t>Bloomberg US 500 Large Cap Premium(SPY) Decrement 15% Distri</t>
+          <t>KEDI U.S. Dividend100 90% Participation + Daily Options Prem</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="34" t="inlineStr">
         <is>
-          <t>RISE 미국배당100데일리고정커버드콜</t>
+          <t>KODEX 테슬라커버드콜채권혼합액티브</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>490600</t>
+          <t>475080</t>
         </is>
       </c>
       <c r="C10" s="34" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D10" s="35" t="n">
-        <v>8865</v>
+        <v>7835</v>
       </c>
       <c r="E10" s="35" t="n">
-        <v>168973500000</v>
+        <v>285403500000</v>
       </c>
       <c r="F10" s="35" t="n">
-        <v>2335600914</v>
+        <v>1454665215</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>0.005953000000000001</v>
+        <v>0.005215</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>0.1459</v>
+        <v>0.1243</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>0.01</v>
+        <v>0.0125</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>0.164354</v>
+        <v>0.164135</v>
       </c>
       <c r="K10" s="35" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L10" s="34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M10" s="34" t="inlineStr">
@@ -2433,53 +2433,53 @@
       <c r="N10" s="34" t="inlineStr"/>
       <c r="O10" s="34" t="inlineStr">
         <is>
-          <t>KEDI U.S. Dividend100 90% Participation + Daily Options Prem</t>
+          <t>KEDI Tesla Income Premium Balanced Index</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>KODEX 테슬라커버드콜채권혼합액티브</t>
+          <t>TIGER 미국AI빅테크10타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>475080</t>
+          <t>493810</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="D11" s="35" t="n">
-        <v>7835</v>
+        <v>11105</v>
       </c>
       <c r="E11" s="35" t="n">
-        <v>285403500000</v>
+        <v>240761500000</v>
       </c>
       <c r="F11" s="35" t="n">
-        <v>1454665215</v>
+        <v>1834264948</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>0.005215</v>
+        <v>0.004813</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>0.1243</v>
+        <v>0.2183</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>0.0125</v>
+        <v>0.0124</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>0.164135</v>
+        <v>0.16353</v>
       </c>
       <c r="K11" s="35" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L11" s="34" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M11" s="34" t="inlineStr">
@@ -2490,53 +2490,53 @@
       <c r="N11" s="34" t="inlineStr"/>
       <c r="O11" s="34" t="inlineStr">
         <is>
-          <t>KEDI Tesla Income Premium Balanced Index</t>
+          <t>KEDI US AI Big Tech 10+15% Daily Premium Index TR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국AI빅테크10타겟데일리커버드콜</t>
+          <t>KODEX 미국S&amp;P500데일리커버드콜OTM</t>
         </is>
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>493810</t>
+          <t>0005A0</t>
         </is>
       </c>
       <c r="C12" s="34" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D12" s="35" t="n">
-        <v>11115</v>
+        <v>9240</v>
       </c>
       <c r="E12" s="35" t="n">
-        <v>240761500000</v>
+        <v>198660000000</v>
       </c>
       <c r="F12" s="35" t="n">
-        <v>1833496002</v>
+        <v>1973358007</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>0.004813</v>
+        <v>0.005639999999999999</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>0.2183</v>
+        <v>0.1473</v>
       </c>
       <c r="I12" s="36" t="n">
         <v>0.0124</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>0.163383</v>
+        <v>0.160281</v>
       </c>
       <c r="K12" s="35" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L12" s="34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M12" s="34" t="inlineStr">
@@ -2547,49 +2547,49 @@
       <c r="N12" s="34" t="inlineStr"/>
       <c r="O12" s="34" t="inlineStr">
         <is>
-          <t>KEDI US AI Big Tech 10+15% Daily Premium Index TR</t>
+          <t>S&amp;P500 Covered Call 1% OTM Daily Index(TR)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국S&amp;P500데일리커버드콜OTM</t>
+          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>0005A0</t>
+          <t>486290</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="D13" s="35" t="n">
-        <v>9240</v>
+        <v>10240</v>
       </c>
       <c r="E13" s="35" t="n">
-        <v>198660000000</v>
+        <v>2435426000000</v>
       </c>
       <c r="F13" s="35" t="n">
-        <v>1973293327</v>
+        <v>29768023851</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>0.005639999999999999</v>
+        <v>0.004563</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>0.1473</v>
+        <v>0.2068</v>
       </c>
       <c r="I13" s="36" t="n">
         <v>0.0124</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>0.160281</v>
+        <v>0.159961</v>
       </c>
       <c r="K13" s="35" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L13" s="34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       <c r="N13" s="34" t="inlineStr"/>
       <c r="O13" s="34" t="inlineStr">
         <is>
-          <t>S&amp;P500 Covered Call 1% OTM Daily Index(TR)</t>
+          <t>NASDAQ 100 Daily Covered Call Target Premium 15% Index</t>
         </is>
       </c>
     </row>
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="D14" s="35" t="n">
-        <v>11510</v>
+        <v>11515</v>
       </c>
       <c r="E14" s="35" t="n">
         <v>451950000000</v>
       </c>
       <c r="F14" s="35" t="n">
-        <v>2928636655</v>
+        <v>2928683301</v>
       </c>
       <c r="G14" s="36" t="n">
         <v>0.005830999999999999</v>
@@ -2643,7 +2643,7 @@
         <v>0.0123</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>0.159861</v>
+        <v>0.159792</v>
       </c>
       <c r="K14" s="35" t="n">
         <v>27</v>
@@ -2688,7 +2688,7 @@
         <v>756407750000</v>
       </c>
       <c r="F15" s="35" t="n">
-        <v>7956706084</v>
+        <v>7957057086</v>
       </c>
       <c r="G15" s="36" t="n">
         <v>0.007784</v>
@@ -2739,13 +2739,13 @@
         </is>
       </c>
       <c r="D16" s="35" t="n">
-        <v>7265</v>
+        <v>7260</v>
       </c>
       <c r="E16" s="35" t="n">
         <v>740576850000</v>
       </c>
       <c r="F16" s="35" t="n">
-        <v>4086859803</v>
+        <v>4087002795</v>
       </c>
       <c r="G16" s="36" t="n">
         <v>0.003244</v>
@@ -2757,7 +2757,7 @@
         <v>0.0101</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>0.132691</v>
+        <v>0.132782</v>
       </c>
       <c r="K16" s="35" t="n">
         <v>29</v>
@@ -2802,7 +2802,7 @@
         <v>272513750000</v>
       </c>
       <c r="F17" s="35" t="n">
-        <v>2164088880</v>
+        <v>2164605991</v>
       </c>
       <c r="G17" s="36" t="n">
         <v>0.0035</v>
@@ -2839,42 +2839,42 @@
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국배당다우존스타겟커버드콜</t>
+          <t>TIGER 미국나스닥100커버드콜(합성)</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>483290</t>
+          <t>441680</t>
         </is>
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="D18" s="35" t="n">
-        <v>10230</v>
+        <v>10610</v>
       </c>
       <c r="E18" s="35" t="n">
-        <v>177915000000</v>
+        <v>279306000000</v>
       </c>
       <c r="F18" s="35" t="n">
-        <v>2277739954</v>
+        <v>960150306</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>0.005798</v>
+        <v>0.004923</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>0.1572</v>
+        <v>0.146</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>0.0098</v>
+        <v>0.01</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>0.121799</v>
+        <v>0.126296</v>
       </c>
       <c r="K18" s="35" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="L18" s="34" t="inlineStr">
         <is>
@@ -2889,53 +2889,53 @@
       <c r="N18" s="34" t="inlineStr"/>
       <c r="O18" s="34" t="inlineStr">
         <is>
-          <t>Dow Jones US Dividend 100 10% Premium Covered Call Index(PR)</t>
+          <t>Cboe NASDAQ-100 BuyWrite V2 Index</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="34" t="inlineStr">
         <is>
-          <t>TIGER 미국S&amp;P500타겟데일리커버드콜</t>
+          <t>KODEX 미국배당다우존스타겟커버드콜</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>482730</t>
+          <t>483290</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D19" s="35" t="n">
-        <v>11445</v>
+        <v>10230</v>
       </c>
       <c r="E19" s="35" t="n">
-        <v>657225000000</v>
+        <v>177915000000</v>
       </c>
       <c r="F19" s="35" t="n">
-        <v>4931971020</v>
+        <v>2277754106</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>0.004313</v>
+        <v>0.005798</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>0.148</v>
+        <v>0.1572</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>0.01</v>
+        <v>0.0098</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>0.107034</v>
+        <v>0.121799</v>
       </c>
       <c r="K19" s="35" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L19" s="34" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M19" s="34" t="inlineStr">
@@ -2946,49 +2946,49 @@
       <c r="N19" s="34" t="inlineStr"/>
       <c r="O19" s="34" t="inlineStr">
         <is>
-          <t>S&amp;P 500 10% Daily Premium Covered Call Index (USD) PR</t>
+          <t>Dow Jones US Dividend 100 10% Premium Covered Call Index(PR)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="34" t="inlineStr">
         <is>
-          <t>KODEX 미국배당커버드콜액티브</t>
+          <t>TIGER 미국배당다우존스타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
         <is>
-          <t>441640</t>
+          <t>0008S0</t>
         </is>
       </c>
       <c r="C20" s="34" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="D20" s="35" t="n">
-        <v>12340</v>
+        <v>9780</v>
       </c>
       <c r="E20" s="35" t="n">
-        <v>1701540000000</v>
+        <v>315077000000</v>
       </c>
       <c r="F20" s="35" t="n">
-        <v>12379897766</v>
+        <v>3346119814</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>0.003631</v>
+        <v>0.004797</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>0.1233</v>
+        <v>0.1437</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>0.09594799999999999</v>
+        <v>0.120348</v>
       </c>
       <c r="K20" s="35" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="L20" s="34" t="inlineStr">
         <is>
@@ -3003,267 +3003,275 @@
       <c r="N20" s="34" t="inlineStr"/>
       <c r="O20" s="34" t="inlineStr">
         <is>
+          <t>Dow Jones U.S. Dividend 100 10% Daily Premium Covered Call I</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>TIGER 미국S&amp;P500타겟데일리커버드콜</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>482730</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="n">
+        <v>11450</v>
+      </c>
+      <c r="E21" s="35" t="n">
+        <v>657225000000</v>
+      </c>
+      <c r="F21" s="35" t="n">
+        <v>4932247083</v>
+      </c>
+      <c r="G21" s="36" t="n">
+        <v>0.004313</v>
+      </c>
+      <c r="H21" s="36" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="I21" s="36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J21" s="36" t="n">
+        <v>0.106987</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="L21" s="34" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M21" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N21" s="34" t="inlineStr"/>
+      <c r="O21" s="34" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 10% Daily Premium Covered Call Index (USD) PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>TIGER 미국테크TOP10타겟커버드콜</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>474220</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="n">
+        <v>14695</v>
+      </c>
+      <c r="E22" s="35" t="n">
+        <v>413976000000</v>
+      </c>
+      <c r="F22" s="35" t="n">
+        <v>1732197702</v>
+      </c>
+      <c r="G22" s="36" t="n">
+        <v>0.006686</v>
+      </c>
+      <c r="H22" s="36" t="n">
+        <v>0.1938</v>
+      </c>
+      <c r="I22" s="36" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="J22" s="36" t="n">
+        <v>0.106703</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="L22" s="34" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M22" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N22" s="34" t="inlineStr"/>
+      <c r="O22" s="34" t="inlineStr">
+        <is>
+          <t>Bloomberg U.S. Tech Top10 + 10% Premium Covered Call Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>TIGER 미국배당다우존스타겟커버드콜2호</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>458760</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="n">
+        <v>10885</v>
+      </c>
+      <c r="E23" s="35" t="n">
+        <v>699584000000</v>
+      </c>
+      <c r="F23" s="35" t="n">
+        <v>3403672825</v>
+      </c>
+      <c r="G23" s="36" t="n">
+        <v>0.005643</v>
+      </c>
+      <c r="H23" s="36" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="I23" s="36" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J23" s="36" t="n">
+        <v>0.099954</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="L23" s="34" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M23" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N23" s="34" t="inlineStr"/>
+      <c r="O23" s="34" t="inlineStr">
+        <is>
+          <t>Dow Jones U.S. Dividend 100 7% Premium Covered Call Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>KODEX 미국배당커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>441640</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="n">
+        <v>12340</v>
+      </c>
+      <c r="E24" s="35" t="n">
+        <v>1701540000000</v>
+      </c>
+      <c r="F24" s="35" t="n">
+        <v>12380637137</v>
+      </c>
+      <c r="G24" s="36" t="n">
+        <v>0.003631</v>
+      </c>
+      <c r="H24" s="36" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="I24" s="36" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="J24" s="36" t="n">
+        <v>0.09594799999999999</v>
+      </c>
+      <c r="K24" s="35" t="n">
+        <v>48</v>
+      </c>
+      <c r="L24" s="34" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M24" s="34" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N24" s="34" t="inlineStr"/>
+      <c r="O24" s="34" t="inlineStr">
+        <is>
           <t>S&amp;P 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="37" t="inlineStr">
-        <is>
-          <t>ACE 고배당주Plus커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B21" s="37" t="inlineStr">
-        <is>
-          <t>0199C0</t>
-        </is>
-      </c>
-      <c r="C21" s="37" t="inlineStr">
-        <is>
-          <t>한국투신운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D21" s="38" t="n"/>
-      <c r="E21" s="38" t="n"/>
-      <c r="F21" s="38" t="n"/>
-      <c r="G21" s="39" t="n"/>
-      <c r="H21" s="39" t="n"/>
-      <c r="I21" s="39" t="n"/>
-      <c r="J21" s="39" t="n"/>
-      <c r="K21" s="38" t="n"/>
-      <c r="L21" s="37" t="n"/>
-      <c r="M21" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N21" s="37" t="inlineStr">
-        <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
-        </is>
-      </c>
-      <c r="O21" s="37" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="37" t="inlineStr">
-        <is>
-          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
-        </is>
-      </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>480040</t>
-        </is>
-      </c>
-      <c r="C22" s="37" t="inlineStr">
-        <is>
-          <t>한국투신운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D22" s="38" t="n">
-        <v>13340</v>
-      </c>
-      <c r="E22" s="38" t="n">
-        <v>181016000000</v>
-      </c>
-      <c r="F22" s="38" t="n">
-        <v>3487753342</v>
-      </c>
-      <c r="G22" s="39" t="n">
-        <v>0.005406999999999999</v>
-      </c>
-      <c r="H22" s="39" t="n">
-        <v>0.4411</v>
-      </c>
-      <c r="I22" s="39" t="n">
-        <v>0.0303</v>
-      </c>
-      <c r="J22" s="39" t="n">
-        <v>0.261019</v>
-      </c>
-      <c r="K22" s="38" t="n">
-        <v>29</v>
-      </c>
-      <c r="L22" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M22" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N22" s="37" t="inlineStr">
-        <is>
-          <t>변동성 44.1%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O22" s="37" t="inlineStr">
-        <is>
-          <t>Bloomberg US Listed Semiconductor Premium(QQQ) Decrement 15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="37" t="inlineStr">
-        <is>
-          <t>ACE 미국배당퀄리티+커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B23" s="37" t="inlineStr">
-        <is>
-          <t>0049M0</t>
-        </is>
-      </c>
-      <c r="C23" s="37" t="inlineStr">
-        <is>
-          <t>한국투신운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D23" s="38" t="n">
-        <v>11010</v>
-      </c>
-      <c r="E23" s="38" t="n">
-        <v>78171000000</v>
-      </c>
-      <c r="F23" s="38" t="n">
-        <v>379517920</v>
-      </c>
-      <c r="G23" s="39" t="n">
-        <v>0.005323</v>
-      </c>
-      <c r="H23" s="39" t="n">
-        <v>0.1288</v>
-      </c>
-      <c r="I23" s="39" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="J23" s="39" t="n">
-        <v>0.075658</v>
-      </c>
-      <c r="K23" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="L23" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M23" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N23" s="37" t="inlineStr">
-        <is>
-          <t>60일 거래대금 3.8억(기준 5억 미만)</t>
-        </is>
-      </c>
-      <c r="O23" s="37" t="inlineStr">
-        <is>
-          <t>Bloomberg WisdomTree U.S. Quality Dividend &amp; B500 Premium De</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="37" t="inlineStr">
-        <is>
-          <t>FOCUS AI반도체위클리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B24" s="37" t="inlineStr">
-        <is>
-          <t>0176P0</t>
-        </is>
-      </c>
-      <c r="C24" s="37" t="inlineStr">
-        <is>
-          <t>브이아이자산운용</t>
-        </is>
-      </c>
-      <c r="D24" s="38" t="n">
-        <v>12650</v>
-      </c>
-      <c r="E24" s="38" t="n">
-        <v>6864000000</v>
-      </c>
-      <c r="F24" s="38" t="n">
-        <v>168942749</v>
-      </c>
-      <c r="G24" s="39" t="n">
-        <v>0.003711</v>
-      </c>
-      <c r="H24" s="39" t="n">
-        <v>0.7998999999999999</v>
-      </c>
-      <c r="I24" s="39" t="n">
-        <v>0.0143</v>
-      </c>
-      <c r="J24" s="39" t="n"/>
-      <c r="K24" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L24" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M24" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N24" s="37" t="inlineStr">
-        <is>
-          <t>순자산 69억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 80.0%(111거래일 기준, 기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O24" s="37" t="inlineStr">
-        <is>
-          <t>AI 반도체 위클리 고정 30% 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="37" t="inlineStr">
         <is>
-          <t>FOCUS 알리바바미국채커버드콜혼합</t>
+          <t>ACE 고배당주Plus커버드콜액티브</t>
         </is>
       </c>
       <c r="B25" s="37" t="inlineStr">
         <is>
-          <t>0073X0</t>
+          <t>0199C0</t>
         </is>
       </c>
       <c r="C25" s="37" t="inlineStr">
         <is>
-          <t>브이아이자산운용</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D25" s="38" t="n">
-        <v>8650</v>
+        <v>9225</v>
       </c>
       <c r="E25" s="38" t="n">
-        <v>4760250000</v>
+        <v>138375000000</v>
       </c>
       <c r="F25" s="38" t="n">
-        <v>30623084</v>
+        <v>6510170634</v>
       </c>
       <c r="G25" s="39" t="n">
-        <v>0.01601</v>
+        <v>0.004522</v>
       </c>
       <c r="H25" s="39" t="n">
-        <v>0.165</v>
+        <v>0.3598</v>
       </c>
       <c r="I25" s="39" t="n">
-        <v>0.0091</v>
-      </c>
-      <c r="J25" s="39" t="n">
-        <v>0.148555</v>
-      </c>
+        <v>0.0179</v>
+      </c>
+      <c r="J25" s="39" t="n"/>
       <c r="K25" s="38" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L25" s="37" t="inlineStr">
         <is>
@@ -3277,1794 +3285,1834 @@
       </c>
       <c r="N25" s="37" t="inlineStr">
         <is>
-          <t>순자산 48억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만)</t>
+          <t>변동성 36.0%(74거래일 기준, 기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O25" s="37" t="inlineStr">
         <is>
-          <t>KEDI 알리바바 미국채커버드콜혼합지수(TR)</t>
+          <t>KRX-Akros 고배당주 20 위클리 고정 30% 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="37" t="inlineStr">
         <is>
-          <t>KIWOOM 코스닥150커버드콜액티브</t>
+          <t>ACE 미국500데일리타겟커버드콜(합성)</t>
         </is>
       </c>
       <c r="B26" s="37" t="inlineStr">
         <is>
-          <t>0198A0</t>
+          <t>480030</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
-        </is>
-      </c>
-      <c r="D26" s="38" t="n">
-        <v>8390</v>
-      </c>
-      <c r="E26" s="38" t="n">
-        <v>72688500000</v>
-      </c>
-      <c r="F26" s="38" t="n">
-        <v>4941048490</v>
-      </c>
-      <c r="G26" s="39" t="n">
-        <v>0.006657</v>
-      </c>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="38" t="n"/>
+      <c r="G26" s="39" t="n"/>
       <c r="H26" s="39" t="n"/>
-      <c r="I26" s="39" t="n">
-        <v>0.0243</v>
-      </c>
+      <c r="I26" s="39" t="n"/>
       <c r="J26" s="39" t="n"/>
-      <c r="K26" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
+      <c r="K26" s="38" t="n"/>
+      <c r="L26" s="37" t="n"/>
       <c r="M26" s="37" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
       <c r="N26" s="37" t="inlineStr">
-        <is>
-          <t>변동성 산출 불가(시세 55일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O26" s="37" t="inlineStr">
-        <is>
-          <t>코스닥 150 위클리 고정 30% 커버드콜 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 200커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B27" s="37" t="inlineStr">
-        <is>
-          <t>0219E0</t>
-        </is>
-      </c>
-      <c r="C27" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D27" s="38" t="n">
-        <v>8180</v>
-      </c>
-      <c r="E27" s="38" t="n">
-        <v>726902000000</v>
-      </c>
-      <c r="F27" s="38" t="n">
-        <v>46393698652</v>
-      </c>
-      <c r="G27" s="39" t="n">
-        <v>0.005278000000000001</v>
-      </c>
-      <c r="H27" s="39" t="n"/>
-      <c r="I27" s="39" t="n">
-        <v>0.0193</v>
-      </c>
-      <c r="J27" s="39" t="n"/>
-      <c r="K27" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M27" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N27" s="37" t="inlineStr">
-        <is>
-          <t>변동성 산출 불가(시세 45일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O27" s="37" t="inlineStr">
-        <is>
-          <t>코스피 200 커버드콜 5% OTM</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 200타겟위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B28" s="37" t="inlineStr">
-        <is>
-          <t>498400</t>
-        </is>
-      </c>
-      <c r="C28" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D28" s="38" t="n">
-        <v>19775</v>
-      </c>
-      <c r="E28" s="38" t="n">
-        <v>5759831000000</v>
-      </c>
-      <c r="F28" s="38" t="n">
-        <v>176445783223</v>
-      </c>
-      <c r="G28" s="39" t="n">
-        <v>0.005095</v>
-      </c>
-      <c r="H28" s="39" t="n">
-        <v>0.5655</v>
-      </c>
-      <c r="I28" s="39" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="J28" s="39" t="n">
-        <v>0.158078</v>
-      </c>
-      <c r="K28" s="38" t="n">
-        <v>21</v>
-      </c>
-      <c r="L28" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M28" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N28" s="37" t="inlineStr">
-        <is>
-          <t>변동성 56.6%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O28" s="37" t="inlineStr">
-        <is>
-          <t>코스피 200 타겟 15% 위클리 커버드콜 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 금융고배당TOP10타겟위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B29" s="37" t="inlineStr">
-        <is>
-          <t>498410</t>
-        </is>
-      </c>
-      <c r="C29" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D29" s="38" t="n">
-        <v>11965</v>
-      </c>
-      <c r="E29" s="38" t="n">
-        <v>843040000000</v>
-      </c>
-      <c r="F29" s="38" t="n">
-        <v>22965862505</v>
-      </c>
-      <c r="G29" s="39" t="n">
-        <v>0.006697</v>
-      </c>
-      <c r="H29" s="39" t="n">
-        <v>0.3274</v>
-      </c>
-      <c r="I29" s="39" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="J29" s="39" t="n">
-        <v>0.157292</v>
-      </c>
-      <c r="K29" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="L29" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M29" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N29" s="37" t="inlineStr">
-        <is>
-          <t>변동성 32.7%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O29" s="37" t="inlineStr">
-        <is>
-          <t>코스피 200 금융 고배당 TOP 10 타겟 15% 분배 위클리 커버드콜</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 미국S&amp;P500변동성확대시커버드콜</t>
-        </is>
-      </c>
-      <c r="B30" s="37" t="inlineStr">
-        <is>
-          <t>0089C0</t>
-        </is>
-      </c>
-      <c r="C30" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D30" s="38" t="n">
-        <v>11170</v>
-      </c>
-      <c r="E30" s="38" t="n">
-        <v>42541000000</v>
-      </c>
-      <c r="F30" s="38" t="n">
-        <v>369289199</v>
-      </c>
-      <c r="G30" s="39" t="n">
-        <v>0.006338</v>
-      </c>
-      <c r="H30" s="39" t="n">
-        <v>0.1398</v>
-      </c>
-      <c r="I30" s="39" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="J30" s="39" t="n">
-        <v>0.022292</v>
-      </c>
-      <c r="K30" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="L30" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M30" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N30" s="37" t="inlineStr">
-        <is>
-          <t>60일 거래대금 3.7억(기준 5억 미만)</t>
-        </is>
-      </c>
-      <c r="O30" s="37" t="inlineStr">
-        <is>
-          <t>Cboe S&amp;P 500 Volatility Contingent Daily Covered Call Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 미국성장커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B31" s="37" t="inlineStr">
-        <is>
-          <t>0144L0</t>
-        </is>
-      </c>
-      <c r="C31" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D31" s="38" t="n">
-        <v>9305</v>
-      </c>
-      <c r="E31" s="38" t="n">
-        <v>339450000000</v>
-      </c>
-      <c r="F31" s="38" t="n">
-        <v>2519924801</v>
-      </c>
-      <c r="G31" s="39" t="n">
-        <v>0.006395</v>
-      </c>
-      <c r="H31" s="39" t="n">
-        <v>0.1816</v>
-      </c>
-      <c r="I31" s="39" t="n">
-        <v>0.009899999999999999</v>
-      </c>
-      <c r="J31" s="39" t="n"/>
-      <c r="K31" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="L31" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M31" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N31" s="37" t="inlineStr">
-        <is>
-          <t>분배 이력 8개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O31" s="37" t="inlineStr">
-        <is>
-          <t>나스닥 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="37" t="inlineStr">
-        <is>
-          <t>KODEX 반도체타겟위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B32" s="37" t="inlineStr">
-        <is>
-          <t>0190G0</t>
-        </is>
-      </c>
-      <c r="C32" s="37" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D32" s="38" t="n">
-        <v>8685</v>
-      </c>
-      <c r="E32" s="38" t="n">
-        <v>166945000000</v>
-      </c>
-      <c r="F32" s="38" t="n">
-        <v>8917001863</v>
-      </c>
-      <c r="G32" s="39" t="n">
-        <v>0.006131</v>
-      </c>
-      <c r="H32" s="39" t="n">
-        <v>0.8571</v>
-      </c>
-      <c r="I32" s="39" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="J32" s="39" t="n"/>
-      <c r="K32" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="L32" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M32" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N32" s="37" t="inlineStr">
-        <is>
-          <t>변동성 85.7%(88거래일 기준, 기준 25% 초과), 분배 이력 4개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O32" s="37" t="inlineStr">
-        <is>
-          <t>KRX 반도체 타겟 9% 분배 위클리 커버드콜 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="37" t="inlineStr">
-        <is>
-          <t>PLUS 200위클리커버드콜채권혼합</t>
-        </is>
-      </c>
-      <c r="B33" s="37" t="inlineStr">
-        <is>
-          <t>0203D0</t>
-        </is>
-      </c>
-      <c r="C33" s="37" t="inlineStr">
-        <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D33" s="38" t="n">
-        <v>8820</v>
-      </c>
-      <c r="E33" s="38" t="n">
-        <v>10560000000</v>
-      </c>
-      <c r="F33" s="38" t="n">
-        <v>273040602</v>
-      </c>
-      <c r="G33" s="39" t="n">
-        <v>0.004914</v>
-      </c>
-      <c r="H33" s="39" t="n">
-        <v>0.3808</v>
-      </c>
-      <c r="I33" s="39" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="J33" s="39" t="n"/>
-      <c r="K33" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M33" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N33" s="37" t="inlineStr">
-        <is>
-          <t>순자산 106억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 38.1%(74거래일 기준, 기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O33" s="37" t="inlineStr">
-        <is>
-          <t>코스피 200 KTB 혼합 위클리 고정 10% 커버드콜 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="37" t="inlineStr">
-        <is>
-          <t>PLUS 200커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B34" s="37" t="inlineStr">
-        <is>
-          <t>0210E0</t>
-        </is>
-      </c>
-      <c r="C34" s="37" t="inlineStr">
-        <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D34" s="38" t="n">
-        <v>7160</v>
-      </c>
-      <c r="E34" s="38" t="n">
-        <v>66881000000</v>
-      </c>
-      <c r="F34" s="38" t="n">
-        <v>3120007789</v>
-      </c>
-      <c r="G34" s="39" t="n">
-        <v>0.006020999999999999</v>
-      </c>
-      <c r="H34" s="39" t="n"/>
-      <c r="I34" s="39" t="n">
-        <v>0.0194</v>
-      </c>
-      <c r="J34" s="39" t="n"/>
-      <c r="K34" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M34" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N34" s="37" t="inlineStr">
-        <is>
-          <t>변동성 산출 불가(시세 60일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O34" s="37" t="inlineStr">
-        <is>
-          <t>코스피 200 위클리 고정 30% 커버드콜 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="37" t="inlineStr">
-        <is>
-          <t>PLUS 고배당주위클리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B35" s="37" t="inlineStr">
-        <is>
-          <t>0018C0</t>
-        </is>
-      </c>
-      <c r="C35" s="37" t="inlineStr">
-        <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D35" s="38" t="n">
-        <v>10575</v>
-      </c>
-      <c r="E35" s="38" t="n">
-        <v>80370000000</v>
-      </c>
-      <c r="F35" s="38" t="n">
-        <v>1033603521</v>
-      </c>
-      <c r="G35" s="39" t="n">
-        <v>0.005958</v>
-      </c>
-      <c r="H35" s="39" t="n">
-        <v>0.2667</v>
-      </c>
-      <c r="I35" s="39" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="J35" s="39" t="n">
-        <v>0.168983</v>
-      </c>
-      <c r="K35" s="38" t="n">
-        <v>19</v>
-      </c>
-      <c r="L35" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M35" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N35" s="37" t="inlineStr">
-        <is>
-          <t>변동성 26.7%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O35" s="37" t="inlineStr">
-        <is>
-          <t>코스피 고배당 위클리 고정 커버드콜 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="37" t="inlineStr">
-        <is>
-          <t>PLUS 고배당주위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B36" s="37" t="inlineStr">
-        <is>
-          <t>489030</t>
-        </is>
-      </c>
-      <c r="C36" s="37" t="inlineStr">
-        <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D36" s="38" t="n">
-        <v>6460</v>
-      </c>
-      <c r="E36" s="38" t="n">
-        <v>303208500000</v>
-      </c>
-      <c r="F36" s="38" t="n">
-        <v>4301390728</v>
-      </c>
-      <c r="G36" s="39" t="n">
-        <v>0.008243</v>
-      </c>
-      <c r="H36" s="39" t="n">
-        <v>0.3069</v>
-      </c>
-      <c r="I36" s="39" t="n">
-        <v>0.0148</v>
-      </c>
-      <c r="J36" s="39" t="n">
-        <v>0.234985</v>
-      </c>
-      <c r="K36" s="38" t="n">
-        <v>25</v>
-      </c>
-      <c r="L36" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M36" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N36" s="37" t="inlineStr">
-        <is>
-          <t>변동성 30.7%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O36" s="37" t="inlineStr">
-        <is>
-          <t>코스피 고배당 위클리 콜매도 ATM 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="37" t="inlineStr">
-        <is>
-          <t>PLUS 미국배당증가성장주데일리커버드콜</t>
-        </is>
-      </c>
-      <c r="B37" s="37" t="inlineStr">
-        <is>
-          <t>494420</t>
-        </is>
-      </c>
-      <c r="C37" s="37" t="inlineStr">
-        <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D37" s="38" t="n">
-        <v>8665</v>
-      </c>
-      <c r="E37" s="38" t="n">
-        <v>15588000000</v>
-      </c>
-      <c r="F37" s="38" t="n">
-        <v>115241283</v>
-      </c>
-      <c r="G37" s="39" t="n">
-        <v>0.007707</v>
-      </c>
-      <c r="H37" s="39" t="n">
-        <v>0.1439</v>
-      </c>
-      <c r="I37" s="39" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="J37" s="39" t="n">
-        <v>0.149336</v>
-      </c>
-      <c r="K37" s="38" t="n">
-        <v>23</v>
-      </c>
-      <c r="L37" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M37" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N37" s="37" t="inlineStr">
-        <is>
-          <t>순자산 156억(기준 300억 미만), 60일 거래대금 1.2억(기준 5억 미만)</t>
-        </is>
-      </c>
-      <c r="O37" s="37" t="inlineStr">
-        <is>
-          <t>Bloomberg U.S. Dividend Growth Partial Covered Call Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="37" t="inlineStr">
-        <is>
-          <t>PLUS 차이나항셍테크위클리타겟커버드콜</t>
-        </is>
-      </c>
-      <c r="B38" s="37" t="inlineStr">
-        <is>
-          <t>0128D0</t>
-        </is>
-      </c>
-      <c r="C38" s="37" t="inlineStr">
-        <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D38" s="38" t="n">
-        <v>6410</v>
-      </c>
-      <c r="E38" s="38" t="n">
-        <v>4476500000</v>
-      </c>
-      <c r="F38" s="38" t="n">
-        <v>29889499</v>
-      </c>
-      <c r="G38" s="39" t="n">
-        <v>0.01153</v>
-      </c>
-      <c r="H38" s="39" t="n">
-        <v>0.2722</v>
-      </c>
-      <c r="I38" s="39" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="J38" s="39" t="n"/>
-      <c r="K38" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="L38" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M38" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N38" s="37" t="inlineStr">
-        <is>
-          <t>순자산 45억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만), 변동성 27.2%(1년 기준, 기준 25% 초과), 분배 이력 9개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O38" s="37" t="inlineStr">
-        <is>
-          <t>HSTECH 15% Target Premium Weekly Covered Call Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="37" t="inlineStr">
-        <is>
-          <t>PLUS 테슬라위클리커버드콜채권혼합</t>
-        </is>
-      </c>
-      <c r="B39" s="37" t="inlineStr">
-        <is>
-          <t>0132K0</t>
-        </is>
-      </c>
-      <c r="C39" s="37" t="inlineStr">
-        <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D39" s="38" t="n">
-        <v>7835</v>
-      </c>
-      <c r="E39" s="38" t="n">
-        <v>108307000000</v>
-      </c>
-      <c r="F39" s="38" t="n">
-        <v>1317359602</v>
-      </c>
-      <c r="G39" s="39" t="n">
-        <v>0.006500000000000001</v>
-      </c>
-      <c r="H39" s="39" t="n">
-        <v>0.1302</v>
-      </c>
-      <c r="I39" s="39" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J39" s="39" t="n"/>
-      <c r="K39" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="L39" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M39" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N39" s="37" t="inlineStr">
-        <is>
-          <t>분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O39" s="37" t="inlineStr">
-        <is>
-          <t>Akros Tesla Weekly Covered Call Treasury Balanced Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="37" t="inlineStr">
-        <is>
-          <t>RISE 200고배당커버드콜ATM</t>
-        </is>
-      </c>
-      <c r="B40" s="37" t="inlineStr">
-        <is>
-          <t>290080</t>
-        </is>
-      </c>
-      <c r="C40" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D40" s="38" t="n">
-        <v>7355</v>
-      </c>
-      <c r="E40" s="38" t="n">
-        <v>12614000000</v>
-      </c>
-      <c r="F40" s="38" t="n">
-        <v>168593114</v>
-      </c>
-      <c r="G40" s="39" t="n">
-        <v>0.00636</v>
-      </c>
-      <c r="H40" s="39" t="n">
-        <v>0.3097</v>
-      </c>
-      <c r="I40" s="39" t="n">
-        <v>0.008100000000000001</v>
-      </c>
-      <c r="J40" s="39" t="n">
-        <v>0.107682</v>
-      </c>
-      <c r="K40" s="38" t="n">
-        <v>49</v>
-      </c>
-      <c r="L40" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M40" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N40" s="37" t="inlineStr">
-        <is>
-          <t>순자산 126억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 31.0%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O40" s="37" t="inlineStr">
-        <is>
-          <t>코스피 200 고배당 커버드콜 ATM</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="37" t="inlineStr">
-        <is>
-          <t>RISE 200위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B41" s="37" t="inlineStr">
-        <is>
-          <t>475720</t>
-        </is>
-      </c>
-      <c r="C41" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D41" s="38" t="n">
-        <v>12395</v>
-      </c>
-      <c r="E41" s="38" t="n">
-        <v>821275000000</v>
-      </c>
-      <c r="F41" s="38" t="n">
-        <v>12909513810</v>
-      </c>
-      <c r="G41" s="39" t="n">
-        <v>0.006305</v>
-      </c>
-      <c r="H41" s="39" t="n">
-        <v>0.4327</v>
-      </c>
-      <c r="I41" s="39" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="J41" s="39" t="n">
-        <v>0.199274</v>
-      </c>
-      <c r="K41" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="L41" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M41" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N41" s="37" t="inlineStr">
-        <is>
-          <t>변동성 43.3%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O41" s="37" t="inlineStr">
-        <is>
-          <t>코스피 200 위클리 커버드콜 ATM 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="37" t="inlineStr">
-        <is>
-          <t>RISE 미국30년국채커버드콜(합성)</t>
-        </is>
-      </c>
-      <c r="B42" s="37" t="inlineStr">
-        <is>
-          <t>472830</t>
-        </is>
-      </c>
-      <c r="C42" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D42" s="38" t="n">
-        <v>7700</v>
-      </c>
-      <c r="E42" s="38" t="n">
-        <v>42707250000</v>
-      </c>
-      <c r="F42" s="38" t="n">
-        <v>286133353</v>
-      </c>
-      <c r="G42" s="39" t="n">
-        <v>0.003419</v>
-      </c>
-      <c r="H42" s="39" t="n">
-        <v>0.1409</v>
-      </c>
-      <c r="I42" s="39" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="J42" s="39" t="n">
-        <v>0.115065</v>
-      </c>
-      <c r="K42" s="38" t="n">
-        <v>32</v>
-      </c>
-      <c r="L42" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M42" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N42" s="37" t="inlineStr">
-        <is>
-          <t>60일 거래대금 2.9억(기준 5억 미만)</t>
-        </is>
-      </c>
-      <c r="O42" s="37" t="inlineStr">
-        <is>
-          <t>Bloomberg U.S. Treasury 20+ Year(TLT) 2% OTM Covered Call In</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="37" t="inlineStr">
-        <is>
-          <t>RISE 미국AI밸류체인데일리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B43" s="37" t="inlineStr">
-        <is>
-          <t>490590</t>
-        </is>
-      </c>
-      <c r="C43" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D43" s="38" t="n">
-        <v>13625</v>
-      </c>
-      <c r="E43" s="38" t="n">
-        <v>760760000000</v>
-      </c>
-      <c r="F43" s="38" t="n">
-        <v>10123027992</v>
-      </c>
-      <c r="G43" s="39" t="n">
-        <v>0.00578</v>
-      </c>
-      <c r="H43" s="39" t="n">
-        <v>0.3307</v>
-      </c>
-      <c r="I43" s="39" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="J43" s="39" t="n">
-        <v>0.212991</v>
-      </c>
-      <c r="K43" s="38" t="n">
-        <v>23</v>
-      </c>
-      <c r="L43" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M43" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N43" s="37" t="inlineStr">
-        <is>
-          <t>변동성 33.1%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O43" s="37" t="inlineStr">
-        <is>
-          <t>KEDI U.S. AI Value Chain 90% Participation + Daily Options P</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="37" t="inlineStr">
-        <is>
-          <t>RISE 미국S&amp;P500데일리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B44" s="37" t="inlineStr">
-        <is>
-          <t>0138T0</t>
-        </is>
-      </c>
-      <c r="C44" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D44" s="38" t="n"/>
-      <c r="E44" s="38" t="n"/>
-      <c r="F44" s="38" t="n"/>
-      <c r="G44" s="39" t="n"/>
-      <c r="H44" s="39" t="n"/>
-      <c r="I44" s="39" t="n"/>
-      <c r="J44" s="39" t="n"/>
-      <c r="K44" s="38" t="n"/>
-      <c r="L44" s="37" t="n"/>
-      <c r="M44" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N44" s="37" t="inlineStr">
-        <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
-        </is>
-      </c>
-      <c r="O44" s="37" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="37" t="inlineStr">
-        <is>
-          <t>RISE 차이나테크TOP10위클리타겟커버드콜</t>
-        </is>
-      </c>
-      <c r="B45" s="37" t="inlineStr">
-        <is>
-          <t>0094L0</t>
-        </is>
-      </c>
-      <c r="C45" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D45" s="38" t="n">
-        <v>7065</v>
-      </c>
-      <c r="E45" s="38" t="n">
-        <v>9870000000</v>
-      </c>
-      <c r="F45" s="38" t="n">
-        <v>60752172</v>
-      </c>
-      <c r="G45" s="39" t="n">
-        <v>0.011533</v>
-      </c>
-      <c r="H45" s="39" t="n">
-        <v>0.2793</v>
-      </c>
-      <c r="I45" s="39" t="n">
-        <v>0.0097</v>
-      </c>
-      <c r="J45" s="39" t="n">
-        <v>0.154282</v>
-      </c>
-      <c r="K45" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="L45" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M45" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N45" s="37" t="inlineStr">
-        <is>
-          <t>순자산 99억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만), 변동성 27.9%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O45" s="37" t="inlineStr">
-        <is>
-          <t>Bloomberg China Tech Select Top 10 + 12% Target Premium Week</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="37" t="inlineStr">
-        <is>
-          <t>RISE 코리아밸류업위클리고정커버드콜</t>
-        </is>
-      </c>
-      <c r="B46" s="37" t="inlineStr">
-        <is>
-          <t>0094M0</t>
-        </is>
-      </c>
-      <c r="C46" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D46" s="38" t="n">
-        <v>16880</v>
-      </c>
-      <c r="E46" s="38" t="n">
-        <v>343230000000</v>
-      </c>
-      <c r="F46" s="38" t="n">
-        <v>9600787404</v>
-      </c>
-      <c r="G46" s="39" t="n">
-        <v>0.005637</v>
-      </c>
-      <c r="H46" s="39" t="n">
-        <v>0.4584</v>
-      </c>
-      <c r="I46" s="39" t="n">
-        <v>0.0299</v>
-      </c>
-      <c r="J46" s="39" t="n">
-        <v>0.248815</v>
-      </c>
-      <c r="K46" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="L46" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M46" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N46" s="37" t="inlineStr">
-        <is>
-          <t>변동성 45.8%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O46" s="37" t="inlineStr">
-        <is>
-          <t>코리아 밸류업 위클리 커버드콜 30% 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="37" t="inlineStr">
-        <is>
-          <t>RISE 코스닥커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B47" s="37" t="inlineStr">
-        <is>
-          <t>0223A0</t>
-        </is>
-      </c>
-      <c r="C47" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D47" s="38" t="n">
-        <v>10440</v>
-      </c>
-      <c r="E47" s="38" t="n">
-        <v>16624000000</v>
-      </c>
-      <c r="F47" s="38" t="n"/>
-      <c r="G47" s="39" t="n">
-        <v>0.003264</v>
-      </c>
-      <c r="H47" s="39" t="n"/>
-      <c r="I47" s="39" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J47" s="39" t="n"/>
-      <c r="K47" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M47" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N47" s="37" t="inlineStr">
-        <is>
-          <t>순자산 166억(기준 300억 미만), 거래대금 미확인, 변동성 산출 불가(시세 36일치뿐), 분배 이력 1개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O47" s="37" t="inlineStr">
-        <is>
-          <t>코스닥 150 타겟 15% 위클리 커버드콜 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="37" t="inlineStr">
-        <is>
-          <t>RISE 테슬라미국채타겟커버드콜혼합(합성)</t>
-        </is>
-      </c>
-      <c r="B48" s="37" t="inlineStr">
-        <is>
-          <t>0013R0</t>
-        </is>
-      </c>
-      <c r="C48" s="37" t="inlineStr">
-        <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D48" s="38" t="n">
-        <v>7620</v>
-      </c>
-      <c r="E48" s="38" t="n">
-        <v>27432000000</v>
-      </c>
-      <c r="F48" s="38" t="n">
-        <v>162123452</v>
-      </c>
-      <c r="G48" s="39" t="n">
-        <v>0.003495</v>
-      </c>
-      <c r="H48" s="39" t="n">
-        <v>0.1854</v>
-      </c>
-      <c r="I48" s="39" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="J48" s="39" t="n">
-        <v>0.183727</v>
-      </c>
-      <c r="K48" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="L48" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M48" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N48" s="37" t="inlineStr">
-        <is>
-          <t>순자산 274억(기준 300억 미만), 60일 거래대금 1.6억(기준 5억 미만)</t>
-        </is>
-      </c>
-      <c r="O48" s="37" t="inlineStr">
-        <is>
-          <t>KEDI Tesla U.S. 30Y Treasury 15% Target Premium Balanced Ind</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="37" t="inlineStr">
-        <is>
-          <t>SOL 200타겟위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B49" s="37" t="inlineStr">
-        <is>
-          <t>0167B0</t>
-        </is>
-      </c>
-      <c r="C49" s="37" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D49" s="38" t="n">
-        <v>11485</v>
-      </c>
-      <c r="E49" s="38" t="n">
-        <v>627507000000</v>
-      </c>
-      <c r="F49" s="38" t="n">
-        <v>21321082573</v>
-      </c>
-      <c r="G49" s="39" t="n">
-        <v>0.00345</v>
-      </c>
-      <c r="H49" s="39" t="n">
-        <v>0.6944</v>
-      </c>
-      <c r="I49" s="39" t="n">
-        <v>0.0139</v>
-      </c>
-      <c r="J49" s="39" t="n"/>
-      <c r="K49" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="L49" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M49" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N49" s="37" t="inlineStr">
-        <is>
-          <t>변동성 69.4%(126거래일 기준, 기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O49" s="37" t="inlineStr">
-        <is>
-          <t>코스피 200 타겟 15% 위클리 커버드콜 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="37" t="inlineStr">
-        <is>
-          <t>SOL 국제금커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B50" s="37" t="inlineStr">
-        <is>
-          <t>0022T0</t>
-        </is>
-      </c>
-      <c r="C50" s="37" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D50" s="38" t="n">
-        <v>12830</v>
-      </c>
-      <c r="E50" s="38" t="n">
-        <v>73074000000</v>
-      </c>
-      <c r="F50" s="38" t="n">
-        <v>1007418276</v>
-      </c>
-      <c r="G50" s="39" t="n">
-        <v>0.006737999999999999</v>
-      </c>
-      <c r="H50" s="39" t="n">
-        <v>0.2874</v>
-      </c>
-      <c r="I50" s="39" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="J50" s="39" t="n">
-        <v>0.044973</v>
-      </c>
-      <c r="K50" s="38" t="n">
-        <v>17</v>
-      </c>
-      <c r="L50" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M50" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N50" s="37" t="inlineStr">
-        <is>
-          <t>변동성 28.7%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O50" s="37" t="inlineStr">
-        <is>
-          <t>KEDI Gold Income Premium Index (Net Total Return)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="37" t="inlineStr">
-        <is>
-          <t>SOL 미국500타겟데일리커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B51" s="37" t="inlineStr">
-        <is>
-          <t>494210</t>
-        </is>
-      </c>
-      <c r="C51" s="37" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D51" s="38" t="n">
-        <v>10605</v>
-      </c>
-      <c r="E51" s="38" t="n">
-        <v>7423500000</v>
-      </c>
-      <c r="F51" s="38" t="n">
-        <v>64446271</v>
-      </c>
-      <c r="G51" s="39" t="n">
-        <v>0.00621</v>
-      </c>
-      <c r="H51" s="39" t="n">
-        <v>0.1571</v>
-      </c>
-      <c r="I51" s="39" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J51" s="39" t="n">
-        <v>0.126638</v>
-      </c>
-      <c r="K51" s="38" t="n">
-        <v>22</v>
-      </c>
-      <c r="L51" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M51" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N51" s="37" t="inlineStr">
-        <is>
-          <t>순자산 74억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만)</t>
-        </is>
-      </c>
-      <c r="O51" s="37" t="inlineStr">
-        <is>
-          <t>KEDI U.S. Quality500 + Monthly 1% Premium Index NTR</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="37" t="inlineStr">
-        <is>
-          <t>TIGER 200커버드콜</t>
-        </is>
-      </c>
-      <c r="B52" s="37" t="inlineStr">
-        <is>
-          <t>289480</t>
-        </is>
-      </c>
-      <c r="C52" s="37" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D52" s="38" t="n">
-        <v>12695</v>
-      </c>
-      <c r="E52" s="38" t="n">
-        <v>26512500000</v>
-      </c>
-      <c r="F52" s="38" t="n">
-        <v>429004958</v>
-      </c>
-      <c r="G52" s="39" t="n">
-        <v>0.007145</v>
-      </c>
-      <c r="H52" s="39" t="n">
-        <v>0.3833</v>
-      </c>
-      <c r="I52" s="39" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="J52" s="39" t="n">
-        <v>0.07026399999999999</v>
-      </c>
-      <c r="K52" s="38" t="n">
-        <v>51</v>
-      </c>
-      <c r="L52" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M52" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N52" s="37" t="inlineStr">
-        <is>
-          <t>순자산 265억(기준 300억 미만), 60일 거래대금 4.3억(기준 5억 미만), 변동성 38.3%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O52" s="37" t="inlineStr">
-        <is>
-          <t>코스피 200 커버드콜 ATM</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="37" t="inlineStr">
-        <is>
-          <t>TIGER 200커버드콜OTM</t>
-        </is>
-      </c>
-      <c r="B53" s="37" t="inlineStr">
-        <is>
-          <t>166400</t>
-        </is>
-      </c>
-      <c r="C53" s="37" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D53" s="38" t="n">
-        <v>24020</v>
-      </c>
-      <c r="E53" s="38" t="n">
-        <v>11965000000</v>
-      </c>
-      <c r="F53" s="38" t="n">
-        <v>48230202</v>
-      </c>
-      <c r="G53" s="39" t="n">
-        <v>0.006403</v>
-      </c>
-      <c r="H53" s="39" t="n">
-        <v>0.4264</v>
-      </c>
-      <c r="I53" s="39" t="n">
-        <v>0.0039</v>
-      </c>
-      <c r="J53" s="39" t="n">
-        <v>0.039592</v>
-      </c>
-      <c r="K53" s="38" t="n">
-        <v>51</v>
-      </c>
-      <c r="L53" s="37" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M53" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N53" s="37" t="inlineStr">
-        <is>
-          <t>순자산 120억(기준 300억 미만), 60일 거래대금 0.5억(기준 5억 미만), 변동성 42.6%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O53" s="37" t="inlineStr">
-        <is>
-          <t>코스피 200 커버드콜 5% OTM</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="37" t="inlineStr">
-        <is>
-          <t>TIGER 200타겟위클리커버드콜</t>
-        </is>
-      </c>
-      <c r="B54" s="37" t="inlineStr">
-        <is>
-          <t>0104N0</t>
-        </is>
-      </c>
-      <c r="C54" s="37" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D54" s="38" t="n">
-        <v>20340</v>
-      </c>
-      <c r="E54" s="38" t="n">
-        <v>208472000000</v>
-      </c>
-      <c r="F54" s="38" t="n">
-        <v>3412458770</v>
-      </c>
-      <c r="G54" s="39" t="n">
-        <v>0.003325</v>
-      </c>
-      <c r="H54" s="39" t="n">
-        <v>0.5913</v>
-      </c>
-      <c r="I54" s="39" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="J54" s="39" t="n">
-        <v>0.060472</v>
-      </c>
-      <c r="K54" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="L54" s="37" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M54" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N54" s="37" t="inlineStr">
-        <is>
-          <t>변동성 59.1%(1년 기준, 기준 25% 초과)</t>
-        </is>
-      </c>
-      <c r="O54" s="37" t="inlineStr">
-        <is>
-          <t>코스피 200 타겟 7% 위클리 커버드콜 지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="37" t="inlineStr">
-        <is>
-          <t>TIGER 미국나스닥100커버드콜(합성)</t>
-        </is>
-      </c>
-      <c r="B55" s="37" t="inlineStr">
-        <is>
-          <t>441680</t>
-        </is>
-      </c>
-      <c r="C55" s="37" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D55" s="38" t="n"/>
-      <c r="E55" s="38" t="n"/>
-      <c r="F55" s="38" t="n"/>
-      <c r="G55" s="39" t="n"/>
-      <c r="H55" s="39" t="n"/>
-      <c r="I55" s="39" t="n"/>
-      <c r="J55" s="39" t="n"/>
-      <c r="K55" s="38" t="n"/>
-      <c r="L55" s="37" t="n"/>
-      <c r="M55" s="37" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N55" s="37" t="inlineStr">
         <is>
           <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
 Call log:
   - )</t>
         </is>
       </c>
-      <c r="O55" s="37" t="inlineStr"/>
+      <c r="O26" s="37" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="37" t="inlineStr">
+        <is>
+          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
+        </is>
+      </c>
+      <c r="B27" s="37" t="inlineStr">
+        <is>
+          <t>480040</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D27" s="38" t="n">
+        <v>13345</v>
+      </c>
+      <c r="E27" s="38" t="n">
+        <v>181016000000</v>
+      </c>
+      <c r="F27" s="38" t="n">
+        <v>3487794407</v>
+      </c>
+      <c r="G27" s="39" t="n">
+        <v>0.005406999999999999</v>
+      </c>
+      <c r="H27" s="39" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="I27" s="39" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="J27" s="39" t="n">
+        <v>0.260922</v>
+      </c>
+      <c r="K27" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="L27" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M27" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N27" s="37" t="inlineStr">
+        <is>
+          <t>변동성 44.1%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O27" s="37" t="inlineStr">
+        <is>
+          <t>Bloomberg US Listed Semiconductor Premium(QQQ) Decrement 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="37" t="inlineStr">
+        <is>
+          <t>ACE 미국배당퀄리티+커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>0049M0</t>
+        </is>
+      </c>
+      <c r="C28" s="37" t="inlineStr">
+        <is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D28" s="38" t="n">
+        <v>11010</v>
+      </c>
+      <c r="E28" s="38" t="n">
+        <v>78171000000</v>
+      </c>
+      <c r="F28" s="38" t="n">
+        <v>379517920</v>
+      </c>
+      <c r="G28" s="39" t="n">
+        <v>0.005323</v>
+      </c>
+      <c r="H28" s="39" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="I28" s="39" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J28" s="39" t="n">
+        <v>0.075658</v>
+      </c>
+      <c r="K28" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="L28" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M28" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N28" s="37" t="inlineStr">
+        <is>
+          <t>60일 거래대금 3.8억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O28" s="37" t="inlineStr">
+        <is>
+          <t>Bloomberg WisdomTree U.S. Quality Dividend &amp; B500 Premium De</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="37" t="inlineStr">
+        <is>
+          <t>FOCUS AI반도체위클리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B29" s="37" t="inlineStr">
+        <is>
+          <t>0176P0</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>브이아이자산운용</t>
+        </is>
+      </c>
+      <c r="D29" s="38" t="n">
+        <v>12660</v>
+      </c>
+      <c r="E29" s="38" t="n">
+        <v>6864000000</v>
+      </c>
+      <c r="F29" s="38" t="n">
+        <v>168943471</v>
+      </c>
+      <c r="G29" s="39" t="n">
+        <v>0.003711</v>
+      </c>
+      <c r="H29" s="39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I29" s="39" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="J29" s="39" t="n"/>
+      <c r="K29" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M29" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N29" s="37" t="inlineStr">
+        <is>
+          <t>순자산 69억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 80.0%(111거래일 기준, 기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O29" s="37" t="inlineStr">
+        <is>
+          <t>AI 반도체 위클리 고정 30% 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="37" t="inlineStr">
+        <is>
+          <t>FOCUS 알리바바미국채커버드콜혼합</t>
+        </is>
+      </c>
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>0073X0</t>
+        </is>
+      </c>
+      <c r="C30" s="37" t="inlineStr">
+        <is>
+          <t>브이아이자산운용</t>
+        </is>
+      </c>
+      <c r="D30" s="38" t="n">
+        <v>8650</v>
+      </c>
+      <c r="E30" s="38" t="n">
+        <v>4760250000</v>
+      </c>
+      <c r="F30" s="38" t="n">
+        <v>30623084</v>
+      </c>
+      <c r="G30" s="39" t="n">
+        <v>0.01601</v>
+      </c>
+      <c r="H30" s="39" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="I30" s="39" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="J30" s="39" t="n">
+        <v>0.148555</v>
+      </c>
+      <c r="K30" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="L30" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M30" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N30" s="37" t="inlineStr">
+        <is>
+          <t>순자산 48억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O30" s="37" t="inlineStr">
+        <is>
+          <t>KEDI 알리바바 미국채커버드콜혼합지수(TR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t>KIWOOM 코스닥150커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B31" s="37" t="inlineStr">
+        <is>
+          <t>0198A0</t>
+        </is>
+      </c>
+      <c r="C31" s="37" t="inlineStr">
+        <is>
+          <t>키움투자자산운용</t>
+        </is>
+      </c>
+      <c r="D31" s="38" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E31" s="38" t="n">
+        <v>72688500000</v>
+      </c>
+      <c r="F31" s="38" t="n">
+        <v>4941985671</v>
+      </c>
+      <c r="G31" s="39" t="n">
+        <v>0.006657</v>
+      </c>
+      <c r="H31" s="39" t="n"/>
+      <c r="I31" s="39" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="J31" s="39" t="n"/>
+      <c r="K31" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M31" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N31" s="37" t="inlineStr">
+        <is>
+          <t>변동성 산출 불가(시세 55일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O31" s="37" t="inlineStr">
+        <is>
+          <t>코스닥 150 위클리 고정 30% 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="37" t="inlineStr">
+        <is>
+          <t>KODEX 200커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B32" s="37" t="inlineStr">
+        <is>
+          <t>0219E0</t>
+        </is>
+      </c>
+      <c r="C32" s="37" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D32" s="38" t="n">
+        <v>8180</v>
+      </c>
+      <c r="E32" s="38" t="n">
+        <v>726902000000</v>
+      </c>
+      <c r="F32" s="38" t="n">
+        <v>46402333642</v>
+      </c>
+      <c r="G32" s="39" t="n">
+        <v>0.005278000000000001</v>
+      </c>
+      <c r="H32" s="39" t="n"/>
+      <c r="I32" s="39" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="J32" s="39" t="n"/>
+      <c r="K32" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M32" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N32" s="37" t="inlineStr">
+        <is>
+          <t>변동성 산출 불가(시세 45일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O32" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 커버드콜 5% OTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="37" t="inlineStr">
+        <is>
+          <t>KODEX 200타겟위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B33" s="37" t="inlineStr">
+        <is>
+          <t>498400</t>
+        </is>
+      </c>
+      <c r="C33" s="37" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D33" s="38" t="n">
+        <v>19795</v>
+      </c>
+      <c r="E33" s="38" t="n">
+        <v>5759831000000</v>
+      </c>
+      <c r="F33" s="38" t="n">
+        <v>176467394162</v>
+      </c>
+      <c r="G33" s="39" t="n">
+        <v>0.005095</v>
+      </c>
+      <c r="H33" s="39" t="n">
+        <v>0.5656</v>
+      </c>
+      <c r="I33" s="39" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="J33" s="39" t="n">
+        <v>0.157919</v>
+      </c>
+      <c r="K33" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="L33" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M33" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N33" s="37" t="inlineStr">
+        <is>
+          <t>변동성 56.6%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O33" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 타겟 15% 위클리 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>KODEX 금융고배당TOP10타겟위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B34" s="37" t="inlineStr">
+        <is>
+          <t>498410</t>
+        </is>
+      </c>
+      <c r="C34" s="37" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D34" s="38" t="n">
+        <v>11955</v>
+      </c>
+      <c r="E34" s="38" t="n">
+        <v>843040000000</v>
+      </c>
+      <c r="F34" s="38" t="n">
+        <v>22966743776</v>
+      </c>
+      <c r="G34" s="39" t="n">
+        <v>0.006697</v>
+      </c>
+      <c r="H34" s="39" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="I34" s="39" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="J34" s="39" t="n">
+        <v>0.157424</v>
+      </c>
+      <c r="K34" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="L34" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M34" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N34" s="37" t="inlineStr">
+        <is>
+          <t>변동성 32.7%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O34" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 금융 고배당 TOP 10 타겟 15% 분배 위클리 커버드콜</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="37" t="inlineStr">
+        <is>
+          <t>KODEX 미국S&amp;P500변동성확대시커버드콜</t>
+        </is>
+      </c>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>0089C0</t>
+        </is>
+      </c>
+      <c r="C35" s="37" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D35" s="38" t="n">
+        <v>11170</v>
+      </c>
+      <c r="E35" s="38" t="n">
+        <v>42541000000</v>
+      </c>
+      <c r="F35" s="38" t="n">
+        <v>369289199</v>
+      </c>
+      <c r="G35" s="39" t="n">
+        <v>0.006338</v>
+      </c>
+      <c r="H35" s="39" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="I35" s="39" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="J35" s="39" t="n">
+        <v>0.022292</v>
+      </c>
+      <c r="K35" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="L35" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M35" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N35" s="37" t="inlineStr">
+        <is>
+          <t>60일 거래대금 3.7억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O35" s="37" t="inlineStr">
+        <is>
+          <t>Cboe S&amp;P 500 Volatility Contingent Daily Covered Call Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>KODEX 미국성장커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>0144L0</t>
+        </is>
+      </c>
+      <c r="C36" s="37" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D36" s="38" t="n">
+        <v>9300</v>
+      </c>
+      <c r="E36" s="38" t="n">
+        <v>339450000000</v>
+      </c>
+      <c r="F36" s="38" t="n">
+        <v>2520136510</v>
+      </c>
+      <c r="G36" s="39" t="n">
+        <v>0.006395</v>
+      </c>
+      <c r="H36" s="39" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="I36" s="39" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="J36" s="39" t="n"/>
+      <c r="K36" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="L36" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M36" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N36" s="37" t="inlineStr">
+        <is>
+          <t>분배 이력 8개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O36" s="37" t="inlineStr">
+        <is>
+          <t>나스닥 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="37" t="inlineStr">
+        <is>
+          <t>KODEX 반도체타겟위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B37" s="37" t="inlineStr">
+        <is>
+          <t>0190G0</t>
+        </is>
+      </c>
+      <c r="C37" s="37" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D37" s="38" t="n">
+        <v>8705</v>
+      </c>
+      <c r="E37" s="38" t="n">
+        <v>166945000000</v>
+      </c>
+      <c r="F37" s="38" t="n">
+        <v>8917091348</v>
+      </c>
+      <c r="G37" s="39" t="n">
+        <v>0.006131</v>
+      </c>
+      <c r="H37" s="39" t="n">
+        <v>0.8572</v>
+      </c>
+      <c r="I37" s="39" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="J37" s="39" t="n"/>
+      <c r="K37" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M37" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N37" s="37" t="inlineStr">
+        <is>
+          <t>변동성 85.7%(88거래일 기준, 기준 25% 초과), 분배 이력 4개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O37" s="37" t="inlineStr">
+        <is>
+          <t>KRX 반도체 타겟 9% 분배 위클리 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 200위클리커버드콜채권혼합</t>
+        </is>
+      </c>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>0203D0</t>
+        </is>
+      </c>
+      <c r="C38" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D38" s="38" t="n">
+        <v>8825</v>
+      </c>
+      <c r="E38" s="38" t="n">
+        <v>10560000000</v>
+      </c>
+      <c r="F38" s="38" t="n">
+        <v>273086713</v>
+      </c>
+      <c r="G38" s="39" t="n">
+        <v>0.004914</v>
+      </c>
+      <c r="H38" s="39" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="I38" s="39" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="J38" s="39" t="n"/>
+      <c r="K38" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M38" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N38" s="37" t="inlineStr">
+        <is>
+          <t>순자산 106억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 38.1%(74거래일 기준, 기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O38" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 KTB 혼합 위클리 고정 10% 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 200커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>0210E0</t>
+        </is>
+      </c>
+      <c r="C39" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D39" s="38" t="n">
+        <v>7155</v>
+      </c>
+      <c r="E39" s="38" t="n">
+        <v>66881000000</v>
+      </c>
+      <c r="F39" s="38" t="n">
+        <v>3120034260</v>
+      </c>
+      <c r="G39" s="39" t="n">
+        <v>0.006020999999999999</v>
+      </c>
+      <c r="H39" s="39" t="n"/>
+      <c r="I39" s="39" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="J39" s="39" t="n"/>
+      <c r="K39" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M39" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N39" s="37" t="inlineStr">
+        <is>
+          <t>변동성 산출 불가(시세 60일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O39" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 위클리 고정 30% 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 고배당주위클리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>0018C0</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D40" s="38" t="n">
+        <v>10575</v>
+      </c>
+      <c r="E40" s="38" t="n">
+        <v>80370000000</v>
+      </c>
+      <c r="F40" s="38" t="n">
+        <v>1033605284</v>
+      </c>
+      <c r="G40" s="39" t="n">
+        <v>0.005958</v>
+      </c>
+      <c r="H40" s="39" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="I40" s="39" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="J40" s="39" t="n">
+        <v>0.168983</v>
+      </c>
+      <c r="K40" s="38" t="n">
+        <v>19</v>
+      </c>
+      <c r="L40" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M40" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N40" s="37" t="inlineStr">
+        <is>
+          <t>변동성 26.7%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O40" s="37" t="inlineStr">
+        <is>
+          <t>코스피 고배당 위클리 고정 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 고배당주위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>489030</t>
+        </is>
+      </c>
+      <c r="C41" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D41" s="38" t="n">
+        <v>6465</v>
+      </c>
+      <c r="E41" s="38" t="n">
+        <v>303208500000</v>
+      </c>
+      <c r="F41" s="38" t="n">
+        <v>4301777394</v>
+      </c>
+      <c r="G41" s="39" t="n">
+        <v>0.008243</v>
+      </c>
+      <c r="H41" s="39" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="I41" s="39" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="J41" s="39" t="n">
+        <v>0.234803</v>
+      </c>
+      <c r="K41" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="L41" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M41" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N41" s="37" t="inlineStr">
+        <is>
+          <t>변동성 30.7%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O41" s="37" t="inlineStr">
+        <is>
+          <t>코스피 고배당 위클리 콜매도 ATM 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 미국배당증가성장주데일리커버드콜</t>
+        </is>
+      </c>
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>494420</t>
+        </is>
+      </c>
+      <c r="C42" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D42" s="38" t="n">
+        <v>8665</v>
+      </c>
+      <c r="E42" s="38" t="n">
+        <v>15588000000</v>
+      </c>
+      <c r="F42" s="38" t="n">
+        <v>115242871</v>
+      </c>
+      <c r="G42" s="39" t="n">
+        <v>0.007707</v>
+      </c>
+      <c r="H42" s="39" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="I42" s="39" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="J42" s="39" t="n">
+        <v>0.149336</v>
+      </c>
+      <c r="K42" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="L42" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M42" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N42" s="37" t="inlineStr">
+        <is>
+          <t>순자산 156억(기준 300억 미만), 60일 거래대금 1.2억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O42" s="37" t="inlineStr">
+        <is>
+          <t>Bloomberg U.S. Dividend Growth Partial Covered Call Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 차이나항셍테크위클리타겟커버드콜</t>
+        </is>
+      </c>
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>0128D0</t>
+        </is>
+      </c>
+      <c r="C43" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D43" s="38" t="n">
+        <v>6410</v>
+      </c>
+      <c r="E43" s="38" t="n">
+        <v>4476500000</v>
+      </c>
+      <c r="F43" s="38" t="n">
+        <v>29889499</v>
+      </c>
+      <c r="G43" s="39" t="n">
+        <v>0.01153</v>
+      </c>
+      <c r="H43" s="39" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="I43" s="39" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J43" s="39" t="n"/>
+      <c r="K43" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="L43" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M43" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N43" s="37" t="inlineStr">
+        <is>
+          <t>순자산 45억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만), 변동성 27.2%(1년 기준, 기준 25% 초과), 분배 이력 9개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O43" s="37" t="inlineStr">
+        <is>
+          <t>HSTECH 15% Target Premium Weekly Covered Call Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="37" t="inlineStr">
+        <is>
+          <t>PLUS 테슬라위클리커버드콜채권혼합</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>0132K0</t>
+        </is>
+      </c>
+      <c r="C44" s="37" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D44" s="38" t="n">
+        <v>7835</v>
+      </c>
+      <c r="E44" s="38" t="n">
+        <v>108307000000</v>
+      </c>
+      <c r="F44" s="38" t="n">
+        <v>1317359602</v>
+      </c>
+      <c r="G44" s="39" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="H44" s="39" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="I44" s="39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J44" s="39" t="n"/>
+      <c r="K44" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="L44" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M44" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N44" s="37" t="inlineStr">
+        <is>
+          <t>분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O44" s="37" t="inlineStr">
+        <is>
+          <t>Akros Tesla Weekly Covered Call Treasury Balanced Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t>RISE 200고배당커버드콜ATM</t>
+        </is>
+      </c>
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>290080</t>
+        </is>
+      </c>
+      <c r="C45" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D45" s="38" t="n">
+        <v>7350</v>
+      </c>
+      <c r="E45" s="38" t="n">
+        <v>12614000000</v>
+      </c>
+      <c r="F45" s="38" t="n">
+        <v>168611625</v>
+      </c>
+      <c r="G45" s="39" t="n">
+        <v>0.00636</v>
+      </c>
+      <c r="H45" s="39" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="I45" s="39" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="J45" s="39" t="n">
+        <v>0.107755</v>
+      </c>
+      <c r="K45" s="38" t="n">
+        <v>49</v>
+      </c>
+      <c r="L45" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M45" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N45" s="37" t="inlineStr">
+        <is>
+          <t>순자산 126억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 31.0%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O45" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 고배당 커버드콜 ATM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="37" t="inlineStr">
+        <is>
+          <t>RISE 200위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B46" s="37" t="inlineStr">
+        <is>
+          <t>475720</t>
+        </is>
+      </c>
+      <c r="C46" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D46" s="38" t="n">
+        <v>12400</v>
+      </c>
+      <c r="E46" s="38" t="n">
+        <v>821275000000</v>
+      </c>
+      <c r="F46" s="38" t="n">
+        <v>12910069960</v>
+      </c>
+      <c r="G46" s="39" t="n">
+        <v>0.006305</v>
+      </c>
+      <c r="H46" s="39" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="I46" s="39" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="J46" s="39" t="n">
+        <v>0.199194</v>
+      </c>
+      <c r="K46" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="L46" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M46" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N46" s="37" t="inlineStr">
+        <is>
+          <t>변동성 43.3%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O46" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 위클리 커버드콜 ATM 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="37" t="inlineStr">
+        <is>
+          <t>RISE 미국30년국채커버드콜(합성)</t>
+        </is>
+      </c>
+      <c r="B47" s="37" t="inlineStr">
+        <is>
+          <t>472830</t>
+        </is>
+      </c>
+      <c r="C47" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="n">
+        <v>7700</v>
+      </c>
+      <c r="E47" s="38" t="n">
+        <v>42707250000</v>
+      </c>
+      <c r="F47" s="38" t="n">
+        <v>286133353</v>
+      </c>
+      <c r="G47" s="39" t="n">
+        <v>0.003419</v>
+      </c>
+      <c r="H47" s="39" t="n">
+        <v>0.1409</v>
+      </c>
+      <c r="I47" s="39" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="J47" s="39" t="n">
+        <v>0.115065</v>
+      </c>
+      <c r="K47" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="L47" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M47" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N47" s="37" t="inlineStr">
+        <is>
+          <t>60일 거래대금 2.9억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O47" s="37" t="inlineStr">
+        <is>
+          <t>Bloomberg U.S. Treasury 20+ Year(TLT) 2% OTM Covered Call In</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="37" t="inlineStr">
+        <is>
+          <t>RISE 미국AI밸류체인데일리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>490590</t>
+        </is>
+      </c>
+      <c r="C48" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D48" s="38" t="n">
+        <v>13630</v>
+      </c>
+      <c r="E48" s="38" t="n">
+        <v>760760000000</v>
+      </c>
+      <c r="F48" s="38" t="n">
+        <v>10123242592</v>
+      </c>
+      <c r="G48" s="39" t="n">
+        <v>0.00578</v>
+      </c>
+      <c r="H48" s="39" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="I48" s="39" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="J48" s="39" t="n">
+        <v>0.212913</v>
+      </c>
+      <c r="K48" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="L48" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M48" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N48" s="37" t="inlineStr">
+        <is>
+          <t>변동성 33.1%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O48" s="37" t="inlineStr">
+        <is>
+          <t>KEDI U.S. AI Value Chain 90% Participation + Daily Options P</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="37" t="inlineStr">
+        <is>
+          <t>RISE 미국S&amp;P500데일리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>0138T0</t>
+        </is>
+      </c>
+      <c r="C49" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D49" s="38" t="n">
+        <v>9235</v>
+      </c>
+      <c r="E49" s="38" t="n">
+        <v>32305000000</v>
+      </c>
+      <c r="F49" s="38" t="n">
+        <v>320376485</v>
+      </c>
+      <c r="G49" s="39" t="n">
+        <v>0.006153</v>
+      </c>
+      <c r="H49" s="39" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="I49" s="39" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J49" s="39" t="n"/>
+      <c r="K49" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="L49" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M49" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N49" s="37" t="inlineStr">
+        <is>
+          <t>60일 거래대금 3.2억(기준 5억 미만), 분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O49" s="37" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 10% Daily Fixed Covered Call Index (USD) TR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="37" t="inlineStr">
+        <is>
+          <t>RISE 차이나테크TOP10위클리타겟커버드콜</t>
+        </is>
+      </c>
+      <c r="B50" s="37" t="inlineStr">
+        <is>
+          <t>0094L0</t>
+        </is>
+      </c>
+      <c r="C50" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D50" s="38" t="n">
+        <v>7075</v>
+      </c>
+      <c r="E50" s="38" t="n">
+        <v>9870000000</v>
+      </c>
+      <c r="F50" s="38" t="n">
+        <v>60754726</v>
+      </c>
+      <c r="G50" s="39" t="n">
+        <v>0.011533</v>
+      </c>
+      <c r="H50" s="39" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="I50" s="39" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="J50" s="39" t="n">
+        <v>0.154064</v>
+      </c>
+      <c r="K50" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="L50" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M50" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N50" s="37" t="inlineStr">
+        <is>
+          <t>순자산 99억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만), 변동성 27.9%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O50" s="37" t="inlineStr">
+        <is>
+          <t>Bloomberg China Tech Select Top 10 + 12% Target Premium Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="37" t="inlineStr">
+        <is>
+          <t>RISE 코리아밸류업위클리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B51" s="37" t="inlineStr">
+        <is>
+          <t>0094M0</t>
+        </is>
+      </c>
+      <c r="C51" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D51" s="38" t="n">
+        <v>16875</v>
+      </c>
+      <c r="E51" s="38" t="n">
+        <v>343230000000</v>
+      </c>
+      <c r="F51" s="38" t="n">
+        <v>9601554523</v>
+      </c>
+      <c r="G51" s="39" t="n">
+        <v>0.005637</v>
+      </c>
+      <c r="H51" s="39" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="I51" s="39" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="J51" s="39" t="n">
+        <v>0.248889</v>
+      </c>
+      <c r="K51" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="L51" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M51" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N51" s="37" t="inlineStr">
+        <is>
+          <t>변동성 45.8%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O51" s="37" t="inlineStr">
+        <is>
+          <t>코리아 밸류업 위클리 커버드콜 30% 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="37" t="inlineStr">
+        <is>
+          <t>RISE 코스닥커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B52" s="37" t="inlineStr">
+        <is>
+          <t>0223A0</t>
+        </is>
+      </c>
+      <c r="C52" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D52" s="38" t="n">
+        <v>10440</v>
+      </c>
+      <c r="E52" s="38" t="n">
+        <v>16624000000</v>
+      </c>
+      <c r="F52" s="38" t="n"/>
+      <c r="G52" s="39" t="n">
+        <v>0.003264</v>
+      </c>
+      <c r="H52" s="39" t="n"/>
+      <c r="I52" s="39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J52" s="39" t="n"/>
+      <c r="K52" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M52" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N52" s="37" t="inlineStr">
+        <is>
+          <t>순자산 166억(기준 300억 미만), 거래대금 미확인, 변동성 산출 불가(시세 36일치뿐), 분배 이력 1개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O52" s="37" t="inlineStr">
+        <is>
+          <t>코스닥 150 타겟 15% 위클리 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>RISE 테슬라미국채타겟커버드콜혼합(합성)</t>
+        </is>
+      </c>
+      <c r="B53" s="37" t="inlineStr">
+        <is>
+          <t>0013R0</t>
+        </is>
+      </c>
+      <c r="C53" s="37" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D53" s="38" t="n">
+        <v>7620</v>
+      </c>
+      <c r="E53" s="38" t="n">
+        <v>27432000000</v>
+      </c>
+      <c r="F53" s="38" t="n">
+        <v>162123452</v>
+      </c>
+      <c r="G53" s="39" t="n">
+        <v>0.003495</v>
+      </c>
+      <c r="H53" s="39" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="I53" s="39" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="J53" s="39" t="n">
+        <v>0.183727</v>
+      </c>
+      <c r="K53" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="L53" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M53" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N53" s="37" t="inlineStr">
+        <is>
+          <t>순자산 274억(기준 300억 미만), 60일 거래대금 1.6억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O53" s="37" t="inlineStr">
+        <is>
+          <t>KEDI Tesla U.S. 30Y Treasury 15% Target Premium Balanced Ind</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t>SOL 200타겟위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B54" s="37" t="inlineStr">
+        <is>
+          <t>0167B0</t>
+        </is>
+      </c>
+      <c r="C54" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D54" s="38" t="n">
+        <v>11485</v>
+      </c>
+      <c r="E54" s="38" t="n">
+        <v>627507000000</v>
+      </c>
+      <c r="F54" s="38" t="n">
+        <v>21321299831</v>
+      </c>
+      <c r="G54" s="39" t="n">
+        <v>0.00345</v>
+      </c>
+      <c r="H54" s="39" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="I54" s="39" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="J54" s="39" t="n"/>
+      <c r="K54" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="L54" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M54" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N54" s="37" t="inlineStr">
+        <is>
+          <t>변동성 69.4%(126거래일 기준, 기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O54" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 타겟 15% 위클리 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="37" t="inlineStr">
+        <is>
+          <t>SOL 국제금커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B55" s="37" t="inlineStr">
+        <is>
+          <t>0022T0</t>
+        </is>
+      </c>
+      <c r="C55" s="37" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D55" s="38" t="n">
+        <v>12840</v>
+      </c>
+      <c r="E55" s="38" t="n">
+        <v>73074000000</v>
+      </c>
+      <c r="F55" s="38" t="n">
+        <v>1007451188</v>
+      </c>
+      <c r="G55" s="39" t="n">
+        <v>0.006737999999999999</v>
+      </c>
+      <c r="H55" s="39" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="I55" s="39" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="J55" s="39" t="n">
+        <v>0.04493800000000001</v>
+      </c>
+      <c r="K55" s="38" t="n">
+        <v>17</v>
+      </c>
+      <c r="L55" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M55" s="37" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N55" s="37" t="inlineStr">
+        <is>
+          <t>변동성 28.7%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O55" s="37" t="inlineStr">
+        <is>
+          <t>KEDI Gold Income Premium Index (Net Total Return)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="37" t="inlineStr">
         <is>
-          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
+          <t>SOL 미국500타겟데일리커버드콜액티브</t>
         </is>
       </c>
       <c r="B56" s="37" t="inlineStr">
         <is>
-          <t>486290</t>
+          <t>494210</t>
         </is>
       </c>
       <c r="C56" s="37" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D56" s="38" t="n"/>
-      <c r="E56" s="38" t="n"/>
-      <c r="F56" s="38" t="n"/>
-      <c r="G56" s="39" t="n"/>
-      <c r="H56" s="39" t="n"/>
-      <c r="I56" s="39" t="n"/>
-      <c r="J56" s="39" t="n"/>
-      <c r="K56" s="38" t="n"/>
-      <c r="L56" s="37" t="n"/>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D56" s="38" t="n">
+        <v>10605</v>
+      </c>
+      <c r="E56" s="38" t="n">
+        <v>7423500000</v>
+      </c>
+      <c r="F56" s="38" t="n">
+        <v>64446271</v>
+      </c>
+      <c r="G56" s="39" t="n">
+        <v>0.00621</v>
+      </c>
+      <c r="H56" s="39" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="I56" s="39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J56" s="39" t="n">
+        <v>0.126638</v>
+      </c>
+      <c r="K56" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="L56" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
       <c r="M56" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -5072,20 +5120,24 @@
       </c>
       <c r="N56" s="37" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 403)</t>
-        </is>
-      </c>
-      <c r="O56" s="37" t="inlineStr"/>
+          <t>순자산 74억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O56" s="37" t="inlineStr">
+        <is>
+          <t>KEDI U.S. Quality500 + Monthly 1% Premium Index NTR</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="37" t="inlineStr">
         <is>
-          <t>TIGER 미국배당다우존스타겟데일리커버드콜</t>
+          <t>TIGER 200커버드콜</t>
         </is>
       </c>
       <c r="B57" s="37" t="inlineStr">
         <is>
-          <t>0008S0</t>
+          <t>289480</t>
         </is>
       </c>
       <c r="C57" s="37" t="inlineStr">
@@ -5093,15 +5145,35 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D57" s="38" t="n"/>
-      <c r="E57" s="38" t="n"/>
-      <c r="F57" s="38" t="n"/>
-      <c r="G57" s="39" t="n"/>
-      <c r="H57" s="39" t="n"/>
-      <c r="I57" s="39" t="n"/>
-      <c r="J57" s="39" t="n"/>
-      <c r="K57" s="38" t="n"/>
-      <c r="L57" s="37" t="n"/>
+      <c r="D57" s="38" t="n">
+        <v>12670</v>
+      </c>
+      <c r="E57" s="38" t="n">
+        <v>26512500000</v>
+      </c>
+      <c r="F57" s="38" t="n">
+        <v>429005104</v>
+      </c>
+      <c r="G57" s="39" t="n">
+        <v>0.007145</v>
+      </c>
+      <c r="H57" s="39" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="I57" s="39" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="J57" s="39" t="n">
+        <v>0.07040300000000001</v>
+      </c>
+      <c r="K57" s="38" t="n">
+        <v>51</v>
+      </c>
+      <c r="L57" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
       <c r="M57" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -5109,20 +5181,24 @@
       </c>
       <c r="N57" s="37" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 403)</t>
-        </is>
-      </c>
-      <c r="O57" s="37" t="inlineStr"/>
+          <t>순자산 265억(기준 300억 미만), 60일 거래대금 4.3억(기준 5억 미만), 변동성 38.3%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O57" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 커버드콜 ATM</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="37" t="inlineStr">
         <is>
-          <t>TIGER 미국배당다우존스타겟커버드콜1호</t>
+          <t>TIGER 200커버드콜OTM</t>
         </is>
       </c>
       <c r="B58" s="37" t="inlineStr">
         <is>
-          <t>458750</t>
+          <t>166400</t>
         </is>
       </c>
       <c r="C58" s="37" t="inlineStr">
@@ -5130,15 +5206,35 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D58" s="38" t="n"/>
-      <c r="E58" s="38" t="n"/>
-      <c r="F58" s="38" t="n"/>
-      <c r="G58" s="39" t="n"/>
-      <c r="H58" s="39" t="n"/>
-      <c r="I58" s="39" t="n"/>
-      <c r="J58" s="39" t="n"/>
-      <c r="K58" s="38" t="n"/>
-      <c r="L58" s="37" t="n"/>
+      <c r="D58" s="38" t="n">
+        <v>24020</v>
+      </c>
+      <c r="E58" s="38" t="n">
+        <v>11965000000</v>
+      </c>
+      <c r="F58" s="38" t="n">
+        <v>48230202</v>
+      </c>
+      <c r="G58" s="39" t="n">
+        <v>0.006403</v>
+      </c>
+      <c r="H58" s="39" t="n">
+        <v>0.4264</v>
+      </c>
+      <c r="I58" s="39" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="J58" s="39" t="n">
+        <v>0.039592</v>
+      </c>
+      <c r="K58" s="38" t="n">
+        <v>51</v>
+      </c>
+      <c r="L58" s="37" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
       <c r="M58" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -5146,22 +5242,24 @@
       </c>
       <c r="N58" s="37" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
-Call log:
-  - )</t>
-        </is>
-      </c>
-      <c r="O58" s="37" t="inlineStr"/>
+          <t>순자산 120억(기준 300억 미만), 60일 거래대금 0.5억(기준 5억 미만), 변동성 42.6%(1년 기준, 기준 25% 초과)</t>
+        </is>
+      </c>
+      <c r="O58" s="37" t="inlineStr">
+        <is>
+          <t>코스피 200 커버드콜 5% OTM</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="37" t="inlineStr">
         <is>
-          <t>TIGER 미국배당다우존스타겟커버드콜2호</t>
+          <t>TIGER 200타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B59" s="37" t="inlineStr">
         <is>
-          <t>458760</t>
+          <t>0104N0</t>
         </is>
       </c>
       <c r="C59" s="37" t="inlineStr">
@@ -5185,9 +5283,7 @@
       </c>
       <c r="N59" s="37" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
-Call log:
-  - )</t>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
         </is>
       </c>
       <c r="O59" s="37" t="inlineStr"/>
@@ -5195,12 +5291,12 @@
     <row r="60">
       <c r="A60" s="37" t="inlineStr">
         <is>
-          <t>TIGER 미국테크TOP10타겟커버드콜</t>
+          <t>TIGER 미국배당다우존스타겟커버드콜1호</t>
         </is>
       </c>
       <c r="B60" s="37" t="inlineStr">
         <is>
-          <t>474220</t>
+          <t>458750</t>
         </is>
       </c>
       <c r="C60" s="37" t="inlineStr">
@@ -5208,15 +5304,35 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D60" s="38" t="n"/>
-      <c r="E60" s="38" t="n"/>
-      <c r="F60" s="38" t="n"/>
-      <c r="G60" s="39" t="n"/>
-      <c r="H60" s="39" t="n"/>
-      <c r="I60" s="39" t="n"/>
-      <c r="J60" s="39" t="n"/>
-      <c r="K60" s="38" t="n"/>
-      <c r="L60" s="37" t="n"/>
+      <c r="D60" s="38" t="n">
+        <v>12835</v>
+      </c>
+      <c r="E60" s="38" t="n">
+        <v>66690000000</v>
+      </c>
+      <c r="F60" s="38" t="n">
+        <v>411188318</v>
+      </c>
+      <c r="G60" s="39" t="n">
+        <v>0.005842000000000001</v>
+      </c>
+      <c r="H60" s="39" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="I60" s="39" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="J60" s="39" t="n">
+        <v>0.059758</v>
+      </c>
+      <c r="K60" s="38" t="n">
+        <v>39</v>
+      </c>
+      <c r="L60" s="37" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
       <c r="M60" s="37" t="inlineStr">
         <is>
           <t>제외</t>
@@ -5224,10 +5340,14 @@
       </c>
       <c r="N60" s="37" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
-        </is>
-      </c>
-      <c r="O60" s="37" t="inlineStr"/>
+          <t>60일 거래대금 4.1억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O60" s="37" t="inlineStr">
+        <is>
+          <t>Dow Jones U.S. Dividend 100 3% Premium Covered Call Index</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="37" t="inlineStr">
@@ -5246,13 +5366,13 @@
         </is>
       </c>
       <c r="D61" s="38" t="n">
-        <v>10845</v>
+        <v>10855</v>
       </c>
       <c r="E61" s="38" t="n">
         <v>818900000000</v>
       </c>
       <c r="F61" s="38" t="n">
-        <v>33032465908</v>
+        <v>33035361948</v>
       </c>
       <c r="G61" s="39" t="n">
         <v>0.005719999999999999</v>
@@ -5305,13 +5425,13 @@
         </is>
       </c>
       <c r="D62" s="38" t="n">
-        <v>19890</v>
+        <v>19895</v>
       </c>
       <c r="E62" s="38" t="n">
         <v>2396790000000</v>
       </c>
       <c r="F62" s="38" t="n">
-        <v>103354864477</v>
+        <v>103364579939</v>
       </c>
       <c r="G62" s="39" t="n">
         <v>0.006008</v>
@@ -5323,7 +5443,7 @@
         <v>0.0197</v>
       </c>
       <c r="J62" s="39" t="n">
-        <v>0.220463</v>
+        <v>0.220407</v>
       </c>
       <c r="K62" s="38" t="n">
         <v>33</v>
@@ -5427,13 +5547,13 @@
         </is>
       </c>
       <c r="D64" s="38" t="n">
-        <v>10985</v>
+        <v>11005</v>
       </c>
       <c r="E64" s="38" t="n">
         <v>18742500000</v>
       </c>
       <c r="F64" s="38" t="n">
-        <v>267092197</v>
+        <v>267114085</v>
       </c>
       <c r="G64" s="39" t="n">
         <v>0.004345</v>
@@ -5555,14 +5675,14 @@
     <row r="12" ht="19" customHeight="1">
       <c r="B12" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 채택 17종목 — 유동성·변동성 기준을 통과한 월배당 커버드콜 ETF</t>
+          <t xml:space="preserve">     · 채택 21종목 — 유동성·변동성 기준을 통과한 월배당 커버드콜 ETF</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="B13" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 제외 44종목 — 사유는 [ETF데이터] 장 맨 오른쪽 칸에 적혀 있습니다.</t>
+          <t xml:space="preserve">     · 제외 40종목 — 사유는 [ETF데이터] 장 맨 오른쪽 칸에 적혀 있습니다.</t>
         </is>
       </c>
     </row>

--- a/고객제안서_월배당ETF.xlsx
+++ b/고객제안서_월배당ETF.xlsx
@@ -12,9 +12,9 @@
     <sheet name="사용법" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="채택종목">'ETF데이터'!$A$4:$A$25</definedName>
+    <definedName name="채택종목">'ETF데이터'!$A$4:$A$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'제안서'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'제안서'!$A$1:$H$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'제안서'!$A$1:$H$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="K2" s="3">
-        <f>IFERROR(MATCH($C$9,'ETF데이터'!$A$4:$A$25,0),0)</f>
+        <f>IFERROR(MATCH($C$9,'ETF데이터'!$A$4:$A$14,0),0)</f>
         <v/>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
+          <t>KODEX 미국배당커버드콜액티브</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="C14" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$B$4:$B$25,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$B$4:$B$14,$K$2))</f>
         <v/>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F14" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$G$4:$G$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$G$4:$G$14,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C15" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$C$4:$C$25,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$C$4:$C$14,$K$2))</f>
         <v/>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="F15" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$H$4:$H$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$H$4:$H$14,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C16" s="14">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$D$4:$D$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$D$4:$D$14,$K$2))</f>
         <v/>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="F16" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$I$4:$I$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$I$4:$I$14,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C17" s="15">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$E$4:$E$25,$K$2)/100000000)</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$E$4:$E$14,$K$2)/100000000)</f>
         <v/>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="F17" s="13">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$J$4:$J$25,$K$2))</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$J$4:$J$14,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C18" s="15">
-        <f>IF($K$2=0,0,INDEX('ETF데이터'!$F$4:$F$25,$K$2)/100000000)</f>
+        <f>IF($K$2=0,0,INDEX('ETF데이터'!$F$4:$F$14,$K$2)/100000000)</f>
         <v/>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="F18" s="12">
-        <f>IF($K$2=0,"",INDEX('ETF데이터'!$O$4:$O$25,$K$2))</f>
+        <f>IF($K$2=0,"",INDEX('ETF데이터'!$O$4:$O$14,$K$2))</f>
         <v/>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>5. 채택 ETF 비교 (1억원 투자 기준) — 연 분배율 상위 12종목 / 전체 22종목</t>
+          <t>5. 채택 ETF 비교 (1억원 투자 기준)</t>
         </is>
       </c>
     </row>
@@ -1736,120 +1736,90 @@
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="29">
-        <f>'ETF데이터'!$A$15</f>
-        <v/>
-      </c>
-      <c r="C58" s="24">
-        <f>'ETF데이터'!$D$15</f>
-        <v/>
-      </c>
-      <c r="D58" s="30">
-        <f>'ETF데이터'!$J$15</f>
-        <v/>
-      </c>
-      <c r="E58" s="31">
-        <f>'ETF데이터'!$J$15/12</f>
-        <v/>
-      </c>
-      <c r="F58" s="24">
-        <f>IF($C58=0,0,ROUNDDOWN(100000000/$C58,0)*$C58*$D58/12)</f>
-        <v/>
-      </c>
-      <c r="G58" s="24">
-        <f>$F58*(1-$C$10)</f>
-        <v/>
-      </c>
-      <c r="H58" s="30">
-        <f>'ETF데이터'!$H$15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>※ 유동성·변동성 기준을 통과한 종목만 실었습니다. 제외 종목과 사유는 [ETF데이터] 장에 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="4" customHeight="1">
-      <c r="A62" s="5" t="n"/>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="n"/>
-    </row>
-    <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="61" ht="4" customHeight="1">
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>6. 유의사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 이 자료는 투자 권유가 아니라 참고 자료입니다. 최종 투자 판단과 그 결과는 투자자 본인에게 귀속됩니다.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 이 자료는 투자 권유가 아니라 참고 자료입니다. 최종 투자 판단과 그 결과는 투자자 본인에게 귀속됩니다.</t>
+          <t xml:space="preserve">  · ETF 는 예금자보호법의 보호를 받지 않으며, 원금 손실이 발생할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  · ETF 는 예금자보호법의 보호를 받지 않으며, 원금 손실이 발생할 수 있습니다.</t>
+      <c r="A65" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 분배금은 확정되지 않습니다. 커버드콜 ETF 의 분배 재원은 옵션 프리미엄이므로, 시장 변동성이 낮아지면 분배금도 함께 줄어듭니다.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 분배금은 확정되지 않습니다. 커버드콜 ETF 의 분배 재원은 옵션 프리미엄이므로, 시장 변동성이 낮아지면 분배금도 함께 줄어듭니다.</t>
+          <t xml:space="preserve">  · 분배금의 일부가 원금에서 지급될 수 있습니다(자본 환급). 이 경우 기준가가 그만큼 낮아집니다.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="17" customHeight="1">
       <c r="A67" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 분배금의 일부가 원금에서 지급될 수 있습니다(자본 환급). 이 경우 기준가가 그만큼 낮아집니다.</t>
+          <t xml:space="preserve">  · 표시된 연 분배율은 최근 12개월 실제 분배금 합계를 현재가로 나눈 값(사후 수치)이며, 앞으로의 수익률을 보장하지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 표시된 연 분배율은 최근 12개월 실제 분배금 합계를 현재가로 나눈 값(사후 수치)이며, 앞으로의 수익률을 보장하지 않습니다.</t>
+          <t xml:space="preserve">  · 세율은 국내 상장 ETF 분배금 기준 15.4%(배당소득세 14% + 지방소득세 1.4%)를 적용했습니다. 금융소득종합과세 대상자는 실효세율이 달라집니다.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="17" customHeight="1">
       <c r="A69" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 세율은 국내 상장 ETF 분배금 기준 15.4%(배당소득세 14% + 지방소득세 1.4%)를 적용했습니다. 금융소득종합과세 대상자는 실효세율이 달라집니다.</t>
+          <t xml:space="preserve">  · 매매수수료·거래세·환율 변동은 반영하지 않았습니다. 총보수는 분배율에 이미 반영되어 있습니다(기준가 차감).</t>
         </is>
       </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="A70" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 매매수수료·거래세·환율 변동은 반영하지 않았습니다. 총보수는 분배율에 이미 반영되어 있습니다(기준가 차감).</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="33" t="inlineStr">
-        <is>
           <t xml:space="preserve">  · 수량은 정수 매수를 가정해 내림 처리했습니다. 남는 금액은 '미투자 잔액'에 표시됩니다.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T04:06:28.111Z · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 연환산 변동성 25% 이하, 분배 이력 12개월 이상</t>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T07:02:43.909Z · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 연환산 변동성 35% 이하, 분배 이력 12개월 이상</t>
         </is>
       </c>
     </row>
@@ -1860,10 +1830,10 @@
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A69:H69"/>
     <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A63:H63"/>
     <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A72:H72"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="A66:H66"/>
     <mergeCell ref="A1:H1"/>
@@ -1992,46 +1962,46 @@
     <row r="4">
       <c r="A4" s="35" t="inlineStr">
         <is>
-          <t>SOL 팔란티어커버드콜OTM채권혼합</t>
+          <t>ACE 미국빅테크7+데일리타겟커버드콜(합성)</t>
         </is>
       </c>
       <c r="B4" s="35" t="inlineStr">
         <is>
-          <t>0040Y0</t>
+          <t>480020</t>
         </is>
       </c>
       <c r="C4" s="35" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D4" s="36" t="n">
-        <v>7925</v>
+        <v>9955</v>
       </c>
       <c r="E4" s="36" t="n">
-        <v>357246500000</v>
+        <v>177926000000</v>
       </c>
       <c r="F4" s="36" t="n">
-        <v>2993143433</v>
+        <v>2887978198</v>
       </c>
       <c r="G4" s="37" t="n">
-        <v>0.007532</v>
+        <v>0.005384</v>
       </c>
       <c r="H4" s="37" t="n">
-        <v>0.1637</v>
+        <v>0.2139</v>
       </c>
       <c r="I4" s="37" t="n">
-        <v>0.0194</v>
+        <v>0.0297</v>
       </c>
       <c r="J4" s="37" t="n">
-        <v>0.282019</v>
+        <v>0.266198</v>
       </c>
       <c r="K4" s="36" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="L4" s="35" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M4" s="35" t="inlineStr">
@@ -2042,53 +2012,53 @@
       <c r="N4" s="35" t="inlineStr"/>
       <c r="O4" s="35" t="inlineStr">
         <is>
-          <t>KEDI Palantir Covered Call OTM Treasury Balanced Index NTR</t>
+          <t>Bloomberg US Big Tech Top 7 Plus Premium(QQQ) Decrement 15%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>ACE 미국빅테크7+데일리타겟커버드콜(합성)</t>
+          <t>PLUS 고배당주위클리커버드콜</t>
         </is>
       </c>
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>480020</t>
+          <t>489030</t>
         </is>
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="D5" s="36" t="n">
-        <v>9890</v>
+        <v>6455</v>
       </c>
       <c r="E5" s="36" t="n">
-        <v>177031000000</v>
+        <v>302036000000</v>
       </c>
       <c r="F5" s="36" t="n">
-        <v>2871996431</v>
+        <v>4313861174</v>
       </c>
       <c r="G5" s="37" t="n">
-        <v>0.005384</v>
+        <v>0.008243</v>
       </c>
       <c r="H5" s="37" t="n">
-        <v>0.2139</v>
+        <v>0.307</v>
       </c>
       <c r="I5" s="37" t="n">
-        <v>0.0297</v>
+        <v>0.0148</v>
       </c>
       <c r="J5" s="37" t="n">
-        <v>0.267947</v>
+        <v>0.235167</v>
       </c>
       <c r="K5" s="36" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L5" s="35" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M5" s="35" t="inlineStr">
@@ -2099,53 +2069,53 @@
       <c r="N5" s="35" t="inlineStr"/>
       <c r="O5" s="35" t="inlineStr">
         <is>
-          <t>Bloomberg US Big Tech Top 7 Plus Premium(QQQ) Decrement 15%</t>
+          <t>코스피 고배당 위클리 콜매도 ATM 지수</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>SOL 팔란티어미국채커버드콜혼합</t>
+          <t>ACE 미국500데일리타겟커버드콜(합성)</t>
         </is>
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>0040X0</t>
+          <t>480030</t>
         </is>
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D6" s="36" t="n">
-        <v>9177</v>
+        <v>9540</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>169371000000</v>
+        <v>160188000000</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>1691907481</v>
+        <v>1356019751</v>
       </c>
       <c r="G6" s="37" t="n">
-        <v>0.007991</v>
+        <v>0.005391</v>
       </c>
       <c r="H6" s="37" t="n">
-        <v>0.2285</v>
+        <v>0.1503</v>
       </c>
       <c r="I6" s="37" t="n">
-        <v>0.0148</v>
+        <v>0.0199</v>
       </c>
       <c r="J6" s="37" t="n">
-        <v>0.250191</v>
+        <v>0.203669</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="L6" s="35" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M6" s="35" t="inlineStr">
@@ -2156,53 +2126,53 @@
       <c r="N6" s="35" t="inlineStr"/>
       <c r="O6" s="35" t="inlineStr">
         <is>
-          <t>KEDI Palantir U.S. Treasury Covered Call Balanced Index NTR</t>
+          <t>Bloomberg US 500 Large Cap Premium(SPY) Decrement 15% Distri</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>KODEX 미국나스닥100데일리커버드콜OTM</t>
+          <t>PLUS 고배당주위클리고정커버드콜</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>494300</t>
+          <t>0018C0</t>
         </is>
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>8785</v>
+        <v>10565</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>1005004000000</v>
+        <v>80294000000</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>13542928908</v>
+        <v>1038488732</v>
       </c>
       <c r="G7" s="37" t="n">
-        <v>0.005108000000000001</v>
+        <v>0.005958</v>
       </c>
       <c r="H7" s="37" t="n">
-        <v>0.1938</v>
+        <v>0.2668</v>
       </c>
       <c r="I7" s="37" t="n">
-        <v>0.0166</v>
+        <v>0.0124</v>
       </c>
       <c r="J7" s="37" t="n">
-        <v>0.229937</v>
+        <v>0.169143</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L7" s="35" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M7" s="35" t="inlineStr">
@@ -2213,49 +2183,49 @@
       <c r="N7" s="35" t="inlineStr"/>
       <c r="O7" s="35" t="inlineStr">
         <is>
-          <t>Nasdaq-100 Daily Covered Call 101 Index TR</t>
+          <t>코스피 고배당 위클리 고정 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>RISE 미국테크100데일리고정커버드콜</t>
+          <t>KODEX 테슬라커버드콜채권혼합액티브</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>491620</t>
+          <t>475080</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D8" s="36" t="n">
-        <v>10240</v>
+        <v>7835</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>561664000000</v>
+        <v>285585750000</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>7570779706</v>
+        <v>1460412580</v>
       </c>
       <c r="G8" s="37" t="n">
-        <v>0.005748</v>
+        <v>0.005215</v>
       </c>
       <c r="H8" s="37" t="n">
-        <v>0.2021</v>
+        <v>0.1243</v>
       </c>
       <c r="I8" s="37" t="n">
-        <v>0.0166</v>
+        <v>0.0125</v>
       </c>
       <c r="J8" s="37" t="n">
-        <v>0.219727</v>
+        <v>0.164135</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L8" s="35" t="inlineStr">
         <is>
@@ -2270,53 +2240,53 @@
       <c r="N8" s="35" t="inlineStr"/>
       <c r="O8" s="35" t="inlineStr">
         <is>
-          <t>KEDI U.S. Tech100 90% Participation + Daily Options Premium</t>
+          <t>KEDI Tesla Income Premium Balanced Index</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>ACE 미국500데일리타겟커버드콜(합성)</t>
+          <t>KODEX 미국S&amp;P500데일리커버드콜OTM</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>480030</t>
+          <t>0005A0</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>9545</v>
+        <v>9220</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>160440000000</v>
+        <v>198445000000</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>1353502477</v>
+        <v>1984616936</v>
       </c>
       <c r="G9" s="37" t="n">
-        <v>0.005391</v>
+        <v>0.005639999999999999</v>
       </c>
       <c r="H9" s="37" t="n">
-        <v>0.1502</v>
+        <v>0.1474</v>
       </c>
       <c r="I9" s="37" t="n">
-        <v>0.0199</v>
+        <v>0.0124</v>
       </c>
       <c r="J9" s="37" t="n">
-        <v>0.203562</v>
+        <v>0.160629</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="L9" s="35" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M9" s="35" t="inlineStr">
@@ -2327,53 +2297,53 @@
       <c r="N9" s="35" t="inlineStr"/>
       <c r="O9" s="35" t="inlineStr">
         <is>
-          <t>Bloomberg US 500 Large Cap Premium(SPY) Decrement 15% Distri</t>
+          <t>S&amp;P500 Covered Call 1% OTM Daily Index(TR)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>RISE 미국배당100데일리고정커버드콜</t>
+          <t>KODEX 미국AI테크TOP10타겟커버드콜</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>490600</t>
+          <t>483280</t>
         </is>
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D10" s="36" t="n">
-        <v>8865</v>
+        <v>11535</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>168878250000</v>
+        <v>452736000000</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>2335780282</v>
+        <v>2935918498</v>
       </c>
       <c r="G10" s="37" t="n">
-        <v>0.005953000000000001</v>
+        <v>0.005830999999999999</v>
       </c>
       <c r="H10" s="37" t="n">
-        <v>0.1459</v>
+        <v>0.2452</v>
       </c>
       <c r="I10" s="37" t="n">
-        <v>0.01</v>
+        <v>0.0123</v>
       </c>
       <c r="J10" s="37" t="n">
-        <v>0.164354</v>
+        <v>0.159515</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L10" s="35" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M10" s="35" t="inlineStr">
@@ -2384,19 +2354,19 @@
       <c r="N10" s="35" t="inlineStr"/>
       <c r="O10" s="35" t="inlineStr">
         <is>
-          <t>KEDI U.S. Dividend100 90% Participation + Daily Options Prem</t>
+          <t>KEDI US AI Tech Top 10+15% Premium Index</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>KODEX 테슬라커버드콜채권혼합액티브</t>
+          <t>KODEX 금융고배당TOP10타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>475080</t>
+          <t>498410</t>
         </is>
       </c>
       <c r="C11" s="35" t="inlineStr">
@@ -2405,28 +2375,28 @@
         </is>
       </c>
       <c r="D11" s="36" t="n">
-        <v>7835</v>
+        <v>11935</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>285585750000</v>
+        <v>837760000000</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>1454675401</v>
+        <v>23026137251</v>
       </c>
       <c r="G11" s="37" t="n">
-        <v>0.005215</v>
+        <v>0.006697</v>
       </c>
       <c r="H11" s="37" t="n">
-        <v>0.1243</v>
+        <v>0.3275</v>
       </c>
       <c r="I11" s="37" t="n">
-        <v>0.0125</v>
+        <v>0.0121</v>
       </c>
       <c r="J11" s="37" t="n">
-        <v>0.164135</v>
+        <v>0.157687</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="L11" s="35" t="inlineStr">
         <is>
@@ -2441,49 +2411,49 @@
       <c r="N11" s="35" t="inlineStr"/>
       <c r="O11" s="35" t="inlineStr">
         <is>
-          <t>KEDI Tesla Income Premium Balanced Index</t>
+          <t>코스피 200 금융 고배당 TOP 10 타겟 15% 분배 위클리 커버드콜</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>TIGER 미국AI빅테크10타겟데일리커버드콜</t>
+          <t>KODEX 미국30년국채타겟커버드콜(합성 H)</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>493810</t>
+          <t>481060</t>
         </is>
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D12" s="36" t="n">
-        <v>11105</v>
+        <v>7250</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>240978500000</v>
+        <v>740576850000</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>1834374517</v>
+        <v>4099200456</v>
       </c>
       <c r="G12" s="37" t="n">
-        <v>0.004813</v>
+        <v>0.003244</v>
       </c>
       <c r="H12" s="37" t="n">
-        <v>0.2183</v>
+        <v>0.0842</v>
       </c>
       <c r="I12" s="37" t="n">
-        <v>0.0124</v>
+        <v>0.0101</v>
       </c>
       <c r="J12" s="37" t="n">
-        <v>0.16353</v>
+        <v>0.132966</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L12" s="35" t="inlineStr">
         <is>
@@ -2498,19 +2468,19 @@
       <c r="N12" s="35" t="inlineStr"/>
       <c r="O12" s="35" t="inlineStr">
         <is>
-          <t>KEDI US AI Big Tech 10+15% Daily Premium Index TR</t>
+          <t>Bloomberg U.S. Treasury 20+ Year + 12% Premium (TLT) Covered</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>KODEX 미국S&amp;P500데일리커버드콜OTM</t>
+          <t>KODEX 미국배당다우존스타겟커버드콜</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>0005A0</t>
+          <t>483290</t>
         </is>
       </c>
       <c r="C13" s="35" t="inlineStr">
@@ -2519,28 +2489,28 @@
         </is>
       </c>
       <c r="D13" s="36" t="n">
-        <v>9240</v>
+        <v>10220</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>198552500000</v>
+        <v>177828000000</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>1975873597</v>
+        <v>2279533322</v>
       </c>
       <c r="G13" s="37" t="n">
-        <v>0.005639999999999999</v>
+        <v>0.005798</v>
       </c>
       <c r="H13" s="37" t="n">
-        <v>0.1473</v>
+        <v>0.1572</v>
       </c>
       <c r="I13" s="37" t="n">
-        <v>0.0124</v>
+        <v>0.0098</v>
       </c>
       <c r="J13" s="37" t="n">
-        <v>0.160281</v>
+        <v>0.121918</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L13" s="35" t="inlineStr">
         <is>
@@ -2555,53 +2525,53 @@
       <c r="N13" s="35" t="inlineStr"/>
       <c r="O13" s="35" t="inlineStr">
         <is>
-          <t>S&amp;P500 Covered Call 1% OTM Daily Index(TR)</t>
+          <t>Dow Jones US Dividend 100 10% Premium Covered Call Index(PR)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
+          <t>KODEX 미국배당커버드콜액티브</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>486290</t>
+          <t>441640</t>
         </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D14" s="36" t="n">
-        <v>10240</v>
+        <v>12340</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>2440192000000</v>
+        <v>1703610000000</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>29770029696</v>
+        <v>12419181539</v>
       </c>
       <c r="G14" s="37" t="n">
-        <v>0.004563</v>
+        <v>0.003631</v>
       </c>
       <c r="H14" s="37" t="n">
-        <v>0.2068</v>
+        <v>0.1234</v>
       </c>
       <c r="I14" s="37" t="n">
-        <v>0.0124</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="J14" s="37" t="n">
-        <v>0.159961</v>
+        <v>0.09594799999999999</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="L14" s="35" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M14" s="35" t="inlineStr">
@@ -2612,674 +2582,680 @@
       <c r="N14" s="35" t="inlineStr"/>
       <c r="O14" s="35" t="inlineStr">
         <is>
-          <t>NASDAQ 100 Daily Covered Call Target Premium 15% Index</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>KODEX 미국AI테크TOP10타겟커버드콜</t>
-        </is>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>483280</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
+        <is>
+          <t>ACE 고배당주Plus커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>0199C0</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D15" s="39" t="n">
+        <v>9245</v>
+      </c>
+      <c r="E15" s="39" t="n">
+        <v>138075000000</v>
+      </c>
+      <c r="F15" s="39" t="n">
+        <v>6530265279</v>
+      </c>
+      <c r="G15" s="40" t="n">
+        <v>0.004522</v>
+      </c>
+      <c r="H15" s="40" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="I15" s="40" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="J15" s="40" t="n"/>
+      <c r="K15" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="38" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M15" s="38" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N15" s="38" t="inlineStr">
+        <is>
+          <t>변동성 36.0%(74거래일 기준, 기준 35% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O15" s="38" t="inlineStr">
+        <is>
+          <t>KRX-Akros 고배당주 20 위클리 고정 30% 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>480040</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="n">
+        <v>13340</v>
+      </c>
+      <c r="E16" s="39" t="n">
+        <v>181220000000</v>
+      </c>
+      <c r="F16" s="39" t="n">
+        <v>3495970337</v>
+      </c>
+      <c r="G16" s="40" t="n">
+        <v>0.005406999999999999</v>
+      </c>
+      <c r="H16" s="40" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="I16" s="40" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="J16" s="40" t="n">
+        <v>0.261019</v>
+      </c>
+      <c r="K16" s="39" t="n">
+        <v>29</v>
+      </c>
+      <c r="L16" s="38" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M16" s="38" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N16" s="38" t="inlineStr">
+        <is>
+          <t>변동성 44.1%(1년 기준, 기준 35% 초과)</t>
+        </is>
+      </c>
+      <c r="O16" s="38" t="inlineStr">
+        <is>
+          <t>Bloomberg US Listed Semiconductor Premium(QQQ) Decrement 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="38" t="inlineStr">
+        <is>
+          <t>ACE 미국배당퀄리티+커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>0049M0</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="inlineStr">
+        <is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D17" s="39" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E17" s="39" t="n">
+        <v>78029000000</v>
+      </c>
+      <c r="F17" s="39" t="n">
+        <v>380480872</v>
+      </c>
+      <c r="G17" s="40" t="n">
+        <v>0.005323</v>
+      </c>
+      <c r="H17" s="40" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="I17" s="40" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J17" s="40" t="n">
+        <v>0.075727</v>
+      </c>
+      <c r="K17" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="L17" s="38" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M17" s="38" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N17" s="38" t="inlineStr">
+        <is>
+          <t>60일 거래대금 3.8억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O17" s="38" t="inlineStr">
+        <is>
+          <t>Bloomberg WisdomTree U.S. Quality Dividend &amp; B500 Premium De</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t>FOCUS AI반도체위클리고정커버드콜</t>
+        </is>
+      </c>
+      <c r="B18" s="38" t="inlineStr">
+        <is>
+          <t>0176P0</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>브이아이자산운용</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="n">
+        <v>12930</v>
+      </c>
+      <c r="E18" s="39" t="n">
+        <v>7020750000</v>
+      </c>
+      <c r="F18" s="39" t="n">
+        <v>169157715</v>
+      </c>
+      <c r="G18" s="40" t="n">
+        <v>0.003711</v>
+      </c>
+      <c r="H18" s="40" t="n">
+        <v>0.8009000000000001</v>
+      </c>
+      <c r="I18" s="40" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="J18" s="40" t="n"/>
+      <c r="K18" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" s="38" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M18" s="38" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N18" s="38" t="inlineStr">
+        <is>
+          <t>순자산 70억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 80.1%(111거래일 기준, 기준 35% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O18" s="38" t="inlineStr">
+        <is>
+          <t>AI 반도체 위클리 고정 30% 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>FOCUS 알리바바미국채커버드콜혼합</t>
+        </is>
+      </c>
+      <c r="B19" s="38" t="inlineStr">
+        <is>
+          <t>0073X0</t>
+        </is>
+      </c>
+      <c r="C19" s="38" t="inlineStr">
+        <is>
+          <t>브이아이자산운용</t>
+        </is>
+      </c>
+      <c r="D19" s="39" t="n">
+        <v>8725</v>
+      </c>
+      <c r="E19" s="39" t="n">
+        <v>4793250000</v>
+      </c>
+      <c r="F19" s="39" t="n">
+        <v>30857524</v>
+      </c>
+      <c r="G19" s="40" t="n">
+        <v>0.01601</v>
+      </c>
+      <c r="H19" s="40" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="I19" s="40" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="J19" s="40" t="n">
+        <v>0.147278</v>
+      </c>
+      <c r="K19" s="39" t="n">
+        <v>14</v>
+      </c>
+      <c r="L19" s="38" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M19" s="38" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N19" s="38" t="inlineStr">
+        <is>
+          <t>순자산 48억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O19" s="38" t="inlineStr">
+        <is>
+          <t>KEDI 알리바바 미국채커버드콜혼합지수(TR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t>KIWOOM 코스닥150커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>0198A0</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr">
+        <is>
+          <t>키움투자자산운용</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="n">
+        <v>8485</v>
+      </c>
+      <c r="E20" s="39" t="n">
+        <v>73645500000</v>
+      </c>
+      <c r="F20" s="39" t="n">
+        <v>4958084161</v>
+      </c>
+      <c r="G20" s="40" t="n">
+        <v>0.006657</v>
+      </c>
+      <c r="H20" s="40" t="n"/>
+      <c r="I20" s="40" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="J20" s="40" t="n"/>
+      <c r="K20" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="38" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M20" s="38" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N20" s="38" t="inlineStr">
+        <is>
+          <t>변동성 산출 불가(시세 55일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O20" s="38" t="inlineStr">
+        <is>
+          <t>코스닥 150 위클리 고정 30% 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>KODEX 200커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B21" s="38" t="inlineStr">
+        <is>
+          <t>0219E0</t>
+        </is>
+      </c>
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="D15" s="36" t="n">
-        <v>11515</v>
-      </c>
-      <c r="E15" s="36" t="n">
-        <v>452736000000</v>
-      </c>
-      <c r="F15" s="36" t="n">
-        <v>2928811694</v>
-      </c>
-      <c r="G15" s="37" t="n">
-        <v>0.005830999999999999</v>
-      </c>
-      <c r="H15" s="37" t="n">
-        <v>0.2452</v>
-      </c>
-      <c r="I15" s="37" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="J15" s="37" t="n">
-        <v>0.159792</v>
-      </c>
-      <c r="K15" s="36" t="n">
-        <v>27</v>
-      </c>
-      <c r="L15" s="35" t="inlineStr">
+      <c r="D21" s="39" t="n">
+        <v>8225</v>
+      </c>
+      <c r="E21" s="39" t="n">
+        <v>730027500000</v>
+      </c>
+      <c r="F21" s="39" t="n">
+        <v>46573768045</v>
+      </c>
+      <c r="G21" s="40" t="n">
+        <v>0.005278000000000001</v>
+      </c>
+      <c r="H21" s="40" t="n"/>
+      <c r="I21" s="40" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="J21" s="40" t="n"/>
+      <c r="K21" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" s="38" t="inlineStr">
         <is>
           <t>20260828</t>
         </is>
       </c>
-      <c r="M15" s="35" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N15" s="35" t="inlineStr"/>
-      <c r="O15" s="35" t="inlineStr">
-        <is>
-          <t>KEDI US AI Tech Top 10+15% Premium Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>TIGER 미국30년국채커버드콜액티브(H)</t>
-        </is>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>476550</t>
-        </is>
-      </c>
-      <c r="C16" s="35" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D16" s="36" t="n">
-        <v>6685</v>
-      </c>
-      <c r="E16" s="36" t="n">
-        <v>756407750000</v>
-      </c>
-      <c r="F16" s="36" t="n">
-        <v>7957126632</v>
-      </c>
-      <c r="G16" s="37" t="n">
-        <v>0.007784</v>
-      </c>
-      <c r="H16" s="37" t="n">
-        <v>0.08939999999999999</v>
-      </c>
-      <c r="I16" s="37" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J16" s="37" t="n">
-        <v>0.135527</v>
-      </c>
-      <c r="K16" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="L16" s="35" t="inlineStr">
+      <c r="M21" s="38" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N21" s="38" t="inlineStr">
+        <is>
+          <t>변동성 산출 불가(시세 45일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O21" s="38" t="inlineStr">
+        <is>
+          <t>코스피 200 커버드콜 5% OTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t>KODEX 200타겟위클리커버드콜</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="inlineStr">
+        <is>
+          <t>498400</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D22" s="39" t="n">
+        <v>19820</v>
+      </c>
+      <c r="E22" s="39" t="n">
+        <v>5772998000000</v>
+      </c>
+      <c r="F22" s="39" t="n">
+        <v>176948781501</v>
+      </c>
+      <c r="G22" s="40" t="n">
+        <v>0.005095</v>
+      </c>
+      <c r="H22" s="40" t="n">
+        <v>0.5656</v>
+      </c>
+      <c r="I22" s="40" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="J22" s="40" t="n">
+        <v>0.157719</v>
+      </c>
+      <c r="K22" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="L22" s="38" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="M22" s="38" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N22" s="38" t="inlineStr">
+        <is>
+          <t>변동성 56.6%(1년 기준, 기준 35% 초과)</t>
+        </is>
+      </c>
+      <c r="O22" s="38" t="inlineStr">
+        <is>
+          <t>코스피 200 타겟 15% 위클리 커버드콜 지수</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>KODEX 미국S&amp;P500변동성확대시커버드콜</t>
+        </is>
+      </c>
+      <c r="B23" s="38" t="inlineStr">
+        <is>
+          <t>0089C0</t>
+        </is>
+      </c>
+      <c r="C23" s="38" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D23" s="39" t="n">
+        <v>11170</v>
+      </c>
+      <c r="E23" s="39" t="n">
+        <v>42446000000</v>
+      </c>
+      <c r="F23" s="39" t="n">
+        <v>369289199</v>
+      </c>
+      <c r="G23" s="40" t="n">
+        <v>0.006338</v>
+      </c>
+      <c r="H23" s="40" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="J23" s="40" t="n">
+        <v>0.022292</v>
+      </c>
+      <c r="K23" s="39" t="n">
+        <v>12</v>
+      </c>
+      <c r="L23" s="38" t="inlineStr">
         <is>
           <t>20260828</t>
         </is>
       </c>
-      <c r="M16" s="35" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N16" s="35" t="inlineStr"/>
-      <c r="O16" s="35" t="inlineStr">
-        <is>
-          <t>KEDI US Treasury 30Y Weekly Covered Call 30 Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>KODEX 미국30년국채타겟커버드콜(합성 H)</t>
-        </is>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>481060</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="M23" s="38" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N23" s="38" t="inlineStr">
+        <is>
+          <t>60일 거래대금 3.7억(기준 5억 미만)</t>
+        </is>
+      </c>
+      <c r="O23" s="38" t="inlineStr">
+        <is>
+          <t>Cboe S&amp;P 500 Volatility Contingent Daily Covered Call Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t>KODEX 미국나스닥100데일리커버드콜OTM</t>
+        </is>
+      </c>
+      <c r="B24" s="38" t="inlineStr">
+        <is>
+          <t>494300</t>
+        </is>
+      </c>
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="D17" s="36" t="n">
-        <v>7260</v>
-      </c>
-      <c r="E17" s="36" t="n">
-        <v>741087100000</v>
-      </c>
-      <c r="F17" s="36" t="n">
-        <v>4087021066</v>
-      </c>
-      <c r="G17" s="37" t="n">
-        <v>0.003244</v>
-      </c>
-      <c r="H17" s="37" t="n">
-        <v>0.0842</v>
-      </c>
-      <c r="I17" s="37" t="n">
-        <v>0.0101</v>
-      </c>
-      <c r="J17" s="37" t="n">
-        <v>0.132782</v>
-      </c>
-      <c r="K17" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="L17" s="35" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M17" s="35" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N17" s="35" t="inlineStr"/>
-      <c r="O17" s="35" t="inlineStr">
-        <is>
-          <t>Bloomberg U.S. Treasury 20+ Year + 12% Premium (TLT) Covered</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>SOL 미국30년국채커버드콜(합성)</t>
-        </is>
-      </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>473330</t>
-        </is>
-      </c>
-      <c r="C18" s="35" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="n">
-        <v>7780</v>
-      </c>
-      <c r="E18" s="36" t="n">
-        <v>272864250000</v>
-      </c>
-      <c r="F18" s="36" t="n">
-        <v>2164813847</v>
-      </c>
-      <c r="G18" s="37" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="H18" s="37" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="I18" s="37" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="J18" s="37" t="n">
-        <v>0.13072</v>
-      </c>
-      <c r="K18" s="36" t="n">
-        <v>32</v>
-      </c>
-      <c r="L18" s="35" t="inlineStr">
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="40" t="n"/>
+      <c r="I24" s="40" t="n"/>
+      <c r="J24" s="40" t="n"/>
+      <c r="K24" s="39" t="n"/>
+      <c r="L24" s="38" t="n"/>
+      <c r="M24" s="38" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N24" s="38" t="inlineStr">
+        <is>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
+        </is>
+      </c>
+      <c r="O24" s="38" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t>KODEX 미국성장커버드콜액티브</t>
+        </is>
+      </c>
+      <c r="B25" s="38" t="inlineStr">
+        <is>
+          <t>0144L0</t>
+        </is>
+      </c>
+      <c r="C25" s="38" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="D25" s="39" t="n">
+        <v>9305</v>
+      </c>
+      <c r="E25" s="39" t="n">
+        <v>339632500000</v>
+      </c>
+      <c r="F25" s="39" t="n">
+        <v>2522959781</v>
+      </c>
+      <c r="G25" s="40" t="n">
+        <v>0.006395</v>
+      </c>
+      <c r="H25" s="40" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="I25" s="40" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="J25" s="40" t="n"/>
+      <c r="K25" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" s="38" t="inlineStr">
         <is>
           <t>20260828</t>
         </is>
       </c>
-      <c r="M18" s="35" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N18" s="35" t="inlineStr"/>
-      <c r="O18" s="35" t="inlineStr">
-        <is>
-          <t>KEDI US Treasury 20Y+ 2% OTM BuyWrite Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>TIGER 미국나스닥100커버드콜(합성)</t>
-        </is>
-      </c>
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>441680</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D19" s="36" t="n">
-        <v>10610</v>
-      </c>
-      <c r="E19" s="36" t="n">
-        <v>278911500000</v>
-      </c>
-      <c r="F19" s="36" t="n">
-        <v>960164983</v>
-      </c>
-      <c r="G19" s="37" t="n">
-        <v>0.004923</v>
-      </c>
-      <c r="H19" s="37" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="I19" s="37" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J19" s="37" t="n">
-        <v>0.126296</v>
-      </c>
-      <c r="K19" s="36" t="n">
-        <v>47</v>
-      </c>
-      <c r="L19" s="35" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M19" s="35" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N19" s="35" t="inlineStr"/>
-      <c r="O19" s="35" t="inlineStr">
-        <is>
-          <t>Cboe NASDAQ-100 BuyWrite V2 Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="35" t="inlineStr">
-        <is>
-          <t>KODEX 미국배당다우존스타겟커버드콜</t>
-        </is>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>483290</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D20" s="36" t="n">
-        <v>10225</v>
-      </c>
-      <c r="E20" s="36" t="n">
-        <v>178002000000</v>
-      </c>
-      <c r="F20" s="36" t="n">
-        <v>2277828026</v>
-      </c>
-      <c r="G20" s="37" t="n">
-        <v>0.005798</v>
-      </c>
-      <c r="H20" s="37" t="n">
-        <v>0.1572</v>
-      </c>
-      <c r="I20" s="37" t="n">
-        <v>0.0098</v>
-      </c>
-      <c r="J20" s="37" t="n">
-        <v>0.121858</v>
-      </c>
-      <c r="K20" s="36" t="n">
-        <v>27</v>
-      </c>
-      <c r="L20" s="35" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M20" s="35" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N20" s="35" t="inlineStr"/>
-      <c r="O20" s="35" t="inlineStr">
-        <is>
-          <t>Dow Jones US Dividend 100 10% Premium Covered Call Index(PR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="35" t="inlineStr">
-        <is>
-          <t>TIGER 미국배당다우존스타겟데일리커버드콜</t>
-        </is>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>0008S0</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D21" s="36" t="n">
-        <v>9765</v>
-      </c>
-      <c r="E21" s="36" t="n">
-        <v>314916000000</v>
-      </c>
-      <c r="F21" s="36" t="n">
-        <v>3346512453</v>
-      </c>
-      <c r="G21" s="37" t="n">
-        <v>0.004797</v>
-      </c>
-      <c r="H21" s="37" t="n">
-        <v>0.1437</v>
-      </c>
-      <c r="I21" s="37" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J21" s="37" t="n">
-        <v>0.120533</v>
-      </c>
-      <c r="K21" s="36" t="n">
-        <v>20</v>
-      </c>
-      <c r="L21" s="35" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M21" s="35" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N21" s="35" t="inlineStr"/>
-      <c r="O21" s="35" t="inlineStr">
-        <is>
-          <t>Dow Jones U.S. Dividend 100 10% Daily Premium Covered Call I</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="35" t="inlineStr">
-        <is>
-          <t>TIGER 미국S&amp;P500타겟데일리커버드콜</t>
-        </is>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>482730</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D22" s="36" t="n">
-        <v>11445</v>
-      </c>
-      <c r="E22" s="36" t="n">
-        <v>658375000000</v>
-      </c>
-      <c r="F22" s="36" t="n">
-        <v>4934439134</v>
-      </c>
-      <c r="G22" s="37" t="n">
-        <v>0.004313</v>
-      </c>
-      <c r="H22" s="37" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="I22" s="37" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J22" s="37" t="n">
-        <v>0.107034</v>
-      </c>
-      <c r="K22" s="36" t="n">
-        <v>28</v>
-      </c>
-      <c r="L22" s="35" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M22" s="35" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N22" s="35" t="inlineStr"/>
-      <c r="O22" s="35" t="inlineStr">
-        <is>
-          <t>S&amp;P 500 10% Daily Premium Covered Call Index (USD) PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>TIGER 미국테크TOP10타겟커버드콜</t>
-        </is>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>474220</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D23" s="36" t="n">
-        <v>14697</v>
-      </c>
-      <c r="E23" s="36" t="n">
-        <v>414540000000</v>
-      </c>
-      <c r="F23" s="36" t="n">
-        <v>1732221761</v>
-      </c>
-      <c r="G23" s="37" t="n">
-        <v>0.006686</v>
-      </c>
-      <c r="H23" s="37" t="n">
-        <v>0.1938</v>
-      </c>
-      <c r="I23" s="37" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="J23" s="37" t="n">
-        <v>0.106688</v>
-      </c>
-      <c r="K23" s="36" t="n">
-        <v>32</v>
-      </c>
-      <c r="L23" s="35" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M23" s="35" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N23" s="35" t="inlineStr"/>
-      <c r="O23" s="35" t="inlineStr">
-        <is>
-          <t>Bloomberg U.S. Tech Top10 + 10% Premium Covered Call Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="35" t="inlineStr">
-        <is>
-          <t>TIGER 미국배당다우존스타겟커버드콜2호</t>
-        </is>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>458760</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="D24" s="36" t="n">
-        <v>10885</v>
-      </c>
-      <c r="E24" s="36" t="n">
-        <v>698941000000</v>
-      </c>
-      <c r="F24" s="36" t="n">
-        <v>3403742307</v>
-      </c>
-      <c r="G24" s="37" t="n">
-        <v>0.005643</v>
-      </c>
-      <c r="H24" s="37" t="n">
-        <v>0.1504</v>
-      </c>
-      <c r="I24" s="37" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J24" s="37" t="n">
-        <v>0.099954</v>
-      </c>
-      <c r="K24" s="36" t="n">
-        <v>38</v>
-      </c>
-      <c r="L24" s="35" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M24" s="35" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N24" s="35" t="inlineStr"/>
-      <c r="O24" s="35" t="inlineStr">
-        <is>
-          <t>Dow Jones U.S. Dividend 100 7% Premium Covered Call Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="35" t="inlineStr">
-        <is>
-          <t>KODEX 미국배당커버드콜액티브</t>
-        </is>
-      </c>
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>441640</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D25" s="36" t="n">
-        <v>12340</v>
-      </c>
-      <c r="E25" s="36" t="n">
-        <v>1702920000000</v>
-      </c>
-      <c r="F25" s="36" t="n">
-        <v>12381452811</v>
-      </c>
-      <c r="G25" s="37" t="n">
-        <v>0.003631</v>
-      </c>
-      <c r="H25" s="37" t="n">
-        <v>0.1233</v>
-      </c>
-      <c r="I25" s="37" t="n">
-        <v>0.007800000000000001</v>
-      </c>
-      <c r="J25" s="37" t="n">
-        <v>0.09594799999999999</v>
-      </c>
-      <c r="K25" s="36" t="n">
-        <v>48</v>
-      </c>
-      <c r="L25" s="35" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="M25" s="35" t="inlineStr">
-        <is>
-          <t>채택</t>
-        </is>
-      </c>
-      <c r="N25" s="35" t="inlineStr"/>
-      <c r="O25" s="35" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
+      <c r="M25" s="38" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="N25" s="38" t="inlineStr">
+        <is>
+          <t>분배 이력 8개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O25" s="38" t="inlineStr">
+        <is>
+          <t>나스닥 100</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="38" t="inlineStr">
         <is>
-          <t>ACE 고배당주Plus커버드콜액티브</t>
+          <t>KODEX 반도체타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B26" s="38" t="inlineStr">
         <is>
-          <t>0199C0</t>
+          <t>0190G0</t>
         </is>
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D26" s="39" t="n">
-        <v>9235</v>
+        <v>8895</v>
       </c>
       <c r="E26" s="39" t="n">
-        <v>138450000000</v>
+        <v>170033000000</v>
       </c>
       <c r="F26" s="39" t="n">
-        <v>6510820592</v>
+        <v>8928852417</v>
       </c>
       <c r="G26" s="40" t="n">
-        <v>0.004522</v>
+        <v>0.006131</v>
       </c>
       <c r="H26" s="40" t="n">
-        <v>0.3598</v>
+        <v>0.8591</v>
       </c>
       <c r="I26" s="40" t="n">
-        <v>0.0179</v>
+        <v>0.0074</v>
       </c>
       <c r="J26" s="40" t="n"/>
       <c r="K26" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L26" s="38" t="inlineStr">
         <is>
@@ -3293,40 +3269,58 @@
       </c>
       <c r="N26" s="38" t="inlineStr">
         <is>
-          <t>변동성 36.0%(74거래일 기준, 기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 85.9%(88거래일 기준, 기준 35% 초과), 분배 이력 4개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O26" s="38" t="inlineStr">
         <is>
-          <t>KRX-Akros 고배당주 20 위클리 고정 30% 커버드콜 지수</t>
+          <t>KRX 반도체 타겟 9% 분배 위클리 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="38" t="inlineStr">
         <is>
-          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
+          <t>PLUS 200위클리커버드콜채권혼합</t>
         </is>
       </c>
       <c r="B27" s="38" t="inlineStr">
         <is>
-          <t>480040</t>
+          <t>0203D0</t>
         </is>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D27" s="39" t="n"/>
-      <c r="E27" s="39" t="n"/>
-      <c r="F27" s="39" t="n"/>
-      <c r="G27" s="40" t="n"/>
-      <c r="H27" s="40" t="n"/>
-      <c r="I27" s="40" t="n"/>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D27" s="39" t="n">
+        <v>8840</v>
+      </c>
+      <c r="E27" s="39" t="n">
+        <v>10578000000</v>
+      </c>
+      <c r="F27" s="39" t="n">
+        <v>274234137</v>
+      </c>
+      <c r="G27" s="40" t="n">
+        <v>0.004914</v>
+      </c>
+      <c r="H27" s="40" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="I27" s="40" t="n">
+        <v>0.006999999999999999</v>
+      </c>
       <c r="J27" s="40" t="n"/>
-      <c r="K27" s="39" t="n"/>
-      <c r="L27" s="38" t="n"/>
+      <c r="K27" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="38" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
       <c r="M27" s="38" t="inlineStr">
         <is>
           <t>제외</t>
@@ -3334,38 +3328,56 @@
       </c>
       <c r="N27" s="38" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
-Call log:
-  - )</t>
-        </is>
-      </c>
-      <c r="O27" s="38" t="inlineStr"/>
+          <t>순자산 106억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 38.1%(74거래일 기준, 기준 35% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O27" s="38" t="inlineStr">
+        <is>
+          <t>코스피 200 KTB 혼합 위클리 고정 10% 커버드콜 지수</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="38" t="inlineStr">
         <is>
-          <t>ACE 미국배당퀄리티+커버드콜액티브</t>
+          <t>PLUS 200커버드콜액티브</t>
         </is>
       </c>
       <c r="B28" s="38" t="inlineStr">
         <is>
-          <t>0049M0</t>
+          <t>0210E0</t>
         </is>
       </c>
       <c r="C28" s="38" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D28" s="39" t="n"/>
-      <c r="E28" s="39" t="n"/>
-      <c r="F28" s="39" t="n"/>
-      <c r="G28" s="40" t="n"/>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="n">
+        <v>7180</v>
+      </c>
+      <c r="E28" s="39" t="n">
+        <v>67210000000</v>
+      </c>
+      <c r="F28" s="39" t="n">
+        <v>3122456313</v>
+      </c>
+      <c r="G28" s="40" t="n">
+        <v>0.006020999999999999</v>
+      </c>
       <c r="H28" s="40" t="n"/>
-      <c r="I28" s="40" t="n"/>
+      <c r="I28" s="40" t="n">
+        <v>0.0194</v>
+      </c>
       <c r="J28" s="40" t="n"/>
-      <c r="K28" s="39" t="n"/>
-      <c r="L28" s="38" t="n"/>
+      <c r="K28" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="38" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
       <c r="M28" s="38" t="inlineStr">
         <is>
           <t>제외</t>
@@ -3373,54 +3385,58 @@
       </c>
       <c r="N28" s="38" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: page.goto: net::ERR_EMPTY_RESPONSE at https://www.etfcheck.co.kr/
-Call log:
-  - )</t>
-        </is>
-      </c>
-      <c r="O28" s="38" t="inlineStr"/>
+          <t>변동성 산출 불가(시세 60일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O28" s="38" t="inlineStr">
+        <is>
+          <t>코스피 200 위클리 고정 30% 커버드콜 지수</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="38" t="inlineStr">
         <is>
-          <t>FOCUS AI반도체위클리고정커버드콜</t>
+          <t>PLUS 미국배당증가성장주데일리커버드콜</t>
         </is>
       </c>
       <c r="B29" s="38" t="inlineStr">
         <is>
-          <t>0176P0</t>
+          <t>494420</t>
         </is>
       </c>
       <c r="C29" s="38" t="inlineStr">
         <is>
-          <t>브이아이자산운용</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="D29" s="39" t="n">
-        <v>12700</v>
+        <v>8655</v>
       </c>
       <c r="E29" s="39" t="n">
-        <v>6963000000</v>
+        <v>15534000000</v>
       </c>
       <c r="F29" s="39" t="n">
-        <v>168944462</v>
+        <v>115395757</v>
       </c>
       <c r="G29" s="40" t="n">
-        <v>0.003711</v>
+        <v>0.007707</v>
       </c>
       <c r="H29" s="40" t="n">
-        <v>0.8001</v>
+        <v>0.1439</v>
       </c>
       <c r="I29" s="40" t="n">
-        <v>0.0143</v>
-      </c>
-      <c r="J29" s="40" t="n"/>
+        <v>0.0119</v>
+      </c>
+      <c r="J29" s="40" t="n">
+        <v>0.149509</v>
+      </c>
       <c r="K29" s="39" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="L29" s="38" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M29" s="38" t="inlineStr">
@@ -3430,54 +3446,52 @@
       </c>
       <c r="N29" s="38" t="inlineStr">
         <is>
-          <t>순자산 70억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 80.0%(111거래일 기준, 기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>순자산 155억(기준 300억 미만), 60일 거래대금 1.2억(기준 5억 미만)</t>
         </is>
       </c>
       <c r="O29" s="38" t="inlineStr">
         <is>
-          <t>AI 반도체 위클리 고정 30% 커버드콜 지수</t>
+          <t>Bloomberg U.S. Dividend Growth Partial Covered Call Index</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="38" t="inlineStr">
         <is>
-          <t>FOCUS 알리바바미국채커버드콜혼합</t>
+          <t>PLUS 차이나항셍테크위클리타겟커버드콜</t>
         </is>
       </c>
       <c r="B30" s="38" t="inlineStr">
         <is>
-          <t>0073X0</t>
+          <t>0128D0</t>
         </is>
       </c>
       <c r="C30" s="38" t="inlineStr">
         <is>
-          <t>브이아이자산운용</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="D30" s="39" t="n">
-        <v>8650</v>
+        <v>6465</v>
       </c>
       <c r="E30" s="39" t="n">
-        <v>4757500000</v>
+        <v>4525500000</v>
       </c>
       <c r="F30" s="39" t="n">
-        <v>30634618</v>
+        <v>30068517</v>
       </c>
       <c r="G30" s="40" t="n">
-        <v>0.01601</v>
+        <v>0.01153</v>
       </c>
       <c r="H30" s="40" t="n">
-        <v>0.165</v>
+        <v>0.2723</v>
       </c>
       <c r="I30" s="40" t="n">
-        <v>0.0091</v>
-      </c>
-      <c r="J30" s="40" t="n">
-        <v>0.148555</v>
-      </c>
+        <v>0.0125</v>
+      </c>
+      <c r="J30" s="40" t="n"/>
       <c r="K30" s="39" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L30" s="38" t="inlineStr">
         <is>
@@ -3491,54 +3505,56 @@
       </c>
       <c r="N30" s="38" t="inlineStr">
         <is>
-          <t>순자산 48억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만)</t>
+          <t>순자산 45억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만), 분배 이력 9개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O30" s="38" t="inlineStr">
         <is>
-          <t>KEDI 알리바바 미국채커버드콜혼합지수(TR)</t>
+          <t>HSTECH 15% Target Premium Weekly Covered Call Index</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="38" t="inlineStr">
         <is>
-          <t>KIWOOM 코스닥150커버드콜액티브</t>
+          <t>PLUS 테슬라위클리커버드콜채권혼합</t>
         </is>
       </c>
       <c r="B31" s="38" t="inlineStr">
         <is>
-          <t>0198A0</t>
+          <t>0132K0</t>
         </is>
       </c>
       <c r="C31" s="38" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="D31" s="39" t="n">
-        <v>8420</v>
+        <v>7840</v>
       </c>
       <c r="E31" s="39" t="n">
-        <v>73123500000</v>
+        <v>108584000000</v>
       </c>
       <c r="F31" s="39" t="n">
-        <v>4943042621</v>
+        <v>1319803252</v>
       </c>
       <c r="G31" s="40" t="n">
-        <v>0.006657</v>
-      </c>
-      <c r="H31" s="40" t="n"/>
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="H31" s="40" t="n">
+        <v>0.1302</v>
+      </c>
       <c r="I31" s="40" t="n">
-        <v>0.0243</v>
+        <v>0.02</v>
       </c>
       <c r="J31" s="40" t="n"/>
       <c r="K31" s="39" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L31" s="38" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M31" s="38" t="inlineStr">
@@ -3548,50 +3564,54 @@
       </c>
       <c r="N31" s="38" t="inlineStr">
         <is>
-          <t>변동성 산출 불가(시세 55일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O31" s="38" t="inlineStr">
         <is>
-          <t>코스닥 150 위클리 고정 30% 커버드콜 지수</t>
+          <t>Akros Tesla Weekly Covered Call Treasury Balanced Index</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="38" t="inlineStr">
         <is>
-          <t>KODEX 200커버드콜액티브</t>
+          <t>RISE 200고배당커버드콜ATM</t>
         </is>
       </c>
       <c r="B32" s="38" t="inlineStr">
         <is>
-          <t>0219E0</t>
+          <t>290080</t>
         </is>
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>KB자산운용</t>
         </is>
       </c>
       <c r="D32" s="39" t="n">
-        <v>8200</v>
+        <v>7420</v>
       </c>
       <c r="E32" s="39" t="n">
-        <v>731813500000</v>
+        <v>12614000000</v>
       </c>
       <c r="F32" s="39" t="n">
-        <v>46408641250</v>
+        <v>169365638</v>
       </c>
       <c r="G32" s="40" t="n">
-        <v>0.005278000000000001</v>
-      </c>
-      <c r="H32" s="40" t="n"/>
+        <v>0.00636</v>
+      </c>
+      <c r="H32" s="40" t="n">
+        <v>0.3097</v>
+      </c>
       <c r="I32" s="40" t="n">
-        <v>0.0193</v>
-      </c>
-      <c r="J32" s="40" t="n"/>
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="J32" s="40" t="n">
+        <v>0.106739</v>
+      </c>
       <c r="K32" s="39" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="L32" s="38" t="inlineStr">
         <is>
@@ -3605,58 +3625,54 @@
       </c>
       <c r="N32" s="38" t="inlineStr">
         <is>
-          <t>변동성 산출 불가(시세 45일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>순자산 126억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만)</t>
         </is>
       </c>
       <c r="O32" s="38" t="inlineStr">
         <is>
-          <t>코스피 200 커버드콜 5% OTM</t>
+          <t>코스피 200 고배당 커버드콜 ATM</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="38" t="inlineStr">
         <is>
-          <t>KODEX 200타겟위클리커버드콜</t>
+          <t>RISE 200위클리커버드콜</t>
         </is>
       </c>
       <c r="B33" s="38" t="inlineStr">
         <is>
-          <t>498400</t>
+          <t>475720</t>
         </is>
       </c>
       <c r="C33" s="38" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D33" s="39" t="n">
-        <v>19820</v>
-      </c>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D33" s="39" t="n"/>
       <c r="E33" s="39" t="n">
-        <v>5794943000000</v>
+        <v>825597500000</v>
       </c>
       <c r="F33" s="39" t="n">
-        <v>176503560216</v>
+        <v>12948681823</v>
       </c>
       <c r="G33" s="40" t="n">
-        <v>0.005095</v>
+        <v>0.006305</v>
       </c>
       <c r="H33" s="40" t="n">
-        <v>0.5656</v>
+        <v>0.4328</v>
       </c>
       <c r="I33" s="40" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="J33" s="40" t="n">
-        <v>0.157719</v>
-      </c>
+        <v>0.0185</v>
+      </c>
+      <c r="J33" s="40" t="n"/>
       <c r="K33" s="39" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L33" s="38" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M33" s="38" t="inlineStr">
@@ -3666,54 +3682,50 @@
       </c>
       <c r="N33" s="38" t="inlineStr">
         <is>
-          <t>변동성 56.6%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 변동성 43.3%(1년 기준, 기준 35% 초과), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O33" s="38" t="inlineStr">
         <is>
-          <t>코스피 200 타겟 15% 위클리 커버드콜 지수</t>
+          <t>코스피 200 위클리 커버드콜 ATM 지수</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="38" t="inlineStr">
         <is>
-          <t>KODEX 금융고배당TOP10타겟위클리커버드콜</t>
+          <t>RISE 미국30년국채커버드콜(합성)</t>
         </is>
       </c>
       <c r="B34" s="38" t="inlineStr">
         <is>
-          <t>498410</t>
+          <t>472830</t>
         </is>
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D34" s="39" t="n">
-        <v>11970</v>
-      </c>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D34" s="39" t="n"/>
       <c r="E34" s="39" t="n">
-        <v>842336000000</v>
+        <v>42735000000</v>
       </c>
       <c r="F34" s="39" t="n">
-        <v>22967962191</v>
+        <v>286796708</v>
       </c>
       <c r="G34" s="40" t="n">
-        <v>0.006697</v>
+        <v>0.003419</v>
       </c>
       <c r="H34" s="40" t="n">
-        <v>0.3274</v>
+        <v>0.1409</v>
       </c>
       <c r="I34" s="40" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="J34" s="40" t="n">
-        <v>0.157226</v>
-      </c>
+        <v>0.0067</v>
+      </c>
+      <c r="J34" s="40" t="n"/>
       <c r="K34" s="39" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="L34" s="38" t="inlineStr">
         <is>
@@ -3727,54 +3739,50 @@
       </c>
       <c r="N34" s="38" t="inlineStr">
         <is>
-          <t>변동성 32.7%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 60일 거래대금 2.9억(기준 5억 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O34" s="38" t="inlineStr">
         <is>
-          <t>코스피 200 금융 고배당 TOP 10 타겟 15% 분배 위클리 커버드콜</t>
+          <t>Bloomberg U.S. Treasury 20+ Year(TLT) 2% OTM Covered Call In</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="38" t="inlineStr">
         <is>
-          <t>KODEX 미국S&amp;P500변동성확대시커버드콜</t>
+          <t>RISE 미국AI밸류체인데일리고정커버드콜</t>
         </is>
       </c>
       <c r="B35" s="38" t="inlineStr">
         <is>
-          <t>0089C0</t>
+          <t>490590</t>
         </is>
       </c>
       <c r="C35" s="38" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D35" s="39" t="n">
-        <v>11170</v>
-      </c>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D35" s="39" t="n"/>
       <c r="E35" s="39" t="n">
-        <v>42446000000</v>
+        <v>765240000000</v>
       </c>
       <c r="F35" s="39" t="n">
-        <v>369289199</v>
+        <v>10137842758</v>
       </c>
       <c r="G35" s="40" t="n">
-        <v>0.006338</v>
+        <v>0.00578</v>
       </c>
       <c r="H35" s="40" t="n">
-        <v>0.1398</v>
+        <v>0.3307</v>
       </c>
       <c r="I35" s="40" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="J35" s="40" t="n">
-        <v>0.022292</v>
-      </c>
+        <v>0.0163</v>
+      </c>
+      <c r="J35" s="40" t="n"/>
       <c r="K35" s="39" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L35" s="38" t="inlineStr">
         <is>
@@ -3788,56 +3796,54 @@
       </c>
       <c r="N35" s="38" t="inlineStr">
         <is>
-          <t>60일 거래대금 3.7억(기준 5억 미만)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O35" s="38" t="inlineStr">
         <is>
-          <t>Cboe S&amp;P 500 Volatility Contingent Daily Covered Call Index</t>
+          <t>KEDI U.S. AI Value Chain 90% Participation + Daily Options P</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="38" t="inlineStr">
         <is>
-          <t>KODEX 미국성장커버드콜액티브</t>
+          <t>RISE 미국S&amp;P500데일리고정커버드콜</t>
         </is>
       </c>
       <c r="B36" s="38" t="inlineStr">
         <is>
-          <t>0144L0</t>
+          <t>0138T0</t>
         </is>
       </c>
       <c r="C36" s="38" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D36" s="39" t="n">
-        <v>9300</v>
-      </c>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="n"/>
       <c r="E36" s="39" t="n">
-        <v>339267500000</v>
+        <v>32357500000</v>
       </c>
       <c r="F36" s="39" t="n">
-        <v>2520200215</v>
+        <v>320763852</v>
       </c>
       <c r="G36" s="40" t="n">
-        <v>0.006395</v>
+        <v>0.006153</v>
       </c>
       <c r="H36" s="40" t="n">
-        <v>0.1816</v>
+        <v>0.1559</v>
       </c>
       <c r="I36" s="40" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="J36" s="40" t="n"/>
       <c r="K36" s="39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L36" s="38" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M36" s="38" t="inlineStr">
@@ -3847,56 +3853,54 @@
       </c>
       <c r="N36" s="38" t="inlineStr">
         <is>
-          <t>분배 이력 8개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>현재가 없음, 60일 거래대금 3.2억(기준 5억 미만), 분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O36" s="38" t="inlineStr">
         <is>
-          <t>나스닥 100</t>
+          <t>S&amp;P 500 10% Daily Fixed Covered Call Index (USD) TR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="38" t="inlineStr">
         <is>
-          <t>KODEX 반도체타겟위클리커버드콜</t>
+          <t>RISE 미국배당100데일리고정커버드콜</t>
         </is>
       </c>
       <c r="B37" s="38" t="inlineStr">
         <is>
-          <t>0190G0</t>
+          <t>490600</t>
         </is>
       </c>
       <c r="C37" s="38" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="D37" s="39" t="n">
-        <v>8725</v>
-      </c>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D37" s="39" t="n"/>
       <c r="E37" s="39" t="n">
-        <v>168199500000</v>
+        <v>168783000000</v>
       </c>
       <c r="F37" s="39" t="n">
-        <v>8917345933</v>
+        <v>2341343904</v>
       </c>
       <c r="G37" s="40" t="n">
-        <v>0.006131</v>
+        <v>0.005953000000000001</v>
       </c>
       <c r="H37" s="40" t="n">
-        <v>0.8573999999999999</v>
+        <v>0.1459</v>
       </c>
       <c r="I37" s="40" t="n">
-        <v>0.0074</v>
+        <v>0.01</v>
       </c>
       <c r="J37" s="40" t="n"/>
       <c r="K37" s="39" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="L37" s="38" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M37" s="38" t="inlineStr">
@@ -3906,52 +3910,50 @@
       </c>
       <c r="N37" s="38" t="inlineStr">
         <is>
-          <t>변동성 85.7%(88거래일 기준, 기준 25% 초과), 분배 이력 4개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O37" s="38" t="inlineStr">
         <is>
-          <t>KRX 반도체 타겟 9% 분배 위클리 커버드콜 지수</t>
+          <t>KEDI U.S. Dividend100 90% Participation + Daily Options Prem</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="38" t="inlineStr">
         <is>
-          <t>PLUS 200위클리커버드콜채권혼합</t>
+          <t>RISE 미국테크100데일리고정커버드콜</t>
         </is>
       </c>
       <c r="B38" s="38" t="inlineStr">
         <is>
-          <t>0203D0</t>
+          <t>491620</t>
         </is>
       </c>
       <c r="C38" s="38" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D38" s="39" t="n">
-        <v>8835</v>
-      </c>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D38" s="39" t="n"/>
       <c r="E38" s="39" t="n">
-        <v>10596000000</v>
+        <v>562486750000</v>
       </c>
       <c r="F38" s="39" t="n">
-        <v>273162887</v>
+        <v>7587406824</v>
       </c>
       <c r="G38" s="40" t="n">
-        <v>0.004914</v>
+        <v>0.005748</v>
       </c>
       <c r="H38" s="40" t="n">
-        <v>0.3809</v>
+        <v>0.2021</v>
       </c>
       <c r="I38" s="40" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0166</v>
       </c>
       <c r="J38" s="40" t="n"/>
       <c r="K38" s="39" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="L38" s="38" t="inlineStr">
         <is>
@@ -3965,50 +3967,50 @@
       </c>
       <c r="N38" s="38" t="inlineStr">
         <is>
-          <t>순자산 106억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 38.1%(74거래일 기준, 기준 25% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O38" s="38" t="inlineStr">
         <is>
-          <t>코스피 200 KTB 혼합 위클리 고정 10% 커버드콜 지수</t>
+          <t>KEDI U.S. Tech100 90% Participation + Daily Options Premium</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="38" t="inlineStr">
         <is>
-          <t>PLUS 200커버드콜액티브</t>
+          <t>RISE 차이나테크TOP10위클리타겟커버드콜</t>
         </is>
       </c>
       <c r="B39" s="38" t="inlineStr">
         <is>
-          <t>0210E0</t>
+          <t>0094L0</t>
         </is>
       </c>
       <c r="C39" s="38" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D39" s="39" t="n">
-        <v>7170</v>
-      </c>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D39" s="39" t="n"/>
       <c r="E39" s="39" t="n">
-        <v>67351000000</v>
+        <v>9940000000</v>
       </c>
       <c r="F39" s="39" t="n">
-        <v>3120424458</v>
+        <v>60764279</v>
       </c>
       <c r="G39" s="40" t="n">
-        <v>0.006020999999999999</v>
-      </c>
-      <c r="H39" s="40" t="n"/>
+        <v>0.011533</v>
+      </c>
+      <c r="H39" s="40" t="n">
+        <v>0.2793</v>
+      </c>
       <c r="I39" s="40" t="n">
-        <v>0.0194</v>
+        <v>0.0097</v>
       </c>
       <c r="J39" s="40" t="n"/>
       <c r="K39" s="39" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L39" s="38" t="inlineStr">
         <is>
@@ -4022,54 +4024,50 @@
       </c>
       <c r="N39" s="38" t="inlineStr">
         <is>
-          <t>변동성 산출 불가(시세 60일치뿐), 분배 이력 2개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>현재가 없음, 순자산 99억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O39" s="38" t="inlineStr">
         <is>
-          <t>코스피 200 위클리 고정 30% 커버드콜 지수</t>
+          <t>Bloomberg China Tech Select Top 10 + 12% Target Premium Week</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="38" t="inlineStr">
         <is>
-          <t>PLUS 고배당주위클리고정커버드콜</t>
+          <t>RISE 코리아밸류업위클리고정커버드콜</t>
         </is>
       </c>
       <c r="B40" s="38" t="inlineStr">
         <is>
-          <t>0018C0</t>
+          <t>0094M0</t>
         </is>
       </c>
       <c r="C40" s="38" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D40" s="39" t="n">
-        <v>10580</v>
-      </c>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D40" s="39" t="n"/>
       <c r="E40" s="39" t="n">
-        <v>80370000000</v>
+        <v>344352000000</v>
       </c>
       <c r="F40" s="39" t="n">
-        <v>1033673631</v>
+        <v>9648314170</v>
       </c>
       <c r="G40" s="40" t="n">
-        <v>0.005958</v>
+        <v>0.005637</v>
       </c>
       <c r="H40" s="40" t="n">
-        <v>0.2667</v>
+        <v>0.4584</v>
       </c>
       <c r="I40" s="40" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="J40" s="40" t="n">
-        <v>0.168904</v>
-      </c>
+        <v>0.0299</v>
+      </c>
+      <c r="J40" s="40" t="n"/>
       <c r="K40" s="39" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L40" s="38" t="inlineStr">
         <is>
@@ -4083,54 +4081,46 @@
       </c>
       <c r="N40" s="38" t="inlineStr">
         <is>
-          <t>변동성 26.7%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 변동성 45.8%(1년 기준, 기준 35% 초과), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O40" s="38" t="inlineStr">
         <is>
-          <t>코스피 고배당 위클리 고정 커버드콜 지수</t>
+          <t>코리아 밸류업 위클리 커버드콜 30% 지수</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="38" t="inlineStr">
         <is>
-          <t>PLUS 고배당주위클리커버드콜</t>
+          <t>RISE 코스닥커버드콜액티브</t>
         </is>
       </c>
       <c r="B41" s="38" t="inlineStr">
         <is>
-          <t>489030</t>
+          <t>0223A0</t>
         </is>
       </c>
       <c r="C41" s="38" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D41" s="39" t="n">
-        <v>6455</v>
-      </c>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D41" s="39" t="n"/>
       <c r="E41" s="39" t="n">
-        <v>302739500000</v>
-      </c>
-      <c r="F41" s="39" t="n">
-        <v>4304986410</v>
-      </c>
+        <v>16984000000</v>
+      </c>
+      <c r="F41" s="39" t="n"/>
       <c r="G41" s="40" t="n">
-        <v>0.008243</v>
-      </c>
-      <c r="H41" s="40" t="n">
-        <v>0.3069</v>
-      </c>
+        <v>0.003264</v>
+      </c>
+      <c r="H41" s="40" t="n"/>
       <c r="I41" s="40" t="n">
-        <v>0.0148</v>
-      </c>
-      <c r="J41" s="40" t="n">
-        <v>0.235167</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="J41" s="40" t="n"/>
       <c r="K41" s="39" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L41" s="38" t="inlineStr">
         <is>
@@ -4144,58 +4134,54 @@
       </c>
       <c r="N41" s="38" t="inlineStr">
         <is>
-          <t>변동성 30.7%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 순자산 170억(기준 300억 미만), 거래대금 미확인, 변동성 산출 불가(시세 36일치뿐), 분배 이력 1개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O41" s="38" t="inlineStr">
         <is>
-          <t>코스피 고배당 위클리 콜매도 ATM 지수</t>
+          <t>코스닥 150 타겟 15% 위클리 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="38" t="inlineStr">
         <is>
-          <t>PLUS 미국배당증가성장주데일리커버드콜</t>
+          <t>RISE 테슬라미국채타겟커버드콜혼합(합성)</t>
         </is>
       </c>
       <c r="B42" s="38" t="inlineStr">
         <is>
-          <t>494420</t>
+          <t>0013R0</t>
         </is>
       </c>
       <c r="C42" s="38" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D42" s="39" t="n">
-        <v>8665</v>
-      </c>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="D42" s="39" t="n"/>
       <c r="E42" s="39" t="n">
-        <v>15597000000</v>
+        <v>27558000000</v>
       </c>
       <c r="F42" s="39" t="n">
-        <v>115243016</v>
+        <v>162171621</v>
       </c>
       <c r="G42" s="40" t="n">
-        <v>0.007707</v>
+        <v>0.003495</v>
       </c>
       <c r="H42" s="40" t="n">
-        <v>0.1439</v>
+        <v>0.1854</v>
       </c>
       <c r="I42" s="40" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="J42" s="40" t="n">
-        <v>0.149336</v>
-      </c>
+        <v>0.0129</v>
+      </c>
+      <c r="J42" s="40" t="n"/>
       <c r="K42" s="39" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L42" s="38" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M42" s="38" t="inlineStr">
@@ -4205,52 +4191,50 @@
       </c>
       <c r="N42" s="38" t="inlineStr">
         <is>
-          <t>순자산 156억(기준 300억 미만), 60일 거래대금 1.2억(기준 5억 미만)</t>
+          <t>현재가 없음, 순자산 276억(기준 300억 미만), 60일 거래대금 1.6억(기준 5억 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O42" s="38" t="inlineStr">
         <is>
-          <t>Bloomberg U.S. Dividend Growth Partial Covered Call Index</t>
+          <t>KEDI Tesla U.S. 30Y Treasury 15% Target Premium Balanced Ind</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="38" t="inlineStr">
         <is>
-          <t>PLUS 차이나항셍테크위클리타겟커버드콜</t>
+          <t>SOL 200타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B43" s="38" t="inlineStr">
         <is>
-          <t>0128D0</t>
+          <t>0167B0</t>
         </is>
       </c>
       <c r="C43" s="38" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D43" s="39" t="n">
-        <v>6410</v>
-      </c>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D43" s="39" t="n"/>
       <c r="E43" s="39" t="n">
-        <v>4487000000</v>
+        <v>631624500000</v>
       </c>
       <c r="F43" s="39" t="n">
-        <v>29889499</v>
+        <v>21344709787</v>
       </c>
       <c r="G43" s="40" t="n">
-        <v>0.01153</v>
+        <v>0.00345</v>
       </c>
       <c r="H43" s="40" t="n">
-        <v>0.2722</v>
+        <v>0.6945999999999999</v>
       </c>
       <c r="I43" s="40" t="n">
-        <v>0.0125</v>
+        <v>0.0139</v>
       </c>
       <c r="J43" s="40" t="n"/>
       <c r="K43" s="39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L43" s="38" t="inlineStr">
         <is>
@@ -4264,56 +4248,54 @@
       </c>
       <c r="N43" s="38" t="inlineStr">
         <is>
-          <t>순자산 45억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만), 변동성 27.2%(1년 기준, 기준 25% 초과), 분배 이력 9개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>현재가 없음, 변동성 69.5%(126거래일 기준, 기준 35% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O43" s="38" t="inlineStr">
         <is>
-          <t>HSTECH 15% Target Premium Weekly Covered Call Index</t>
+          <t>코스피 200 타겟 15% 위클리 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="38" t="inlineStr">
         <is>
-          <t>PLUS 테슬라위클리커버드콜채권혼합</t>
+          <t>SOL 국제금커버드콜액티브</t>
         </is>
       </c>
       <c r="B44" s="38" t="inlineStr">
         <is>
-          <t>0132K0</t>
+          <t>0022T0</t>
         </is>
       </c>
       <c r="C44" s="38" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="D44" s="39" t="n">
-        <v>7835</v>
-      </c>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D44" s="39" t="n"/>
       <c r="E44" s="39" t="n">
-        <v>108514750000</v>
+        <v>73302000000</v>
       </c>
       <c r="F44" s="39" t="n">
-        <v>1317376578</v>
+        <v>1009694074</v>
       </c>
       <c r="G44" s="40" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.006737999999999999</v>
       </c>
       <c r="H44" s="40" t="n">
-        <v>0.1302</v>
+        <v>0.2874</v>
       </c>
       <c r="I44" s="40" t="n">
-        <v>0.02</v>
+        <v>0.0033</v>
       </c>
       <c r="J44" s="40" t="n"/>
       <c r="K44" s="39" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L44" s="38" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M44" s="38" t="inlineStr">
@@ -4323,54 +4305,50 @@
       </c>
       <c r="N44" s="38" t="inlineStr">
         <is>
-          <t>분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O44" s="38" t="inlineStr">
         <is>
-          <t>Akros Tesla Weekly Covered Call Treasury Balanced Index</t>
+          <t>KEDI Gold Income Premium Index (Net Total Return)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="38" t="inlineStr">
         <is>
-          <t>RISE 200고배당커버드콜ATM</t>
+          <t>SOL 미국30년국채커버드콜(합성)</t>
         </is>
       </c>
       <c r="B45" s="38" t="inlineStr">
         <is>
-          <t>290080</t>
+          <t>473330</t>
         </is>
       </c>
       <c r="C45" s="38" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D45" s="39" t="n">
-        <v>7355</v>
-      </c>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D45" s="39" t="n"/>
       <c r="E45" s="39" t="n">
-        <v>12495000000</v>
+        <v>272689000000</v>
       </c>
       <c r="F45" s="39" t="n">
-        <v>168643128</v>
+        <v>2177943115</v>
       </c>
       <c r="G45" s="40" t="n">
-        <v>0.00636</v>
+        <v>0.0035</v>
       </c>
       <c r="H45" s="40" t="n">
-        <v>0.3097</v>
+        <v>0.1351</v>
       </c>
       <c r="I45" s="40" t="n">
-        <v>0.008100000000000001</v>
-      </c>
-      <c r="J45" s="40" t="n">
-        <v>0.107682</v>
-      </c>
+        <v>0.0074</v>
+      </c>
+      <c r="J45" s="40" t="n"/>
       <c r="K45" s="39" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="L45" s="38" t="inlineStr">
         <is>
@@ -4384,54 +4362,50 @@
       </c>
       <c r="N45" s="38" t="inlineStr">
         <is>
-          <t>순자산 125억(기준 300억 미만), 60일 거래대금 1.7억(기준 5억 미만), 변동성 31.0%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O45" s="38" t="inlineStr">
         <is>
-          <t>코스피 200 고배당 커버드콜 ATM</t>
+          <t>KEDI US Treasury 20Y+ 2% OTM BuyWrite Index</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="38" t="inlineStr">
         <is>
-          <t>RISE 200위클리커버드콜</t>
+          <t>SOL 미국500타겟데일리커버드콜액티브</t>
         </is>
       </c>
       <c r="B46" s="38" t="inlineStr">
         <is>
-          <t>475720</t>
+          <t>494210</t>
         </is>
       </c>
       <c r="C46" s="38" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D46" s="39" t="n">
-        <v>12420</v>
-      </c>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D46" s="39" t="n"/>
       <c r="E46" s="39" t="n">
-        <v>825597500000</v>
+        <v>7420000000</v>
       </c>
       <c r="F46" s="39" t="n">
-        <v>12917181577</v>
+        <v>65338513</v>
       </c>
       <c r="G46" s="40" t="n">
-        <v>0.006305</v>
+        <v>0.00621</v>
       </c>
       <c r="H46" s="40" t="n">
-        <v>0.4327</v>
+        <v>0.1571</v>
       </c>
       <c r="I46" s="40" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="J46" s="40" t="n">
-        <v>0.198873</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="J46" s="40" t="n"/>
       <c r="K46" s="39" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="L46" s="38" t="inlineStr">
         <is>
@@ -4445,54 +4419,50 @@
       </c>
       <c r="N46" s="38" t="inlineStr">
         <is>
-          <t>변동성 43.3%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 순자산 74억(기준 300억 미만), 60일 거래대금 0.7억(기준 5억 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O46" s="38" t="inlineStr">
         <is>
-          <t>코스피 200 위클리 커버드콜 ATM 지수</t>
+          <t>KEDI U.S. Quality500 + Monthly 1% Premium Index NTR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="38" t="inlineStr">
         <is>
-          <t>RISE 미국30년국채커버드콜(합성)</t>
+          <t>SOL 팔란티어미국채커버드콜혼합</t>
         </is>
       </c>
       <c r="B47" s="38" t="inlineStr">
         <is>
-          <t>472830</t>
+          <t>0040X0</t>
         </is>
       </c>
       <c r="C47" s="38" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D47" s="39" t="n">
-        <v>7700</v>
-      </c>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D47" s="39" t="n"/>
       <c r="E47" s="39" t="n">
-        <v>42735000000</v>
+        <v>169555500000</v>
       </c>
       <c r="F47" s="39" t="n">
-        <v>286133353</v>
+        <v>1695910034</v>
       </c>
       <c r="G47" s="40" t="n">
-        <v>0.003419</v>
+        <v>0.007991</v>
       </c>
       <c r="H47" s="40" t="n">
-        <v>0.1409</v>
+        <v>0.2285</v>
       </c>
       <c r="I47" s="40" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="J47" s="40" t="n">
-        <v>0.115065</v>
-      </c>
+        <v>0.0148</v>
+      </c>
+      <c r="J47" s="40" t="n"/>
       <c r="K47" s="39" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="L47" s="38" t="inlineStr">
         <is>
@@ -4506,54 +4476,50 @@
       </c>
       <c r="N47" s="38" t="inlineStr">
         <is>
-          <t>60일 거래대금 2.9억(기준 5억 미만)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O47" s="38" t="inlineStr">
         <is>
-          <t>Bloomberg U.S. Treasury 20+ Year(TLT) 2% OTM Covered Call In</t>
+          <t>KEDI Palantir U.S. Treasury Covered Call Balanced Index NTR</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="38" t="inlineStr">
         <is>
-          <t>RISE 미국AI밸류체인데일리고정커버드콜</t>
+          <t>SOL 팔란티어커버드콜OTM채권혼합</t>
         </is>
       </c>
       <c r="B48" s="38" t="inlineStr">
         <is>
-          <t>490590</t>
+          <t>0040Y0</t>
         </is>
       </c>
       <c r="C48" s="38" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D48" s="39" t="n">
-        <v>13630</v>
-      </c>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D48" s="39" t="n"/>
       <c r="E48" s="39" t="n">
-        <v>763000000000</v>
+        <v>357021250000</v>
       </c>
       <c r="F48" s="39" t="n">
-        <v>10123807101</v>
+        <v>3002215180</v>
       </c>
       <c r="G48" s="40" t="n">
-        <v>0.00578</v>
+        <v>0.007532</v>
       </c>
       <c r="H48" s="40" t="n">
-        <v>0.3307</v>
+        <v>0.1637</v>
       </c>
       <c r="I48" s="40" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="J48" s="40" t="n">
-        <v>0.212913</v>
-      </c>
+        <v>0.0194</v>
+      </c>
+      <c r="J48" s="40" t="n"/>
       <c r="K48" s="39" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L48" s="38" t="inlineStr">
         <is>
@@ -4567,56 +4533,54 @@
       </c>
       <c r="N48" s="38" t="inlineStr">
         <is>
-          <t>변동성 33.1%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O48" s="38" t="inlineStr">
         <is>
-          <t>KEDI U.S. AI Value Chain 90% Participation + Daily Options P</t>
+          <t>KEDI Palantir Covered Call OTM Treasury Balanced Index NTR</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="38" t="inlineStr">
         <is>
-          <t>RISE 미국S&amp;P500데일리고정커버드콜</t>
+          <t>TIGER 200커버드콜</t>
         </is>
       </c>
       <c r="B49" s="38" t="inlineStr">
         <is>
-          <t>0138T0</t>
+          <t>289480</t>
         </is>
       </c>
       <c r="C49" s="38" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D49" s="39" t="n">
-        <v>9235</v>
-      </c>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D49" s="39" t="n"/>
       <c r="E49" s="39" t="n">
-        <v>32322500000</v>
+        <v>26649000000</v>
       </c>
       <c r="F49" s="39" t="n">
-        <v>320410346</v>
+        <v>429876707</v>
       </c>
       <c r="G49" s="40" t="n">
-        <v>0.006153</v>
+        <v>0.007145</v>
       </c>
       <c r="H49" s="40" t="n">
-        <v>0.1559</v>
+        <v>0.3833</v>
       </c>
       <c r="I49" s="40" t="n">
-        <v>0.008</v>
+        <v>0.0069</v>
       </c>
       <c r="J49" s="40" t="n"/>
       <c r="K49" s="39" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="L49" s="38" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M49" s="38" t="inlineStr">
@@ -4626,54 +4590,50 @@
       </c>
       <c r="N49" s="38" t="inlineStr">
         <is>
-          <t>60일 거래대금 3.2억(기준 5억 미만), 분배 이력 10개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>현재가 없음, 순자산 266억(기준 300억 미만), 60일 거래대금 4.3억(기준 5억 미만), 변동성 38.3%(1년 기준, 기준 35% 초과), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O49" s="38" t="inlineStr">
         <is>
-          <t>S&amp;P 500 10% Daily Fixed Covered Call Index (USD) TR</t>
+          <t>코스피 200 커버드콜 ATM</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="38" t="inlineStr">
         <is>
-          <t>RISE 차이나테크TOP10위클리타겟커버드콜</t>
+          <t>TIGER 200커버드콜OTM</t>
         </is>
       </c>
       <c r="B50" s="38" t="inlineStr">
         <is>
-          <t>0094L0</t>
+          <t>166400</t>
         </is>
       </c>
       <c r="C50" s="38" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D50" s="39" t="n">
-        <v>7075</v>
-      </c>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D50" s="39" t="n"/>
       <c r="E50" s="39" t="n">
-        <v>9905000000</v>
+        <v>12000000000</v>
       </c>
       <c r="F50" s="39" t="n">
-        <v>60754726</v>
+        <v>48259687</v>
       </c>
       <c r="G50" s="40" t="n">
-        <v>0.011533</v>
+        <v>0.006403</v>
       </c>
       <c r="H50" s="40" t="n">
-        <v>0.2793</v>
+        <v>0.4265</v>
       </c>
       <c r="I50" s="40" t="n">
-        <v>0.0097</v>
-      </c>
-      <c r="J50" s="40" t="n">
-        <v>0.154064</v>
-      </c>
+        <v>0.0039</v>
+      </c>
+      <c r="J50" s="40" t="n"/>
       <c r="K50" s="39" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="L50" s="38" t="inlineStr">
         <is>
@@ -4687,52 +4647,48 @@
       </c>
       <c r="N50" s="38" t="inlineStr">
         <is>
-          <t>순자산 99억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만), 변동성 27.9%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 순자산 120억(기준 300억 미만), 60일 거래대금 0.5억(기준 5억 미만), 변동성 42.6%(1년 기준, 기준 35% 초과), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O50" s="38" t="inlineStr">
         <is>
-          <t>Bloomberg China Tech Select Top 10 + 12% Target Premium Week</t>
+          <t>코스피 200 커버드콜 5% OTM</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="38" t="inlineStr">
         <is>
-          <t>RISE 코리아밸류업위클리고정커버드콜</t>
+          <t>TIGER 200타겟위클리커버드콜</t>
         </is>
       </c>
       <c r="B51" s="38" t="inlineStr">
         <is>
-          <t>0094M0</t>
+          <t>0104N0</t>
         </is>
       </c>
       <c r="C51" s="38" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D51" s="39" t="n">
-        <v>16910</v>
-      </c>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D51" s="39" t="n"/>
       <c r="E51" s="39" t="n">
-        <v>344658000000</v>
+        <v>209965500000</v>
       </c>
       <c r="F51" s="39" t="n">
-        <v>9615449973</v>
+        <v>3414033386</v>
       </c>
       <c r="G51" s="40" t="n">
-        <v>0.005637</v>
+        <v>0.003325</v>
       </c>
       <c r="H51" s="40" t="n">
-        <v>0.4584</v>
+        <v>0.5914</v>
       </c>
       <c r="I51" s="40" t="n">
-        <v>0.0299</v>
-      </c>
-      <c r="J51" s="40" t="n">
-        <v>0.248374</v>
-      </c>
+        <v>0.0059</v>
+      </c>
+      <c r="J51" s="40" t="n"/>
       <c r="K51" s="39" t="n">
         <v>12</v>
       </c>
@@ -4748,48 +4704,50 @@
       </c>
       <c r="N51" s="38" t="inlineStr">
         <is>
-          <t>변동성 45.8%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 변동성 59.1%(1년 기준, 기준 35% 초과), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O51" s="38" t="inlineStr">
         <is>
-          <t>코리아 밸류업 위클리 커버드콜 30% 지수</t>
+          <t>코스피 200 타겟 7% 위클리 커버드콜 지수</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="38" t="inlineStr">
         <is>
-          <t>RISE 코스닥커버드콜액티브</t>
+          <t>TIGER 미국30년국채커버드콜액티브(H)</t>
         </is>
       </c>
       <c r="B52" s="38" t="inlineStr">
         <is>
-          <t>0223A0</t>
+          <t>476550</t>
         </is>
       </c>
       <c r="C52" s="38" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D52" s="39" t="n">
-        <v>10460</v>
-      </c>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D52" s="39" t="n"/>
       <c r="E52" s="39" t="n">
-        <v>16712000000</v>
-      </c>
-      <c r="F52" s="39" t="n"/>
+        <v>755842000000</v>
+      </c>
+      <c r="F52" s="39" t="n">
+        <v>7975050426</v>
+      </c>
       <c r="G52" s="40" t="n">
-        <v>0.003264</v>
-      </c>
-      <c r="H52" s="40" t="n"/>
+        <v>0.007784</v>
+      </c>
+      <c r="H52" s="40" t="n">
+        <v>0.08939999999999999</v>
+      </c>
       <c r="I52" s="40" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="J52" s="40" t="n"/>
       <c r="K52" s="39" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L52" s="38" t="inlineStr">
         <is>
@@ -4803,58 +4761,54 @@
       </c>
       <c r="N52" s="38" t="inlineStr">
         <is>
-          <t>순자산 167억(기준 300억 미만), 거래대금 미확인, 변동성 산출 불가(시세 36일치뿐), 분배 이력 1개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O52" s="38" t="inlineStr">
         <is>
-          <t>코스닥 150 타겟 15% 위클리 커버드콜 지수</t>
+          <t>KEDI US Treasury 30Y Weekly Covered Call 30 Index</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="38" t="inlineStr">
         <is>
-          <t>RISE 테슬라미국채타겟커버드콜혼합(합성)</t>
+          <t>TIGER 미국AI빅테크10타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B53" s="38" t="inlineStr">
         <is>
-          <t>0013R0</t>
+          <t>493810</t>
         </is>
       </c>
       <c r="C53" s="38" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="D53" s="39" t="n">
-        <v>7655</v>
-      </c>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D53" s="39" t="n"/>
       <c r="E53" s="39" t="n">
-        <v>27432000000</v>
+        <v>241304000000</v>
       </c>
       <c r="F53" s="39" t="n">
-        <v>162151463</v>
+        <v>1839382960</v>
       </c>
       <c r="G53" s="40" t="n">
-        <v>0.003495</v>
+        <v>0.004813</v>
       </c>
       <c r="H53" s="40" t="n">
-        <v>0.1854</v>
+        <v>0.2183</v>
       </c>
       <c r="I53" s="40" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="J53" s="40" t="n">
-        <v>0.182887</v>
-      </c>
+        <v>0.0124</v>
+      </c>
+      <c r="J53" s="40" t="n"/>
       <c r="K53" s="39" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L53" s="38" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M53" s="38" t="inlineStr">
@@ -4864,56 +4818,54 @@
       </c>
       <c r="N53" s="38" t="inlineStr">
         <is>
-          <t>순자산 274억(기준 300억 미만), 60일 거래대금 1.6억(기준 5억 미만)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O53" s="38" t="inlineStr">
         <is>
-          <t>KEDI Tesla U.S. 30Y Treasury 15% Target Premium Balanced Ind</t>
+          <t>KEDI US AI Big Tech 10+15% Daily Premium Index TR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="38" t="inlineStr">
         <is>
-          <t>SOL 200타겟위클리커버드콜</t>
+          <t>TIGER 미국S&amp;P500타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B54" s="38" t="inlineStr">
         <is>
-          <t>0167B0</t>
+          <t>482730</t>
         </is>
       </c>
       <c r="C54" s="38" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D54" s="39" t="n">
-        <v>11525</v>
-      </c>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D54" s="39" t="n"/>
       <c r="E54" s="39" t="n">
-        <v>631899000000</v>
+        <v>658087500000</v>
       </c>
       <c r="F54" s="39" t="n">
-        <v>21324949707</v>
+        <v>4950416545</v>
       </c>
       <c r="G54" s="40" t="n">
-        <v>0.00345</v>
+        <v>0.004313</v>
       </c>
       <c r="H54" s="40" t="n">
-        <v>0.6945</v>
+        <v>0.148</v>
       </c>
       <c r="I54" s="40" t="n">
-        <v>0.0139</v>
+        <v>0.01</v>
       </c>
       <c r="J54" s="40" t="n"/>
       <c r="K54" s="39" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="L54" s="38" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M54" s="38" t="inlineStr">
@@ -4923,54 +4875,50 @@
       </c>
       <c r="N54" s="38" t="inlineStr">
         <is>
-          <t>변동성 69.4%(126거래일 기준, 기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O54" s="38" t="inlineStr">
         <is>
-          <t>코스피 200 타겟 15% 위클리 커버드콜 지수</t>
+          <t>S&amp;P 500 10% Daily Premium Covered Call Index (USD) PR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="38" t="inlineStr">
         <is>
-          <t>SOL 국제금커버드콜액티브</t>
+          <t>TIGER 미국나스닥100커버드콜(합성)</t>
         </is>
       </c>
       <c r="B55" s="38" t="inlineStr">
         <is>
-          <t>0022T0</t>
+          <t>441680</t>
         </is>
       </c>
       <c r="C55" s="38" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D55" s="39" t="n">
-        <v>12840</v>
-      </c>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D55" s="39" t="n"/>
       <c r="E55" s="39" t="n">
-        <v>73245000000</v>
+        <v>279437500000</v>
       </c>
       <c r="F55" s="39" t="n">
-        <v>1007599918</v>
+        <v>960728975</v>
       </c>
       <c r="G55" s="40" t="n">
-        <v>0.006737999999999999</v>
+        <v>0.004923</v>
       </c>
       <c r="H55" s="40" t="n">
-        <v>0.2874</v>
+        <v>0.146</v>
       </c>
       <c r="I55" s="40" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="J55" s="40" t="n">
-        <v>0.04493800000000001</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="J55" s="40" t="n"/>
       <c r="K55" s="39" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="L55" s="38" t="inlineStr">
         <is>
@@ -4984,54 +4932,50 @@
       </c>
       <c r="N55" s="38" t="inlineStr">
         <is>
-          <t>변동성 28.7%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O55" s="38" t="inlineStr">
         <is>
-          <t>KEDI Gold Income Premium Index (Net Total Return)</t>
+          <t>Cboe NASDAQ-100 BuyWrite V2 Index</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="38" t="inlineStr">
         <is>
-          <t>SOL 미국500타겟데일리커버드콜액티브</t>
+          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B56" s="38" t="inlineStr">
         <is>
-          <t>494210</t>
+          <t>486290</t>
         </is>
       </c>
       <c r="C56" s="38" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="D56" s="39" t="n">
-        <v>10605</v>
-      </c>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="D56" s="39" t="n"/>
       <c r="E56" s="39" t="n">
-        <v>7423500000</v>
+        <v>2439000500000</v>
       </c>
       <c r="F56" s="39" t="n">
-        <v>64446271</v>
+        <v>29892919911</v>
       </c>
       <c r="G56" s="40" t="n">
-        <v>0.00621</v>
+        <v>0.004563</v>
       </c>
       <c r="H56" s="40" t="n">
-        <v>0.1571</v>
+        <v>0.2068</v>
       </c>
       <c r="I56" s="40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J56" s="40" t="n">
-        <v>0.126638</v>
-      </c>
+        <v>0.0124</v>
+      </c>
+      <c r="J56" s="40" t="n"/>
       <c r="K56" s="39" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L56" s="38" t="inlineStr">
         <is>
@@ -5045,24 +4989,24 @@
       </c>
       <c r="N56" s="38" t="inlineStr">
         <is>
-          <t>순자산 74억(기준 300억 미만), 60일 거래대금 0.6억(기준 5억 미만)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O56" s="38" t="inlineStr">
         <is>
-          <t>KEDI U.S. Quality500 + Monthly 1% Premium Index NTR</t>
+          <t>NASDAQ 100 Daily Covered Call Target Premium 15% Index</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="38" t="inlineStr">
         <is>
-          <t>TIGER 200커버드콜</t>
+          <t>TIGER 미국배당다우존스타겟데일리커버드콜</t>
         </is>
       </c>
       <c r="B57" s="38" t="inlineStr">
         <is>
-          <t>289480</t>
+          <t>0008S0</t>
         </is>
       </c>
       <c r="C57" s="38" t="inlineStr">
@@ -5070,33 +5014,29 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D57" s="39" t="n">
-        <v>12695</v>
-      </c>
+      <c r="D57" s="39" t="n"/>
       <c r="E57" s="39" t="n">
-        <v>26607000000</v>
+        <v>314594000000</v>
       </c>
       <c r="F57" s="39" t="n">
-        <v>429039658</v>
+        <v>3361797749</v>
       </c>
       <c r="G57" s="40" t="n">
-        <v>0.007145</v>
+        <v>0.004797</v>
       </c>
       <c r="H57" s="40" t="n">
-        <v>0.3833</v>
+        <v>0.1437</v>
       </c>
       <c r="I57" s="40" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="J57" s="40" t="n">
-        <v>0.07026399999999999</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="J57" s="40" t="n"/>
       <c r="K57" s="39" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="L57" s="38" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M57" s="38" t="inlineStr">
@@ -5106,24 +5046,24 @@
       </c>
       <c r="N57" s="38" t="inlineStr">
         <is>
-          <t>순자산 266억(기준 300억 미만), 60일 거래대금 4.3억(기준 5억 미만), 변동성 38.3%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O57" s="38" t="inlineStr">
         <is>
-          <t>코스피 200 커버드콜 ATM</t>
+          <t>Dow Jones U.S. Dividend 100 10% Daily Premium Covered Call I</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="38" t="inlineStr">
         <is>
-          <t>TIGER 200커버드콜OTM</t>
+          <t>TIGER 미국배당다우존스타겟커버드콜1호</t>
         </is>
       </c>
       <c r="B58" s="38" t="inlineStr">
         <is>
-          <t>166400</t>
+          <t>458750</t>
         </is>
       </c>
       <c r="C58" s="38" t="inlineStr">
@@ -5131,33 +5071,29 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D58" s="39" t="n">
-        <v>24125</v>
-      </c>
+      <c r="D58" s="39" t="n"/>
       <c r="E58" s="39" t="n">
-        <v>12010000000</v>
+        <v>66690000000</v>
       </c>
       <c r="F58" s="39" t="n">
-        <v>48233218</v>
+        <v>411787738</v>
       </c>
       <c r="G58" s="40" t="n">
-        <v>0.006403</v>
+        <v>0.005842000000000001</v>
       </c>
       <c r="H58" s="40" t="n">
-        <v>0.4265</v>
+        <v>0.1448</v>
       </c>
       <c r="I58" s="40" t="n">
-        <v>0.0039</v>
-      </c>
-      <c r="J58" s="40" t="n">
-        <v>0.03942</v>
-      </c>
+        <v>0.0052</v>
+      </c>
+      <c r="J58" s="40" t="n"/>
       <c r="K58" s="39" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="L58" s="38" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M58" s="38" t="inlineStr">
@@ -5167,24 +5103,24 @@
       </c>
       <c r="N58" s="38" t="inlineStr">
         <is>
-          <t>순자산 120억(기준 300억 미만), 60일 거래대금 0.5억(기준 5억 미만), 변동성 42.6%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 60일 거래대금 4.1억(기준 5억 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O58" s="38" t="inlineStr">
         <is>
-          <t>코스피 200 커버드콜 5% OTM</t>
+          <t>Dow Jones U.S. Dividend 100 3% Premium Covered Call Index</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="38" t="inlineStr">
         <is>
-          <t>TIGER 200타겟위클리커버드콜</t>
+          <t>TIGER 미국배당다우존스타겟커버드콜2호</t>
         </is>
       </c>
       <c r="B59" s="38" t="inlineStr">
         <is>
-          <t>0104N0</t>
+          <t>458760</t>
         </is>
       </c>
       <c r="C59" s="38" t="inlineStr">
@@ -5192,33 +5128,29 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D59" s="39" t="n">
-        <v>20400</v>
-      </c>
+      <c r="D59" s="39" t="n"/>
       <c r="E59" s="39" t="n">
-        <v>209914000000</v>
+        <v>699262500000</v>
       </c>
       <c r="F59" s="39" t="n">
-        <v>3412743960</v>
+        <v>3411008086</v>
       </c>
       <c r="G59" s="40" t="n">
-        <v>0.003325</v>
+        <v>0.005643</v>
       </c>
       <c r="H59" s="40" t="n">
-        <v>0.5913</v>
+        <v>0.1504</v>
       </c>
       <c r="I59" s="40" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="J59" s="40" t="n">
-        <v>0.060294</v>
-      </c>
+        <v>0.008</v>
+      </c>
+      <c r="J59" s="40" t="n"/>
       <c r="K59" s="39" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L59" s="38" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M59" s="38" t="inlineStr">
@@ -5228,24 +5160,24 @@
       </c>
       <c r="N59" s="38" t="inlineStr">
         <is>
-          <t>변동성 59.1%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O59" s="38" t="inlineStr">
         <is>
-          <t>코스피 200 타겟 7% 위클리 커버드콜 지수</t>
+          <t>Dow Jones U.S. Dividend 100 7% Premium Covered Call Index</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="38" t="inlineStr">
         <is>
-          <t>TIGER 미국배당다우존스타겟커버드콜1호</t>
+          <t>TIGER 미국테크TOP10타겟커버드콜</t>
         </is>
       </c>
       <c r="B60" s="38" t="inlineStr">
         <is>
-          <t>458750</t>
+          <t>474220</t>
         </is>
       </c>
       <c r="C60" s="38" t="inlineStr">
@@ -5253,29 +5185,25 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D60" s="39" t="n">
-        <v>12825</v>
-      </c>
+      <c r="D60" s="39" t="n"/>
       <c r="E60" s="39" t="n">
-        <v>66742000000</v>
+        <v>414681000000</v>
       </c>
       <c r="F60" s="39" t="n">
-        <v>411188170</v>
+        <v>1737321680</v>
       </c>
       <c r="G60" s="40" t="n">
-        <v>0.005842000000000001</v>
+        <v>0.006686</v>
       </c>
       <c r="H60" s="40" t="n">
-        <v>0.1448</v>
+        <v>0.1938</v>
       </c>
       <c r="I60" s="40" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="J60" s="40" t="n">
-        <v>0.059805</v>
-      </c>
+        <v>0.0083</v>
+      </c>
+      <c r="J60" s="40" t="n"/>
       <c r="K60" s="39" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L60" s="38" t="inlineStr">
         <is>
@@ -5289,12 +5217,12 @@
       </c>
       <c r="N60" s="38" t="inlineStr">
         <is>
-          <t>60일 거래대금 4.1억(기준 5억 미만)</t>
+          <t>현재가 없음, 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O60" s="38" t="inlineStr">
         <is>
-          <t>Dow Jones U.S. Dividend 100 3% Premium Covered Call Index</t>
+          <t>Bloomberg U.S. Tech Top10 + 10% Premium Covered Call Index</t>
         </is>
       </c>
     </row>
@@ -5314,20 +5242,18 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D61" s="39" t="n">
-        <v>10890</v>
-      </c>
+      <c r="D61" s="39" t="n"/>
       <c r="E61" s="39" t="n">
-        <v>826120000000</v>
+        <v>836000000000</v>
       </c>
       <c r="F61" s="39" t="n">
-        <v>33042101961</v>
+        <v>33112219077</v>
       </c>
       <c r="G61" s="40" t="n">
         <v>0.005719999999999999</v>
       </c>
       <c r="H61" s="40" t="n">
-        <v>0.9131</v>
+        <v>0.9140999999999999</v>
       </c>
       <c r="I61" s="40" t="n">
         <v>0.0155</v>
@@ -5348,7 +5274,7 @@
       </c>
       <c r="N61" s="38" t="inlineStr">
         <is>
-          <t>변동성 91.3%(101거래일 기준, 기준 25% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>현재가 없음, 변동성 91.4%(101거래일 기준, 기준 35% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O61" s="38" t="inlineStr">
@@ -5373,27 +5299,23 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D62" s="39" t="n">
-        <v>19940</v>
-      </c>
+      <c r="D62" s="39" t="n"/>
       <c r="E62" s="39" t="n">
-        <v>2410710750000</v>
+        <v>2419789500000</v>
       </c>
       <c r="F62" s="39" t="n">
-        <v>103382002125</v>
+        <v>103652019312</v>
       </c>
       <c r="G62" s="40" t="n">
         <v>0.006008</v>
       </c>
       <c r="H62" s="40" t="n">
-        <v>0.5732</v>
+        <v>0.5733</v>
       </c>
       <c r="I62" s="40" t="n">
         <v>0.0197</v>
       </c>
-      <c r="J62" s="40" t="n">
-        <v>0.21991</v>
-      </c>
+      <c r="J62" s="40" t="n"/>
       <c r="K62" s="39" t="n">
         <v>33</v>
       </c>
@@ -5409,7 +5331,7 @@
       </c>
       <c r="N62" s="38" t="inlineStr">
         <is>
-          <t>변동성 57.3%(1년 기준, 기준 25% 초과)</t>
+          <t>현재가 없음, 변동성 57.3%(1년 기준, 기준 35% 초과), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O62" s="38" t="inlineStr">
@@ -5434,14 +5356,12 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D63" s="39" t="n">
-        <v>8735</v>
-      </c>
+      <c r="D63" s="39" t="n"/>
       <c r="E63" s="39" t="n">
-        <v>60271500000</v>
+        <v>60375000000</v>
       </c>
       <c r="F63" s="39" t="n">
-        <v>357388632</v>
+        <v>357703464</v>
       </c>
       <c r="G63" s="40" t="n">
         <v>0.004741</v>
@@ -5452,9 +5372,7 @@
       <c r="I63" s="40" t="n">
         <v>0.009899999999999999</v>
       </c>
-      <c r="J63" s="40" t="n">
-        <v>0.137722</v>
-      </c>
+      <c r="J63" s="40" t="n"/>
       <c r="K63" s="39" t="n">
         <v>21</v>
       </c>
@@ -5470,7 +5388,7 @@
       </c>
       <c r="N63" s="38" t="inlineStr">
         <is>
-          <t>60일 거래대금 3.6억(기준 5억 미만)</t>
+          <t>현재가 없음, 60일 거래대금 3.6억(기준 5억 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O63" s="38" t="inlineStr">
@@ -5495,14 +5413,12 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D64" s="39" t="n">
-        <v>11010</v>
-      </c>
+      <c r="D64" s="39" t="n"/>
       <c r="E64" s="39" t="n">
-        <v>18717000000</v>
+        <v>18623500000</v>
       </c>
       <c r="F64" s="39" t="n">
-        <v>267133352</v>
+        <v>269902541</v>
       </c>
       <c r="G64" s="40" t="n">
         <v>0.004345</v>
@@ -5529,7 +5445,7 @@
       </c>
       <c r="N64" s="38" t="inlineStr">
         <is>
-          <t>순자산 187억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 변동성 31.1%(1년 기준, 기준 25% 초과), 분배 이력 11개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>현재가 없음, 순자산 186억(기준 300억 미만), 60일 거래대금 2.7억(기준 5억 미만), 분배 이력 11개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O64" s="38" t="inlineStr">
@@ -5624,14 +5540,14 @@
     <row r="12" ht="19" customHeight="1">
       <c r="B12" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 채택 22종목 — 유동성·변동성 기준을 통과한 월배당 커버드콜 ETF</t>
+          <t xml:space="preserve">     · 채택 11종목 — 유동성·변동성 기준을 통과한 월배당 커버드콜 ETF</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="B13" s="42" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 제외 39종목 — 사유는 [ETF데이터] 장 맨 오른쪽 칸에 적혀 있습니다.</t>
+          <t xml:space="preserve">     · 제외 50종목 — 사유는 [ETF데이터] 장 맨 오른쪽 칸에 적혀 있습니다.</t>
         </is>
       </c>
     </row>

--- a/고객제안서_월배당ETF.xlsx
+++ b/고객제안서_월배당ETF.xlsx
@@ -12,9 +12,9 @@
     <sheet name="사용법" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="채택종목">'ETF데이터'!$A$4:$A$75</definedName>
+    <definedName name="채택종목">'ETF데이터'!$A$4:$A$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'제안서'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'제안서'!$A$1:$H$77</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'제안서'!$A$1:$H$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -849,7 +849,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>KODEX CD금리액티브(합성)</t>
+          <t>TIGER 미국배당다우존스</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
@@ -860,15 +860,15 @@
         <v/>
       </c>
       <c r="E15" s="15">
-        <f>IF($K15=0,0,ROUNDDOWN($D15/INDEX('ETF데이터'!$D$4:$D$75,$K15),0))</f>
+        <f>IF($K15=0,0,ROUNDDOWN($D15/INDEX('ETF데이터'!$D$4:$D$76,$K15),0))</f>
         <v/>
       </c>
       <c r="F15" s="14">
-        <f>IF($K15=0,0,$E15*INDEX('ETF데이터'!$D$4:$D$75,$K15))</f>
+        <f>IF($K15=0,0,$E15*INDEX('ETF데이터'!$D$4:$D$76,$K15))</f>
         <v/>
       </c>
       <c r="G15" s="14">
-        <f>IF($K15=0,0,$F15*INDEX('ETF데이터'!$J$4:$J$75,$K15)/12)</f>
+        <f>IF($K15=0,0,$F15*INDEX('ETF데이터'!$J$4:$J$76,$K15)/12)</f>
         <v/>
       </c>
       <c r="H15" s="14">
@@ -888,15 +888,15 @@
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>IF($K16=0,0,ROUNDDOWN($D16/INDEX('ETF데이터'!$D$4:$D$75,$K16),0))</f>
+        <f>IF($K16=0,0,ROUNDDOWN($D16/INDEX('ETF데이터'!$D$4:$D$76,$K16),0))</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>IF($K16=0,0,$E16*INDEX('ETF데이터'!$D$4:$D$75,$K16))</f>
+        <f>IF($K16=0,0,$E16*INDEX('ETF데이터'!$D$4:$D$76,$K16))</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IF($K16=0,0,$F16*INDEX('ETF데이터'!$J$4:$J$75,$K16)/12)</f>
+        <f>IF($K16=0,0,$F16*INDEX('ETF데이터'!$J$4:$J$76,$K16)/12)</f>
         <v/>
       </c>
       <c r="H16" s="16">
@@ -916,15 +916,15 @@
         <v/>
       </c>
       <c r="E17" s="15">
-        <f>IF($K17=0,0,ROUNDDOWN($D17/INDEX('ETF데이터'!$D$4:$D$75,$K17),0))</f>
+        <f>IF($K17=0,0,ROUNDDOWN($D17/INDEX('ETF데이터'!$D$4:$D$76,$K17),0))</f>
         <v/>
       </c>
       <c r="F17" s="14">
-        <f>IF($K17=0,0,$E17*INDEX('ETF데이터'!$D$4:$D$75,$K17))</f>
+        <f>IF($K17=0,0,$E17*INDEX('ETF데이터'!$D$4:$D$76,$K17))</f>
         <v/>
       </c>
       <c r="G17" s="14">
-        <f>IF($K17=0,0,$F17*INDEX('ETF데이터'!$J$4:$J$75,$K17)/12)</f>
+        <f>IF($K17=0,0,$F17*INDEX('ETF데이터'!$J$4:$J$76,$K17)/12)</f>
         <v/>
       </c>
       <c r="H17" s="14">
@@ -944,15 +944,15 @@
         <v/>
       </c>
       <c r="E18" s="17">
-        <f>IF($K18=0,0,ROUNDDOWN($D18/INDEX('ETF데이터'!$D$4:$D$75,$K18),0))</f>
+        <f>IF($K18=0,0,ROUNDDOWN($D18/INDEX('ETF데이터'!$D$4:$D$76,$K18),0))</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>IF($K18=0,0,$E18*INDEX('ETF데이터'!$D$4:$D$75,$K18))</f>
+        <f>IF($K18=0,0,$E18*INDEX('ETF데이터'!$D$4:$D$76,$K18))</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>IF($K18=0,0,$F18*INDEX('ETF데이터'!$J$4:$J$75,$K18)/12)</f>
+        <f>IF($K18=0,0,$F18*INDEX('ETF데이터'!$J$4:$J$76,$K18)/12)</f>
         <v/>
       </c>
       <c r="H18" s="16">
@@ -972,15 +972,15 @@
         <v/>
       </c>
       <c r="E19" s="15">
-        <f>IF($K19=0,0,ROUNDDOWN($D19/INDEX('ETF데이터'!$D$4:$D$75,$K19),0))</f>
+        <f>IF($K19=0,0,ROUNDDOWN($D19/INDEX('ETF데이터'!$D$4:$D$76,$K19),0))</f>
         <v/>
       </c>
       <c r="F19" s="14">
-        <f>IF($K19=0,0,$E19*INDEX('ETF데이터'!$D$4:$D$75,$K19))</f>
+        <f>IF($K19=0,0,$E19*INDEX('ETF데이터'!$D$4:$D$76,$K19))</f>
         <v/>
       </c>
       <c r="G19" s="14">
-        <f>IF($K19=0,0,$F19*INDEX('ETF데이터'!$J$4:$J$75,$K19)/12)</f>
+        <f>IF($K19=0,0,$F19*INDEX('ETF데이터'!$J$4:$J$76,$K19)/12)</f>
         <v/>
       </c>
       <c r="H19" s="14">
@@ -1409,7 +1409,7 @@
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>5. 채택 ETF 비교 (1억원 단독 투자 기준) — 연 분배율 상위 12종목 / 전체 72종목</t>
+          <t>5. 채택 ETF 비교 (1억원 단독 투자 기준) — 연 분배율 상위 12종목 / 전체 73종목</t>
         </is>
       </c>
     </row>
@@ -1897,26 +1897,34 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T20:29:20.608Z · 대상: 국내 상장 월배당 ETF · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 연환산 변동성 35% 이하, 분배 이력 12개월 이상</t>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 목록에는 커버드콜뿐 아니라 리츠·채권형·배당주·파킹형 월배당 ETF 가 함께 있습니다. 분배 재원과 위험이 서로 다르므로 [ETF데이터] 장의 '유형'·'자산군' 칸을 확인하십시오.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  자료 출처: ETFCHECK (www.etfcheck.co.kr) · 수집 시각 2026-09-16T20:51:14.596Z · 대상: 국내 상장 월배당 ETF · 채택 기준: 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 연환산 변동성 35% 이하, 분배 이력 12개월 이상</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A70:H70"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="A67:H67"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A78:H78"/>
     <mergeCell ref="A69:H69"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A71:H71"/>
     <mergeCell ref="A72:H72"/>
     <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A76:H76"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A75:H75"/>
@@ -1942,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P195"/>
+  <dimension ref="A1:Q195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1961,6 +1969,7 @@
     <col width="30" customWidth="1" min="14" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2051,6 +2060,11 @@
           <t>유형</t>
         </is>
       </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>자산군</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="36" t="inlineStr">
@@ -2113,6 +2127,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q4" s="36" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
@@ -2175,6 +2194,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q5" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="36" t="inlineStr">
@@ -2237,6 +2261,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q6" s="36" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="36" t="inlineStr">
@@ -2299,6 +2328,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q7" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="36" t="inlineStr">
@@ -2361,6 +2395,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q8" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="36" t="inlineStr">
@@ -2423,6 +2462,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q9" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="36" t="inlineStr">
@@ -2485,6 +2529,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q10" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="36" t="inlineStr">
@@ -2547,6 +2596,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q11" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="36" t="inlineStr">
@@ -2609,6 +2663,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q12" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="36" t="inlineStr">
@@ -2671,6 +2730,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q13" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="36" t="inlineStr">
@@ -2733,6 +2797,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q14" s="36" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
@@ -2795,6 +2864,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q15" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="36" t="inlineStr">
@@ -2857,6 +2931,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q16" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="36" t="inlineStr">
@@ -2919,6 +2998,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q17" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="36" t="inlineStr">
@@ -2981,6 +3065,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q18" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="36" t="inlineStr">
@@ -3043,6 +3132,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q19" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="36" t="inlineStr">
@@ -3105,6 +3199,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q20" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="36" t="inlineStr">
@@ -3167,6 +3266,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q21" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="36" t="inlineStr">
@@ -3229,6 +3333,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q22" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="36" t="inlineStr">
@@ -3291,6 +3400,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q23" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="36" t="inlineStr">
@@ -3353,6 +3467,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q24" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="36" t="inlineStr">
@@ -3415,6 +3534,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q25" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="36" t="inlineStr">
@@ -3477,6 +3601,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q26" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="36" t="inlineStr">
@@ -3539,6 +3668,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q27" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="36" t="inlineStr">
@@ -3601,6 +3735,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q28" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="36" t="inlineStr">
@@ -3663,6 +3802,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q29" s="36" t="inlineStr">
+        <is>
+          <t>부동산</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="36" t="inlineStr">
@@ -3725,6 +3869,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q30" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="36" t="inlineStr">
@@ -3787,6 +3936,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q31" s="36" t="inlineStr">
+        <is>
+          <t>부동산</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="36" t="inlineStr">
@@ -3849,6 +4003,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q32" s="36" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="36" t="inlineStr">
@@ -3911,6 +4070,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q33" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="36" t="inlineStr">
@@ -3973,6 +4137,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q34" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="36" t="inlineStr">
@@ -4035,6 +4204,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q35" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="36" t="inlineStr">
@@ -4097,6 +4271,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q36" s="36" t="inlineStr">
+        <is>
+          <t>단기자금(파킹형)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="36" t="inlineStr">
@@ -4159,6 +4338,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q37" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="36" t="inlineStr">
@@ -4221,6 +4405,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q38" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
@@ -4283,6 +4472,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q39" s="36" t="inlineStr">
+        <is>
+          <t>원자재</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="36" t="inlineStr">
@@ -4345,6 +4539,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q40" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="36" t="inlineStr">
@@ -4407,6 +4606,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q41" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="36" t="inlineStr">
@@ -4469,6 +4673,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q42" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="36" t="inlineStr">
@@ -4531,6 +4740,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q43" s="36" t="inlineStr">
+        <is>
+          <t>단기자금(파킹형)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="36" t="inlineStr">
@@ -4593,6 +4807,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q44" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="36" t="inlineStr">
@@ -4655,6 +4874,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q45" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="36" t="inlineStr">
@@ -4717,6 +4941,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q46" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="36" t="inlineStr">
@@ -4779,6 +5008,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q47" s="36" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="36" t="inlineStr">
@@ -4841,6 +5075,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q48" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="36" t="inlineStr">
@@ -4903,6 +5142,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q49" s="36" t="inlineStr">
+        <is>
+          <t>단기자금(파킹형)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="36" t="inlineStr">
@@ -4965,6 +5209,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q50" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="36" t="inlineStr">
@@ -5027,6 +5276,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q51" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="36" t="inlineStr">
@@ -5089,6 +5343,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q52" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="36" t="inlineStr">
@@ -5151,6 +5410,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q53" s="36" t="inlineStr">
+        <is>
+          <t>단기자금(파킹형)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="36" t="inlineStr">
@@ -5213,6 +5477,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q54" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="36" t="inlineStr">
@@ -5275,6 +5544,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q55" s="36" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="36" t="inlineStr">
@@ -5337,50 +5611,55 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q56" s="36" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="36" t="inlineStr">
         <is>
-          <t>TIGER 미국배당다우존스</t>
+          <t>ACE 미국배당다우존스</t>
         </is>
       </c>
       <c r="B57" s="36" t="inlineStr">
         <is>
-          <t>458730</t>
+          <t>402970</t>
         </is>
       </c>
       <c r="C57" s="36" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="D57" s="37" t="n">
-        <v>14820</v>
+        <v>15060</v>
       </c>
       <c r="E57" s="37" t="n">
-        <v>4314843000000</v>
+        <v>965346000000</v>
       </c>
       <c r="F57" s="37" t="n">
-        <v>32333713168</v>
+        <v>4726752404</v>
       </c>
       <c r="G57" s="38" t="n">
-        <v>0.001034</v>
+        <v>0.001481</v>
       </c>
       <c r="H57" s="38" t="n">
-        <v>0.1414</v>
+        <v>0.1406</v>
       </c>
       <c r="I57" s="38" t="n">
-        <v>0.002</v>
+        <v>0.0024</v>
       </c>
       <c r="J57" s="38" t="n">
-        <v>0.029217</v>
+        <v>0.029283</v>
       </c>
       <c r="K57" s="37" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L57" s="36" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M57" s="36" t="inlineStr">
@@ -5399,50 +5678,55 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q57" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="36" t="inlineStr">
         <is>
-          <t>KODEX 미국배당다우존스</t>
+          <t>TIGER 미국배당다우존스</t>
         </is>
       </c>
       <c r="B58" s="36" t="inlineStr">
         <is>
-          <t>489250</t>
+          <t>458730</t>
         </is>
       </c>
       <c r="C58" s="36" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="D58" s="37" t="n">
-        <v>12760</v>
+        <v>14820</v>
       </c>
       <c r="E58" s="37" t="n">
-        <v>604824000000</v>
+        <v>4314843000000</v>
       </c>
       <c r="F58" s="37" t="n">
-        <v>5508918758</v>
+        <v>32333713168</v>
       </c>
       <c r="G58" s="38" t="n">
-        <v>0.001834</v>
+        <v>0.001034</v>
       </c>
       <c r="H58" s="38" t="n">
-        <v>0.1415</v>
+        <v>0.1414</v>
       </c>
       <c r="I58" s="38" t="n">
-        <v>0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="J58" s="38" t="n">
-        <v>0.02884</v>
+        <v>0.029217</v>
       </c>
       <c r="K58" s="37" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L58" s="36" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M58" s="36" t="inlineStr">
@@ -5461,16 +5745,21 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q58" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="36" t="inlineStr">
         <is>
-          <t>KODEX CD1년금리플러스액티브(합성)</t>
+          <t>KODEX 미국배당다우존스</t>
         </is>
       </c>
       <c r="B59" s="36" t="inlineStr">
         <is>
-          <t>481050</t>
+          <t>489250</t>
         </is>
       </c>
       <c r="C59" s="36" t="inlineStr">
@@ -5479,32 +5768,32 @@
         </is>
       </c>
       <c r="D59" s="37" t="n">
-        <v>1023035</v>
+        <v>12760</v>
       </c>
       <c r="E59" s="37" t="n">
-        <v>2513290084500</v>
+        <v>604824000000</v>
       </c>
       <c r="F59" s="37" t="n">
-        <v>23384891627</v>
+        <v>5508918758</v>
       </c>
       <c r="G59" s="38" t="n">
-        <v>0.000659</v>
+        <v>0.001834</v>
       </c>
       <c r="H59" s="38" t="n">
-        <v>0.0083</v>
+        <v>0.1415</v>
       </c>
       <c r="I59" s="38" t="n">
-        <v>0.0027</v>
+        <v>0.0019</v>
       </c>
       <c r="J59" s="38" t="n">
-        <v>0.028805</v>
+        <v>0.02884</v>
       </c>
       <c r="K59" s="37" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L59" s="36" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M59" s="36" t="inlineStr">
@@ -5515,51 +5804,56 @@
       <c r="N59" s="36" t="inlineStr"/>
       <c r="O59" s="36" t="inlineStr">
         <is>
-          <t>KAP 1년은행CD+추가금리 지수</t>
+          <t>Dow Jones U.S. Dividend 100 Price Return Index</t>
         </is>
       </c>
       <c r="P59" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q59" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="36" t="inlineStr">
         <is>
-          <t>TIGER CD금리플러스액티브(합성)</t>
+          <t>KODEX CD1년금리플러스액티브(합성)</t>
         </is>
       </c>
       <c r="B60" s="36" t="inlineStr">
         <is>
-          <t>499660</t>
+          <t>481050</t>
         </is>
       </c>
       <c r="C60" s="36" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D60" s="37" t="n">
-        <v>1001755</v>
+        <v>1023035</v>
       </c>
       <c r="E60" s="37" t="n">
-        <v>450088521500</v>
+        <v>2513290084500</v>
       </c>
       <c r="F60" s="37" t="n">
-        <v>12782829717</v>
+        <v>23384891627</v>
       </c>
       <c r="G60" s="38" t="n">
-        <v>0.000328</v>
+        <v>0.000659</v>
       </c>
       <c r="H60" s="38" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="I60" s="38" t="n">
-        <v>0.0024</v>
+        <v>0.0027</v>
       </c>
       <c r="J60" s="38" t="n">
-        <v>0.028161</v>
+        <v>0.028805</v>
       </c>
       <c r="K60" s="37" t="n">
         <v>21</v>
@@ -5577,54 +5871,59 @@
       <c r="N60" s="36" t="inlineStr"/>
       <c r="O60" s="36" t="inlineStr">
         <is>
-          <t>KIS CD+CPI연동금리 월분배 지수(PR지수)</t>
+          <t>KAP 1년은행CD+추가금리 지수</t>
         </is>
       </c>
       <c r="P60" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q60" s="36" t="inlineStr">
+        <is>
+          <t>단기자금(파킹형)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="36" t="inlineStr">
         <is>
-          <t>SOL 미국배당다우존스(H)</t>
+          <t>TIGER CD금리플러스액티브(합성)</t>
         </is>
       </c>
       <c r="B61" s="36" t="inlineStr">
         <is>
-          <t>452360</t>
+          <t>499660</t>
         </is>
       </c>
       <c r="C61" s="36" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="D61" s="37" t="n">
-        <v>13385</v>
+        <v>1001755</v>
       </c>
       <c r="E61" s="37" t="n">
-        <v>230222000000</v>
+        <v>450088521500</v>
       </c>
       <c r="F61" s="37" t="n">
-        <v>1863486602</v>
+        <v>12782829717</v>
       </c>
       <c r="G61" s="38" t="n">
-        <v>0.002404</v>
+        <v>0.000328</v>
       </c>
       <c r="H61" s="38" t="n">
-        <v>0.1096</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="I61" s="38" t="n">
-        <v>0.0019</v>
+        <v>0.0024</v>
       </c>
       <c r="J61" s="38" t="n">
-        <v>0.027867</v>
+        <v>0.028161</v>
       </c>
       <c r="K61" s="37" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="L61" s="36" t="inlineStr">
         <is>
@@ -5639,54 +5938,59 @@
       <c r="N61" s="36" t="inlineStr"/>
       <c r="O61" s="36" t="inlineStr">
         <is>
-          <t>Dow Jones U.S. Dividend 100 Price Return Index</t>
+          <t>KIS CD+CPI연동금리 월분배 지수(PR지수)</t>
         </is>
       </c>
       <c r="P61" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q61" s="36" t="inlineStr">
+        <is>
+          <t>단기자금(파킹형)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="36" t="inlineStr">
         <is>
-          <t>KODEX CD금리액티브(합성)</t>
+          <t>SOL 미국배당다우존스(H)</t>
         </is>
       </c>
       <c r="B62" s="36" t="inlineStr">
         <is>
-          <t>459580</t>
+          <t>452360</t>
         </is>
       </c>
       <c r="C62" s="36" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="D62" s="37" t="n">
-        <v>1074855</v>
+        <v>13385</v>
       </c>
       <c r="E62" s="37" t="n">
-        <v>6835755343500</v>
+        <v>230222000000</v>
       </c>
       <c r="F62" s="37" t="n">
-        <v>505125898052</v>
+        <v>1863486602</v>
       </c>
       <c r="G62" s="38" t="n">
-        <v>0.000332</v>
+        <v>0.002404</v>
       </c>
       <c r="H62" s="38" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1096</v>
       </c>
       <c r="I62" s="38" t="n">
-        <v>0.0026</v>
+        <v>0.0019</v>
       </c>
       <c r="J62" s="38" t="n">
-        <v>0.027523</v>
+        <v>0.027867</v>
       </c>
       <c r="K62" s="37" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="L62" s="36" t="inlineStr">
         <is>
@@ -5701,54 +6005,59 @@
       <c r="N62" s="36" t="inlineStr"/>
       <c r="O62" s="36" t="inlineStr">
         <is>
-          <t>KAP 양도성예금증서(CD) 금리 지수</t>
+          <t>Dow Jones U.S. Dividend 100 Price Return Index</t>
         </is>
       </c>
       <c r="P62" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q62" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="36" t="inlineStr">
         <is>
-          <t>RISE 중기우량회사채</t>
+          <t>KODEX CD금리액티브(합성)</t>
         </is>
       </c>
       <c r="B63" s="36" t="inlineStr">
         <is>
-          <t>136340</t>
+          <t>459580</t>
         </is>
       </c>
       <c r="C63" s="36" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D63" s="37" t="n">
-        <v>103865</v>
+        <v>1074855</v>
       </c>
       <c r="E63" s="37" t="n">
-        <v>290198810000</v>
+        <v>6835755343500</v>
       </c>
       <c r="F63" s="37" t="n">
-        <v>562177723</v>
+        <v>505125898052</v>
       </c>
       <c r="G63" s="38" t="n">
-        <v>0.001037</v>
+        <v>0.000332</v>
       </c>
       <c r="H63" s="38" t="n">
-        <v>0.0212</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="I63" s="38" t="n">
-        <v>0.0012</v>
+        <v>0.0026</v>
       </c>
       <c r="J63" s="38" t="n">
-        <v>0.027228</v>
+        <v>0.027523</v>
       </c>
       <c r="K63" s="37" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="L63" s="36" t="inlineStr">
         <is>
@@ -5763,58 +6072,63 @@
       <c r="N63" s="36" t="inlineStr"/>
       <c r="O63" s="36" t="inlineStr">
         <is>
-          <t>KOBI Credit</t>
+          <t>KAP 양도성예금증서(CD) 금리 지수</t>
         </is>
       </c>
       <c r="P63" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q63" s="36" t="inlineStr">
+        <is>
+          <t>단기자금(파킹형)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="36" t="inlineStr">
         <is>
-          <t>KODEX 단기채권PLUS</t>
+          <t>RISE 중기우량회사채</t>
         </is>
       </c>
       <c r="B64" s="36" t="inlineStr">
         <is>
-          <t>214980</t>
+          <t>136340</t>
         </is>
       </c>
       <c r="C64" s="36" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>KB자산운용</t>
         </is>
       </c>
       <c r="D64" s="37" t="n">
-        <v>114425</v>
+        <v>103865</v>
       </c>
       <c r="E64" s="37" t="n">
-        <v>1839839575000</v>
+        <v>290198810000</v>
       </c>
       <c r="F64" s="37" t="n">
-        <v>3813171299</v>
+        <v>562177723</v>
       </c>
       <c r="G64" s="38" t="n">
-        <v>0.001704</v>
+        <v>0.001037</v>
       </c>
       <c r="H64" s="38" t="n">
-        <v>0.0083</v>
+        <v>0.0212</v>
       </c>
       <c r="I64" s="38" t="n">
-        <v>0.0025</v>
+        <v>0.0012</v>
       </c>
       <c r="J64" s="38" t="n">
-        <v>0.026961</v>
+        <v>0.027228</v>
       </c>
       <c r="K64" s="37" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="L64" s="36" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M64" s="36" t="inlineStr">
@@ -5825,24 +6139,29 @@
       <c r="N64" s="36" t="inlineStr"/>
       <c r="O64" s="36" t="inlineStr">
         <is>
-          <t>KRW Cash+PLUS Index</t>
+          <t>KOBI Credit</t>
         </is>
       </c>
       <c r="P64" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q64" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="36" t="inlineStr">
         <is>
-          <t>KODEX 코리아배당성장</t>
+          <t>KODEX 단기채권PLUS</t>
         </is>
       </c>
       <c r="B65" s="36" t="inlineStr">
         <is>
-          <t>211900</t>
+          <t>214980</t>
         </is>
       </c>
       <c r="C65" s="36" t="inlineStr">
@@ -5851,32 +6170,32 @@
         </is>
       </c>
       <c r="D65" s="37" t="n">
-        <v>27960</v>
+        <v>114425</v>
       </c>
       <c r="E65" s="37" t="n">
-        <v>90870000000</v>
+        <v>1839839575000</v>
       </c>
       <c r="F65" s="37" t="n">
-        <v>541467058</v>
+        <v>3813171299</v>
       </c>
       <c r="G65" s="38" t="n">
-        <v>0.002156</v>
+        <v>0.001704</v>
       </c>
       <c r="H65" s="38" t="n">
-        <v>0.3459</v>
+        <v>0.0083</v>
       </c>
       <c r="I65" s="38" t="n">
-        <v>0.0009</v>
+        <v>0.0025</v>
       </c>
       <c r="J65" s="38" t="n">
-        <v>0.026574</v>
+        <v>0.026961</v>
       </c>
       <c r="K65" s="37" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L65" s="36" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M65" s="36" t="inlineStr">
@@ -5887,24 +6206,29 @@
       <c r="N65" s="36" t="inlineStr"/>
       <c r="O65" s="36" t="inlineStr">
         <is>
-          <t>코스피 배당성장 50</t>
+          <t>KRW Cash+PLUS Index</t>
         </is>
       </c>
       <c r="P65" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q65" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="36" t="inlineStr">
         <is>
-          <t>KODEX TRF3070</t>
+          <t>KODEX 코리아배당성장</t>
         </is>
       </c>
       <c r="B66" s="36" t="inlineStr">
         <is>
-          <t>329650</t>
+          <t>211900</t>
         </is>
       </c>
       <c r="C66" s="36" t="inlineStr">
@@ -5913,32 +6237,32 @@
         </is>
       </c>
       <c r="D66" s="37" t="n">
-        <v>13905</v>
+        <v>27960</v>
       </c>
       <c r="E66" s="37" t="n">
-        <v>229432500000</v>
+        <v>90870000000</v>
       </c>
       <c r="F66" s="37" t="n">
-        <v>665462053</v>
+        <v>541467058</v>
       </c>
       <c r="G66" s="38" t="n">
-        <v>0.003135</v>
+        <v>0.002156</v>
       </c>
       <c r="H66" s="38" t="n">
-        <v>0.0484</v>
+        <v>0.3459</v>
       </c>
       <c r="I66" s="38" t="n">
-        <v>0.0022</v>
+        <v>0.0009</v>
       </c>
       <c r="J66" s="38" t="n">
-        <v>0.026106</v>
+        <v>0.026574</v>
       </c>
       <c r="K66" s="37" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L66" s="36" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M66" s="36" t="inlineStr">
@@ -5949,24 +6273,29 @@
       <c r="N66" s="36" t="inlineStr"/>
       <c r="O66" s="36" t="inlineStr">
         <is>
-          <t>FnGuide TRF 3070 지수</t>
+          <t>코스피 배당성장 50</t>
         </is>
       </c>
       <c r="P66" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q66" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="36" t="inlineStr">
         <is>
-          <t>KODEX KOFR금리액티브(합성)</t>
+          <t>KODEX TRF3070</t>
         </is>
       </c>
       <c r="B67" s="36" t="inlineStr">
         <is>
-          <t>423160</t>
+          <t>329650</t>
         </is>
       </c>
       <c r="C67" s="36" t="inlineStr">
@@ -5975,32 +6304,32 @@
         </is>
       </c>
       <c r="D67" s="37" t="n">
-        <v>110805</v>
+        <v>13905</v>
       </c>
       <c r="E67" s="37" t="n">
-        <v>3626758455000</v>
+        <v>229432500000</v>
       </c>
       <c r="F67" s="37" t="n">
-        <v>11083007184</v>
+        <v>665462053</v>
       </c>
       <c r="G67" s="38" t="n">
-        <v>0.0006180000000000001</v>
+        <v>0.003135</v>
       </c>
       <c r="H67" s="38" t="n">
-        <v>0.0076</v>
+        <v>0.0484</v>
       </c>
       <c r="I67" s="38" t="n">
-        <v>0.0024</v>
+        <v>0.0022</v>
       </c>
       <c r="J67" s="38" t="n">
-        <v>0.026082</v>
+        <v>0.026106</v>
       </c>
       <c r="K67" s="37" t="n">
         <v>14</v>
       </c>
       <c r="L67" s="36" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M67" s="36" t="inlineStr">
@@ -6011,24 +6340,29 @@
       <c r="N67" s="36" t="inlineStr"/>
       <c r="O67" s="36" t="inlineStr">
         <is>
-          <t>KOFR 인덱스</t>
+          <t>FnGuide TRF 3070 지수</t>
         </is>
       </c>
       <c r="P67" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q67" s="36" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="36" t="inlineStr">
         <is>
-          <t>KODEX 단기변동금리부채권액티브</t>
+          <t>KODEX KOFR금리액티브(합성)</t>
         </is>
       </c>
       <c r="B68" s="36" t="inlineStr">
         <is>
-          <t>273140</t>
+          <t>423160</t>
         </is>
       </c>
       <c r="C68" s="36" t="inlineStr">
@@ -6037,32 +6371,32 @@
         </is>
       </c>
       <c r="D68" s="37" t="n">
-        <v>114575</v>
+        <v>110805</v>
       </c>
       <c r="E68" s="37" t="n">
-        <v>279677575000</v>
+        <v>3626758455000</v>
       </c>
       <c r="F68" s="37" t="n">
-        <v>500766244</v>
+        <v>11083007184</v>
       </c>
       <c r="G68" s="38" t="n">
-        <v>0.001725</v>
+        <v>0.0006180000000000001</v>
       </c>
       <c r="H68" s="38" t="n">
-        <v>0.0077</v>
+        <v>0.0076</v>
       </c>
       <c r="I68" s="38" t="n">
-        <v>0.0023</v>
+        <v>0.0024</v>
       </c>
       <c r="J68" s="38" t="n">
-        <v>0.025538</v>
+        <v>0.026082</v>
       </c>
       <c r="K68" s="37" t="n">
         <v>14</v>
       </c>
       <c r="L68" s="36" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M68" s="36" t="inlineStr">
@@ -6073,24 +6407,29 @@
       <c r="N68" s="36" t="inlineStr"/>
       <c r="O68" s="36" t="inlineStr">
         <is>
-          <t>KAP 단기변동금리부 은행채</t>
+          <t>KOFR 인덱스</t>
         </is>
       </c>
       <c r="P68" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q68" s="36" t="inlineStr">
+        <is>
+          <t>단기자금(파킹형)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="36" t="inlineStr">
         <is>
-          <t>KODEX 단기채권</t>
+          <t>KODEX 단기변동금리부채권액티브</t>
         </is>
       </c>
       <c r="B69" s="36" t="inlineStr">
         <is>
-          <t>153130</t>
+          <t>273140</t>
         </is>
       </c>
       <c r="C69" s="36" t="inlineStr">
@@ -6099,25 +6438,25 @@
         </is>
       </c>
       <c r="D69" s="37" t="n">
-        <v>113135</v>
+        <v>114575</v>
       </c>
       <c r="E69" s="37" t="n">
-        <v>811404220000</v>
+        <v>279677575000</v>
       </c>
       <c r="F69" s="37" t="n">
-        <v>4053185219</v>
+        <v>500766244</v>
       </c>
       <c r="G69" s="38" t="n">
-        <v>0.001779</v>
+        <v>0.001725</v>
       </c>
       <c r="H69" s="38" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0077</v>
       </c>
       <c r="I69" s="38" t="n">
-        <v>0.0022</v>
+        <v>0.0023</v>
       </c>
       <c r="J69" s="38" t="n">
-        <v>0.025173</v>
+        <v>0.025538</v>
       </c>
       <c r="K69" s="37" t="n">
         <v>14</v>
@@ -6135,24 +6474,29 @@
       <c r="N69" s="36" t="inlineStr"/>
       <c r="O69" s="36" t="inlineStr">
         <is>
-          <t>KRW Cash Index</t>
+          <t>KAP 단기변동금리부 은행채</t>
         </is>
       </c>
       <c r="P69" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q69" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="36" t="inlineStr">
         <is>
-          <t>KODEX 삼성전자채권혼합</t>
+          <t>KODEX 단기채권</t>
         </is>
       </c>
       <c r="B70" s="36" t="inlineStr">
         <is>
-          <t>448330</t>
+          <t>153130</t>
         </is>
       </c>
       <c r="C70" s="36" t="inlineStr">
@@ -6161,28 +6505,28 @@
         </is>
       </c>
       <c r="D70" s="37" t="n">
-        <v>17105</v>
+        <v>113135</v>
       </c>
       <c r="E70" s="37" t="n">
-        <v>1264059500000</v>
+        <v>811404220000</v>
       </c>
       <c r="F70" s="37" t="n">
-        <v>13818369369</v>
+        <v>4053185219</v>
       </c>
       <c r="G70" s="38" t="n">
-        <v>0.001635</v>
+        <v>0.001779</v>
       </c>
       <c r="H70" s="38" t="n">
-        <v>0.2311</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="I70" s="38" t="n">
-        <v>0.0021</v>
+        <v>0.0022</v>
       </c>
       <c r="J70" s="38" t="n">
-        <v>0.021163</v>
+        <v>0.025173</v>
       </c>
       <c r="K70" s="37" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L70" s="36" t="inlineStr">
         <is>
@@ -6197,58 +6541,63 @@
       <c r="N70" s="36" t="inlineStr"/>
       <c r="O70" s="36" t="inlineStr">
         <is>
-          <t>Wise 삼성전자 채권혼합 지수</t>
+          <t>KRW Cash Index</t>
         </is>
       </c>
       <c r="P70" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q70" s="36" t="inlineStr">
+        <is>
+          <t>채권</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="36" t="inlineStr">
         <is>
-          <t>TIGER 미국S&amp;P500배당귀족</t>
+          <t>KODEX 삼성전자채권혼합</t>
         </is>
       </c>
       <c r="B71" s="36" t="inlineStr">
         <is>
-          <t>429000</t>
+          <t>448330</t>
         </is>
       </c>
       <c r="C71" s="36" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D71" s="37" t="n">
-        <v>12985</v>
+        <v>17105</v>
       </c>
       <c r="E71" s="37" t="n">
-        <v>185685500000</v>
+        <v>1264059500000</v>
       </c>
       <c r="F71" s="37" t="n">
-        <v>1349510753</v>
+        <v>13818369369</v>
       </c>
       <c r="G71" s="38" t="n">
-        <v>0.004159</v>
+        <v>0.001635</v>
       </c>
       <c r="H71" s="38" t="n">
-        <v>0.1469</v>
+        <v>0.2311</v>
       </c>
       <c r="I71" s="38" t="n">
-        <v>0.0015</v>
+        <v>0.0021</v>
       </c>
       <c r="J71" s="38" t="n">
-        <v>0.021101</v>
+        <v>0.021163</v>
       </c>
       <c r="K71" s="37" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L71" s="36" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M71" s="36" t="inlineStr">
@@ -6259,58 +6608,63 @@
       <c r="N71" s="36" t="inlineStr"/>
       <c r="O71" s="36" t="inlineStr">
         <is>
-          <t>S&amp;P 500 Dividend Aristocrats Index</t>
+          <t>Wise 삼성전자 채권혼합 지수</t>
         </is>
       </c>
       <c r="P71" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q71" s="36" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="36" t="inlineStr">
         <is>
-          <t>SOL 미국S&amp;P500미국채혼합50</t>
+          <t>TIGER 미국S&amp;P500배당귀족</t>
         </is>
       </c>
       <c r="B72" s="36" t="inlineStr">
         <is>
-          <t>0080X0</t>
+          <t>429000</t>
         </is>
       </c>
       <c r="C72" s="36" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="D72" s="37" t="n">
-        <v>10680</v>
+        <v>12985</v>
       </c>
       <c r="E72" s="37" t="n">
-        <v>74760000000</v>
+        <v>185685500000</v>
       </c>
       <c r="F72" s="37" t="n">
-        <v>687657325</v>
+        <v>1349510753</v>
       </c>
       <c r="G72" s="38" t="n">
-        <v>0.004903</v>
+        <v>0.004159</v>
       </c>
       <c r="H72" s="38" t="n">
-        <v>0.1089</v>
+        <v>0.1469</v>
       </c>
       <c r="I72" s="38" t="n">
-        <v>0.0019</v>
+        <v>0.0015</v>
       </c>
       <c r="J72" s="38" t="n">
-        <v>0.020131</v>
+        <v>0.021101</v>
       </c>
       <c r="K72" s="37" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="L72" s="36" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M72" s="36" t="inlineStr">
@@ -6321,54 +6675,59 @@
       <c r="N72" s="36" t="inlineStr"/>
       <c r="O72" s="36" t="inlineStr">
         <is>
-          <t>S&amp;P 500 and iBoxx $ Treasuries 7-10Y 50/50 Blend Index (USD)</t>
+          <t>S&amp;P 500 Dividend Aristocrats Index</t>
         </is>
       </c>
       <c r="P72" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q72" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="36" t="inlineStr">
         <is>
-          <t>KODEX 200미국채혼합50</t>
+          <t>SOL 미국S&amp;P500미국채혼합50</t>
         </is>
       </c>
       <c r="B73" s="36" t="inlineStr">
         <is>
-          <t>284430</t>
+          <t>0080X0</t>
         </is>
       </c>
       <c r="C73" s="36" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="D73" s="37" t="n">
-        <v>20420</v>
+        <v>10680</v>
       </c>
       <c r="E73" s="37" t="n">
-        <v>1986457600000</v>
+        <v>74760000000</v>
       </c>
       <c r="F73" s="37" t="n">
-        <v>21752897374</v>
+        <v>687657325</v>
       </c>
       <c r="G73" s="38" t="n">
-        <v>0.006232</v>
+        <v>0.004903</v>
       </c>
       <c r="H73" s="38" t="n">
-        <v>0.2505</v>
+        <v>0.1089</v>
       </c>
       <c r="I73" s="38" t="n">
-        <v>0.0013</v>
+        <v>0.0019</v>
       </c>
       <c r="J73" s="38" t="n">
-        <v>0.01714</v>
+        <v>0.020131</v>
       </c>
       <c r="K73" s="37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L73" s="36" t="inlineStr">
         <is>
@@ -6383,58 +6742,63 @@
       <c r="N73" s="36" t="inlineStr"/>
       <c r="O73" s="36" t="inlineStr">
         <is>
-          <t>코스피 200 미국채 혼합지수</t>
+          <t>S&amp;P 500 and iBoxx $ Treasuries 7-10Y 50/50 Blend Index (USD)</t>
         </is>
       </c>
       <c r="P73" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q73" s="36" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="36" t="inlineStr">
         <is>
-          <t>TIGER 미국다우존스30</t>
+          <t>KODEX 200미국채혼합50</t>
         </is>
       </c>
       <c r="B74" s="36" t="inlineStr">
         <is>
-          <t>245340</t>
+          <t>284430</t>
         </is>
       </c>
       <c r="C74" s="36" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="D74" s="37" t="n">
-        <v>34800</v>
+        <v>20420</v>
       </c>
       <c r="E74" s="37" t="n">
-        <v>141288000000</v>
+        <v>1986457600000</v>
       </c>
       <c r="F74" s="37" t="n">
-        <v>875469740</v>
+        <v>21752897374</v>
       </c>
       <c r="G74" s="38" t="n">
-        <v>0.004859</v>
+        <v>0.006232</v>
       </c>
       <c r="H74" s="38" t="n">
-        <v>0.1454</v>
+        <v>0.2505</v>
       </c>
       <c r="I74" s="38" t="n">
-        <v>0.001</v>
+        <v>0.0013</v>
       </c>
       <c r="J74" s="38" t="n">
-        <v>0.013506</v>
+        <v>0.01714</v>
       </c>
       <c r="K74" s="37" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="L74" s="36" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="M74" s="36" t="inlineStr">
@@ -6445,54 +6809,59 @@
       <c r="N74" s="36" t="inlineStr"/>
       <c r="O74" s="36" t="inlineStr">
         <is>
-          <t>DowJones Industrial Average Index</t>
+          <t>코스피 200 미국채 혼합지수</t>
         </is>
       </c>
       <c r="P74" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q74" s="36" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="36" t="inlineStr">
         <is>
-          <t>SOL 미국S&amp;P500</t>
+          <t>TIGER 미국다우존스30</t>
         </is>
       </c>
       <c r="B75" s="36" t="inlineStr">
         <is>
-          <t>433330</t>
+          <t>245340</t>
         </is>
       </c>
       <c r="C75" s="36" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="D75" s="37" t="n">
-        <v>21540</v>
+        <v>34800</v>
       </c>
       <c r="E75" s="37" t="n">
-        <v>297252000000</v>
+        <v>141288000000</v>
       </c>
       <c r="F75" s="37" t="n">
-        <v>2011598545</v>
+        <v>875469740</v>
       </c>
       <c r="G75" s="38" t="n">
-        <v>0.00143</v>
+        <v>0.004859</v>
       </c>
       <c r="H75" s="38" t="n">
-        <v>0.1452</v>
+        <v>0.1454</v>
       </c>
       <c r="I75" s="38" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="J75" s="38" t="n">
-        <v>0.009099000000000001</v>
+        <v>0.013506</v>
       </c>
       <c r="K75" s="37" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L75" s="36" t="inlineStr">
         <is>
@@ -6507,90 +6876,96 @@
       <c r="N75" s="36" t="inlineStr"/>
       <c r="O75" s="36" t="inlineStr">
         <is>
+          <t>DowJones Industrial Average Index</t>
+        </is>
+      </c>
+      <c r="P75" s="36" t="inlineStr">
+        <is>
+          <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q75" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="36" t="inlineStr">
+        <is>
+          <t>SOL 미국S&amp;P500</t>
+        </is>
+      </c>
+      <c r="B76" s="36" t="inlineStr">
+        <is>
+          <t>433330</t>
+        </is>
+      </c>
+      <c r="C76" s="36" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="D76" s="37" t="n">
+        <v>21540</v>
+      </c>
+      <c r="E76" s="37" t="n">
+        <v>297252000000</v>
+      </c>
+      <c r="F76" s="37" t="n">
+        <v>2011598545</v>
+      </c>
+      <c r="G76" s="38" t="n">
+        <v>0.00143</v>
+      </c>
+      <c r="H76" s="38" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="I76" s="38" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="J76" s="38" t="n">
+        <v>0.009099000000000001</v>
+      </c>
+      <c r="K76" s="37" t="n">
+        <v>50</v>
+      </c>
+      <c r="L76" s="36" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="M76" s="36" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="N76" s="36" t="inlineStr"/>
+      <c r="O76" s="36" t="inlineStr">
+        <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
-      <c r="P75" s="36" t="inlineStr">
+      <c r="P76" s="36" t="inlineStr">
         <is>
           <t>월배당</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="39" t="inlineStr">
-        <is>
-          <t>1Q 미국배당TOP30</t>
-        </is>
-      </c>
-      <c r="B76" s="39" t="inlineStr">
-        <is>
-          <t>0004G0</t>
-        </is>
-      </c>
-      <c r="C76" s="39" t="inlineStr">
-        <is>
-          <t>하나자산운용</t>
-        </is>
-      </c>
-      <c r="D76" s="40" t="n">
-        <v>8825</v>
-      </c>
-      <c r="E76" s="40" t="n">
-        <v>13237500000</v>
-      </c>
-      <c r="F76" s="40" t="n">
-        <v>90427309</v>
-      </c>
-      <c r="G76" s="41" t="n">
-        <v>0.004354</v>
-      </c>
-      <c r="H76" s="41" t="n">
-        <v>0.1577</v>
-      </c>
-      <c r="I76" s="41" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J76" s="41" t="n">
-        <v>0.034901</v>
-      </c>
-      <c r="K76" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="L76" s="39" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
-      <c r="M76" s="39" t="inlineStr">
-        <is>
-          <t>제외</t>
-        </is>
-      </c>
-      <c r="N76" s="39" t="inlineStr">
-        <is>
-          <t>순자산 132억(기준 300억 미만), 60일 거래대금 0.9억(기준 5억 미만)</t>
-        </is>
-      </c>
-      <c r="O76" s="39" t="inlineStr">
-        <is>
-          <t>Solactive U.S. Dividend 30 Index PR</t>
-        </is>
-      </c>
-      <c r="P76" s="39" t="inlineStr">
-        <is>
-          <t>월배당</t>
+      <c r="Q76" s="36" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="39" t="inlineStr">
         <is>
-          <t>1Q 엔비디아알파벳미국채혼합50</t>
+          <t>1Q 미국배당TOP30</t>
         </is>
       </c>
       <c r="B77" s="39" t="inlineStr">
         <is>
-          <t>0224X0</t>
+          <t>0004G0</t>
         </is>
       </c>
       <c r="C77" s="39" t="inlineStr">
@@ -6599,22 +6974,28 @@
         </is>
       </c>
       <c r="D77" s="40" t="n">
-        <v>9620</v>
+        <v>8825</v>
       </c>
       <c r="E77" s="40" t="n">
-        <v>27417000000</v>
-      </c>
-      <c r="F77" s="40" t="n"/>
+        <v>13237500000</v>
+      </c>
+      <c r="F77" s="40" t="n">
+        <v>90427309</v>
+      </c>
       <c r="G77" s="41" t="n">
-        <v>0.005663</v>
-      </c>
-      <c r="H77" s="41" t="n"/>
+        <v>0.004354</v>
+      </c>
+      <c r="H77" s="41" t="n">
+        <v>0.1577</v>
+      </c>
       <c r="I77" s="41" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="J77" s="41" t="n"/>
+        <v>0.0028</v>
+      </c>
+      <c r="J77" s="41" t="n">
+        <v>0.034901</v>
+      </c>
       <c r="K77" s="40" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L77" s="39" t="inlineStr">
         <is>
@@ -6628,29 +7009,34 @@
       </c>
       <c r="N77" s="39" t="inlineStr">
         <is>
-          <t>순자산 274억(기준 300억 미만), 거래대금 미확인, 변동성 산출 불가(시세 37일치뿐), 분배 이력 1개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>순자산 132억(기준 300억 미만), 60일 거래대금 0.9억(기준 5억 미만)</t>
         </is>
       </c>
       <c r="O77" s="39" t="inlineStr">
         <is>
-          <t>KEDI Nvidia Alphabet U.S. Short-Term Treasury Balanced 50 In</t>
+          <t>Solactive U.S. Dividend 30 Index PR</t>
         </is>
       </c>
       <c r="P77" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q77" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="39" t="inlineStr">
         <is>
-          <t>1Q 코리아밸류업</t>
+          <t>1Q 엔비디아알파벳미국채혼합50</t>
         </is>
       </c>
       <c r="B78" s="39" t="inlineStr">
         <is>
-          <t>495330</t>
+          <t>0224X0</t>
         </is>
       </c>
       <c r="C78" s="39" t="inlineStr">
@@ -6659,28 +7045,22 @@
         </is>
       </c>
       <c r="D78" s="40" t="n">
-        <v>31205</v>
+        <v>9620</v>
       </c>
       <c r="E78" s="40" t="n">
-        <v>134181500000</v>
-      </c>
-      <c r="F78" s="40" t="n">
-        <v>608840211</v>
-      </c>
+        <v>27417000000</v>
+      </c>
+      <c r="F78" s="40" t="n"/>
       <c r="G78" s="41" t="n">
-        <v>0.00091</v>
-      </c>
-      <c r="H78" s="41" t="n">
-        <v>0.5262</v>
-      </c>
+        <v>0.005663</v>
+      </c>
+      <c r="H78" s="41" t="n"/>
       <c r="I78" s="41" t="n">
         <v>0.0012</v>
       </c>
-      <c r="J78" s="41" t="n">
-        <v>0.011825</v>
-      </c>
+      <c r="J78" s="41" t="n"/>
       <c r="K78" s="40" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L78" s="39" t="inlineStr">
         <is>
@@ -6694,57 +7074,64 @@
       </c>
       <c r="N78" s="39" t="inlineStr">
         <is>
-          <t>변동성 52.6%(1년 기준, 기준 35% 초과)</t>
+          <t>순자산 274억(기준 300억 미만), 거래대금 미확인, 변동성 산출 불가(시세 37일치뿐), 분배 이력 1개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O78" s="39" t="inlineStr">
         <is>
-          <t>코리아 밸류업 지수</t>
+          <t>KEDI Nvidia Alphabet U.S. Short-Term Treasury Balanced 50 In</t>
         </is>
       </c>
       <c r="P78" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q78" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="39" t="inlineStr">
         <is>
-          <t>ACE 고배당주</t>
+          <t>1Q 코리아밸류업</t>
         </is>
       </c>
       <c r="B79" s="39" t="inlineStr">
         <is>
-          <t>0139P0</t>
+          <t>495330</t>
         </is>
       </c>
       <c r="C79" s="39" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>하나자산운용</t>
         </is>
       </c>
       <c r="D79" s="40" t="n">
-        <v>13440</v>
+        <v>31205</v>
       </c>
       <c r="E79" s="40" t="n">
-        <v>49728000000</v>
+        <v>134181500000</v>
       </c>
       <c r="F79" s="40" t="n">
-        <v>612779217</v>
+        <v>608840211</v>
       </c>
       <c r="G79" s="41" t="n">
-        <v>0.002439</v>
+        <v>0.00091</v>
       </c>
       <c r="H79" s="41" t="n">
-        <v>0.3903</v>
+        <v>0.5262</v>
       </c>
       <c r="I79" s="41" t="n">
-        <v>0.0038</v>
-      </c>
-      <c r="J79" s="41" t="n"/>
+        <v>0.0012</v>
+      </c>
+      <c r="J79" s="41" t="n">
+        <v>0.011825</v>
+      </c>
       <c r="K79" s="40" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L79" s="39" t="inlineStr">
         <is>
@@ -6758,29 +7145,34 @@
       </c>
       <c r="N79" s="39" t="inlineStr">
         <is>
-          <t>변동성 39.0%(184거래일 기준, 기준 35% 초과), 분배 이력 9개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 52.6%(1년 기준, 기준 35% 초과)</t>
         </is>
       </c>
       <c r="O79" s="39" t="inlineStr">
         <is>
-          <t>KRX-Akros 고배당주 20 지수</t>
+          <t>코리아 밸류업 지수</t>
         </is>
       </c>
       <c r="P79" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q79" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="39" t="inlineStr">
         <is>
-          <t>ACE 고배당주Plus커버드콜액티브</t>
+          <t>ACE 고배당주</t>
         </is>
       </c>
       <c r="B80" s="39" t="inlineStr">
         <is>
-          <t>0199C0</t>
+          <t>0139P0</t>
         </is>
       </c>
       <c r="C80" s="39" t="inlineStr">
@@ -6789,26 +7181,26 @@
         </is>
       </c>
       <c r="D80" s="40" t="n">
-        <v>9245</v>
+        <v>13440</v>
       </c>
       <c r="E80" s="40" t="n">
-        <v>138675000000</v>
+        <v>49728000000</v>
       </c>
       <c r="F80" s="40" t="n">
-        <v>6365628474</v>
+        <v>612779217</v>
       </c>
       <c r="G80" s="41" t="n">
-        <v>0.004522</v>
+        <v>0.002439</v>
       </c>
       <c r="H80" s="41" t="n">
-        <v>0.3598</v>
+        <v>0.3903</v>
       </c>
       <c r="I80" s="41" t="n">
-        <v>0.0179</v>
+        <v>0.0038</v>
       </c>
       <c r="J80" s="41" t="n"/>
       <c r="K80" s="40" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L80" s="39" t="inlineStr">
         <is>
@@ -6822,29 +7214,34 @@
       </c>
       <c r="N80" s="39" t="inlineStr">
         <is>
-          <t>변동성 36.0%(74거래일 기준, 기준 35% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 39.0%(184거래일 기준, 기준 35% 초과), 분배 이력 9개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O80" s="39" t="inlineStr">
         <is>
-          <t>KRX-Akros 고배당주 20 위클리 고정 30% 커버드콜 지수</t>
+          <t>KRX-Akros 고배당주 20 지수</t>
         </is>
       </c>
       <c r="P80" s="39" t="inlineStr">
         <is>
-          <t>커버드콜</t>
+          <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q80" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="39" t="inlineStr">
         <is>
-          <t>ACE 리츠부동산인프라액티브</t>
+          <t>ACE 고배당주Plus커버드콜액티브</t>
         </is>
       </c>
       <c r="B81" s="39" t="inlineStr">
         <is>
-          <t>0153P0</t>
+          <t>0199C0</t>
         </is>
       </c>
       <c r="C81" s="39" t="inlineStr">
@@ -6853,26 +7250,26 @@
         </is>
       </c>
       <c r="D81" s="40" t="n">
-        <v>9410</v>
+        <v>9245</v>
       </c>
       <c r="E81" s="40" t="n">
-        <v>13644500000</v>
+        <v>138675000000</v>
       </c>
       <c r="F81" s="40" t="n">
-        <v>71992972</v>
+        <v>6365628474</v>
       </c>
       <c r="G81" s="41" t="n">
-        <v>0.001217</v>
+        <v>0.004522</v>
       </c>
       <c r="H81" s="41" t="n">
-        <v>0.1906</v>
+        <v>0.3598</v>
       </c>
       <c r="I81" s="41" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0179</v>
       </c>
       <c r="J81" s="41" t="n"/>
       <c r="K81" s="40" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L81" s="39" t="inlineStr">
         <is>
@@ -6886,29 +7283,34 @@
       </c>
       <c r="N81" s="39" t="inlineStr">
         <is>
-          <t>순자산 136억(기준 300억 미만), 60일 거래대금 0.7억(기준 5억 미만), 분배 이력 7개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+          <t>변동성 36.0%(74거래일 기준, 기준 35% 초과), 분배 이력 3개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O81" s="39" t="inlineStr">
         <is>
-          <t>FnGuide 맥쿼리인프라 배당 리츠 지수</t>
+          <t>KRX-Akros 고배당주 20 위클리 고정 30% 커버드콜 지수</t>
         </is>
       </c>
       <c r="P81" s="39" t="inlineStr">
         <is>
-          <t>월배당</t>
+          <t>커버드콜</t>
+        </is>
+      </c>
+      <c r="Q81" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="39" t="inlineStr">
         <is>
-          <t>ACE 미국10년국채액티브(H)</t>
+          <t>ACE 리츠부동산인프라액티브</t>
         </is>
       </c>
       <c r="B82" s="39" t="inlineStr">
         <is>
-          <t>0085N0</t>
+          <t>0153P0</t>
         </is>
       </c>
       <c r="C82" s="39" t="inlineStr">
@@ -6917,28 +7319,26 @@
         </is>
       </c>
       <c r="D82" s="40" t="n">
-        <v>9600</v>
+        <v>9410</v>
       </c>
       <c r="E82" s="40" t="n">
-        <v>34560000000</v>
+        <v>13644500000</v>
       </c>
       <c r="F82" s="40" t="n">
-        <v>284127203</v>
+        <v>71992972</v>
       </c>
       <c r="G82" s="41" t="n">
-        <v>0.002432</v>
+        <v>0.001217</v>
       </c>
       <c r="H82" s="41" t="n">
-        <v>0.044</v>
+        <v>0.1906</v>
       </c>
       <c r="I82" s="41" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="J82" s="41" t="n">
-        <v>0.038125</v>
-      </c>
+        <v>0.005699999999999999</v>
+      </c>
+      <c r="J82" s="41" t="n"/>
       <c r="K82" s="40" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L82" s="39" t="inlineStr">
         <is>
@@ -6952,29 +7352,34 @@
       </c>
       <c r="N82" s="39" t="inlineStr">
         <is>
-          <t>60일 거래대금 2.8억(기준 5억 미만)</t>
+          <t>순자산 136억(기준 300억 미만), 60일 거래대금 0.7억(기준 5억 미만), 분배 이력 7개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
         </is>
       </c>
       <c r="O82" s="39" t="inlineStr">
         <is>
-          <t>ICE U.S.Treasury 7-10 Year Bond Index</t>
+          <t>FnGuide 맥쿼리인프라 배당 리츠 지수</t>
         </is>
       </c>
       <c r="P82" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q82" s="39" t="inlineStr">
+        <is>
+          <t>부동산</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="39" t="inlineStr">
         <is>
-          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
+          <t>ACE 미국10년국채액티브(H)</t>
         </is>
       </c>
       <c r="B83" s="39" t="inlineStr">
         <is>
-          <t>480040</t>
+          <t>0085N0</t>
         </is>
       </c>
       <c r="C83" s="39" t="inlineStr">
@@ -6983,32 +7388,32 @@
         </is>
       </c>
       <c r="D83" s="40" t="n">
-        <v>13340</v>
+        <v>9600</v>
       </c>
       <c r="E83" s="40" t="n">
-        <v>181424000000</v>
+        <v>34560000000</v>
       </c>
       <c r="F83" s="40" t="n">
-        <v>3418835883</v>
+        <v>284127203</v>
       </c>
       <c r="G83" s="41" t="n">
-        <v>0.005406999999999999</v>
+        <v>0.002432</v>
       </c>
       <c r="H83" s="41" t="n">
-        <v>0.4411</v>
+        <v>0.044</v>
       </c>
       <c r="I83" s="41" t="n">
-        <v>0.0303</v>
+        <v>0.0033</v>
       </c>
       <c r="J83" s="41" t="n">
-        <v>0.261019</v>
+        <v>0.038125</v>
       </c>
       <c r="K83" s="40" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="L83" s="39" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="M83" s="39" t="inlineStr">
@@ -7018,29 +7423,34 @@
       </c>
       <c r="N83" s="39" t="inlineStr">
         <is>
-          <t>변동성 44.1%(1년 기준, 기준 35% 초과)</t>
+          <t>60일 거래대금 2.8억(기준 5억 미만)</t>
         </is>
       </c>
       <c r="O83" s="39" t="inlineStr">
         <is>
-          <t>Bloomberg US Listed Semiconductor Premium(QQQ) Decrement 15%</t>
+          <t>ICE U.S.Treasury 7-10 Year Bond Index</t>
         </is>
       </c>
       <c r="P83" s="39" t="inlineStr">
         <is>
-          <t>커버드콜</t>
+          <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q83" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="39" t="inlineStr">
         <is>
-          <t>ACE 미국배당다우존스</t>
+          <t>ACE 미국반도체데일리타겟커버드콜(합성)</t>
         </is>
       </c>
       <c r="B84" s="39" t="inlineStr">
         <is>
-          <t>402970</t>
+          <t>480040</t>
         </is>
       </c>
       <c r="C84" s="39" t="inlineStr">
@@ -7048,15 +7458,35 @@
           <t>한국투신운용(ETF)</t>
         </is>
       </c>
-      <c r="D84" s="40" t="n"/>
-      <c r="E84" s="40" t="n"/>
-      <c r="F84" s="40" t="n"/>
-      <c r="G84" s="41" t="n"/>
-      <c r="H84" s="41" t="n"/>
-      <c r="I84" s="41" t="n"/>
-      <c r="J84" s="41" t="n"/>
-      <c r="K84" s="40" t="n"/>
-      <c r="L84" s="39" t="n"/>
+      <c r="D84" s="40" t="n">
+        <v>13340</v>
+      </c>
+      <c r="E84" s="40" t="n">
+        <v>181424000000</v>
+      </c>
+      <c r="F84" s="40" t="n">
+        <v>3418835883</v>
+      </c>
+      <c r="G84" s="41" t="n">
+        <v>0.005406999999999999</v>
+      </c>
+      <c r="H84" s="41" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="I84" s="41" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="J84" s="41" t="n">
+        <v>0.261019</v>
+      </c>
+      <c r="K84" s="40" t="n">
+        <v>29</v>
+      </c>
+      <c r="L84" s="39" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
       <c r="M84" s="39" t="inlineStr">
         <is>
           <t>제외</t>
@@ -7064,13 +7494,22 @@
       </c>
       <c r="N84" s="39" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 0)</t>
-        </is>
-      </c>
-      <c r="O84" s="39" t="inlineStr"/>
+          <t>변동성 44.1%(1년 기준, 기준 35% 초과)</t>
+        </is>
+      </c>
+      <c r="O84" s="39" t="inlineStr">
+        <is>
+          <t>Bloomberg US Listed Semiconductor Premium(QQQ) Decrement 15%</t>
+        </is>
+      </c>
       <c r="P84" s="39" t="inlineStr">
         <is>
-          <t>월배당</t>
+          <t>커버드콜</t>
+        </is>
+      </c>
+      <c r="Q84" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -7139,6 +7578,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q85" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="39" t="inlineStr">
@@ -7205,6 +7649,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q86" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="39" t="inlineStr">
@@ -7271,6 +7720,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q87" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="39" t="inlineStr">
@@ -7337,6 +7791,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q88" s="39" t="inlineStr">
+        <is>
+          <t>부동산</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="39" t="inlineStr">
@@ -7401,6 +7860,11 @@
       <c r="P89" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q89" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
         </is>
       </c>
     </row>
@@ -7457,6 +7921,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q90" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="39" t="inlineStr">
@@ -7521,6 +7990,11 @@
       <c r="P91" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q91" s="39" t="inlineStr">
+        <is>
+          <t>부동산</t>
         </is>
       </c>
     </row>
@@ -7587,6 +8061,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q92" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="39" t="inlineStr">
@@ -7651,6 +8130,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q93" s="39" t="inlineStr">
+        <is>
+          <t>부동산</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="39" t="inlineStr">
@@ -7715,6 +8199,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q94" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="39" t="inlineStr">
@@ -7781,6 +8270,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q95" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="39" t="inlineStr">
@@ -7847,6 +8341,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q96" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="39" t="inlineStr">
@@ -7911,6 +8410,11 @@
       <c r="P97" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q97" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -7977,6 +8481,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q98" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="39" t="inlineStr">
@@ -8041,6 +8550,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q99" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="39" t="inlineStr">
@@ -8105,6 +8619,11 @@
       <c r="P100" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q100" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
         </is>
       </c>
     </row>
@@ -8171,6 +8690,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q101" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="39" t="inlineStr">
@@ -8235,6 +8759,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q102" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="39" t="inlineStr">
@@ -8299,6 +8828,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q103" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="39" t="inlineStr">
@@ -8363,6 +8897,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q104" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="39" t="inlineStr">
@@ -8427,6 +8966,11 @@
       <c r="P105" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q105" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -8491,6 +9035,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q106" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="39" t="inlineStr">
@@ -8555,6 +9104,11 @@
       <c r="P107" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q107" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
         </is>
       </c>
     </row>
@@ -8621,6 +9175,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q108" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="39" t="inlineStr">
@@ -8685,6 +9244,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q109" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="39" t="inlineStr">
@@ -8751,6 +9315,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q110" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="39" t="inlineStr">
@@ -8815,6 +9384,11 @@
       <c r="P111" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q111" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -8879,6 +9453,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q112" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="39" t="inlineStr">
@@ -8945,6 +9524,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q113" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="39" t="inlineStr">
@@ -9009,6 +9593,11 @@
       <c r="P114" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q114" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -9073,6 +9662,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q115" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="39" t="inlineStr">
@@ -9133,6 +9727,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q116" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="39" t="inlineStr">
@@ -9199,6 +9798,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q117" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="39" t="inlineStr">
@@ -9265,6 +9869,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q118" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="39" t="inlineStr">
@@ -9329,6 +9938,11 @@
       <c r="P119" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q119" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -9393,6 +10007,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q120" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="39" t="inlineStr">
@@ -9459,6 +10078,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q121" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="39" t="inlineStr">
@@ -9525,6 +10149,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q122" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="39" t="inlineStr">
@@ -9591,6 +10220,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q123" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="39" t="inlineStr">
@@ -9655,6 +10289,11 @@
       <c r="P124" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q124" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
         </is>
       </c>
     </row>
@@ -9721,6 +10360,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q125" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="39" t="inlineStr">
@@ -9787,6 +10431,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q126" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="39" t="inlineStr">
@@ -9853,6 +10502,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q127" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="39" t="inlineStr">
@@ -9917,6 +10571,11 @@
       <c r="P128" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q128" s="39" t="inlineStr">
+        <is>
+          <t>부동산</t>
         </is>
       </c>
     </row>
@@ -9983,6 +10642,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q129" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="39" t="inlineStr">
@@ -10047,6 +10711,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q130" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="39" t="inlineStr">
@@ -10111,6 +10780,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q131" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="39" t="inlineStr">
@@ -10177,6 +10851,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q132" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="39" t="inlineStr">
@@ -10241,6 +10920,11 @@
       <c r="P133" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q133" s="39" t="inlineStr">
+        <is>
+          <t>부동산</t>
         </is>
       </c>
     </row>
@@ -10307,6 +10991,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q134" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="39" t="inlineStr">
@@ -10371,6 +11060,11 @@
       <c r="P135" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q135" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -10437,6 +11131,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q136" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="39" t="inlineStr">
@@ -10501,6 +11200,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q137" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="39" t="inlineStr">
@@ -10565,6 +11269,11 @@
       <c r="P138" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q138" s="39" t="inlineStr">
+        <is>
+          <t>부동산</t>
         </is>
       </c>
     </row>
@@ -10631,6 +11340,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q139" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="39" t="inlineStr">
@@ -10695,6 +11409,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q140" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="39" t="inlineStr">
@@ -10759,6 +11478,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q141" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="39" t="inlineStr">
@@ -10825,6 +11549,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q142" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="39" t="inlineStr">
@@ -10891,6 +11620,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q143" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="39" t="inlineStr">
@@ -10957,6 +11691,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q144" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="39" t="inlineStr">
@@ -11023,6 +11762,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q145" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="39" t="inlineStr">
@@ -11040,33 +11784,15 @@
           <t>한화자산운용</t>
         </is>
       </c>
-      <c r="D146" s="40" t="n">
-        <v>6465</v>
-      </c>
-      <c r="E146" s="40" t="n">
-        <v>4525500000</v>
-      </c>
-      <c r="F146" s="40" t="n">
-        <v>28634091</v>
-      </c>
-      <c r="G146" s="41" t="n">
-        <v>0.01153</v>
-      </c>
-      <c r="H146" s="41" t="n">
-        <v>0.2719</v>
-      </c>
-      <c r="I146" s="41" t="n">
-        <v>0.0125</v>
-      </c>
+      <c r="D146" s="40" t="n"/>
+      <c r="E146" s="40" t="n"/>
+      <c r="F146" s="40" t="n"/>
+      <c r="G146" s="41" t="n"/>
+      <c r="H146" s="41" t="n"/>
+      <c r="I146" s="41" t="n"/>
       <c r="J146" s="41" t="n"/>
-      <c r="K146" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="L146" s="39" t="inlineStr">
-        <is>
-          <t>20260828</t>
-        </is>
-      </c>
+      <c r="K146" s="40" t="n"/>
+      <c r="L146" s="39" t="n"/>
       <c r="M146" s="39" t="inlineStr">
         <is>
           <t>제외</t>
@@ -11074,19 +11800,16 @@
       </c>
       <c r="N146" s="39" t="inlineStr">
         <is>
-          <t>순자산 45억(기준 300억 미만), 60일 거래대금 0.3억(기준 5억 미만), 분배 이력 9개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
-        </is>
-      </c>
-      <c r="O146" s="39" t="inlineStr">
-        <is>
-          <t>HSTECH 15% Target Premium Weekly Covered Call Index</t>
-        </is>
-      </c>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 403)</t>
+        </is>
+      </c>
+      <c r="O146" s="39" t="inlineStr"/>
       <c r="P146" s="39" t="inlineStr">
         <is>
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q146" s="39" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="39" t="inlineStr">
@@ -11104,35 +11827,15 @@
           <t>한화자산운용</t>
         </is>
       </c>
-      <c r="D147" s="40" t="n">
-        <v>31110</v>
-      </c>
-      <c r="E147" s="40" t="n">
-        <v>83997000000</v>
-      </c>
-      <c r="F147" s="40" t="n">
-        <v>190084083</v>
-      </c>
-      <c r="G147" s="41" t="n">
-        <v>0.001792</v>
-      </c>
-      <c r="H147" s="41" t="n">
-        <v>0.5246999999999999</v>
-      </c>
-      <c r="I147" s="41" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="J147" s="41" t="n">
-        <v>0.010125</v>
-      </c>
-      <c r="K147" s="40" t="n">
-        <v>21</v>
-      </c>
-      <c r="L147" s="39" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
+      <c r="D147" s="40" t="n"/>
+      <c r="E147" s="40" t="n"/>
+      <c r="F147" s="40" t="n"/>
+      <c r="G147" s="41" t="n"/>
+      <c r="H147" s="41" t="n"/>
+      <c r="I147" s="41" t="n"/>
+      <c r="J147" s="41" t="n"/>
+      <c r="K147" s="40" t="n"/>
+      <c r="L147" s="39" t="n"/>
       <c r="M147" s="39" t="inlineStr">
         <is>
           <t>제외</t>
@@ -11140,19 +11843,16 @@
       </c>
       <c r="N147" s="39" t="inlineStr">
         <is>
-          <t>60일 거래대금 1.9억(기준 5억 미만), 변동성 52.5%(1년 기준, 기준 35% 초과)</t>
-        </is>
-      </c>
-      <c r="O147" s="39" t="inlineStr">
-        <is>
-          <t>코리아 밸류업 지수</t>
-        </is>
-      </c>
+          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 403)</t>
+        </is>
+      </c>
+      <c r="O147" s="39" t="inlineStr"/>
       <c r="P147" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q147" s="39" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="39" t="inlineStr">
@@ -11217,6 +11917,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q148" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="39" t="inlineStr">
@@ -11283,6 +11988,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q149" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="39" t="inlineStr">
@@ -11349,6 +12059,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q150" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="39" t="inlineStr">
@@ -11415,6 +12130,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q151" s="39" t="inlineStr">
+        <is>
+          <t>부동산</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="39" t="inlineStr">
@@ -11481,6 +12201,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q152" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="39" t="inlineStr">
@@ -11547,6 +12272,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q153" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="39" t="inlineStr">
@@ -11613,6 +12343,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q154" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="39" t="inlineStr">
@@ -11677,6 +12412,11 @@
       <c r="P155" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q155" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -11743,6 +12483,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q156" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="39" t="inlineStr">
@@ -11807,6 +12552,11 @@
       <c r="P157" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q157" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -11873,6 +12623,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q158" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="39" t="inlineStr">
@@ -11939,6 +12694,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q159" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="39" t="inlineStr">
@@ -12005,6 +12765,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q160" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="39" t="inlineStr">
@@ -12071,6 +12836,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q161" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="39" t="inlineStr">
@@ -12137,6 +12907,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q162" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="39" t="inlineStr">
@@ -12201,6 +12976,11 @@
       <c r="P163" s="39" t="inlineStr">
         <is>
           <t>커버드콜</t>
+        </is>
+      </c>
+      <c r="Q163" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -12263,6 +13043,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q164" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="39" t="inlineStr">
@@ -12327,6 +13112,11 @@
       <c r="P165" s="39" t="inlineStr">
         <is>
           <t>커버드콜</t>
+        </is>
+      </c>
+      <c r="Q165" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
         </is>
       </c>
     </row>
@@ -12393,6 +13183,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q166" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="39" t="inlineStr">
@@ -12459,6 +13254,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q167" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="39" t="inlineStr">
@@ -12525,6 +13325,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q168" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="39" t="inlineStr">
@@ -12591,6 +13396,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q169" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="39" t="inlineStr">
@@ -12655,6 +13465,11 @@
       <c r="P170" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q170" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -12721,6 +13536,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q171" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="39" t="inlineStr">
@@ -12785,6 +13605,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q172" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="39" t="inlineStr">
@@ -12849,6 +13674,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q173" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="39" t="inlineStr">
@@ -12915,6 +13745,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q174" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="39" t="inlineStr">
@@ -12981,6 +13816,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q175" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="39" t="inlineStr">
@@ -13047,6 +13887,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q176" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="39" t="inlineStr">
@@ -13113,6 +13958,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q177" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="39" t="inlineStr">
@@ -13179,6 +14029,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q178" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="39" t="inlineStr">
@@ -13245,6 +14100,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q179" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="39" t="inlineStr">
@@ -13311,6 +14171,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q180" s="39" t="inlineStr">
+        <is>
+          <t>부동산</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="39" t="inlineStr">
@@ -13377,6 +14242,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q181" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="39" t="inlineStr">
@@ -13441,6 +14311,11 @@
       <c r="P182" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q182" s="39" t="inlineStr">
+        <is>
+          <t>부동산</t>
         </is>
       </c>
     </row>
@@ -13497,6 +14372,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q183" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="39" t="inlineStr">
@@ -13563,6 +14443,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q184" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="39" t="inlineStr">
@@ -13629,6 +14514,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q185" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="39" t="inlineStr">
@@ -13695,6 +14585,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q186" s="39" t="inlineStr">
+        <is>
+          <t>채권</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="39" t="inlineStr">
@@ -13712,15 +14607,33 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="D187" s="40" t="n"/>
-      <c r="E187" s="40" t="n"/>
-      <c r="F187" s="40" t="n"/>
-      <c r="G187" s="41" t="n"/>
-      <c r="H187" s="41" t="n"/>
-      <c r="I187" s="41" t="n"/>
+      <c r="D187" s="40" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E187" s="40" t="n">
+        <v>836000000000</v>
+      </c>
+      <c r="F187" s="40" t="n">
+        <v>31458730663</v>
+      </c>
+      <c r="G187" s="41" t="n">
+        <v>0.005719999999999999</v>
+      </c>
+      <c r="H187" s="41" t="n">
+        <v>0.9140999999999999</v>
+      </c>
+      <c r="I187" s="41" t="n">
+        <v>0.0155</v>
+      </c>
       <c r="J187" s="41" t="n"/>
-      <c r="K187" s="40" t="n"/>
-      <c r="L187" s="39" t="n"/>
+      <c r="K187" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="L187" s="39" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
       <c r="M187" s="39" t="inlineStr">
         <is>
           <t>제외</t>
@@ -13728,13 +14641,22 @@
       </c>
       <c r="N187" s="39" t="inlineStr">
         <is>
-          <t>수집 실패(세 번 다시 물었으나 답이 오지 않음: HTTP 403)</t>
-        </is>
-      </c>
-      <c r="O187" s="39" t="inlineStr"/>
+          <t>변동성 91.4%(101거래일 기준, 기준 35% 초과), 분배 이력 5개월(기준 12개월 미만), 연 분배율 산출 불가(12회 분배 이력 없음)</t>
+        </is>
+      </c>
+      <c r="O187" s="39" t="inlineStr">
+        <is>
+          <t>FnGuide 반도체 TOP10 Capped 지수</t>
+        </is>
+      </c>
       <c r="P187" s="39" t="inlineStr">
         <is>
           <t>커버드콜</t>
+        </is>
+      </c>
+      <c r="Q187" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -13801,6 +14723,11 @@
       <c r="P188" s="39" t="inlineStr">
         <is>
           <t>커버드콜</t>
+        </is>
+      </c>
+      <c r="Q188" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
         </is>
       </c>
     </row>
@@ -13857,6 +14784,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q189" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="39" t="inlineStr">
@@ -13921,6 +14853,11 @@
       <c r="P190" s="39" t="inlineStr">
         <is>
           <t>커버드콜</t>
+        </is>
+      </c>
+      <c r="Q190" s="39" t="inlineStr">
+        <is>
+          <t>멀티에셋</t>
         </is>
       </c>
     </row>
@@ -13987,6 +14924,11 @@
           <t>커버드콜</t>
         </is>
       </c>
+      <c r="Q191" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="39" t="inlineStr">
@@ -14053,6 +14995,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q192" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="39" t="inlineStr">
@@ -14119,6 +15066,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q193" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="39" t="inlineStr">
@@ -14185,6 +15137,11 @@
           <t>월배당</t>
         </is>
       </c>
+      <c r="Q194" s="39" t="inlineStr">
+        <is>
+          <t>주식</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="39" t="inlineStr">
@@ -14249,6 +15206,11 @@
       <c r="P195" s="39" t="inlineStr">
         <is>
           <t>월배당</t>
+        </is>
+      </c>
+      <c r="Q195" s="39" t="inlineStr">
+        <is>
+          <t>부동산</t>
         </is>
       </c>
     </row>
@@ -14411,14 +15373,14 @@
     <row r="23" ht="19" customHeight="1">
       <c r="B23" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 채택 72종목 — 유동성·변동성 기준을 통과한 국내 상장 월배당 ETF</t>
+          <t xml:space="preserve">     · 채택 73종목 — 유동성·변동성 기준을 통과한 국내 상장 월배당 ETF</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="B24" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">     · 제외 120종목 — 사유는 [ETF데이터] 장 '제외 사유' 칸에 적혀 있습니다.</t>
+          <t xml:space="preserve">     · 제외 119종목 — 사유는 [ETF데이터] 장 '제외 사유' 칸에 적혀 있습니다.</t>
         </is>
       </c>
     </row>

--- a/고객제안서_월배당ETF.xlsx
+++ b/고객제안서_월배당ETF.xlsx
@@ -1469,8 +1469,9 @@
         <f>IF(담긴수=0,"TIGER 미국배당다우존스",IFERROR(INDEX(담긴목록,1),""))</f>
         <v/>
       </c>
-      <c r="C20" s="22" t="n">
-        <v>100</v>
+      <c r="C20" s="22">
+        <f>IF($B20="","",IF($C$12="비율",IF(1&lt;MAX(담긴수,1),ROUND(100/MAX(담긴수,1),2),100-ROUND(100/MAX(담긴수,1),2)*(MAX(담긴수,1)-1)),IF(1&lt;MAX(담긴수,1),ROUNDDOWN($C$11/MAX(담긴수,1),0),$C$11-ROUNDDOWN($C$11/MAX(담긴수,1),0)*(MAX(담긴수,1)-1))))</f>
+        <v/>
       </c>
       <c r="D20" s="23">
         <f>IF($K20=0,0,IF($C$12="비율",ROUND($C$11*$C20/100,0),$C20))</f>
@@ -1514,7 +1515,10 @@
         <f>IF(담긴수=0,"",IFERROR(INDEX(담긴목록,2),""))</f>
         <v/>
       </c>
-      <c r="C21" s="22" t="n"/>
+      <c r="C21" s="22">
+        <f>IF($B21="","",IF($C$12="비율",IF(2&lt;MAX(담긴수,1),ROUND(100/MAX(담긴수,1),2),100-ROUND(100/MAX(담긴수,1),2)*(MAX(담긴수,1)-1)),IF(2&lt;MAX(담긴수,1),ROUNDDOWN($C$11/MAX(담긴수,1),0),$C$11-ROUNDDOWN($C$11/MAX(담긴수,1),0)*(MAX(담긴수,1)-1))))</f>
+        <v/>
+      </c>
       <c r="D21" s="26">
         <f>IF($K21=0,0,IF($C$12="비율",ROUND($C$11*$C21/100,0),$C21))</f>
         <v/>
@@ -1557,7 +1561,10 @@
         <f>IF(담긴수=0,"",IFERROR(INDEX(담긴목록,3),""))</f>
         <v/>
       </c>
-      <c r="C22" s="22" t="n"/>
+      <c r="C22" s="22">
+        <f>IF($B22="","",IF($C$12="비율",IF(3&lt;MAX(담긴수,1),ROUND(100/MAX(담긴수,1),2),100-ROUND(100/MAX(담긴수,1),2)*(MAX(담긴수,1)-1)),IF(3&lt;MAX(담긴수,1),ROUNDDOWN($C$11/MAX(담긴수,1),0),$C$11-ROUNDDOWN($C$11/MAX(담긴수,1),0)*(MAX(담긴수,1)-1))))</f>
+        <v/>
+      </c>
       <c r="D22" s="23">
         <f>IF($K22=0,0,IF($C$12="비율",ROUND($C$11*$C22/100,0),$C22))</f>
         <v/>
@@ -1600,7 +1607,10 @@
         <f>IF(담긴수=0,"",IFERROR(INDEX(담긴목록,4),""))</f>
         <v/>
       </c>
-      <c r="C23" s="22" t="n"/>
+      <c r="C23" s="22">
+        <f>IF($B23="","",IF($C$12="비율",IF(4&lt;MAX(담긴수,1),ROUND(100/MAX(담긴수,1),2),100-ROUND(100/MAX(담긴수,1),2)*(MAX(담긴수,1)-1)),IF(4&lt;MAX(담긴수,1),ROUNDDOWN($C$11/MAX(담긴수,1),0),$C$11-ROUNDDOWN($C$11/MAX(담긴수,1),0)*(MAX(담긴수,1)-1))))</f>
+        <v/>
+      </c>
       <c r="D23" s="26">
         <f>IF($K23=0,0,IF($C$12="비율",ROUND($C$11*$C23/100,0),$C23))</f>
         <v/>
@@ -1643,7 +1653,10 @@
         <f>IF(담긴수=0,"",IFERROR(INDEX(담긴목록,5),""))</f>
         <v/>
       </c>
-      <c r="C24" s="22" t="n"/>
+      <c r="C24" s="22">
+        <f>IF($B24="","",IF($C$12="비율",IF(5&lt;MAX(담긴수,1),ROUND(100/MAX(담긴수,1),2),100-ROUND(100/MAX(담긴수,1),2)*(MAX(담긴수,1)-1)),IF(5&lt;MAX(담긴수,1),ROUNDDOWN($C$11/MAX(담긴수,1),0),$C$11-ROUNDDOWN($C$11/MAX(담긴수,1),0)*(MAX(담긴수,1)-1))))</f>
+        <v/>
+      </c>
       <c r="D24" s="23">
         <f>IF($K24=0,0,IF($C$12="비율",ROUND($C$11*$C24/100,0),$C24))</f>
         <v/>
@@ -1686,7 +1699,10 @@
         <f>IF(담긴수=0,"",IFERROR(INDEX(담긴목록,6),""))</f>
         <v/>
       </c>
-      <c r="C25" s="22" t="n"/>
+      <c r="C25" s="22">
+        <f>IF($B25="","",IF($C$12="비율",IF(6&lt;MAX(담긴수,1),ROUND(100/MAX(담긴수,1),2),100-ROUND(100/MAX(담긴수,1),2)*(MAX(담긴수,1)-1)),IF(6&lt;MAX(담긴수,1),ROUNDDOWN($C$11/MAX(담긴수,1),0),$C$11-ROUNDDOWN($C$11/MAX(담긴수,1),0)*(MAX(담긴수,1)-1))))</f>
+        <v/>
+      </c>
       <c r="D25" s="26">
         <f>IF($K25=0,0,IF($C$12="비율",ROUND($C$11*$C25/100,0),$C25))</f>
         <v/>
@@ -1729,7 +1745,10 @@
         <f>IF(담긴수=0,"",IFERROR(INDEX(담긴목록,7),""))</f>
         <v/>
       </c>
-      <c r="C26" s="22" t="n"/>
+      <c r="C26" s="22">
+        <f>IF($B26="","",IF($C$12="비율",IF(7&lt;MAX(담긴수,1),ROUND(100/MAX(담긴수,1),2),100-ROUND(100/MAX(담긴수,1),2)*(MAX(담긴수,1)-1)),IF(7&lt;MAX(담긴수,1),ROUNDDOWN($C$11/MAX(담긴수,1),0),$C$11-ROUNDDOWN($C$11/MAX(담긴수,1),0)*(MAX(담긴수,1)-1))))</f>
+        <v/>
+      </c>
       <c r="D26" s="23">
         <f>IF($K26=0,0,IF($C$12="비율",ROUND($C$11*$C26/100,0),$C26))</f>
         <v/>
@@ -1772,7 +1791,10 @@
         <f>IF(담긴수=0,"",IFERROR(INDEX(담긴목록,8),""))</f>
         <v/>
       </c>
-      <c r="C27" s="22" t="n"/>
+      <c r="C27" s="22">
+        <f>IF($B27="","",IF($C$12="비율",IF(8&lt;MAX(담긴수,1),ROUND(100/MAX(담긴수,1),2),100-ROUND(100/MAX(담긴수,1),2)*(MAX(담긴수,1)-1)),IF(8&lt;MAX(담긴수,1),ROUNDDOWN($C$11/MAX(담긴수,1),0),$C$11-ROUNDDOWN($C$11/MAX(담긴수,1),0)*(MAX(담긴수,1)-1))))</f>
+        <v/>
+      </c>
       <c r="D27" s="26">
         <f>IF($K27=0,0,IF($C$12="비율",ROUND($C$11*$C27/100,0),$C27))</f>
         <v/>
@@ -1815,7 +1837,10 @@
         <f>IF(담긴수=0,"",IFERROR(INDEX(담긴목록,9),""))</f>
         <v/>
       </c>
-      <c r="C28" s="22" t="n"/>
+      <c r="C28" s="22">
+        <f>IF($B28="","",IF($C$12="비율",IF(9&lt;MAX(담긴수,1),ROUND(100/MAX(담긴수,1),2),100-ROUND(100/MAX(담긴수,1),2)*(MAX(담긴수,1)-1)),IF(9&lt;MAX(담긴수,1),ROUNDDOWN($C$11/MAX(담긴수,1),0),$C$11-ROUNDDOWN($C$11/MAX(담긴수,1),0)*(MAX(담긴수,1)-1))))</f>
+        <v/>
+      </c>
       <c r="D28" s="23">
         <f>IF($K28=0,0,IF($C$12="비율",ROUND($C$11*$C28/100,0),$C28))</f>
         <v/>
@@ -1858,7 +1883,10 @@
         <f>IF(담긴수=0,"",IFERROR(INDEX(담긴목록,10),""))</f>
         <v/>
       </c>
-      <c r="C29" s="22" t="n"/>
+      <c r="C29" s="22">
+        <f>IF($B29="","",IF($C$12="비율",IF(10&lt;MAX(담긴수,1),ROUND(100/MAX(담긴수,1),2),100-ROUND(100/MAX(담긴수,1),2)*(MAX(담긴수,1)-1)),IF(10&lt;MAX(담긴수,1),ROUNDDOWN($C$11/MAX(담긴수,1),0),$C$11-ROUNDDOWN($C$11/MAX(담긴수,1),0)*(MAX(담긴수,1)-1))))</f>
+        <v/>
+      </c>
       <c r="D29" s="26">
         <f>IF($K29=0,0,IF($C$12="비율",ROUND($C$11*$C29/100,0),$C29))</f>
         <v/>
@@ -3236,7 +3264,7 @@
         <v/>
       </c>
       <c r="H20" s="77">
-        <f>IF($K20=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K20))</f>
+        <f>IF($K20=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K20)/100000000)</f>
         <v/>
       </c>
       <c r="I20" s="73">
@@ -3287,7 +3315,7 @@
         <v/>
       </c>
       <c r="H21" s="83">
-        <f>IF($K21=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K21))</f>
+        <f>IF($K21=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K21)/100000000)</f>
         <v/>
       </c>
       <c r="I21" s="79">
@@ -3338,7 +3366,7 @@
         <v/>
       </c>
       <c r="H22" s="77">
-        <f>IF($K22=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K22))</f>
+        <f>IF($K22=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K22)/100000000)</f>
         <v/>
       </c>
       <c r="I22" s="73">
@@ -3389,7 +3417,7 @@
         <v/>
       </c>
       <c r="H23" s="83">
-        <f>IF($K23=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K23))</f>
+        <f>IF($K23=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K23)/100000000)</f>
         <v/>
       </c>
       <c r="I23" s="79">
@@ -3440,7 +3468,7 @@
         <v/>
       </c>
       <c r="H24" s="77">
-        <f>IF($K24=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K24))</f>
+        <f>IF($K24=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K24)/100000000)</f>
         <v/>
       </c>
       <c r="I24" s="73">
@@ -3491,7 +3519,7 @@
         <v/>
       </c>
       <c r="H25" s="83">
-        <f>IF($K25=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K25))</f>
+        <f>IF($K25=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K25)/100000000)</f>
         <v/>
       </c>
       <c r="I25" s="79">
@@ -3542,7 +3570,7 @@
         <v/>
       </c>
       <c r="H26" s="77">
-        <f>IF($K26=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K26))</f>
+        <f>IF($K26=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K26)/100000000)</f>
         <v/>
       </c>
       <c r="I26" s="73">
@@ -3593,7 +3621,7 @@
         <v/>
       </c>
       <c r="H27" s="83">
-        <f>IF($K27=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K27))</f>
+        <f>IF($K27=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K27)/100000000)</f>
         <v/>
       </c>
       <c r="I27" s="79">
@@ -3644,7 +3672,7 @@
         <v/>
       </c>
       <c r="H28" s="77">
-        <f>IF($K28=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K28))</f>
+        <f>IF($K28=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K28)/100000000)</f>
         <v/>
       </c>
       <c r="I28" s="73">
@@ -3695,7 +3723,7 @@
         <v/>
       </c>
       <c r="H29" s="83">
-        <f>IF($K29=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K29))</f>
+        <f>IF($K29=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K29)/100000000)</f>
         <v/>
       </c>
       <c r="I29" s="79">
@@ -3746,7 +3774,7 @@
         <v/>
       </c>
       <c r="H30" s="77">
-        <f>IF($K30=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K30))</f>
+        <f>IF($K30=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K30)/100000000)</f>
         <v/>
       </c>
       <c r="I30" s="73">
@@ -3797,7 +3825,7 @@
         <v/>
       </c>
       <c r="H31" s="83">
-        <f>IF($K31=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K31))</f>
+        <f>IF($K31=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K31)/100000000)</f>
         <v/>
       </c>
       <c r="I31" s="79">
@@ -3848,7 +3876,7 @@
         <v/>
       </c>
       <c r="H32" s="77">
-        <f>IF($K32=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K32))</f>
+        <f>IF($K32=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K32)/100000000)</f>
         <v/>
       </c>
       <c r="I32" s="73">
@@ -3899,7 +3927,7 @@
         <v/>
       </c>
       <c r="H33" s="83">
-        <f>IF($K33=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K33))</f>
+        <f>IF($K33=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K33)/100000000)</f>
         <v/>
       </c>
       <c r="I33" s="79">
@@ -3950,7 +3978,7 @@
         <v/>
       </c>
       <c r="H34" s="77">
-        <f>IF($K34=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K34))</f>
+        <f>IF($K34=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K34)/100000000)</f>
         <v/>
       </c>
       <c r="I34" s="73">
@@ -4001,7 +4029,7 @@
         <v/>
       </c>
       <c r="H35" s="83">
-        <f>IF($K35=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K35))</f>
+        <f>IF($K35=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K35)/100000000)</f>
         <v/>
       </c>
       <c r="I35" s="79">
@@ -4052,7 +4080,7 @@
         <v/>
       </c>
       <c r="H36" s="77">
-        <f>IF($K36=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K36))</f>
+        <f>IF($K36=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K36)/100000000)</f>
         <v/>
       </c>
       <c r="I36" s="73">
@@ -4103,7 +4131,7 @@
         <v/>
       </c>
       <c r="H37" s="83">
-        <f>IF($K37=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K37))</f>
+        <f>IF($K37=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K37)/100000000)</f>
         <v/>
       </c>
       <c r="I37" s="79">
@@ -4154,7 +4182,7 @@
         <v/>
       </c>
       <c r="H38" s="77">
-        <f>IF($K38=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K38))</f>
+        <f>IF($K38=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K38)/100000000)</f>
         <v/>
       </c>
       <c r="I38" s="73">
@@ -4205,7 +4233,7 @@
         <v/>
       </c>
       <c r="H39" s="83">
-        <f>IF($K39=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K39))</f>
+        <f>IF($K39=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K39)/100000000)</f>
         <v/>
       </c>
       <c r="I39" s="79">
@@ -4256,7 +4284,7 @@
         <v/>
       </c>
       <c r="H40" s="77">
-        <f>IF($K40=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K40))</f>
+        <f>IF($K40=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K40)/100000000)</f>
         <v/>
       </c>
       <c r="I40" s="73">
@@ -4307,7 +4335,7 @@
         <v/>
       </c>
       <c r="H41" s="83">
-        <f>IF($K41=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K41))</f>
+        <f>IF($K41=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K41)/100000000)</f>
         <v/>
       </c>
       <c r="I41" s="79">
@@ -4358,7 +4386,7 @@
         <v/>
       </c>
       <c r="H42" s="77">
-        <f>IF($K42=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K42))</f>
+        <f>IF($K42=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K42)/100000000)</f>
         <v/>
       </c>
       <c r="I42" s="73">
@@ -4409,7 +4437,7 @@
         <v/>
       </c>
       <c r="H43" s="83">
-        <f>IF($K43=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K43))</f>
+        <f>IF($K43=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K43)/100000000)</f>
         <v/>
       </c>
       <c r="I43" s="79">
@@ -4460,7 +4488,7 @@
         <v/>
       </c>
       <c r="H44" s="77">
-        <f>IF($K44=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K44))</f>
+        <f>IF($K44=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K44)/100000000)</f>
         <v/>
       </c>
       <c r="I44" s="73">
@@ -4511,7 +4539,7 @@
         <v/>
       </c>
       <c r="H45" s="83">
-        <f>IF($K45=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K45))</f>
+        <f>IF($K45=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K45)/100000000)</f>
         <v/>
       </c>
       <c r="I45" s="79">
@@ -4562,7 +4590,7 @@
         <v/>
       </c>
       <c r="H46" s="77">
-        <f>IF($K46=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K46))</f>
+        <f>IF($K46=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K46)/100000000)</f>
         <v/>
       </c>
       <c r="I46" s="73">
@@ -4613,7 +4641,7 @@
         <v/>
       </c>
       <c r="H47" s="83">
-        <f>IF($K47=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K47))</f>
+        <f>IF($K47=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K47)/100000000)</f>
         <v/>
       </c>
       <c r="I47" s="79">
@@ -4664,7 +4692,7 @@
         <v/>
       </c>
       <c r="H48" s="77">
-        <f>IF($K48=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K48))</f>
+        <f>IF($K48=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K48)/100000000)</f>
         <v/>
       </c>
       <c r="I48" s="73">
@@ -4715,7 +4743,7 @@
         <v/>
       </c>
       <c r="H49" s="83">
-        <f>IF($K49=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K49))</f>
+        <f>IF($K49=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K49)/100000000)</f>
         <v/>
       </c>
       <c r="I49" s="79">
@@ -4766,7 +4794,7 @@
         <v/>
       </c>
       <c r="H50" s="77">
-        <f>IF($K50=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K50))</f>
+        <f>IF($K50=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K50)/100000000)</f>
         <v/>
       </c>
       <c r="I50" s="73">
@@ -4817,7 +4845,7 @@
         <v/>
       </c>
       <c r="H51" s="83">
-        <f>IF($K51=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K51))</f>
+        <f>IF($K51=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K51)/100000000)</f>
         <v/>
       </c>
       <c r="I51" s="79">
@@ -4868,7 +4896,7 @@
         <v/>
       </c>
       <c r="H52" s="77">
-        <f>IF($K52=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K52))</f>
+        <f>IF($K52=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K52)/100000000)</f>
         <v/>
       </c>
       <c r="I52" s="73">
@@ -4919,7 +4947,7 @@
         <v/>
       </c>
       <c r="H53" s="83">
-        <f>IF($K53=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K53))</f>
+        <f>IF($K53=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K53)/100000000)</f>
         <v/>
       </c>
       <c r="I53" s="79">
@@ -4970,7 +4998,7 @@
         <v/>
       </c>
       <c r="H54" s="77">
-        <f>IF($K54=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K54))</f>
+        <f>IF($K54=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K54)/100000000)</f>
         <v/>
       </c>
       <c r="I54" s="73">
@@ -5021,7 +5049,7 @@
         <v/>
       </c>
       <c r="H55" s="83">
-        <f>IF($K55=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K55))</f>
+        <f>IF($K55=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K55)/100000000)</f>
         <v/>
       </c>
       <c r="I55" s="79">
@@ -5072,7 +5100,7 @@
         <v/>
       </c>
       <c r="H56" s="77">
-        <f>IF($K56=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K56))</f>
+        <f>IF($K56=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K56)/100000000)</f>
         <v/>
       </c>
       <c r="I56" s="73">
@@ -5123,7 +5151,7 @@
         <v/>
       </c>
       <c r="H57" s="83">
-        <f>IF($K57=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K57))</f>
+        <f>IF($K57=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K57)/100000000)</f>
         <v/>
       </c>
       <c r="I57" s="79">
@@ -5174,7 +5202,7 @@
         <v/>
       </c>
       <c r="H58" s="77">
-        <f>IF($K58=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K58))</f>
+        <f>IF($K58=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K58)/100000000)</f>
         <v/>
       </c>
       <c r="I58" s="73">
@@ -5225,7 +5253,7 @@
         <v/>
       </c>
       <c r="H59" s="83">
-        <f>IF($K59=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K59))</f>
+        <f>IF($K59=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K59)/100000000)</f>
         <v/>
       </c>
       <c r="I59" s="79">
@@ -5276,7 +5304,7 @@
         <v/>
       </c>
       <c r="H60" s="77">
-        <f>IF($K60=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K60))</f>
+        <f>IF($K60=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K60)/100000000)</f>
         <v/>
       </c>
       <c r="I60" s="73">
@@ -5327,7 +5355,7 @@
         <v/>
       </c>
       <c r="H61" s="83">
-        <f>IF($K61=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K61))</f>
+        <f>IF($K61=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K61)/100000000)</f>
         <v/>
       </c>
       <c r="I61" s="79">
@@ -5378,7 +5406,7 @@
         <v/>
       </c>
       <c r="H62" s="77">
-        <f>IF($K62=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K62))</f>
+        <f>IF($K62=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K62)/100000000)</f>
         <v/>
       </c>
       <c r="I62" s="73">
@@ -5429,7 +5457,7 @@
         <v/>
       </c>
       <c r="H63" s="83">
-        <f>IF($K63=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K63))</f>
+        <f>IF($K63=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K63)/100000000)</f>
         <v/>
       </c>
       <c r="I63" s="79">
@@ -5480,7 +5508,7 @@
         <v/>
       </c>
       <c r="H64" s="77">
-        <f>IF($K64=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K64))</f>
+        <f>IF($K64=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K64)/100000000)</f>
         <v/>
       </c>
       <c r="I64" s="73">
@@ -5531,7 +5559,7 @@
         <v/>
       </c>
       <c r="H65" s="83">
-        <f>IF($K65=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K65))</f>
+        <f>IF($K65=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K65)/100000000)</f>
         <v/>
       </c>
       <c r="I65" s="79">
@@ -5582,7 +5610,7 @@
         <v/>
       </c>
       <c r="H66" s="77">
-        <f>IF($K66=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K66))</f>
+        <f>IF($K66=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K66)/100000000)</f>
         <v/>
       </c>
       <c r="I66" s="73">
@@ -5633,7 +5661,7 @@
         <v/>
       </c>
       <c r="H67" s="83">
-        <f>IF($K67=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K67))</f>
+        <f>IF($K67=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K67)/100000000)</f>
         <v/>
       </c>
       <c r="I67" s="79">
@@ -5684,7 +5712,7 @@
         <v/>
       </c>
       <c r="H68" s="77">
-        <f>IF($K68=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K68))</f>
+        <f>IF($K68=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K68)/100000000)</f>
         <v/>
       </c>
       <c r="I68" s="73">
@@ -5735,7 +5763,7 @@
         <v/>
       </c>
       <c r="H69" s="83">
-        <f>IF($K69=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K69))</f>
+        <f>IF($K69=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K69)/100000000)</f>
         <v/>
       </c>
       <c r="I69" s="79">
@@ -5786,7 +5814,7 @@
         <v/>
       </c>
       <c r="H70" s="77">
-        <f>IF($K70=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K70))</f>
+        <f>IF($K70=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K70)/100000000)</f>
         <v/>
       </c>
       <c r="I70" s="73">
@@ -5837,7 +5865,7 @@
         <v/>
       </c>
       <c r="H71" s="83">
-        <f>IF($K71=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K71))</f>
+        <f>IF($K71=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K71)/100000000)</f>
         <v/>
       </c>
       <c r="I71" s="79">
@@ -5888,7 +5916,7 @@
         <v/>
       </c>
       <c r="H72" s="77">
-        <f>IF($K72=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K72))</f>
+        <f>IF($K72=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K72)/100000000)</f>
         <v/>
       </c>
       <c r="I72" s="73">
@@ -5939,7 +5967,7 @@
         <v/>
       </c>
       <c r="H73" s="83">
-        <f>IF($K73=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K73))</f>
+        <f>IF($K73=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K73)/100000000)</f>
         <v/>
       </c>
       <c r="I73" s="79">
@@ -5990,7 +6018,7 @@
         <v/>
       </c>
       <c r="H74" s="77">
-        <f>IF($K74=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K74))</f>
+        <f>IF($K74=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K74)/100000000)</f>
         <v/>
       </c>
       <c r="I74" s="73">
@@ -6041,7 +6069,7 @@
         <v/>
       </c>
       <c r="H75" s="83">
-        <f>IF($K75=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K75))</f>
+        <f>IF($K75=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K75)/100000000)</f>
         <v/>
       </c>
       <c r="I75" s="79">
@@ -6092,7 +6120,7 @@
         <v/>
       </c>
       <c r="H76" s="77">
-        <f>IF($K76=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K76))</f>
+        <f>IF($K76=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K76)/100000000)</f>
         <v/>
       </c>
       <c r="I76" s="73">
@@ -6143,7 +6171,7 @@
         <v/>
       </c>
       <c r="H77" s="83">
-        <f>IF($K77=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K77))</f>
+        <f>IF($K77=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K77)/100000000)</f>
         <v/>
       </c>
       <c r="I77" s="79">
@@ -6194,7 +6222,7 @@
         <v/>
       </c>
       <c r="H78" s="77">
-        <f>IF($K78=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K78))</f>
+        <f>IF($K78=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K78)/100000000)</f>
         <v/>
       </c>
       <c r="I78" s="73">
@@ -6245,7 +6273,7 @@
         <v/>
       </c>
       <c r="H79" s="88">
-        <f>IF($K79=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K79))</f>
+        <f>IF($K79=0,"",INDEX('ETF데이터'!$E$4:$E$580,$K79)/100000000)</f>
         <v/>
       </c>
       <c r="I79" s="84">

--- a/고객제안서_월배당ETF.xlsx
+++ b/고객제안서_월배당ETF.xlsx
@@ -22,7 +22,7 @@
     <definedName name="조회_최소">'종목조회'!$C$11</definedName>
     <definedName name="조회_최대">'종목조회'!$C$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'제안서'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'제안서'!$A$1:$H$99</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'제안서'!$A$1:$H$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ETF데이터'!$A$3:$T$664</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1247,6 +1247,7 @@
     <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
     <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1518,7 +1519,11 @@
         <v/>
       </c>
       <c r="O20" s="3">
-        <f>IF($K20=0,1,INDEX('ETF데이터'!$T$4:$T$576,$K20))</f>
+        <f>IF($K20=0,1,IF(INDEX('ETF데이터'!$T$4:$T$576,$K20)="",1,INDEX('ETF데이터'!$T$4:$T$576,$K20)))</f>
+        <v/>
+      </c>
+      <c r="P20" s="3">
+        <f>IF($K20=0,0,IF(INDEX('ETF데이터'!$T$4:$T$576,$K20)="",1,0))</f>
         <v/>
       </c>
     </row>
@@ -1568,7 +1573,11 @@
         <v/>
       </c>
       <c r="O21" s="3">
-        <f>IF($K21=0,1,INDEX('ETF데이터'!$T$4:$T$576,$K21))</f>
+        <f>IF($K21=0,1,IF(INDEX('ETF데이터'!$T$4:$T$576,$K21)="",1,INDEX('ETF데이터'!$T$4:$T$576,$K21)))</f>
+        <v/>
+      </c>
+      <c r="P21" s="3">
+        <f>IF($K21=0,0,IF(INDEX('ETF데이터'!$T$4:$T$576,$K21)="",1,0))</f>
         <v/>
       </c>
     </row>
@@ -1618,7 +1627,11 @@
         <v/>
       </c>
       <c r="O22" s="3">
-        <f>IF($K22=0,1,INDEX('ETF데이터'!$T$4:$T$576,$K22))</f>
+        <f>IF($K22=0,1,IF(INDEX('ETF데이터'!$T$4:$T$576,$K22)="",1,INDEX('ETF데이터'!$T$4:$T$576,$K22)))</f>
+        <v/>
+      </c>
+      <c r="P22" s="3">
+        <f>IF($K22=0,0,IF(INDEX('ETF데이터'!$T$4:$T$576,$K22)="",1,0))</f>
         <v/>
       </c>
     </row>
@@ -1668,7 +1681,11 @@
         <v/>
       </c>
       <c r="O23" s="3">
-        <f>IF($K23=0,1,INDEX('ETF데이터'!$T$4:$T$576,$K23))</f>
+        <f>IF($K23=0,1,IF(INDEX('ETF데이터'!$T$4:$T$576,$K23)="",1,INDEX('ETF데이터'!$T$4:$T$576,$K23)))</f>
+        <v/>
+      </c>
+      <c r="P23" s="3">
+        <f>IF($K23=0,0,IF(INDEX('ETF데이터'!$T$4:$T$576,$K23)="",1,0))</f>
         <v/>
       </c>
     </row>
@@ -1718,7 +1735,11 @@
         <v/>
       </c>
       <c r="O24" s="3">
-        <f>IF($K24=0,1,INDEX('ETF데이터'!$T$4:$T$576,$K24))</f>
+        <f>IF($K24=0,1,IF(INDEX('ETF데이터'!$T$4:$T$576,$K24)="",1,INDEX('ETF데이터'!$T$4:$T$576,$K24)))</f>
+        <v/>
+      </c>
+      <c r="P24" s="3">
+        <f>IF($K24=0,0,IF(INDEX('ETF데이터'!$T$4:$T$576,$K24)="",1,0))</f>
         <v/>
       </c>
     </row>
@@ -1768,7 +1789,11 @@
         <v/>
       </c>
       <c r="O25" s="3">
-        <f>IF($K25=0,1,INDEX('ETF데이터'!$T$4:$T$576,$K25))</f>
+        <f>IF($K25=0,1,IF(INDEX('ETF데이터'!$T$4:$T$576,$K25)="",1,INDEX('ETF데이터'!$T$4:$T$576,$K25)))</f>
+        <v/>
+      </c>
+      <c r="P25" s="3">
+        <f>IF($K25=0,0,IF(INDEX('ETF데이터'!$T$4:$T$576,$K25)="",1,0))</f>
         <v/>
       </c>
     </row>
@@ -1818,7 +1843,11 @@
         <v/>
       </c>
       <c r="O26" s="3">
-        <f>IF($K26=0,1,INDEX('ETF데이터'!$T$4:$T$576,$K26))</f>
+        <f>IF($K26=0,1,IF(INDEX('ETF데이터'!$T$4:$T$576,$K26)="",1,INDEX('ETF데이터'!$T$4:$T$576,$K26)))</f>
+        <v/>
+      </c>
+      <c r="P26" s="3">
+        <f>IF($K26=0,0,IF(INDEX('ETF데이터'!$T$4:$T$576,$K26)="",1,0))</f>
         <v/>
       </c>
     </row>
@@ -1868,7 +1897,11 @@
         <v/>
       </c>
       <c r="O27" s="3">
-        <f>IF($K27=0,1,INDEX('ETF데이터'!$T$4:$T$576,$K27))</f>
+        <f>IF($K27=0,1,IF(INDEX('ETF데이터'!$T$4:$T$576,$K27)="",1,INDEX('ETF데이터'!$T$4:$T$576,$K27)))</f>
+        <v/>
+      </c>
+      <c r="P27" s="3">
+        <f>IF($K27=0,0,IF(INDEX('ETF데이터'!$T$4:$T$576,$K27)="",1,0))</f>
         <v/>
       </c>
     </row>
@@ -1918,7 +1951,11 @@
         <v/>
       </c>
       <c r="O28" s="3">
-        <f>IF($K28=0,1,INDEX('ETF데이터'!$T$4:$T$576,$K28))</f>
+        <f>IF($K28=0,1,IF(INDEX('ETF데이터'!$T$4:$T$576,$K28)="",1,INDEX('ETF데이터'!$T$4:$T$576,$K28)))</f>
+        <v/>
+      </c>
+      <c r="P28" s="3">
+        <f>IF($K28=0,0,IF(INDEX('ETF데이터'!$T$4:$T$576,$K28)="",1,0))</f>
         <v/>
       </c>
     </row>
@@ -1968,7 +2005,11 @@
         <v/>
       </c>
       <c r="O29" s="3">
-        <f>IF($K29=0,1,INDEX('ETF데이터'!$T$4:$T$576,$K29))</f>
+        <f>IF($K29=0,1,IF(INDEX('ETF데이터'!$T$4:$T$576,$K29)="",1,INDEX('ETF데이터'!$T$4:$T$576,$K29)))</f>
+        <v/>
+      </c>
+      <c r="P29" s="3">
+        <f>IF($K29=0,0,IF(INDEX('ETF데이터'!$T$4:$T$576,$K29)="",1,0))</f>
         <v/>
       </c>
     </row>
@@ -2018,1018 +2059,1030 @@
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="34" ht="17" customHeight="1">
+      <c r="B34" s="35">
+        <f>IF(SUM($P$20:$P$29)&gt;0,"※ 과세표준을 확인하지 못한 종목이 담겨 있습니다. 그 종목은 분배금 전액에 세율을 적용해 계산했으므로, 실제 세후 수령액은 표시된 금액보다 많을 수 있습니다.","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>빈 줄은 계산에서 빠집니다. 한 종목만 담으려면 첫 줄에만 넣고 배분을 100 으로 두십시오.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="4" customHeight="1">
-      <c r="A36" s="8" t="n"/>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-    </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="37" ht="4" customHeight="1">
+      <c r="A37" s="8" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>예상 분배금 요약</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="6" customHeight="1"/>
-    <row r="39" ht="34" customHeight="1">
-      <c r="B39" s="11" t="inlineStr">
+    <row r="39" ht="6" customHeight="1"/>
+    <row r="40" ht="34" customHeight="1">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>총 투자금액</t>
         </is>
       </c>
-      <c r="C39" s="36">
+      <c r="C40" s="36">
         <f>$C$11</f>
         <v/>
       </c>
-      <c r="F39" s="37" t="inlineStr">
+      <c r="F40" s="37" t="inlineStr">
         <is>
           <t>월 예상 분배금 (세전)</t>
         </is>
       </c>
-      <c r="G39" s="38">
+      <c r="G40" s="38">
         <f>$G$30</f>
         <v/>
       </c>
-      <c r="H39" s="39" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>실제 투자금액</t>
-        </is>
-      </c>
-      <c r="C40" s="40">
-        <f>$F$30</f>
-        <v/>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>월 예상 분배금 (세후)</t>
-        </is>
-      </c>
-      <c r="G40" s="36">
-        <f>$H$30</f>
-        <v/>
-      </c>
+      <c r="H40" s="39" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>미투자 잔액</t>
+          <t>실제 투자금액</t>
         </is>
       </c>
       <c r="C41" s="40">
-        <f>$C$11-$F$30</f>
+        <f>$F$30</f>
         <v/>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>연 예상 분배금 (세전)</t>
-        </is>
-      </c>
-      <c r="G41" s="40">
-        <f>$G$30*12</f>
+          <t>월 예상 분배금 (세후)</t>
+        </is>
+      </c>
+      <c r="G41" s="36">
+        <f>$H$30</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>담은 종목 수</t>
-        </is>
-      </c>
-      <c r="C42" s="41">
-        <f>COUNTIF($K$20:$K$29,"&gt;0")</f>
+          <t>미투자 잔액</t>
+        </is>
+      </c>
+      <c r="C42" s="40">
+        <f>$C$11-$F$30</f>
         <v/>
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>연 예상 분배금 (세후)</t>
-        </is>
-      </c>
-      <c r="G42" s="42">
-        <f>$H$30*12</f>
+          <t>연 예상 분배금 (세전)</t>
+        </is>
+      </c>
+      <c r="G42" s="40">
+        <f>$G$30*12</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>연 수익률 (세전, 가중평균)</t>
-        </is>
-      </c>
-      <c r="C43" s="43">
-        <f>IF($F$30=0,0,$G$30*12/$F$30)</f>
+          <t>담은 종목 수</t>
+        </is>
+      </c>
+      <c r="C43" s="41">
+        <f>COUNTIF($K$20:$K$29,"&gt;0")</f>
         <v/>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>월 수익률 (세전)</t>
-        </is>
-      </c>
-      <c r="G43" s="44">
-        <f>IF($F$30=0,0,$G$30/$F$30)</f>
+          <t>연 예상 분배금 (세후)</t>
+        </is>
+      </c>
+      <c r="G43" s="42">
+        <f>$H$30*12</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="B44" s="11" t="inlineStr">
         <is>
+          <t>연 수익률 (세전, 가중평균)</t>
+        </is>
+      </c>
+      <c r="C44" s="43">
+        <f>IF($F$30=0,0,$G$30*12/$F$30)</f>
+        <v/>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>월 수익률 (세전)</t>
+        </is>
+      </c>
+      <c r="G44" s="44">
+        <f>IF($F$30=0,0,$G$30/$F$30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="B45" s="11" t="inlineStr">
+        <is>
           <t>연 수익률 (세후, 가중평균)</t>
         </is>
       </c>
-      <c r="C44" s="45">
+      <c r="C45" s="45">
         <f>IF($F$30=0,0,$H$30*12/$F$30)</f>
         <v/>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>월 수익률 (세후)</t>
         </is>
       </c>
-      <c r="G44" s="46">
+      <c r="G45" s="46">
         <f>IF($F$30=0,0,$H$30/$F$30)</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="7" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>연 수익률은 담은 종목들의 최근 12개월 실제 분배금을 투자 비중으로 가중한 값입니다. 확정 수익률이 아니며 매월 달라집니다.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="4" customHeight="1">
-      <c r="A47" s="8" t="n"/>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-    </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
+    <row r="48" ht="4" customHeight="1">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="8" t="n"/>
+      <c r="H48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>총 투자금액별 예상 분배금  (위 구성을 그대로 두고 금액만 바꿨을 때)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="6" customHeight="1"/>
-    <row r="50" ht="28" customHeight="1">
-      <c r="B50" s="18" t="inlineStr">
+    <row r="50" ht="6" customHeight="1"/>
+    <row r="51" ht="28" customHeight="1">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>투자금액 구간</t>
         </is>
       </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>월 분배금(세전)</t>
         </is>
       </c>
-      <c r="D50" s="19" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>월 분배금(세후)</t>
         </is>
       </c>
-      <c r="E50" s="19" t="inlineStr">
+      <c r="E51" s="19" t="inlineStr">
         <is>
           <t>연 분배금(세전)</t>
         </is>
       </c>
-      <c r="F50" s="20" t="inlineStr">
+      <c r="F51" s="20" t="inlineStr">
         <is>
           <t>연 분배금(세후)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="B51" s="47" t="n">
+    <row r="52" ht="19" customHeight="1">
+      <c r="B52" s="47" t="n">
         <v>10000000</v>
       </c>
-      <c r="C51" s="48">
-        <f>$B51*$C$43/12</f>
-        <v/>
-      </c>
-      <c r="D51" s="48">
-        <f>$C51*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-      <c r="E51" s="48">
-        <f>$B51*$C$43</f>
-        <v/>
-      </c>
-      <c r="F51" s="49">
-        <f>$E51*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="19" customHeight="1">
-      <c r="B52" s="50" t="n">
+      <c r="C52" s="48">
+        <f>$B52*$C$44/12</f>
+        <v/>
+      </c>
+      <c r="D52" s="48">
+        <f>$C52*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+      <c r="E52" s="48">
+        <f>$B52*$C$44</f>
+        <v/>
+      </c>
+      <c r="F52" s="49">
+        <f>$E52*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="B53" s="50" t="n">
         <v>30000000</v>
       </c>
-      <c r="C52" s="51">
-        <f>$B52*$C$43/12</f>
-        <v/>
-      </c>
-      <c r="D52" s="51">
-        <f>$C52*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-      <c r="E52" s="51">
-        <f>$B52*$C$43</f>
-        <v/>
-      </c>
-      <c r="F52" s="52">
-        <f>$E52*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="B53" s="47" t="n">
+      <c r="C53" s="51">
+        <f>$B53*$C$44/12</f>
+        <v/>
+      </c>
+      <c r="D53" s="51">
+        <f>$C53*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+      <c r="E53" s="51">
+        <f>$B53*$C$44</f>
+        <v/>
+      </c>
+      <c r="F53" s="52">
+        <f>$E53*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="B54" s="47" t="n">
         <v>50000000</v>
       </c>
-      <c r="C53" s="48">
-        <f>$B53*$C$43/12</f>
-        <v/>
-      </c>
-      <c r="D53" s="48">
-        <f>$C53*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-      <c r="E53" s="48">
-        <f>$B53*$C$43</f>
-        <v/>
-      </c>
-      <c r="F53" s="49">
-        <f>$E53*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="19" customHeight="1">
-      <c r="B54" s="50" t="n">
+      <c r="C54" s="48">
+        <f>$B54*$C$44/12</f>
+        <v/>
+      </c>
+      <c r="D54" s="48">
+        <f>$C54*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+      <c r="E54" s="48">
+        <f>$B54*$C$44</f>
+        <v/>
+      </c>
+      <c r="F54" s="49">
+        <f>$E54*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="B55" s="50" t="n">
         <v>100000000</v>
       </c>
-      <c r="C54" s="51">
-        <f>$B54*$C$43/12</f>
-        <v/>
-      </c>
-      <c r="D54" s="51">
-        <f>$C54*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-      <c r="E54" s="51">
-        <f>$B54*$C$43</f>
-        <v/>
-      </c>
-      <c r="F54" s="52">
-        <f>$E54*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="B55" s="47" t="n">
+      <c r="C55" s="51">
+        <f>$B55*$C$44/12</f>
+        <v/>
+      </c>
+      <c r="D55" s="51">
+        <f>$C55*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+      <c r="E55" s="51">
+        <f>$B55*$C$44</f>
+        <v/>
+      </c>
+      <c r="F55" s="52">
+        <f>$E55*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="19" customHeight="1">
+      <c r="B56" s="47" t="n">
         <v>200000000</v>
       </c>
-      <c r="C55" s="48">
-        <f>$B55*$C$43/12</f>
-        <v/>
-      </c>
-      <c r="D55" s="48">
-        <f>$C55*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-      <c r="E55" s="48">
-        <f>$B55*$C$43</f>
-        <v/>
-      </c>
-      <c r="F55" s="49">
-        <f>$E55*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="B56" s="50" t="n">
+      <c r="C56" s="48">
+        <f>$B56*$C$44/12</f>
+        <v/>
+      </c>
+      <c r="D56" s="48">
+        <f>$C56*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+      <c r="E56" s="48">
+        <f>$B56*$C$44</f>
+        <v/>
+      </c>
+      <c r="F56" s="49">
+        <f>$E56*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="19" customHeight="1">
+      <c r="B57" s="50" t="n">
         <v>300000000</v>
       </c>
-      <c r="C56" s="51">
-        <f>$B56*$C$43/12</f>
-        <v/>
-      </c>
-      <c r="D56" s="51">
-        <f>$C56*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-      <c r="E56" s="51">
-        <f>$B56*$C$43</f>
-        <v/>
-      </c>
-      <c r="F56" s="52">
-        <f>$E56*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="B57" s="47" t="n">
+      <c r="C57" s="51">
+        <f>$B57*$C$44/12</f>
+        <v/>
+      </c>
+      <c r="D57" s="51">
+        <f>$C57*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+      <c r="E57" s="51">
+        <f>$B57*$C$44</f>
+        <v/>
+      </c>
+      <c r="F57" s="52">
+        <f>$E57*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="19" customHeight="1">
+      <c r="B58" s="47" t="n">
         <v>500000000</v>
       </c>
-      <c r="C57" s="48">
-        <f>$B57*$C$43/12</f>
-        <v/>
-      </c>
-      <c r="D57" s="48">
-        <f>$C57*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-      <c r="E57" s="48">
-        <f>$B57*$C$43</f>
-        <v/>
-      </c>
-      <c r="F57" s="49">
-        <f>$E57*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="B58" s="53" t="n">
+      <c r="C58" s="48">
+        <f>$B58*$C$44/12</f>
+        <v/>
+      </c>
+      <c r="D58" s="48">
+        <f>$C58*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+      <c r="E58" s="48">
+        <f>$B58*$C$44</f>
+        <v/>
+      </c>
+      <c r="F58" s="49">
+        <f>$E58*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="19" customHeight="1">
+      <c r="B59" s="53" t="n">
         <v>1000000000</v>
       </c>
-      <c r="C58" s="54">
-        <f>$B58*$C$43/12</f>
-        <v/>
-      </c>
-      <c r="D58" s="54">
-        <f>$C58*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-      <c r="E58" s="54">
-        <f>$B58*$C$43</f>
-        <v/>
-      </c>
-      <c r="F58" s="55">
-        <f>$E58*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="7" t="inlineStr">
+      <c r="C59" s="54">
+        <f>$B59*$C$44/12</f>
+        <v/>
+      </c>
+      <c r="D59" s="54">
+        <f>$C59*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+      <c r="E59" s="54">
+        <f>$B59*$C$44</f>
+        <v/>
+      </c>
+      <c r="F59" s="55">
+        <f>$E59*IF($G$30=0,1-$C$13,$H$30/$G$30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>※ 단주 절사를 반영하지 않은 근사치라 2·3. 의 값과 몇 천 원 차이가 날 수 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="4" customHeight="1">
-      <c r="A61" s="8" t="n"/>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="n"/>
-    </row>
-    <row r="62" ht="26" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
+    <row r="62" ht="4" customHeight="1">
+      <c r="A62" s="8" t="n"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="n"/>
+      <c r="H62" s="8" t="n"/>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>월배당 ETF 비교  (1억원 단독 투자 기준 · 연 분배율 상위 8 + 순자산 상위 6, 파킹형 제외 · 채택 월배당 64종목 중)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="6" customHeight="1"/>
-    <row r="64" ht="30" customHeight="1">
-      <c r="B64" s="18" t="inlineStr">
+    <row r="64" ht="6" customHeight="1"/>
+    <row r="65" ht="30" customHeight="1">
+      <c r="B65" s="18" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C64" s="19" t="inlineStr">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>유형</t>
         </is>
       </c>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>현재가</t>
         </is>
       </c>
-      <c r="E64" s="19" t="inlineStr">
+      <c r="E65" s="19" t="inlineStr">
         <is>
           <t>연 분배율</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
+      <c r="F65" s="19" t="inlineStr">
         <is>
           <t>월 분배금(세전)</t>
         </is>
       </c>
-      <c r="G64" s="19" t="inlineStr">
+      <c r="G65" s="19" t="inlineStr">
         <is>
           <t>월 분배금(세후)</t>
         </is>
       </c>
-      <c r="H64" s="20" t="inlineStr">
+      <c r="H65" s="20" t="inlineStr">
         <is>
           <t>변동성(1년)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="19" customHeight="1">
-      <c r="B65" s="56">
+    <row r="66" ht="19" customHeight="1">
+      <c r="B66" s="56">
         <f>'ETF데이터'!$A$4</f>
         <v/>
       </c>
-      <c r="C65" s="57">
+      <c r="C66" s="57">
         <f>'ETF데이터'!$P$4</f>
         <v/>
       </c>
-      <c r="D65" s="48">
+      <c r="D66" s="48">
         <f>'ETF데이터'!$D$4</f>
         <v/>
       </c>
-      <c r="E65" s="58">
+      <c r="E66" s="58">
         <f>'ETF데이터'!$J$4</f>
         <v/>
       </c>
-      <c r="F65" s="48">
-        <f>IF($D65=0,0,ROUNDDOWN(100000000/$D65,0)*$D65*$E65/12)</f>
-        <v/>
-      </c>
-      <c r="G65" s="48">
-        <f>$F65*(1-$C$13*'ETF데이터'!$T$4)</f>
-        <v/>
-      </c>
-      <c r="H65" s="59">
+      <c r="F66" s="48">
+        <f>IF($D66=0,0,ROUNDDOWN(100000000/$D66,0)*$D66*$E66/12)</f>
+        <v/>
+      </c>
+      <c r="G66" s="48">
+        <f>$F66*(1-$C$13*'ETF데이터'!$T$4)</f>
+        <v/>
+      </c>
+      <c r="H66" s="59">
         <f>'ETF데이터'!$H$4</f>
         <v/>
       </c>
     </row>
-    <row r="66" ht="19" customHeight="1">
-      <c r="B66" s="60">
+    <row r="67" ht="19" customHeight="1">
+      <c r="B67" s="60">
         <f>'ETF데이터'!$A$5</f>
         <v/>
       </c>
-      <c r="C66" s="61">
+      <c r="C67" s="61">
         <f>'ETF데이터'!$P$5</f>
         <v/>
       </c>
-      <c r="D66" s="51">
+      <c r="D67" s="51">
         <f>'ETF데이터'!$D$5</f>
         <v/>
       </c>
-      <c r="E66" s="62">
+      <c r="E67" s="62">
         <f>'ETF데이터'!$J$5</f>
         <v/>
       </c>
-      <c r="F66" s="51">
-        <f>IF($D66=0,0,ROUNDDOWN(100000000/$D66,0)*$D66*$E66/12)</f>
-        <v/>
-      </c>
-      <c r="G66" s="51">
-        <f>$F66*(1-$C$13*'ETF데이터'!$T$5)</f>
-        <v/>
-      </c>
-      <c r="H66" s="63">
+      <c r="F67" s="51">
+        <f>IF($D67=0,0,ROUNDDOWN(100000000/$D67,0)*$D67*$E67/12)</f>
+        <v/>
+      </c>
+      <c r="G67" s="51">
+        <f>$F67*(1-$C$13*'ETF데이터'!$T$5)</f>
+        <v/>
+      </c>
+      <c r="H67" s="63">
         <f>'ETF데이터'!$H$5</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="19" customHeight="1">
-      <c r="B67" s="56">
+    <row r="68" ht="19" customHeight="1">
+      <c r="B68" s="56">
         <f>'ETF데이터'!$A$6</f>
         <v/>
       </c>
-      <c r="C67" s="57">
+      <c r="C68" s="57">
         <f>'ETF데이터'!$P$6</f>
         <v/>
       </c>
-      <c r="D67" s="48">
+      <c r="D68" s="48">
         <f>'ETF데이터'!$D$6</f>
         <v/>
       </c>
-      <c r="E67" s="58">
+      <c r="E68" s="58">
         <f>'ETF데이터'!$J$6</f>
         <v/>
       </c>
-      <c r="F67" s="48">
-        <f>IF($D67=0,0,ROUNDDOWN(100000000/$D67,0)*$D67*$E67/12)</f>
-        <v/>
-      </c>
-      <c r="G67" s="48">
-        <f>$F67*(1-$C$13*'ETF데이터'!$T$6)</f>
-        <v/>
-      </c>
-      <c r="H67" s="59">
+      <c r="F68" s="48">
+        <f>IF($D68=0,0,ROUNDDOWN(100000000/$D68,0)*$D68*$E68/12)</f>
+        <v/>
+      </c>
+      <c r="G68" s="48">
+        <f>$F68*(1-$C$13*'ETF데이터'!$T$6)</f>
+        <v/>
+      </c>
+      <c r="H68" s="59">
         <f>'ETF데이터'!$H$6</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="19" customHeight="1">
-      <c r="B68" s="60">
+    <row r="69" ht="19" customHeight="1">
+      <c r="B69" s="60">
         <f>'ETF데이터'!$A$7</f>
         <v/>
       </c>
-      <c r="C68" s="61">
+      <c r="C69" s="61">
         <f>'ETF데이터'!$P$7</f>
         <v/>
       </c>
-      <c r="D68" s="51">
+      <c r="D69" s="51">
         <f>'ETF데이터'!$D$7</f>
         <v/>
       </c>
-      <c r="E68" s="62">
+      <c r="E69" s="62">
         <f>'ETF데이터'!$J$7</f>
         <v/>
       </c>
-      <c r="F68" s="51">
-        <f>IF($D68=0,0,ROUNDDOWN(100000000/$D68,0)*$D68*$E68/12)</f>
-        <v/>
-      </c>
-      <c r="G68" s="51">
-        <f>$F68*(1-$C$13*'ETF데이터'!$T$7)</f>
-        <v/>
-      </c>
-      <c r="H68" s="63">
+      <c r="F69" s="51">
+        <f>IF($D69=0,0,ROUNDDOWN(100000000/$D69,0)*$D69*$E69/12)</f>
+        <v/>
+      </c>
+      <c r="G69" s="51">
+        <f>$F69*(1-$C$13*'ETF데이터'!$T$7)</f>
+        <v/>
+      </c>
+      <c r="H69" s="63">
         <f>'ETF데이터'!$H$7</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="19" customHeight="1">
-      <c r="B69" s="56">
+    <row r="70" ht="19" customHeight="1">
+      <c r="B70" s="56">
         <f>'ETF데이터'!$A$8</f>
         <v/>
       </c>
-      <c r="C69" s="57">
+      <c r="C70" s="57">
         <f>'ETF데이터'!$P$8</f>
         <v/>
       </c>
-      <c r="D69" s="48">
+      <c r="D70" s="48">
         <f>'ETF데이터'!$D$8</f>
         <v/>
       </c>
-      <c r="E69" s="58">
+      <c r="E70" s="58">
         <f>'ETF데이터'!$J$8</f>
         <v/>
       </c>
-      <c r="F69" s="48">
-        <f>IF($D69=0,0,ROUNDDOWN(100000000/$D69,0)*$D69*$E69/12)</f>
-        <v/>
-      </c>
-      <c r="G69" s="48">
-        <f>$F69*(1-$C$13*'ETF데이터'!$T$8)</f>
-        <v/>
-      </c>
-      <c r="H69" s="59">
+      <c r="F70" s="48">
+        <f>IF($D70=0,0,ROUNDDOWN(100000000/$D70,0)*$D70*$E70/12)</f>
+        <v/>
+      </c>
+      <c r="G70" s="48">
+        <f>$F70*(1-$C$13*'ETF데이터'!$T$8)</f>
+        <v/>
+      </c>
+      <c r="H70" s="59">
         <f>'ETF데이터'!$H$8</f>
         <v/>
       </c>
     </row>
-    <row r="70" ht="19" customHeight="1">
-      <c r="B70" s="60">
+    <row r="71" ht="19" customHeight="1">
+      <c r="B71" s="60">
         <f>'ETF데이터'!$A$9</f>
         <v/>
       </c>
-      <c r="C70" s="61">
+      <c r="C71" s="61">
         <f>'ETF데이터'!$P$9</f>
         <v/>
       </c>
-      <c r="D70" s="51">
+      <c r="D71" s="51">
         <f>'ETF데이터'!$D$9</f>
         <v/>
       </c>
-      <c r="E70" s="62">
+      <c r="E71" s="62">
         <f>'ETF데이터'!$J$9</f>
         <v/>
       </c>
-      <c r="F70" s="51">
-        <f>IF($D70=0,0,ROUNDDOWN(100000000/$D70,0)*$D70*$E70/12)</f>
-        <v/>
-      </c>
-      <c r="G70" s="51">
-        <f>$F70*(1-$C$13*'ETF데이터'!$T$9)</f>
-        <v/>
-      </c>
-      <c r="H70" s="63">
+      <c r="F71" s="51">
+        <f>IF($D71=0,0,ROUNDDOWN(100000000/$D71,0)*$D71*$E71/12)</f>
+        <v/>
+      </c>
+      <c r="G71" s="51">
+        <f>$F71*(1-$C$13*'ETF데이터'!$T$9)</f>
+        <v/>
+      </c>
+      <c r="H71" s="63">
         <f>'ETF데이터'!$H$9</f>
         <v/>
       </c>
     </row>
-    <row r="71" ht="19" customHeight="1">
-      <c r="B71" s="56">
+    <row r="72" ht="19" customHeight="1">
+      <c r="B72" s="56">
         <f>'ETF데이터'!$A$10</f>
         <v/>
       </c>
-      <c r="C71" s="57">
+      <c r="C72" s="57">
         <f>'ETF데이터'!$P$10</f>
         <v/>
       </c>
-      <c r="D71" s="48">
+      <c r="D72" s="48">
         <f>'ETF데이터'!$D$10</f>
         <v/>
       </c>
-      <c r="E71" s="58">
+      <c r="E72" s="58">
         <f>'ETF데이터'!$J$10</f>
         <v/>
       </c>
-      <c r="F71" s="48">
-        <f>IF($D71=0,0,ROUNDDOWN(100000000/$D71,0)*$D71*$E71/12)</f>
-        <v/>
-      </c>
-      <c r="G71" s="48">
-        <f>$F71*(1-$C$13*'ETF데이터'!$T$10)</f>
-        <v/>
-      </c>
-      <c r="H71" s="59">
+      <c r="F72" s="48">
+        <f>IF($D72=0,0,ROUNDDOWN(100000000/$D72,0)*$D72*$E72/12)</f>
+        <v/>
+      </c>
+      <c r="G72" s="48">
+        <f>$F72*(1-$C$13*'ETF데이터'!$T$10)</f>
+        <v/>
+      </c>
+      <c r="H72" s="59">
         <f>'ETF데이터'!$H$10</f>
         <v/>
       </c>
     </row>
-    <row r="72" ht="19" customHeight="1">
-      <c r="B72" s="60">
+    <row r="73" ht="19" customHeight="1">
+      <c r="B73" s="60">
         <f>'ETF데이터'!$A$11</f>
         <v/>
       </c>
-      <c r="C72" s="61">
+      <c r="C73" s="61">
         <f>'ETF데이터'!$P$11</f>
         <v/>
       </c>
-      <c r="D72" s="51">
+      <c r="D73" s="51">
         <f>'ETF데이터'!$D$11</f>
         <v/>
       </c>
-      <c r="E72" s="62">
+      <c r="E73" s="62">
         <f>'ETF데이터'!$J$11</f>
         <v/>
       </c>
-      <c r="F72" s="51">
-        <f>IF($D72=0,0,ROUNDDOWN(100000000/$D72,0)*$D72*$E72/12)</f>
-        <v/>
-      </c>
-      <c r="G72" s="51">
-        <f>$F72*(1-$C$13*'ETF데이터'!$T$11)</f>
-        <v/>
-      </c>
-      <c r="H72" s="63">
+      <c r="F73" s="51">
+        <f>IF($D73=0,0,ROUNDDOWN(100000000/$D73,0)*$D73*$E73/12)</f>
+        <v/>
+      </c>
+      <c r="G73" s="51">
+        <f>$F73*(1-$C$13*'ETF데이터'!$T$11)</f>
+        <v/>
+      </c>
+      <c r="H73" s="63">
         <f>'ETF데이터'!$H$11</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="19" customHeight="1">
-      <c r="B73" s="56">
+    <row r="74" ht="19" customHeight="1">
+      <c r="B74" s="56">
         <f>'ETF데이터'!$A$20</f>
         <v/>
       </c>
-      <c r="C73" s="57">
+      <c r="C74" s="57">
         <f>'ETF데이터'!$P$20</f>
         <v/>
       </c>
-      <c r="D73" s="48">
+      <c r="D74" s="48">
         <f>'ETF데이터'!$D$20</f>
         <v/>
       </c>
-      <c r="E73" s="58">
+      <c r="E74" s="58">
         <f>'ETF데이터'!$J$20</f>
         <v/>
       </c>
-      <c r="F73" s="48">
-        <f>IF($D73=0,0,ROUNDDOWN(100000000/$D73,0)*$D73*$E73/12)</f>
-        <v/>
-      </c>
-      <c r="G73" s="48">
-        <f>$F73*(1-$C$13*'ETF데이터'!$T$20)</f>
-        <v/>
-      </c>
-      <c r="H73" s="59">
+      <c r="F74" s="48">
+        <f>IF($D74=0,0,ROUNDDOWN(100000000/$D74,0)*$D74*$E74/12)</f>
+        <v/>
+      </c>
+      <c r="G74" s="48">
+        <f>$F74*(1-$C$13*'ETF데이터'!$T$20)</f>
+        <v/>
+      </c>
+      <c r="H74" s="59">
         <f>'ETF데이터'!$H$20</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="19" customHeight="1">
-      <c r="B74" s="60">
+    <row r="75" ht="19" customHeight="1">
+      <c r="B75" s="60">
         <f>'ETF데이터'!$A$21</f>
         <v/>
       </c>
-      <c r="C74" s="61">
+      <c r="C75" s="61">
         <f>'ETF데이터'!$P$21</f>
         <v/>
       </c>
-      <c r="D74" s="51">
+      <c r="D75" s="51">
         <f>'ETF데이터'!$D$21</f>
         <v/>
       </c>
-      <c r="E74" s="62">
+      <c r="E75" s="62">
         <f>'ETF데이터'!$J$21</f>
         <v/>
       </c>
-      <c r="F74" s="51">
-        <f>IF($D74=0,0,ROUNDDOWN(100000000/$D74,0)*$D74*$E74/12)</f>
-        <v/>
-      </c>
-      <c r="G74" s="51">
-        <f>$F74*(1-$C$13*'ETF데이터'!$T$21)</f>
-        <v/>
-      </c>
-      <c r="H74" s="63">
+      <c r="F75" s="51">
+        <f>IF($D75=0,0,ROUNDDOWN(100000000/$D75,0)*$D75*$E75/12)</f>
+        <v/>
+      </c>
+      <c r="G75" s="51">
+        <f>$F75*(1-$C$13*'ETF데이터'!$T$21)</f>
+        <v/>
+      </c>
+      <c r="H75" s="63">
         <f>'ETF데이터'!$H$21</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="19" customHeight="1">
-      <c r="B75" s="56">
+    <row r="76" ht="19" customHeight="1">
+      <c r="B76" s="56">
         <f>'ETF데이터'!$A$37</f>
         <v/>
       </c>
-      <c r="C75" s="57">
+      <c r="C76" s="57">
         <f>'ETF데이터'!$P$37</f>
         <v/>
       </c>
-      <c r="D75" s="48">
+      <c r="D76" s="48">
         <f>'ETF데이터'!$D$37</f>
         <v/>
       </c>
-      <c r="E75" s="58">
+      <c r="E76" s="58">
         <f>'ETF데이터'!$J$37</f>
         <v/>
       </c>
-      <c r="F75" s="48">
-        <f>IF($D75=0,0,ROUNDDOWN(100000000/$D75,0)*$D75*$E75/12)</f>
-        <v/>
-      </c>
-      <c r="G75" s="48">
-        <f>$F75*(1-$C$13*'ETF데이터'!$T$37)</f>
-        <v/>
-      </c>
-      <c r="H75" s="59">
+      <c r="F76" s="48">
+        <f>IF($D76=0,0,ROUNDDOWN(100000000/$D76,0)*$D76*$E76/12)</f>
+        <v/>
+      </c>
+      <c r="G76" s="48">
+        <f>$F76*(1-$C$13*'ETF데이터'!$T$37)</f>
+        <v/>
+      </c>
+      <c r="H76" s="59">
         <f>'ETF데이터'!$H$37</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="19" customHeight="1">
-      <c r="B76" s="60">
+    <row r="77" ht="19" customHeight="1">
+      <c r="B77" s="60">
         <f>'ETF데이터'!$A$55</f>
         <v/>
       </c>
-      <c r="C76" s="61">
+      <c r="C77" s="61">
         <f>'ETF데이터'!$P$55</f>
         <v/>
       </c>
-      <c r="D76" s="51">
+      <c r="D77" s="51">
         <f>'ETF데이터'!$D$55</f>
         <v/>
       </c>
-      <c r="E76" s="62">
+      <c r="E77" s="62">
         <f>'ETF데이터'!$J$55</f>
         <v/>
       </c>
-      <c r="F76" s="51">
-        <f>IF($D76=0,0,ROUNDDOWN(100000000/$D76,0)*$D76*$E76/12)</f>
-        <v/>
-      </c>
-      <c r="G76" s="51">
-        <f>$F76*(1-$C$13*'ETF데이터'!$T$55)</f>
-        <v/>
-      </c>
-      <c r="H76" s="63">
+      <c r="F77" s="51">
+        <f>IF($D77=0,0,ROUNDDOWN(100000000/$D77,0)*$D77*$E77/12)</f>
+        <v/>
+      </c>
+      <c r="G77" s="51">
+        <f>$F77*(1-$C$13*'ETF데이터'!$T$55)</f>
+        <v/>
+      </c>
+      <c r="H77" s="63">
         <f>'ETF데이터'!$H$55</f>
         <v/>
       </c>
     </row>
-    <row r="77" ht="19" customHeight="1">
-      <c r="B77" s="56">
+    <row r="78" ht="19" customHeight="1">
+      <c r="B78" s="56">
         <f>'ETF데이터'!$A$61</f>
         <v/>
       </c>
-      <c r="C77" s="57">
+      <c r="C78" s="57">
         <f>'ETF데이터'!$P$61</f>
         <v/>
       </c>
-      <c r="D77" s="48">
+      <c r="D78" s="48">
         <f>'ETF데이터'!$D$61</f>
         <v/>
       </c>
-      <c r="E77" s="58">
+      <c r="E78" s="58">
         <f>'ETF데이터'!$J$61</f>
         <v/>
       </c>
-      <c r="F77" s="48">
-        <f>IF($D77=0,0,ROUNDDOWN(100000000/$D77,0)*$D77*$E77/12)</f>
-        <v/>
-      </c>
-      <c r="G77" s="48">
-        <f>$F77*(1-$C$13*'ETF데이터'!$T$61)</f>
-        <v/>
-      </c>
-      <c r="H77" s="59">
+      <c r="F78" s="48">
+        <f>IF($D78=0,0,ROUNDDOWN(100000000/$D78,0)*$D78*$E78/12)</f>
+        <v/>
+      </c>
+      <c r="G78" s="48">
+        <f>$F78*(1-$C$13*'ETF데이터'!$T$61)</f>
+        <v/>
+      </c>
+      <c r="H78" s="59">
         <f>'ETF데이터'!$H$61</f>
         <v/>
       </c>
     </row>
-    <row r="78" ht="19" customHeight="1">
-      <c r="B78" s="64">
+    <row r="79" ht="19" customHeight="1">
+      <c r="B79" s="64">
         <f>'ETF데이터'!$A$82</f>
         <v/>
       </c>
-      <c r="C78" s="65">
+      <c r="C79" s="65">
         <f>'ETF데이터'!$P$82</f>
         <v/>
       </c>
-      <c r="D78" s="54">
+      <c r="D79" s="54">
         <f>'ETF데이터'!$D$82</f>
         <v/>
       </c>
-      <c r="E78" s="66">
+      <c r="E79" s="66">
         <f>'ETF데이터'!$J$82</f>
         <v/>
       </c>
-      <c r="F78" s="54">
-        <f>IF($D78=0,0,ROUNDDOWN(100000000/$D78,0)*$D78*$E78/12)</f>
-        <v/>
-      </c>
-      <c r="G78" s="54">
-        <f>$F78*(1-$C$13*'ETF데이터'!$T$82)</f>
-        <v/>
-      </c>
-      <c r="H78" s="67">
+      <c r="F79" s="54">
+        <f>IF($D79=0,0,ROUNDDOWN(100000000/$D79,0)*$D79*$E79/12)</f>
+        <v/>
+      </c>
+      <c r="G79" s="54">
+        <f>$F79*(1-$C$13*'ETF데이터'!$T$82)</f>
+        <v/>
+      </c>
+      <c r="H79" s="67">
         <f>'ETF데이터'!$H$82</f>
         <v/>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="7" t="inlineStr">
+    <row r="80">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>※ 드롭다운에는 기준 미달 종목까지 전부 담겨 있습니다. 위 표에는 기준을 통과한 종목만 실었습니다.</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="4" customHeight="1">
-      <c r="A81" s="8" t="n"/>
-      <c r="B81" s="8" t="n"/>
-      <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
-      <c r="E81" s="8" t="n"/>
-      <c r="F81" s="8" t="n"/>
-      <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
-    </row>
-    <row r="82" ht="26" customHeight="1">
-      <c r="A82" s="9" t="inlineStr">
+    <row r="82" ht="4" customHeight="1">
+      <c r="A82" s="8" t="n"/>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="n"/>
+      <c r="E82" s="8" t="n"/>
+      <c r="F82" s="8" t="n"/>
+      <c r="G82" s="8" t="n"/>
+      <c r="H82" s="8" t="n"/>
+    </row>
+    <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>유의사항</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="6" customHeight="1"/>
-    <row r="84" ht="16" customHeight="1">
-      <c r="B84" s="68" t="inlineStr">
-        <is>
-          <t>· 이 자료는 투자 권유가 아니라 참고 자료입니다. 최종 투자 판단과 그 결과는 투자자 본인에게 귀속됩니다.</t>
-        </is>
-      </c>
-    </row>
+    <row r="84" ht="6" customHeight="1"/>
     <row r="85" ht="16" customHeight="1">
       <c r="B85" s="68" t="inlineStr">
         <is>
+          <t>· 이 자료는 투자 권유가 아니라 참고 자료입니다. 최종 투자 판단과 그 결과는 투자자 본인에게 귀속됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="B86" s="68" t="inlineStr">
+        <is>
           <t>· ETF 는 예금자보호법의 보호를 받지 않으며, 원금 손실이 발생할 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>· 분배금은 확정되지 않습니다. 커버드콜 ETF 의 분배 재원은 옵션 프리미엄이므로, 시장 변동성이 낮아지면 분배금도 함께 줄어듭니다.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>· 분배금의 일부가 원금에서 지급될 수 있습니다(자본 환급). 이 경우 기준가가 그만큼 낮아집니다.</t>
+          <t>· 분배금은 확정되지 않습니다. 커버드콜 ETF 의 분배 재원은 옵션 프리미엄이므로, 시장 변동성이 낮아지면 분배금도 함께 줄어듭니다.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>· 표시된 연 분배율은 최근 12개월 실제 분배금 합계를 현재가로 나눈 값(사후 수치)이며, 앞으로의 수익률을 보장하지 않습니다.</t>
+          <t>· 분배금의 일부가 원금에서 지급될 수 있습니다(자본 환급). 이 경우 기준가가 그만큼 낮아집니다.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>· 세율은 국내 상장 ETF 분배금 기준 15.4%(배당소득세 14% + 지방소득세 1.4%)를 적용했습니다. 금융소득종합과세 대상자는 실효세율이 달라집니다.</t>
+          <t>· 표시된 연 분배율은 최근 12개월 실제 분배금 합계를 현재가로 나눈 값(사후 수치)이며, 앞으로의 수익률을 보장하지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>· 세금은 분배금 전액이 아니라 과세표준액에만 붙습니다. 국내주식 매매차익과 장내파생 손익은 과세표준에 들어가지 않으므로, 그 재원으로 분배하는 종목은 분배금의 상당 부분이 비과세입니다. 그래서 종목마다 다른 과세비율을 적용했고, 그 비율은 [ETF데이터] 장의 '과세비율' 칸에 있습니다.</t>
+          <t>· 세율은 국내 상장 ETF 분배금 기준 15.4%(배당소득세 14% + 지방소득세 1.4%)를 적용했습니다. 금융소득종합과세 대상자는 실효세율이 달라집니다.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>· 과세비율은 최근 12개월에 실제로 매겨진 과세표준액을 같은 기간 분배금으로 나눈 값입니다. 지나간 실적이므로 앞으로도 같다는 뜻은 아닙니다 — 분배 재원(배당·이자·매매차익·파생손익)의 구성이 바뀌면 비율도 함께 바뀌고, 실제로 한 종목 안에서도 회차마다 0%에서 17%까지 움직인 사례가 있습니다. 실제 세액은 지급 시점의 과세표준으로 확정되므로 이 표와 다를 수 있습니다. 과세비율을 구하지 못한 종목은 전액 과세로 보수적으로 계산했습니다.</t>
+          <t>· 세금은 분배금 전액이 아니라 과세표준액에만 붙습니다. 국내주식 매매차익과 장내파생 손익은 과세표준에 들어가지 않으므로, 그 재원으로 분배하는 종목은 분배금의 상당 부분이 비과세입니다.</t>
         </is>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>· 세무 상담이 필요한 사안은 이 문서로 갈음하지 마시고 세무 전문가의 확인을 받으십시오.</t>
+          <t>· 다만 이번 자료에서는 고를 수 있는 573종목 중 3종목만 과세표준을 확인할 수 있었습니다. 나머지 종목은 정확한 과세표준을 확인하지 못해 부득이 분배금 전액에 15.4%를 적용했습니다. 그 종목들의 실제 세후 수령액은 표시된 금액보다 많을 수 있습니다. 확인된 종목은 [ETF데이터] 장의 '과세비율' 칸에 값이 적혀 있고, 확인하지 못한 종목은 그 칸이 비어 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>· 매매수수료·거래세·환율 변동은 반영하지 않았습니다. 총보수는 분배율에 이미 반영되어 있습니다(기준가 차감).</t>
+          <t>· 과세비율은 최근 12개월에 실제로 매겨진 과세표준액을 같은 기간 분배금으로 나눈 값입니다. 지나간 실적이므로 앞으로도 같다는 뜻은 아닙니다 — 분배 재원(배당·이자·매매차익·파생손익)의 구성이 바뀌면 비율도 함께 바뀌고, 실제로 한 종목 안에서도 회차마다 0%에서 17%까지 움직인 사례가 있습니다. 실제 세액은 지급 시점의 과세표준으로 확정되므로 이 표와 다를 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>· 수량은 정수 매수를 가정해 내림 처리했습니다. 남는 금액은 '미투자 잔액'에 표시됩니다.</t>
+          <t>· 세무 상담이 필요한 사안은 이 문서로 갈음하지 마시고 세무 전문가의 확인을 받으십시오.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>· 여러 종목에 나눠 담아도 분배 시기는 종목마다 다릅니다. 매월 같은 날 한꺼번에 들어오지 않습니다.</t>
+          <t>· 매매수수료·거래세·환율 변동은 반영하지 않았습니다. 총보수는 분배율에 이미 반영되어 있습니다(기준가 차감).</t>
         </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>· 목록에는 커버드콜뿐 아니라 리츠·채권형·배당주·파킹형 월배당 ETF 가 함께 있습니다. 분배 재원과 위험이 서로 다르므로 [ETF데이터] 장의 '유형'·'자산군' 칸을 확인하십시오.</t>
+          <t>· 수량은 정수 매수를 가정해 내림 처리했습니다. 남는 금액은 '미투자 잔액'에 표시됩니다.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1">
       <c r="B97" s="7" t="inlineStr">
         <is>
+          <t>· 여러 종목에 나눠 담아도 분배 시기는 종목마다 다릅니다. 매월 같은 날 한꺼번에 들어오지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>· 목록에는 커버드콜뿐 아니라 리츠·채권형·배당주·파킹형 월배당 ETF 가 함께 있습니다. 분배 재원과 위험이 서로 다르므로 [ETF데이터] 장의 '유형'·'자산군' 칸을 확인하십시오.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="B99" s="7" t="inlineStr">
+        <is>
           <t>· 드롭다운에는 유동성·변동성 기준에 미달한 종목도 담겨 있습니다. 담으면 2. 아래에 안내가 뜹니다.</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="15" customHeight="1">
-      <c r="B99" s="69" t="inlineStr">
+    <row r="101" ht="15" customHeight="1">
+      <c r="B101" s="69" t="inlineStr">
         <is>
           <t>자료 출처 ETFCHECK (www.etfcheck.co.kr) · 수집 2026-09-18T00:41:51.124Z · 대상 국내 상장 월배당 ETF · 채택 기준 순자산 300억원 이상, 60일 평균거래대금 5억원 이상, 연환산 변동성 35% 이하, 분배 이력 12개월 이상</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
     <mergeCell ref="B99:H99"/>
-    <mergeCell ref="B84:H84"/>
     <mergeCell ref="B92:H92"/>
     <mergeCell ref="B95:H95"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B89:H89"/>
-    <mergeCell ref="G39:H39"/>
     <mergeCell ref="B85:H85"/>
     <mergeCell ref="B32:H32"/>
     <mergeCell ref="B94:H94"/>
     <mergeCell ref="B97:H97"/>
+    <mergeCell ref="B35:H35"/>
     <mergeCell ref="B91:H91"/>
     <mergeCell ref="B90:H90"/>
     <mergeCell ref="B31:H31"/>
@@ -3039,8 +3092,11 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B86:H86"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="B98:H98"/>
+    <mergeCell ref="B101:H101"/>
     <mergeCell ref="B88:H88"/>
     <mergeCell ref="B87:H87"/>
+    <mergeCell ref="G40:H40"/>
     <mergeCell ref="B34:H34"/>
   </mergeCells>
   <dataValidations count="2">
@@ -6636,9 +6692,7 @@
       <c r="S4" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T4" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T4" s="74" t="n"/>
       <c r="U4">
         <f>IF(AND($J4&lt;&gt;"",OR(조회_주기="전체",$R4=조회_주기),$J4&gt;=조회_최소,$J4&lt;=조회_최대),1,0)</f>
         <v/>
@@ -6734,9 +6788,7 @@
       <c r="S5" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T5" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T5" s="74" t="n"/>
       <c r="U5">
         <f>IF(AND($J5&lt;&gt;"",OR(조회_주기="전체",$R5=조회_주기),$J5&gt;=조회_최소,$J5&lt;=조회_최대),1,0)</f>
         <v/>
@@ -6832,9 +6884,7 @@
       <c r="S6" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T6" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T6" s="74" t="n"/>
       <c r="U6">
         <f>IF(AND($J6&lt;&gt;"",OR(조회_주기="전체",$R6=조회_주기),$J6&gt;=조회_최소,$J6&lt;=조회_최대),1,0)</f>
         <v/>
@@ -6930,9 +6980,7 @@
       <c r="S7" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T7" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" s="74" t="n"/>
       <c r="U7">
         <f>IF(AND($J7&lt;&gt;"",OR(조회_주기="전체",$R7=조회_주기),$J7&gt;=조회_최소,$J7&lt;=조회_최대),1,0)</f>
         <v/>
@@ -7028,9 +7076,7 @@
       <c r="S8" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T8" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T8" s="74" t="n"/>
       <c r="U8">
         <f>IF(AND($J8&lt;&gt;"",OR(조회_주기="전체",$R8=조회_주기),$J8&gt;=조회_최소,$J8&lt;=조회_최대),1,0)</f>
         <v/>
@@ -7126,9 +7172,7 @@
       <c r="S9" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T9" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T9" s="74" t="n"/>
       <c r="U9">
         <f>IF(AND($J9&lt;&gt;"",OR(조회_주기="전체",$R9=조회_주기),$J9&gt;=조회_최소,$J9&lt;=조회_최대),1,0)</f>
         <v/>
@@ -7224,9 +7268,7 @@
       <c r="S10" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T10" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T10" s="74" t="n"/>
       <c r="U10">
         <f>IF(AND($J10&lt;&gt;"",OR(조회_주기="전체",$R10=조회_주기),$J10&gt;=조회_최소,$J10&lt;=조회_최대),1,0)</f>
         <v/>
@@ -7322,9 +7364,7 @@
       <c r="S11" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T11" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T11" s="74" t="n"/>
       <c r="U11">
         <f>IF(AND($J11&lt;&gt;"",OR(조회_주기="전체",$R11=조회_주기),$J11&gt;=조회_최소,$J11&lt;=조회_최대),1,0)</f>
         <v/>
@@ -7420,9 +7460,7 @@
       <c r="S12" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T12" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T12" s="74" t="n"/>
       <c r="U12">
         <f>IF(AND($J12&lt;&gt;"",OR(조회_주기="전체",$R12=조회_주기),$J12&gt;=조회_최소,$J12&lt;=조회_최대),1,0)</f>
         <v/>
@@ -7518,9 +7556,7 @@
       <c r="S13" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T13" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T13" s="74" t="n"/>
       <c r="U13">
         <f>IF(AND($J13&lt;&gt;"",OR(조회_주기="전체",$R13=조회_주기),$J13&gt;=조회_최소,$J13&lt;=조회_최대),1,0)</f>
         <v/>
@@ -7616,9 +7652,7 @@
       <c r="S14" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T14" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T14" s="74" t="n"/>
       <c r="U14">
         <f>IF(AND($J14&lt;&gt;"",OR(조회_주기="전체",$R14=조회_주기),$J14&gt;=조회_최소,$J14&lt;=조회_최대),1,0)</f>
         <v/>
@@ -7714,9 +7748,7 @@
       <c r="S15" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T15" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T15" s="74" t="n"/>
       <c r="U15">
         <f>IF(AND($J15&lt;&gt;"",OR(조회_주기="전체",$R15=조회_주기),$J15&gt;=조회_최소,$J15&lt;=조회_최대),1,0)</f>
         <v/>
@@ -7812,9 +7844,7 @@
       <c r="S16" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T16" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T16" s="74" t="n"/>
       <c r="U16">
         <f>IF(AND($J16&lt;&gt;"",OR(조회_주기="전체",$R16=조회_주기),$J16&gt;=조회_최소,$J16&lt;=조회_최대),1,0)</f>
         <v/>
@@ -7910,9 +7940,7 @@
       <c r="S17" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T17" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T17" s="74" t="n"/>
       <c r="U17">
         <f>IF(AND($J17&lt;&gt;"",OR(조회_주기="전체",$R17=조회_주기),$J17&gt;=조회_최소,$J17&lt;=조회_최대),1,0)</f>
         <v/>
@@ -8008,9 +8036,7 @@
       <c r="S18" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T18" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T18" s="74" t="n"/>
       <c r="U18">
         <f>IF(AND($J18&lt;&gt;"",OR(조회_주기="전체",$R18=조회_주기),$J18&gt;=조회_최소,$J18&lt;=조회_최대),1,0)</f>
         <v/>
@@ -8106,9 +8132,7 @@
       <c r="S19" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T19" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T19" s="74" t="n"/>
       <c r="U19">
         <f>IF(AND($J19&lt;&gt;"",OR(조회_주기="전체",$R19=조회_주기),$J19&gt;=조회_최소,$J19&lt;=조회_최대),1,0)</f>
         <v/>
@@ -8204,9 +8228,7 @@
       <c r="S20" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T20" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T20" s="74" t="n"/>
       <c r="U20">
         <f>IF(AND($J20&lt;&gt;"",OR(조회_주기="전체",$R20=조회_주기),$J20&gt;=조회_최소,$J20&lt;=조회_최대),1,0)</f>
         <v/>
@@ -8302,9 +8324,7 @@
       <c r="S21" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T21" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T21" s="74" t="n"/>
       <c r="U21">
         <f>IF(AND($J21&lt;&gt;"",OR(조회_주기="전체",$R21=조회_주기),$J21&gt;=조회_최소,$J21&lt;=조회_최대),1,0)</f>
         <v/>
@@ -8400,9 +8420,7 @@
       <c r="S22" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T22" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T22" s="74" t="n"/>
       <c r="U22">
         <f>IF(AND($J22&lt;&gt;"",OR(조회_주기="전체",$R22=조회_주기),$J22&gt;=조회_최소,$J22&lt;=조회_최대),1,0)</f>
         <v/>
@@ -8498,9 +8516,7 @@
       <c r="S23" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T23" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T23" s="74" t="n"/>
       <c r="U23">
         <f>IF(AND($J23&lt;&gt;"",OR(조회_주기="전체",$R23=조회_주기),$J23&gt;=조회_최소,$J23&lt;=조회_최대),1,0)</f>
         <v/>
@@ -8596,9 +8612,7 @@
       <c r="S24" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T24" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T24" s="74" t="n"/>
       <c r="U24">
         <f>IF(AND($J24&lt;&gt;"",OR(조회_주기="전체",$R24=조회_주기),$J24&gt;=조회_최소,$J24&lt;=조회_최대),1,0)</f>
         <v/>
@@ -8694,9 +8708,7 @@
       <c r="S25" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T25" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T25" s="74" t="n"/>
       <c r="U25">
         <f>IF(AND($J25&lt;&gt;"",OR(조회_주기="전체",$R25=조회_주기),$J25&gt;=조회_최소,$J25&lt;=조회_최대),1,0)</f>
         <v/>
@@ -8792,9 +8804,7 @@
       <c r="S26" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T26" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T26" s="74" t="n"/>
       <c r="U26">
         <f>IF(AND($J26&lt;&gt;"",OR(조회_주기="전체",$R26=조회_주기),$J26&gt;=조회_최소,$J26&lt;=조회_최대),1,0)</f>
         <v/>
@@ -8890,9 +8900,7 @@
       <c r="S27" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="T27" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T27" s="74" t="n"/>
       <c r="U27">
         <f>IF(AND($J27&lt;&gt;"",OR(조회_주기="전체",$R27=조회_주기),$J27&gt;=조회_최소,$J27&lt;=조회_최대),1,0)</f>
         <v/>
@@ -8988,9 +8996,7 @@
       <c r="S28" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T28" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T28" s="74" t="n"/>
       <c r="U28">
         <f>IF(AND($J28&lt;&gt;"",OR(조회_주기="전체",$R28=조회_주기),$J28&gt;=조회_최소,$J28&lt;=조회_최대),1,0)</f>
         <v/>
@@ -9086,9 +9092,7 @@
       <c r="S29" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T29" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T29" s="74" t="n"/>
       <c r="U29">
         <f>IF(AND($J29&lt;&gt;"",OR(조회_주기="전체",$R29=조회_주기),$J29&gt;=조회_최소,$J29&lt;=조회_최대),1,0)</f>
         <v/>
@@ -9184,9 +9188,7 @@
       <c r="S30" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T30" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T30" s="74" t="n"/>
       <c r="U30">
         <f>IF(AND($J30&lt;&gt;"",OR(조회_주기="전체",$R30=조회_주기),$J30&gt;=조회_최소,$J30&lt;=조회_최대),1,0)</f>
         <v/>
@@ -9282,9 +9284,7 @@
       <c r="S31" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T31" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T31" s="74" t="n"/>
       <c r="U31">
         <f>IF(AND($J31&lt;&gt;"",OR(조회_주기="전체",$R31=조회_주기),$J31&gt;=조회_최소,$J31&lt;=조회_최대),1,0)</f>
         <v/>
@@ -9380,9 +9380,7 @@
       <c r="S32" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T32" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T32" s="74" t="n"/>
       <c r="U32">
         <f>IF(AND($J32&lt;&gt;"",OR(조회_주기="전체",$R32=조회_주기),$J32&gt;=조회_최소,$J32&lt;=조회_최대),1,0)</f>
         <v/>
@@ -9478,9 +9476,7 @@
       <c r="S33" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T33" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T33" s="74" t="n"/>
       <c r="U33">
         <f>IF(AND($J33&lt;&gt;"",OR(조회_주기="전체",$R33=조회_주기),$J33&gt;=조회_최소,$J33&lt;=조회_최대),1,0)</f>
         <v/>
@@ -9576,9 +9572,7 @@
       <c r="S34" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T34" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T34" s="74" t="n"/>
       <c r="U34">
         <f>IF(AND($J34&lt;&gt;"",OR(조회_주기="전체",$R34=조회_주기),$J34&gt;=조회_최소,$J34&lt;=조회_최대),1,0)</f>
         <v/>
@@ -9674,9 +9668,7 @@
       <c r="S35" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T35" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T35" s="74" t="n"/>
       <c r="U35">
         <f>IF(AND($J35&lt;&gt;"",OR(조회_주기="전체",$R35=조회_주기),$J35&gt;=조회_최소,$J35&lt;=조회_최대),1,0)</f>
         <v/>
@@ -9772,9 +9764,7 @@
       <c r="S36" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T36" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T36" s="74" t="n"/>
       <c r="U36">
         <f>IF(AND($J36&lt;&gt;"",OR(조회_주기="전체",$R36=조회_주기),$J36&gt;=조회_최소,$J36&lt;=조회_최대),1,0)</f>
         <v/>
@@ -9870,9 +9860,7 @@
       <c r="S37" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T37" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T37" s="74" t="n"/>
       <c r="U37">
         <f>IF(AND($J37&lt;&gt;"",OR(조회_주기="전체",$R37=조회_주기),$J37&gt;=조회_최소,$J37&lt;=조회_최대),1,0)</f>
         <v/>
@@ -9968,9 +9956,7 @@
       <c r="S38" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T38" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T38" s="74" t="n"/>
       <c r="U38">
         <f>IF(AND($J38&lt;&gt;"",OR(조회_주기="전체",$R38=조회_주기),$J38&gt;=조회_최소,$J38&lt;=조회_최대),1,0)</f>
         <v/>
@@ -10066,9 +10052,7 @@
       <c r="S39" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T39" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T39" s="74" t="n"/>
       <c r="U39">
         <f>IF(AND($J39&lt;&gt;"",OR(조회_주기="전체",$R39=조회_주기),$J39&gt;=조회_최소,$J39&lt;=조회_최대),1,0)</f>
         <v/>
@@ -10164,9 +10148,7 @@
       <c r="S40" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T40" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T40" s="74" t="n"/>
       <c r="U40">
         <f>IF(AND($J40&lt;&gt;"",OR(조회_주기="전체",$R40=조회_주기),$J40&gt;=조회_최소,$J40&lt;=조회_최대),1,0)</f>
         <v/>
@@ -10262,9 +10244,7 @@
       <c r="S41" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T41" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T41" s="74" t="n"/>
       <c r="U41">
         <f>IF(AND($J41&lt;&gt;"",OR(조회_주기="전체",$R41=조회_주기),$J41&gt;=조회_최소,$J41&lt;=조회_최대),1,0)</f>
         <v/>
@@ -10360,9 +10340,7 @@
       <c r="S42" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T42" s="74" t="n"/>
       <c r="U42">
         <f>IF(AND($J42&lt;&gt;"",OR(조회_주기="전체",$R42=조회_주기),$J42&gt;=조회_최소,$J42&lt;=조회_최대),1,0)</f>
         <v/>
@@ -10458,9 +10436,7 @@
       <c r="S43" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T43" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T43" s="74" t="n"/>
       <c r="U43">
         <f>IF(AND($J43&lt;&gt;"",OR(조회_주기="전체",$R43=조회_주기),$J43&gt;=조회_최소,$J43&lt;=조회_최대),1,0)</f>
         <v/>
@@ -10556,9 +10532,7 @@
       <c r="S44" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T44" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T44" s="74" t="n"/>
       <c r="U44">
         <f>IF(AND($J44&lt;&gt;"",OR(조회_주기="전체",$R44=조회_주기),$J44&gt;=조회_최소,$J44&lt;=조회_최대),1,0)</f>
         <v/>
@@ -10654,9 +10628,7 @@
       <c r="S45" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T45" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T45" s="74" t="n"/>
       <c r="U45">
         <f>IF(AND($J45&lt;&gt;"",OR(조회_주기="전체",$R45=조회_주기),$J45&gt;=조회_최소,$J45&lt;=조회_최대),1,0)</f>
         <v/>
@@ -10752,9 +10724,7 @@
       <c r="S46" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T46" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T46" s="74" t="n"/>
       <c r="U46">
         <f>IF(AND($J46&lt;&gt;"",OR(조회_주기="전체",$R46=조회_주기),$J46&gt;=조회_최소,$J46&lt;=조회_최대),1,0)</f>
         <v/>
@@ -10850,9 +10820,7 @@
       <c r="S47" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T47" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T47" s="74" t="n"/>
       <c r="U47">
         <f>IF(AND($J47&lt;&gt;"",OR(조회_주기="전체",$R47=조회_주기),$J47&gt;=조회_최소,$J47&lt;=조회_최대),1,0)</f>
         <v/>
@@ -10948,9 +10916,7 @@
       <c r="S48" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T48" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T48" s="74" t="n"/>
       <c r="U48">
         <f>IF(AND($J48&lt;&gt;"",OR(조회_주기="전체",$R48=조회_주기),$J48&gt;=조회_최소,$J48&lt;=조회_최대),1,0)</f>
         <v/>
@@ -11046,9 +11012,7 @@
       <c r="S49" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T49" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T49" s="74" t="n"/>
       <c r="U49">
         <f>IF(AND($J49&lt;&gt;"",OR(조회_주기="전체",$R49=조회_주기),$J49&gt;=조회_최소,$J49&lt;=조회_최대),1,0)</f>
         <v/>
@@ -11144,9 +11108,7 @@
       <c r="S50" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T50" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T50" s="74" t="n"/>
       <c r="U50">
         <f>IF(AND($J50&lt;&gt;"",OR(조회_주기="전체",$R50=조회_주기),$J50&gt;=조회_최소,$J50&lt;=조회_최대),1,0)</f>
         <v/>
@@ -11242,9 +11204,7 @@
       <c r="S51" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T51" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T51" s="74" t="n"/>
       <c r="U51">
         <f>IF(AND($J51&lt;&gt;"",OR(조회_주기="전체",$R51=조회_주기),$J51&gt;=조회_최소,$J51&lt;=조회_최대),1,0)</f>
         <v/>
@@ -11340,9 +11300,7 @@
       <c r="S52" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T52" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T52" s="74" t="n"/>
       <c r="U52">
         <f>IF(AND($J52&lt;&gt;"",OR(조회_주기="전체",$R52=조회_주기),$J52&gt;=조회_최소,$J52&lt;=조회_최대),1,0)</f>
         <v/>
@@ -11438,9 +11396,7 @@
       <c r="S53" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T53" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T53" s="74" t="n"/>
       <c r="U53">
         <f>IF(AND($J53&lt;&gt;"",OR(조회_주기="전체",$R53=조회_주기),$J53&gt;=조회_최소,$J53&lt;=조회_최대),1,0)</f>
         <v/>
@@ -11536,9 +11492,7 @@
       <c r="S54" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T54" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T54" s="74" t="n"/>
       <c r="U54">
         <f>IF(AND($J54&lt;&gt;"",OR(조회_주기="전체",$R54=조회_주기),$J54&gt;=조회_최소,$J54&lt;=조회_최대),1,0)</f>
         <v/>
@@ -11634,9 +11588,7 @@
       <c r="S55" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T55" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T55" s="74" t="n"/>
       <c r="U55">
         <f>IF(AND($J55&lt;&gt;"",OR(조회_주기="전체",$R55=조회_주기),$J55&gt;=조회_최소,$J55&lt;=조회_최대),1,0)</f>
         <v/>
@@ -11732,9 +11684,7 @@
       <c r="S56" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T56" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T56" s="74" t="n"/>
       <c r="U56">
         <f>IF(AND($J56&lt;&gt;"",OR(조회_주기="전체",$R56=조회_주기),$J56&gt;=조회_최소,$J56&lt;=조회_최대),1,0)</f>
         <v/>
@@ -11830,9 +11780,7 @@
       <c r="S57" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T57" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T57" s="74" t="n"/>
       <c r="U57">
         <f>IF(AND($J57&lt;&gt;"",OR(조회_주기="전체",$R57=조회_주기),$J57&gt;=조회_최소,$J57&lt;=조회_최대),1,0)</f>
         <v/>
@@ -11928,9 +11876,7 @@
       <c r="S58" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T58" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T58" s="74" t="n"/>
       <c r="U58">
         <f>IF(AND($J58&lt;&gt;"",OR(조회_주기="전체",$R58=조회_주기),$J58&gt;=조회_최소,$J58&lt;=조회_최대),1,0)</f>
         <v/>
@@ -12026,9 +11972,7 @@
       <c r="S59" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T59" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T59" s="74" t="n"/>
       <c r="U59">
         <f>IF(AND($J59&lt;&gt;"",OR(조회_주기="전체",$R59=조회_주기),$J59&gt;=조회_최소,$J59&lt;=조회_최대),1,0)</f>
         <v/>
@@ -12124,9 +12068,7 @@
       <c r="S60" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T60" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T60" s="74" t="n"/>
       <c r="U60">
         <f>IF(AND($J60&lt;&gt;"",OR(조회_주기="전체",$R60=조회_주기),$J60&gt;=조회_최소,$J60&lt;=조회_최대),1,0)</f>
         <v/>
@@ -12222,9 +12164,7 @@
       <c r="S61" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T61" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T61" s="74" t="n"/>
       <c r="U61">
         <f>IF(AND($J61&lt;&gt;"",OR(조회_주기="전체",$R61=조회_주기),$J61&gt;=조회_최소,$J61&lt;=조회_최대),1,0)</f>
         <v/>
@@ -12320,9 +12260,7 @@
       <c r="S62" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T62" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T62" s="74" t="n"/>
       <c r="U62">
         <f>IF(AND($J62&lt;&gt;"",OR(조회_주기="전체",$R62=조회_주기),$J62&gt;=조회_최소,$J62&lt;=조회_최대),1,0)</f>
         <v/>
@@ -12418,9 +12356,7 @@
       <c r="S63" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T63" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T63" s="74" t="n"/>
       <c r="U63">
         <f>IF(AND($J63&lt;&gt;"",OR(조회_주기="전체",$R63=조회_주기),$J63&gt;=조회_최소,$J63&lt;=조회_최대),1,0)</f>
         <v/>
@@ -12516,9 +12452,7 @@
       <c r="S64" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T64" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T64" s="74" t="n"/>
       <c r="U64">
         <f>IF(AND($J64&lt;&gt;"",OR(조회_주기="전체",$R64=조회_주기),$J64&gt;=조회_최소,$J64&lt;=조회_최대),1,0)</f>
         <v/>
@@ -12614,9 +12548,7 @@
       <c r="S65" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T65" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T65" s="74" t="n"/>
       <c r="U65">
         <f>IF(AND($J65&lt;&gt;"",OR(조회_주기="전체",$R65=조회_주기),$J65&gt;=조회_최소,$J65&lt;=조회_최대),1,0)</f>
         <v/>
@@ -12712,9 +12644,7 @@
       <c r="S66" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T66" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T66" s="74" t="n"/>
       <c r="U66">
         <f>IF(AND($J66&lt;&gt;"",OR(조회_주기="전체",$R66=조회_주기),$J66&gt;=조회_최소,$J66&lt;=조회_최대),1,0)</f>
         <v/>
@@ -12810,9 +12740,7 @@
       <c r="S67" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T67" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T67" s="74" t="n"/>
       <c r="U67">
         <f>IF(AND($J67&lt;&gt;"",OR(조회_주기="전체",$R67=조회_주기),$J67&gt;=조회_최소,$J67&lt;=조회_최대),1,0)</f>
         <v/>
@@ -12908,9 +12836,7 @@
       <c r="S68" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T68" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T68" s="74" t="n"/>
       <c r="U68">
         <f>IF(AND($J68&lt;&gt;"",OR(조회_주기="전체",$R68=조회_주기),$J68&gt;=조회_최소,$J68&lt;=조회_최대),1,0)</f>
         <v/>
@@ -13006,9 +12932,7 @@
       <c r="S69" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T69" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T69" s="74" t="n"/>
       <c r="U69">
         <f>IF(AND($J69&lt;&gt;"",OR(조회_주기="전체",$R69=조회_주기),$J69&gt;=조회_최소,$J69&lt;=조회_최대),1,0)</f>
         <v/>
@@ -13104,9 +13028,7 @@
       <c r="S70" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T70" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T70" s="74" t="n"/>
       <c r="U70">
         <f>IF(AND($J70&lt;&gt;"",OR(조회_주기="전체",$R70=조회_주기),$J70&gt;=조회_최소,$J70&lt;=조회_최대),1,0)</f>
         <v/>
@@ -13202,9 +13124,7 @@
       <c r="S71" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T71" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T71" s="74" t="n"/>
       <c r="U71">
         <f>IF(AND($J71&lt;&gt;"",OR(조회_주기="전체",$R71=조회_주기),$J71&gt;=조회_최소,$J71&lt;=조회_최대),1,0)</f>
         <v/>
@@ -13300,9 +13220,7 @@
       <c r="S72" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T72" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T72" s="74" t="n"/>
       <c r="U72">
         <f>IF(AND($J72&lt;&gt;"",OR(조회_주기="전체",$R72=조회_주기),$J72&gt;=조회_최소,$J72&lt;=조회_최대),1,0)</f>
         <v/>
@@ -13398,9 +13316,7 @@
       <c r="S73" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T73" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T73" s="74" t="n"/>
       <c r="U73">
         <f>IF(AND($J73&lt;&gt;"",OR(조회_주기="전체",$R73=조회_주기),$J73&gt;=조회_최소,$J73&lt;=조회_최대),1,0)</f>
         <v/>
@@ -13496,9 +13412,7 @@
       <c r="S74" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T74" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T74" s="74" t="n"/>
       <c r="U74">
         <f>IF(AND($J74&lt;&gt;"",OR(조회_주기="전체",$R74=조회_주기),$J74&gt;=조회_최소,$J74&lt;=조회_최대),1,0)</f>
         <v/>
@@ -13594,9 +13508,7 @@
       <c r="S75" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T75" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T75" s="74" t="n"/>
       <c r="U75">
         <f>IF(AND($J75&lt;&gt;"",OR(조회_주기="전체",$R75=조회_주기),$J75&gt;=조회_최소,$J75&lt;=조회_최대),1,0)</f>
         <v/>
@@ -13692,9 +13604,7 @@
       <c r="S76" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T76" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T76" s="74" t="n"/>
       <c r="U76">
         <f>IF(AND($J76&lt;&gt;"",OR(조회_주기="전체",$R76=조회_주기),$J76&gt;=조회_최소,$J76&lt;=조회_최대),1,0)</f>
         <v/>
@@ -13790,9 +13700,7 @@
       <c r="S77" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T77" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T77" s="74" t="n"/>
       <c r="U77">
         <f>IF(AND($J77&lt;&gt;"",OR(조회_주기="전체",$R77=조회_주기),$J77&gt;=조회_최소,$J77&lt;=조회_최대),1,0)</f>
         <v/>
@@ -13888,9 +13796,7 @@
       <c r="S78" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T78" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T78" s="74" t="n"/>
       <c r="U78">
         <f>IF(AND($J78&lt;&gt;"",OR(조회_주기="전체",$R78=조회_주기),$J78&gt;=조회_최소,$J78&lt;=조회_최대),1,0)</f>
         <v/>
@@ -13986,9 +13892,7 @@
       <c r="S79" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T79" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T79" s="74" t="n"/>
       <c r="U79">
         <f>IF(AND($J79&lt;&gt;"",OR(조회_주기="전체",$R79=조회_주기),$J79&gt;=조회_최소,$J79&lt;=조회_최대),1,0)</f>
         <v/>
@@ -14084,9 +13988,7 @@
       <c r="S80" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T80" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T80" s="74" t="n"/>
       <c r="U80">
         <f>IF(AND($J80&lt;&gt;"",OR(조회_주기="전체",$R80=조회_주기),$J80&gt;=조회_최소,$J80&lt;=조회_최대),1,0)</f>
         <v/>
@@ -14182,9 +14084,7 @@
       <c r="S81" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T81" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T81" s="74" t="n"/>
       <c r="U81">
         <f>IF(AND($J81&lt;&gt;"",OR(조회_주기="전체",$R81=조회_주기),$J81&gt;=조회_최소,$J81&lt;=조회_최대),1,0)</f>
         <v/>
@@ -14280,9 +14180,7 @@
       <c r="S82" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="T82" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T82" s="74" t="n"/>
       <c r="U82">
         <f>IF(AND($J82&lt;&gt;"",OR(조회_주기="전체",$R82=조회_주기),$J82&gt;=조회_최소,$J82&lt;=조회_최대),1,0)</f>
         <v/>
@@ -14378,9 +14276,7 @@
       <c r="S83" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T83" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T83" s="74" t="n"/>
       <c r="U83">
         <f>IF(AND($J83&lt;&gt;"",OR(조회_주기="전체",$R83=조회_주기),$J83&gt;=조회_최소,$J83&lt;=조회_최대),1,0)</f>
         <v/>
@@ -14476,9 +14372,7 @@
       <c r="S84" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T84" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T84" s="74" t="n"/>
       <c r="U84">
         <f>IF(AND($J84&lt;&gt;"",OR(조회_주기="전체",$R84=조회_주기),$J84&gt;=조회_최소,$J84&lt;=조회_최대),1,0)</f>
         <v/>
@@ -14574,9 +14468,7 @@
       <c r="S85" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T85" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T85" s="74" t="n"/>
       <c r="U85">
         <f>IF(AND($J85&lt;&gt;"",OR(조회_주기="전체",$R85=조회_주기),$J85&gt;=조회_최소,$J85&lt;=조회_최대),1,0)</f>
         <v/>
@@ -14672,9 +14564,7 @@
       <c r="S86" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T86" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T86" s="74" t="n"/>
       <c r="U86">
         <f>IF(AND($J86&lt;&gt;"",OR(조회_주기="전체",$R86=조회_주기),$J86&gt;=조회_최소,$J86&lt;=조회_최대),1,0)</f>
         <v/>
@@ -14770,9 +14660,7 @@
       <c r="S87" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="T87" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T87" s="74" t="n"/>
       <c r="U87">
         <f>IF(AND($J87&lt;&gt;"",OR(조회_주기="전체",$R87=조회_주기),$J87&gt;=조회_최소,$J87&lt;=조회_최대),1,0)</f>
         <v/>
@@ -14868,9 +14756,7 @@
       <c r="S88" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T88" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T88" s="74" t="n"/>
       <c r="U88">
         <f>IF(AND($J88&lt;&gt;"",OR(조회_주기="전체",$R88=조회_주기),$J88&gt;=조회_최소,$J88&lt;=조회_최대),1,0)</f>
         <v/>
@@ -14966,9 +14852,7 @@
       <c r="S89" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T89" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T89" s="74" t="n"/>
       <c r="U89">
         <f>IF(AND($J89&lt;&gt;"",OR(조회_주기="전체",$R89=조회_주기),$J89&gt;=조회_최소,$J89&lt;=조회_최대),1,0)</f>
         <v/>
@@ -15064,9 +14948,7 @@
       <c r="S90" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T90" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T90" s="74" t="n"/>
       <c r="U90">
         <f>IF(AND($J90&lt;&gt;"",OR(조회_주기="전체",$R90=조회_주기),$J90&gt;=조회_최소,$J90&lt;=조회_최대),1,0)</f>
         <v/>
@@ -15162,9 +15044,7 @@
       <c r="S91" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T91" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T91" s="74" t="n"/>
       <c r="U91">
         <f>IF(AND($J91&lt;&gt;"",OR(조회_주기="전체",$R91=조회_주기),$J91&gt;=조회_최소,$J91&lt;=조회_최대),1,0)</f>
         <v/>
@@ -15260,9 +15140,7 @@
       <c r="S92" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="T92" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T92" s="74" t="n"/>
       <c r="U92">
         <f>IF(AND($J92&lt;&gt;"",OR(조회_주기="전체",$R92=조회_주기),$J92&gt;=조회_최소,$J92&lt;=조회_최대),1,0)</f>
         <v/>
@@ -15358,9 +15236,7 @@
       <c r="S93" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T93" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T93" s="74" t="n"/>
       <c r="U93">
         <f>IF(AND($J93&lt;&gt;"",OR(조회_주기="전체",$R93=조회_주기),$J93&gt;=조회_최소,$J93&lt;=조회_최대),1,0)</f>
         <v/>
@@ -15456,9 +15332,7 @@
       <c r="S94" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T94" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T94" s="74" t="n"/>
       <c r="U94">
         <f>IF(AND($J94&lt;&gt;"",OR(조회_주기="전체",$R94=조회_주기),$J94&gt;=조회_최소,$J94&lt;=조회_최대),1,0)</f>
         <v/>
@@ -15554,9 +15428,7 @@
       <c r="S95" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T95" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T95" s="74" t="n"/>
       <c r="U95">
         <f>IF(AND($J95&lt;&gt;"",OR(조회_주기="전체",$R95=조회_주기),$J95&gt;=조회_최소,$J95&lt;=조회_최대),1,0)</f>
         <v/>
@@ -15652,9 +15524,7 @@
       <c r="S96" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T96" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T96" s="74" t="n"/>
       <c r="U96">
         <f>IF(AND($J96&lt;&gt;"",OR(조회_주기="전체",$R96=조회_주기),$J96&gt;=조회_최소,$J96&lt;=조회_최대),1,0)</f>
         <v/>
@@ -15750,9 +15620,7 @@
       <c r="S97" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T97" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T97" s="74" t="n"/>
       <c r="U97">
         <f>IF(AND($J97&lt;&gt;"",OR(조회_주기="전체",$R97=조회_주기),$J97&gt;=조회_최소,$J97&lt;=조회_최대),1,0)</f>
         <v/>
@@ -15848,9 +15716,7 @@
       <c r="S98" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T98" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T98" s="74" t="n"/>
       <c r="U98">
         <f>IF(AND($J98&lt;&gt;"",OR(조회_주기="전체",$R98=조회_주기),$J98&gt;=조회_최소,$J98&lt;=조회_최대),1,0)</f>
         <v/>
@@ -15946,9 +15812,7 @@
       <c r="S99" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T99" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T99" s="74" t="n"/>
       <c r="U99">
         <f>IF(AND($J99&lt;&gt;"",OR(조회_주기="전체",$R99=조회_주기),$J99&gt;=조회_최소,$J99&lt;=조회_최대),1,0)</f>
         <v/>
@@ -16044,9 +15908,7 @@
       <c r="S100" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T100" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T100" s="74" t="n"/>
       <c r="U100">
         <f>IF(AND($J100&lt;&gt;"",OR(조회_주기="전체",$R100=조회_주기),$J100&gt;=조회_최소,$J100&lt;=조회_최대),1,0)</f>
         <v/>
@@ -16142,9 +16004,7 @@
       <c r="S101" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T101" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T101" s="74" t="n"/>
       <c r="U101">
         <f>IF(AND($J101&lt;&gt;"",OR(조회_주기="전체",$R101=조회_주기),$J101&gt;=조회_최소,$J101&lt;=조회_최대),1,0)</f>
         <v/>
@@ -16240,9 +16100,7 @@
       <c r="S102" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T102" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T102" s="74" t="n"/>
       <c r="U102">
         <f>IF(AND($J102&lt;&gt;"",OR(조회_주기="전체",$R102=조회_주기),$J102&gt;=조회_최소,$J102&lt;=조회_최대),1,0)</f>
         <v/>
@@ -16338,9 +16196,7 @@
       <c r="S103" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T103" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T103" s="74" t="n"/>
       <c r="U103">
         <f>IF(AND($J103&lt;&gt;"",OR(조회_주기="전체",$R103=조회_주기),$J103&gt;=조회_최소,$J103&lt;=조회_최대),1,0)</f>
         <v/>
@@ -16436,9 +16292,7 @@
       <c r="S104" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T104" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T104" s="74" t="n"/>
       <c r="U104">
         <f>IF(AND($J104&lt;&gt;"",OR(조회_주기="전체",$R104=조회_주기),$J104&gt;=조회_최소,$J104&lt;=조회_최대),1,0)</f>
         <v/>
@@ -16534,9 +16388,7 @@
       <c r="S105" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T105" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T105" s="74" t="n"/>
       <c r="U105">
         <f>IF(AND($J105&lt;&gt;"",OR(조회_주기="전체",$R105=조회_주기),$J105&gt;=조회_최소,$J105&lt;=조회_최대),1,0)</f>
         <v/>
@@ -16632,9 +16484,7 @@
       <c r="S106" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T106" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T106" s="74" t="n"/>
       <c r="U106">
         <f>IF(AND($J106&lt;&gt;"",OR(조회_주기="전체",$R106=조회_주기),$J106&gt;=조회_최소,$J106&lt;=조회_최대),1,0)</f>
         <v/>
@@ -16730,9 +16580,7 @@
       <c r="S107" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T107" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T107" s="74" t="n"/>
       <c r="U107">
         <f>IF(AND($J107&lt;&gt;"",OR(조회_주기="전체",$R107=조회_주기),$J107&gt;=조회_최소,$J107&lt;=조회_최대),1,0)</f>
         <v/>
@@ -16828,9 +16676,7 @@
       <c r="S108" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T108" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T108" s="74" t="n"/>
       <c r="U108">
         <f>IF(AND($J108&lt;&gt;"",OR(조회_주기="전체",$R108=조회_주기),$J108&gt;=조회_최소,$J108&lt;=조회_최대),1,0)</f>
         <v/>
@@ -16926,9 +16772,7 @@
       <c r="S109" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T109" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T109" s="74" t="n"/>
       <c r="U109">
         <f>IF(AND($J109&lt;&gt;"",OR(조회_주기="전체",$R109=조회_주기),$J109&gt;=조회_최소,$J109&lt;=조회_최대),1,0)</f>
         <v/>
@@ -17024,9 +16868,7 @@
       <c r="S110" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T110" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T110" s="74" t="n"/>
       <c r="U110">
         <f>IF(AND($J110&lt;&gt;"",OR(조회_주기="전체",$R110=조회_주기),$J110&gt;=조회_최소,$J110&lt;=조회_최대),1,0)</f>
         <v/>
@@ -17122,9 +16964,7 @@
       <c r="S111" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T111" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T111" s="74" t="n"/>
       <c r="U111">
         <f>IF(AND($J111&lt;&gt;"",OR(조회_주기="전체",$R111=조회_주기),$J111&gt;=조회_최소,$J111&lt;=조회_최대),1,0)</f>
         <v/>
@@ -17220,9 +17060,7 @@
       <c r="S112" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T112" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T112" s="74" t="n"/>
       <c r="U112">
         <f>IF(AND($J112&lt;&gt;"",OR(조회_주기="전체",$R112=조회_주기),$J112&gt;=조회_최소,$J112&lt;=조회_최대),1,0)</f>
         <v/>
@@ -17318,9 +17156,7 @@
       <c r="S113" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T113" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T113" s="74" t="n"/>
       <c r="U113">
         <f>IF(AND($J113&lt;&gt;"",OR(조회_주기="전체",$R113=조회_주기),$J113&gt;=조회_최소,$J113&lt;=조회_최대),1,0)</f>
         <v/>
@@ -17416,9 +17252,7 @@
       <c r="S114" s="94" t="n">
         <v>3</v>
       </c>
-      <c r="T114" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T114" s="74" t="n"/>
       <c r="U114">
         <f>IF(AND($J114&lt;&gt;"",OR(조회_주기="전체",$R114=조회_주기),$J114&gt;=조회_최소,$J114&lt;=조회_최대),1,0)</f>
         <v/>
@@ -17514,9 +17348,7 @@
       <c r="S115" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T115" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T115" s="74" t="n"/>
       <c r="U115">
         <f>IF(AND($J115&lt;&gt;"",OR(조회_주기="전체",$R115=조회_주기),$J115&gt;=조회_최소,$J115&lt;=조회_최대),1,0)</f>
         <v/>
@@ -17612,9 +17444,7 @@
       <c r="S116" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T116" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T116" s="74" t="n"/>
       <c r="U116">
         <f>IF(AND($J116&lt;&gt;"",OR(조회_주기="전체",$R116=조회_주기),$J116&gt;=조회_최소,$J116&lt;=조회_최대),1,0)</f>
         <v/>
@@ -17710,9 +17540,7 @@
       <c r="S117" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T117" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T117" s="74" t="n"/>
       <c r="U117">
         <f>IF(AND($J117&lt;&gt;"",OR(조회_주기="전체",$R117=조회_주기),$J117&gt;=조회_최소,$J117&lt;=조회_최대),1,0)</f>
         <v/>
@@ -17808,9 +17636,7 @@
       <c r="S118" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T118" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T118" s="74" t="n"/>
       <c r="U118">
         <f>IF(AND($J118&lt;&gt;"",OR(조회_주기="전체",$R118=조회_주기),$J118&gt;=조회_최소,$J118&lt;=조회_최대),1,0)</f>
         <v/>
@@ -17906,9 +17732,7 @@
       <c r="S119" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T119" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T119" s="74" t="n"/>
       <c r="U119">
         <f>IF(AND($J119&lt;&gt;"",OR(조회_주기="전체",$R119=조회_주기),$J119&gt;=조회_최소,$J119&lt;=조회_최대),1,0)</f>
         <v/>
@@ -18004,9 +17828,7 @@
       <c r="S120" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T120" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T120" s="74" t="n"/>
       <c r="U120">
         <f>IF(AND($J120&lt;&gt;"",OR(조회_주기="전체",$R120=조회_주기),$J120&gt;=조회_최소,$J120&lt;=조회_최대),1,0)</f>
         <v/>
@@ -18102,9 +17924,7 @@
       <c r="S121" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T121" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T121" s="74" t="n"/>
       <c r="U121">
         <f>IF(AND($J121&lt;&gt;"",OR(조회_주기="전체",$R121=조회_주기),$J121&gt;=조회_최소,$J121&lt;=조회_최대),1,0)</f>
         <v/>
@@ -18200,9 +18020,7 @@
       <c r="S122" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T122" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T122" s="74" t="n"/>
       <c r="U122">
         <f>IF(AND($J122&lt;&gt;"",OR(조회_주기="전체",$R122=조회_주기),$J122&gt;=조회_최소,$J122&lt;=조회_최대),1,0)</f>
         <v/>
@@ -18298,9 +18116,7 @@
       <c r="S123" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T123" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T123" s="74" t="n"/>
       <c r="U123">
         <f>IF(AND($J123&lt;&gt;"",OR(조회_주기="전체",$R123=조회_주기),$J123&gt;=조회_최소,$J123&lt;=조회_최대),1,0)</f>
         <v/>
@@ -18396,9 +18212,7 @@
       <c r="S124" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T124" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T124" s="74" t="n"/>
       <c r="U124">
         <f>IF(AND($J124&lt;&gt;"",OR(조회_주기="전체",$R124=조회_주기),$J124&gt;=조회_최소,$J124&lt;=조회_최대),1,0)</f>
         <v/>
@@ -18494,9 +18308,7 @@
       <c r="S125" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T125" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T125" s="74" t="n"/>
       <c r="U125">
         <f>IF(AND($J125&lt;&gt;"",OR(조회_주기="전체",$R125=조회_주기),$J125&gt;=조회_최소,$J125&lt;=조회_최대),1,0)</f>
         <v/>
@@ -18592,9 +18404,7 @@
       <c r="S126" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T126" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T126" s="74" t="n"/>
       <c r="U126">
         <f>IF(AND($J126&lt;&gt;"",OR(조회_주기="전체",$R126=조회_주기),$J126&gt;=조회_최소,$J126&lt;=조회_최대),1,0)</f>
         <v/>
@@ -18690,9 +18500,7 @@
       <c r="S127" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="T127" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T127" s="74" t="n"/>
       <c r="U127">
         <f>IF(AND($J127&lt;&gt;"",OR(조회_주기="전체",$R127=조회_주기),$J127&gt;=조회_최소,$J127&lt;=조회_최대),1,0)</f>
         <v/>
@@ -18788,9 +18596,7 @@
       <c r="S128" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T128" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T128" s="74" t="n"/>
       <c r="U128">
         <f>IF(AND($J128&lt;&gt;"",OR(조회_주기="전체",$R128=조회_주기),$J128&gt;=조회_최소,$J128&lt;=조회_최대),1,0)</f>
         <v/>
@@ -18886,9 +18692,7 @@
       <c r="S129" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="T129" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T129" s="74" t="n"/>
       <c r="U129">
         <f>IF(AND($J129&lt;&gt;"",OR(조회_주기="전체",$R129=조회_주기),$J129&gt;=조회_최소,$J129&lt;=조회_최대),1,0)</f>
         <v/>
@@ -18984,9 +18788,7 @@
       <c r="S130" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T130" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T130" s="74" t="n"/>
       <c r="U130">
         <f>IF(AND($J130&lt;&gt;"",OR(조회_주기="전체",$R130=조회_주기),$J130&gt;=조회_최소,$J130&lt;=조회_최대),1,0)</f>
         <v/>
@@ -19082,9 +18884,7 @@
       <c r="S131" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T131" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T131" s="74" t="n"/>
       <c r="U131">
         <f>IF(AND($J131&lt;&gt;"",OR(조회_주기="전체",$R131=조회_주기),$J131&gt;=조회_최소,$J131&lt;=조회_최대),1,0)</f>
         <v/>
@@ -19180,9 +18980,7 @@
       <c r="S132" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T132" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T132" s="74" t="n"/>
       <c r="U132">
         <f>IF(AND($J132&lt;&gt;"",OR(조회_주기="전체",$R132=조회_주기),$J132&gt;=조회_최소,$J132&lt;=조회_최대),1,0)</f>
         <v/>
@@ -19278,9 +19076,7 @@
       <c r="S133" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T133" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T133" s="74" t="n"/>
       <c r="U133">
         <f>IF(AND($J133&lt;&gt;"",OR(조회_주기="전체",$R133=조회_주기),$J133&gt;=조회_최소,$J133&lt;=조회_최대),1,0)</f>
         <v/>
@@ -19376,9 +19172,7 @@
       <c r="S134" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="T134" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T134" s="74" t="n"/>
       <c r="U134">
         <f>IF(AND($J134&lt;&gt;"",OR(조회_주기="전체",$R134=조회_주기),$J134&gt;=조회_최소,$J134&lt;=조회_최대),1,0)</f>
         <v/>
@@ -19474,9 +19268,7 @@
       <c r="S135" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T135" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T135" s="74" t="n"/>
       <c r="U135">
         <f>IF(AND($J135&lt;&gt;"",OR(조회_주기="전체",$R135=조회_주기),$J135&gt;=조회_최소,$J135&lt;=조회_최대),1,0)</f>
         <v/>
@@ -19572,9 +19364,7 @@
       <c r="S136" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T136" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T136" s="74" t="n"/>
       <c r="U136">
         <f>IF(AND($J136&lt;&gt;"",OR(조회_주기="전체",$R136=조회_주기),$J136&gt;=조회_최소,$J136&lt;=조회_최대),1,0)</f>
         <v/>
@@ -19670,9 +19460,7 @@
       <c r="S137" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T137" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T137" s="74" t="n"/>
       <c r="U137">
         <f>IF(AND($J137&lt;&gt;"",OR(조회_주기="전체",$R137=조회_주기),$J137&gt;=조회_최소,$J137&lt;=조회_최대),1,0)</f>
         <v/>
@@ -19768,9 +19556,7 @@
       <c r="S138" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T138" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T138" s="74" t="n"/>
       <c r="U138">
         <f>IF(AND($J138&lt;&gt;"",OR(조회_주기="전체",$R138=조회_주기),$J138&gt;=조회_최소,$J138&lt;=조회_최대),1,0)</f>
         <v/>
@@ -19866,9 +19652,7 @@
       <c r="S139" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T139" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T139" s="74" t="n"/>
       <c r="U139">
         <f>IF(AND($J139&lt;&gt;"",OR(조회_주기="전체",$R139=조회_주기),$J139&gt;=조회_최소,$J139&lt;=조회_최대),1,0)</f>
         <v/>
@@ -19964,9 +19748,7 @@
       <c r="S140" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T140" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T140" s="74" t="n"/>
       <c r="U140">
         <f>IF(AND($J140&lt;&gt;"",OR(조회_주기="전체",$R140=조회_주기),$J140&gt;=조회_최소,$J140&lt;=조회_최대),1,0)</f>
         <v/>
@@ -20062,9 +19844,7 @@
       <c r="S141" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T141" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T141" s="74" t="n"/>
       <c r="U141">
         <f>IF(AND($J141&lt;&gt;"",OR(조회_주기="전체",$R141=조회_주기),$J141&gt;=조회_최소,$J141&lt;=조회_최대),1,0)</f>
         <v/>
@@ -20160,9 +19940,7 @@
       <c r="S142" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T142" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T142" s="74" t="n"/>
       <c r="U142">
         <f>IF(AND($J142&lt;&gt;"",OR(조회_주기="전체",$R142=조회_주기),$J142&gt;=조회_최소,$J142&lt;=조회_최대),1,0)</f>
         <v/>
@@ -20258,9 +20036,7 @@
       <c r="S143" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="T143" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T143" s="74" t="n"/>
       <c r="U143">
         <f>IF(AND($J143&lt;&gt;"",OR(조회_주기="전체",$R143=조회_주기),$J143&gt;=조회_최소,$J143&lt;=조회_최대),1,0)</f>
         <v/>
@@ -20356,9 +20132,7 @@
       <c r="S144" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T144" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T144" s="74" t="n"/>
       <c r="U144">
         <f>IF(AND($J144&lt;&gt;"",OR(조회_주기="전체",$R144=조회_주기),$J144&gt;=조회_최소,$J144&lt;=조회_최대),1,0)</f>
         <v/>
@@ -20454,9 +20228,7 @@
       <c r="S145" s="94" t="n">
         <v>3</v>
       </c>
-      <c r="T145" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T145" s="74" t="n"/>
       <c r="U145">
         <f>IF(AND($J145&lt;&gt;"",OR(조회_주기="전체",$R145=조회_주기),$J145&gt;=조회_최소,$J145&lt;=조회_최대),1,0)</f>
         <v/>
@@ -20552,9 +20324,7 @@
       <c r="S146" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T146" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T146" s="74" t="n"/>
       <c r="U146">
         <f>IF(AND($J146&lt;&gt;"",OR(조회_주기="전체",$R146=조회_주기),$J146&gt;=조회_최소,$J146&lt;=조회_최대),1,0)</f>
         <v/>
@@ -20650,9 +20420,7 @@
       <c r="S147" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T147" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T147" s="74" t="n"/>
       <c r="U147">
         <f>IF(AND($J147&lt;&gt;"",OR(조회_주기="전체",$R147=조회_주기),$J147&gt;=조회_최소,$J147&lt;=조회_최대),1,0)</f>
         <v/>
@@ -20748,9 +20516,7 @@
       <c r="S148" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T148" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T148" s="74" t="n"/>
       <c r="U148">
         <f>IF(AND($J148&lt;&gt;"",OR(조회_주기="전체",$R148=조회_주기),$J148&gt;=조회_최소,$J148&lt;=조회_최대),1,0)</f>
         <v/>
@@ -20846,9 +20612,7 @@
       <c r="S149" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T149" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T149" s="74" t="n"/>
       <c r="U149">
         <f>IF(AND($J149&lt;&gt;"",OR(조회_주기="전체",$R149=조회_주기),$J149&gt;=조회_최소,$J149&lt;=조회_최대),1,0)</f>
         <v/>
@@ -20944,9 +20708,7 @@
       <c r="S150" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T150" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T150" s="74" t="n"/>
       <c r="U150">
         <f>IF(AND($J150&lt;&gt;"",OR(조회_주기="전체",$R150=조회_주기),$J150&gt;=조회_최소,$J150&lt;=조회_최대),1,0)</f>
         <v/>
@@ -21042,9 +20804,7 @@
       <c r="S151" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T151" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T151" s="74" t="n"/>
       <c r="U151">
         <f>IF(AND($J151&lt;&gt;"",OR(조회_주기="전체",$R151=조회_주기),$J151&gt;=조회_최소,$J151&lt;=조회_최대),1,0)</f>
         <v/>
@@ -21140,9 +20900,7 @@
       <c r="S152" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T152" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T152" s="74" t="n"/>
       <c r="U152">
         <f>IF(AND($J152&lt;&gt;"",OR(조회_주기="전체",$R152=조회_주기),$J152&gt;=조회_최소,$J152&lt;=조회_최대),1,0)</f>
         <v/>
@@ -21238,9 +20996,7 @@
       <c r="S153" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T153" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T153" s="74" t="n"/>
       <c r="U153">
         <f>IF(AND($J153&lt;&gt;"",OR(조회_주기="전체",$R153=조회_주기),$J153&gt;=조회_최소,$J153&lt;=조회_최대),1,0)</f>
         <v/>
@@ -21336,9 +21092,7 @@
       <c r="S154" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T154" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T154" s="74" t="n"/>
       <c r="U154">
         <f>IF(AND($J154&lt;&gt;"",OR(조회_주기="전체",$R154=조회_주기),$J154&gt;=조회_최소,$J154&lt;=조회_최대),1,0)</f>
         <v/>
@@ -21434,9 +21188,7 @@
       <c r="S155" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T155" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T155" s="74" t="n"/>
       <c r="U155">
         <f>IF(AND($J155&lt;&gt;"",OR(조회_주기="전체",$R155=조회_주기),$J155&gt;=조회_최소,$J155&lt;=조회_최대),1,0)</f>
         <v/>
@@ -21532,9 +21284,7 @@
       <c r="S156" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T156" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T156" s="74" t="n"/>
       <c r="U156">
         <f>IF(AND($J156&lt;&gt;"",OR(조회_주기="전체",$R156=조회_주기),$J156&gt;=조회_최소,$J156&lt;=조회_최대),1,0)</f>
         <v/>
@@ -21630,9 +21380,7 @@
       <c r="S157" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T157" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T157" s="74" t="n"/>
       <c r="U157">
         <f>IF(AND($J157&lt;&gt;"",OR(조회_주기="전체",$R157=조회_주기),$J157&gt;=조회_최소,$J157&lt;=조회_최대),1,0)</f>
         <v/>
@@ -21728,9 +21476,7 @@
       <c r="S158" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T158" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T158" s="74" t="n"/>
       <c r="U158">
         <f>IF(AND($J158&lt;&gt;"",OR(조회_주기="전체",$R158=조회_주기),$J158&gt;=조회_최소,$J158&lt;=조회_최대),1,0)</f>
         <v/>
@@ -21826,9 +21572,7 @@
       <c r="S159" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T159" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T159" s="74" t="n"/>
       <c r="U159">
         <f>IF(AND($J159&lt;&gt;"",OR(조회_주기="전체",$R159=조회_주기),$J159&gt;=조회_최소,$J159&lt;=조회_최대),1,0)</f>
         <v/>
@@ -21924,9 +21668,7 @@
       <c r="S160" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T160" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T160" s="74" t="n"/>
       <c r="U160">
         <f>IF(AND($J160&lt;&gt;"",OR(조회_주기="전체",$R160=조회_주기),$J160&gt;=조회_최소,$J160&lt;=조회_최대),1,0)</f>
         <v/>
@@ -22022,9 +21764,7 @@
       <c r="S161" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T161" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T161" s="74" t="n"/>
       <c r="U161">
         <f>IF(AND($J161&lt;&gt;"",OR(조회_주기="전체",$R161=조회_주기),$J161&gt;=조회_최소,$J161&lt;=조회_최대),1,0)</f>
         <v/>
@@ -22120,9 +21860,7 @@
       <c r="S162" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T162" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T162" s="74" t="n"/>
       <c r="U162">
         <f>IF(AND($J162&lt;&gt;"",OR(조회_주기="전체",$R162=조회_주기),$J162&gt;=조회_최소,$J162&lt;=조회_최대),1,0)</f>
         <v/>
@@ -22218,9 +21956,7 @@
       <c r="S163" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T163" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T163" s="74" t="n"/>
       <c r="U163">
         <f>IF(AND($J163&lt;&gt;"",OR(조회_주기="전체",$R163=조회_주기),$J163&gt;=조회_최소,$J163&lt;=조회_최대),1,0)</f>
         <v/>
@@ -22316,9 +22052,7 @@
       <c r="S164" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="T164" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T164" s="74" t="n"/>
       <c r="U164">
         <f>IF(AND($J164&lt;&gt;"",OR(조회_주기="전체",$R164=조회_주기),$J164&gt;=조회_최소,$J164&lt;=조회_최대),1,0)</f>
         <v/>
@@ -22414,9 +22148,7 @@
       <c r="S165" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T165" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T165" s="74" t="n"/>
       <c r="U165">
         <f>IF(AND($J165&lt;&gt;"",OR(조회_주기="전체",$R165=조회_주기),$J165&gt;=조회_최소,$J165&lt;=조회_최대),1,0)</f>
         <v/>
@@ -22512,9 +22244,7 @@
       <c r="S166" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T166" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T166" s="74" t="n"/>
       <c r="U166">
         <f>IF(AND($J166&lt;&gt;"",OR(조회_주기="전체",$R166=조회_주기),$J166&gt;=조회_최소,$J166&lt;=조회_최대),1,0)</f>
         <v/>
@@ -22610,9 +22340,7 @@
       <c r="S167" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="T167" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T167" s="74" t="n"/>
       <c r="U167">
         <f>IF(AND($J167&lt;&gt;"",OR(조회_주기="전체",$R167=조회_주기),$J167&gt;=조회_최소,$J167&lt;=조회_최대),1,0)</f>
         <v/>
@@ -22708,9 +22436,7 @@
       <c r="S168" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T168" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T168" s="74" t="n"/>
       <c r="U168">
         <f>IF(AND($J168&lt;&gt;"",OR(조회_주기="전체",$R168=조회_주기),$J168&gt;=조회_최소,$J168&lt;=조회_최대),1,0)</f>
         <v/>
@@ -22806,9 +22532,7 @@
       <c r="S169" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T169" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T169" s="74" t="n"/>
       <c r="U169">
         <f>IF(AND($J169&lt;&gt;"",OR(조회_주기="전체",$R169=조회_주기),$J169&gt;=조회_최소,$J169&lt;=조회_최대),1,0)</f>
         <v/>
@@ -22904,9 +22628,7 @@
       <c r="S170" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T170" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T170" s="74" t="n"/>
       <c r="U170">
         <f>IF(AND($J170&lt;&gt;"",OR(조회_주기="전체",$R170=조회_주기),$J170&gt;=조회_최소,$J170&lt;=조회_최대),1,0)</f>
         <v/>
@@ -23002,9 +22724,7 @@
       <c r="S171" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T171" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T171" s="74" t="n"/>
       <c r="U171">
         <f>IF(AND($J171&lt;&gt;"",OR(조회_주기="전체",$R171=조회_주기),$J171&gt;=조회_최소,$J171&lt;=조회_최대),1,0)</f>
         <v/>
@@ -23100,9 +22820,7 @@
       <c r="S172" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T172" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T172" s="74" t="n"/>
       <c r="U172">
         <f>IF(AND($J172&lt;&gt;"",OR(조회_주기="전체",$R172=조회_주기),$J172&gt;=조회_최소,$J172&lt;=조회_최대),1,0)</f>
         <v/>
@@ -23198,9 +22916,7 @@
       <c r="S173" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T173" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T173" s="74" t="n"/>
       <c r="U173">
         <f>IF(AND($J173&lt;&gt;"",OR(조회_주기="전체",$R173=조회_주기),$J173&gt;=조회_최소,$J173&lt;=조회_최대),1,0)</f>
         <v/>
@@ -23296,9 +23012,7 @@
       <c r="S174" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T174" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T174" s="74" t="n"/>
       <c r="U174">
         <f>IF(AND($J174&lt;&gt;"",OR(조회_주기="전체",$R174=조회_주기),$J174&gt;=조회_최소,$J174&lt;=조회_최대),1,0)</f>
         <v/>
@@ -23394,9 +23108,7 @@
       <c r="S175" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T175" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T175" s="74" t="n"/>
       <c r="U175">
         <f>IF(AND($J175&lt;&gt;"",OR(조회_주기="전체",$R175=조회_주기),$J175&gt;=조회_최소,$J175&lt;=조회_최대),1,0)</f>
         <v/>
@@ -23492,9 +23204,7 @@
       <c r="S176" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="T176" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T176" s="74" t="n"/>
       <c r="U176">
         <f>IF(AND($J176&lt;&gt;"",OR(조회_주기="전체",$R176=조회_주기),$J176&gt;=조회_최소,$J176&lt;=조회_최대),1,0)</f>
         <v/>
@@ -23590,9 +23300,7 @@
       <c r="S177" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T177" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T177" s="74" t="n"/>
       <c r="U177">
         <f>IF(AND($J177&lt;&gt;"",OR(조회_주기="전체",$R177=조회_주기),$J177&gt;=조회_최소,$J177&lt;=조회_최대),1,0)</f>
         <v/>
@@ -23688,9 +23396,7 @@
       <c r="S178" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T178" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T178" s="74" t="n"/>
       <c r="U178">
         <f>IF(AND($J178&lt;&gt;"",OR(조회_주기="전체",$R178=조회_주기),$J178&gt;=조회_최소,$J178&lt;=조회_최대),1,0)</f>
         <v/>
@@ -23786,9 +23492,7 @@
       <c r="S179" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T179" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T179" s="74" t="n"/>
       <c r="U179">
         <f>IF(AND($J179&lt;&gt;"",OR(조회_주기="전체",$R179=조회_주기),$J179&gt;=조회_최소,$J179&lt;=조회_최대),1,0)</f>
         <v/>
@@ -23884,9 +23588,7 @@
       <c r="S180" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T180" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T180" s="74" t="n"/>
       <c r="U180">
         <f>IF(AND($J180&lt;&gt;"",OR(조회_주기="전체",$R180=조회_주기),$J180&gt;=조회_최소,$J180&lt;=조회_최대),1,0)</f>
         <v/>
@@ -23982,9 +23684,7 @@
       <c r="S181" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T181" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T181" s="74" t="n"/>
       <c r="U181">
         <f>IF(AND($J181&lt;&gt;"",OR(조회_주기="전체",$R181=조회_주기),$J181&gt;=조회_최소,$J181&lt;=조회_최대),1,0)</f>
         <v/>
@@ -24080,9 +23780,7 @@
       <c r="S182" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T182" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T182" s="74" t="n"/>
       <c r="U182">
         <f>IF(AND($J182&lt;&gt;"",OR(조회_주기="전체",$R182=조회_주기),$J182&gt;=조회_최소,$J182&lt;=조회_최대),1,0)</f>
         <v/>
@@ -24178,9 +23876,7 @@
       <c r="S183" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T183" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T183" s="74" t="n"/>
       <c r="U183">
         <f>IF(AND($J183&lt;&gt;"",OR(조회_주기="전체",$R183=조회_주기),$J183&gt;=조회_최소,$J183&lt;=조회_최대),1,0)</f>
         <v/>
@@ -24276,9 +23972,7 @@
       <c r="S184" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T184" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T184" s="74" t="n"/>
       <c r="U184">
         <f>IF(AND($J184&lt;&gt;"",OR(조회_주기="전체",$R184=조회_주기),$J184&gt;=조회_최소,$J184&lt;=조회_최대),1,0)</f>
         <v/>
@@ -24374,9 +24068,7 @@
       <c r="S185" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T185" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T185" s="74" t="n"/>
       <c r="U185">
         <f>IF(AND($J185&lt;&gt;"",OR(조회_주기="전체",$R185=조회_주기),$J185&gt;=조회_최소,$J185&lt;=조회_최대),1,0)</f>
         <v/>
@@ -24472,9 +24164,7 @@
       <c r="S186" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T186" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T186" s="74" t="n"/>
       <c r="U186">
         <f>IF(AND($J186&lt;&gt;"",OR(조회_주기="전체",$R186=조회_주기),$J186&gt;=조회_최소,$J186&lt;=조회_최대),1,0)</f>
         <v/>
@@ -24570,9 +24260,7 @@
       <c r="S187" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="T187" s="74" t="n">
-        <v>1</v>
-      </c>
+      <c r="T187" s="74" t="n"/>
       <c r="U187">
         <f>IF(AND($J187&lt;&gt;"",OR(조회_주기="전체",$R187=조회_주기),$J187&gt;=조회_최소,$J187&lt;=조회_최대),1,0)</f>
         <v/>
@@ -24672,9 +24360,7 @@
       <c r="S188" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T188" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T188" s="98" t="n"/>
       <c r="U188">
         <f>IF(AND($J188&lt;&gt;"",OR(조회_주기="전체",$R188=조회_주기),$J188&gt;=조회_최소,$J188&lt;=조회_최대),1,0)</f>
         <v/>
@@ -24774,9 +24460,7 @@
       <c r="S189" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T189" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T189" s="98" t="n"/>
       <c r="U189">
         <f>IF(AND($J189&lt;&gt;"",OR(조회_주기="전체",$R189=조회_주기),$J189&gt;=조회_최소,$J189&lt;=조회_최대),1,0)</f>
         <v/>
@@ -24876,9 +24560,7 @@
       <c r="S190" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T190" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T190" s="98" t="n"/>
       <c r="U190">
         <f>IF(AND($J190&lt;&gt;"",OR(조회_주기="전체",$R190=조회_주기),$J190&gt;=조회_최소,$J190&lt;=조회_최대),1,0)</f>
         <v/>
@@ -24978,9 +24660,7 @@
       <c r="S191" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T191" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T191" s="98" t="n"/>
       <c r="U191">
         <f>IF(AND($J191&lt;&gt;"",OR(조회_주기="전체",$R191=조회_주기),$J191&gt;=조회_최소,$J191&lt;=조회_최대),1,0)</f>
         <v/>
@@ -25080,9 +24760,7 @@
       <c r="S192" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T192" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T192" s="98" t="n"/>
       <c r="U192">
         <f>IF(AND($J192&lt;&gt;"",OR(조회_주기="전체",$R192=조회_주기),$J192&gt;=조회_최소,$J192&lt;=조회_최대),1,0)</f>
         <v/>
@@ -25182,9 +24860,7 @@
       <c r="S193" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T193" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T193" s="98" t="n"/>
       <c r="U193">
         <f>IF(AND($J193&lt;&gt;"",OR(조회_주기="전체",$R193=조회_주기),$J193&gt;=조회_최소,$J193&lt;=조회_최대),1,0)</f>
         <v/>
@@ -25284,9 +24960,7 @@
       <c r="S194" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T194" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T194" s="98" t="n"/>
       <c r="U194">
         <f>IF(AND($J194&lt;&gt;"",OR(조회_주기="전체",$R194=조회_주기),$J194&gt;=조회_최소,$J194&lt;=조회_최대),1,0)</f>
         <v/>
@@ -25386,9 +25060,7 @@
       <c r="S195" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T195" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T195" s="98" t="n"/>
       <c r="U195">
         <f>IF(AND($J195&lt;&gt;"",OR(조회_주기="전체",$R195=조회_주기),$J195&gt;=조회_최소,$J195&lt;=조회_최대),1,0)</f>
         <v/>
@@ -25488,9 +25160,7 @@
       <c r="S196" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T196" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T196" s="98" t="n"/>
       <c r="U196">
         <f>IF(AND($J196&lt;&gt;"",OR(조회_주기="전체",$R196=조회_주기),$J196&gt;=조회_최소,$J196&lt;=조회_최대),1,0)</f>
         <v/>
@@ -25590,9 +25260,7 @@
       <c r="S197" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T197" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T197" s="98" t="n"/>
       <c r="U197">
         <f>IF(AND($J197&lt;&gt;"",OR(조회_주기="전체",$R197=조회_주기),$J197&gt;=조회_최소,$J197&lt;=조회_최대),1,0)</f>
         <v/>
@@ -25692,9 +25360,7 @@
       <c r="S198" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T198" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T198" s="98" t="n"/>
       <c r="U198">
         <f>IF(AND($J198&lt;&gt;"",OR(조회_주기="전체",$R198=조회_주기),$J198&gt;=조회_최소,$J198&lt;=조회_최대),1,0)</f>
         <v/>
@@ -25794,9 +25460,7 @@
       <c r="S199" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T199" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T199" s="98" t="n"/>
       <c r="U199">
         <f>IF(AND($J199&lt;&gt;"",OR(조회_주기="전체",$R199=조회_주기),$J199&gt;=조회_최소,$J199&lt;=조회_최대),1,0)</f>
         <v/>
@@ -25896,9 +25560,7 @@
       <c r="S200" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T200" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T200" s="98" t="n"/>
       <c r="U200">
         <f>IF(AND($J200&lt;&gt;"",OR(조회_주기="전체",$R200=조회_주기),$J200&gt;=조회_최소,$J200&lt;=조회_최대),1,0)</f>
         <v/>
@@ -25998,9 +25660,7 @@
       <c r="S201" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T201" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T201" s="98" t="n"/>
       <c r="U201">
         <f>IF(AND($J201&lt;&gt;"",OR(조회_주기="전체",$R201=조회_주기),$J201&gt;=조회_최소,$J201&lt;=조회_최대),1,0)</f>
         <v/>
@@ -26100,9 +25760,7 @@
       <c r="S202" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T202" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T202" s="98" t="n"/>
       <c r="U202">
         <f>IF(AND($J202&lt;&gt;"",OR(조회_주기="전체",$R202=조회_주기),$J202&gt;=조회_최소,$J202&lt;=조회_최대),1,0)</f>
         <v/>
@@ -26202,9 +25860,7 @@
       <c r="S203" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T203" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T203" s="98" t="n"/>
       <c r="U203">
         <f>IF(AND($J203&lt;&gt;"",OR(조회_주기="전체",$R203=조회_주기),$J203&gt;=조회_최소,$J203&lt;=조회_최대),1,0)</f>
         <v/>
@@ -26304,9 +25960,7 @@
       <c r="S204" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T204" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T204" s="98" t="n"/>
       <c r="U204">
         <f>IF(AND($J204&lt;&gt;"",OR(조회_주기="전체",$R204=조회_주기),$J204&gt;=조회_최소,$J204&lt;=조회_최대),1,0)</f>
         <v/>
@@ -26406,9 +26060,7 @@
       <c r="S205" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T205" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T205" s="98" t="n"/>
       <c r="U205">
         <f>IF(AND($J205&lt;&gt;"",OR(조회_주기="전체",$R205=조회_주기),$J205&gt;=조회_최소,$J205&lt;=조회_최대),1,0)</f>
         <v/>
@@ -26508,9 +26160,7 @@
       <c r="S206" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T206" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T206" s="98" t="n"/>
       <c r="U206">
         <f>IF(AND($J206&lt;&gt;"",OR(조회_주기="전체",$R206=조회_주기),$J206&gt;=조회_최소,$J206&lt;=조회_최대),1,0)</f>
         <v/>
@@ -26610,9 +26260,7 @@
       <c r="S207" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T207" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T207" s="98" t="n"/>
       <c r="U207">
         <f>IF(AND($J207&lt;&gt;"",OR(조회_주기="전체",$R207=조회_주기),$J207&gt;=조회_최소,$J207&lt;=조회_최대),1,0)</f>
         <v/>
@@ -26712,9 +26360,7 @@
       <c r="S208" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T208" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T208" s="98" t="n"/>
       <c r="U208">
         <f>IF(AND($J208&lt;&gt;"",OR(조회_주기="전체",$R208=조회_주기),$J208&gt;=조회_최소,$J208&lt;=조회_최대),1,0)</f>
         <v/>
@@ -26814,9 +26460,7 @@
       <c r="S209" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T209" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T209" s="98" t="n"/>
       <c r="U209">
         <f>IF(AND($J209&lt;&gt;"",OR(조회_주기="전체",$R209=조회_주기),$J209&gt;=조회_최소,$J209&lt;=조회_최대),1,0)</f>
         <v/>
@@ -26916,9 +26560,7 @@
       <c r="S210" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T210" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T210" s="98" t="n"/>
       <c r="U210">
         <f>IF(AND($J210&lt;&gt;"",OR(조회_주기="전체",$R210=조회_주기),$J210&gt;=조회_최소,$J210&lt;=조회_최대),1,0)</f>
         <v/>
@@ -27018,9 +26660,7 @@
       <c r="S211" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T211" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T211" s="98" t="n"/>
       <c r="U211">
         <f>IF(AND($J211&lt;&gt;"",OR(조회_주기="전체",$R211=조회_주기),$J211&gt;=조회_최소,$J211&lt;=조회_최대),1,0)</f>
         <v/>
@@ -27120,9 +26760,7 @@
       <c r="S212" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T212" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T212" s="98" t="n"/>
       <c r="U212">
         <f>IF(AND($J212&lt;&gt;"",OR(조회_주기="전체",$R212=조회_주기),$J212&gt;=조회_최소,$J212&lt;=조회_최대),1,0)</f>
         <v/>
@@ -27222,9 +26860,7 @@
       <c r="S213" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T213" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T213" s="98" t="n"/>
       <c r="U213">
         <f>IF(AND($J213&lt;&gt;"",OR(조회_주기="전체",$R213=조회_주기),$J213&gt;=조회_최소,$J213&lt;=조회_최대),1,0)</f>
         <v/>
@@ -27324,9 +26960,7 @@
       <c r="S214" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T214" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T214" s="98" t="n"/>
       <c r="U214">
         <f>IF(AND($J214&lt;&gt;"",OR(조회_주기="전체",$R214=조회_주기),$J214&gt;=조회_최소,$J214&lt;=조회_최대),1,0)</f>
         <v/>
@@ -27426,9 +27060,7 @@
       <c r="S215" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T215" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T215" s="98" t="n"/>
       <c r="U215">
         <f>IF(AND($J215&lt;&gt;"",OR(조회_주기="전체",$R215=조회_주기),$J215&gt;=조회_최소,$J215&lt;=조회_최대),1,0)</f>
         <v/>
@@ -27528,9 +27160,7 @@
       <c r="S216" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="T216" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T216" s="98" t="n"/>
       <c r="U216">
         <f>IF(AND($J216&lt;&gt;"",OR(조회_주기="전체",$R216=조회_주기),$J216&gt;=조회_최소,$J216&lt;=조회_최대),1,0)</f>
         <v/>
@@ -27630,9 +27260,7 @@
       <c r="S217" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="T217" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T217" s="98" t="n"/>
       <c r="U217">
         <f>IF(AND($J217&lt;&gt;"",OR(조회_주기="전체",$R217=조회_주기),$J217&gt;=조회_최소,$J217&lt;=조회_최대),1,0)</f>
         <v/>
@@ -27732,9 +27360,7 @@
       <c r="S218" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T218" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T218" s="98" t="n"/>
       <c r="U218">
         <f>IF(AND($J218&lt;&gt;"",OR(조회_주기="전체",$R218=조회_주기),$J218&gt;=조회_최소,$J218&lt;=조회_최대),1,0)</f>
         <v/>
@@ -27834,9 +27460,7 @@
       <c r="S219" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T219" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T219" s="98" t="n"/>
       <c r="U219">
         <f>IF(AND($J219&lt;&gt;"",OR(조회_주기="전체",$R219=조회_주기),$J219&gt;=조회_최소,$J219&lt;=조회_최대),1,0)</f>
         <v/>
@@ -27936,9 +27560,7 @@
       <c r="S220" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T220" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T220" s="98" t="n"/>
       <c r="U220">
         <f>IF(AND($J220&lt;&gt;"",OR(조회_주기="전체",$R220=조회_주기),$J220&gt;=조회_최소,$J220&lt;=조회_최대),1,0)</f>
         <v/>
@@ -28038,9 +27660,7 @@
       <c r="S221" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T221" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T221" s="98" t="n"/>
       <c r="U221">
         <f>IF(AND($J221&lt;&gt;"",OR(조회_주기="전체",$R221=조회_주기),$J221&gt;=조회_최소,$J221&lt;=조회_최대),1,0)</f>
         <v/>
@@ -28140,9 +27760,7 @@
       <c r="S222" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T222" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T222" s="98" t="n"/>
       <c r="U222">
         <f>IF(AND($J222&lt;&gt;"",OR(조회_주기="전체",$R222=조회_주기),$J222&gt;=조회_최소,$J222&lt;=조회_최대),1,0)</f>
         <v/>
@@ -28242,9 +27860,7 @@
       <c r="S223" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T223" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T223" s="98" t="n"/>
       <c r="U223">
         <f>IF(AND($J223&lt;&gt;"",OR(조회_주기="전체",$R223=조회_주기),$J223&gt;=조회_최소,$J223&lt;=조회_최대),1,0)</f>
         <v/>
@@ -28344,9 +27960,7 @@
       <c r="S224" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T224" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T224" s="98" t="n"/>
       <c r="U224">
         <f>IF(AND($J224&lt;&gt;"",OR(조회_주기="전체",$R224=조회_주기),$J224&gt;=조회_최소,$J224&lt;=조회_최대),1,0)</f>
         <v/>
@@ -28446,9 +28060,7 @@
       <c r="S225" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T225" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T225" s="98" t="n"/>
       <c r="U225">
         <f>IF(AND($J225&lt;&gt;"",OR(조회_주기="전체",$R225=조회_주기),$J225&gt;=조회_최소,$J225&lt;=조회_최대),1,0)</f>
         <v/>
@@ -28548,9 +28160,7 @@
       <c r="S226" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T226" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T226" s="98" t="n"/>
       <c r="U226">
         <f>IF(AND($J226&lt;&gt;"",OR(조회_주기="전체",$R226=조회_주기),$J226&gt;=조회_최소,$J226&lt;=조회_최대),1,0)</f>
         <v/>
@@ -28650,9 +28260,7 @@
       <c r="S227" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T227" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T227" s="98" t="n"/>
       <c r="U227">
         <f>IF(AND($J227&lt;&gt;"",OR(조회_주기="전체",$R227=조회_주기),$J227&gt;=조회_최소,$J227&lt;=조회_최대),1,0)</f>
         <v/>
@@ -28752,9 +28360,7 @@
       <c r="S228" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T228" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T228" s="98" t="n"/>
       <c r="U228">
         <f>IF(AND($J228&lt;&gt;"",OR(조회_주기="전체",$R228=조회_주기),$J228&gt;=조회_최소,$J228&lt;=조회_최대),1,0)</f>
         <v/>
@@ -28854,9 +28460,7 @@
       <c r="S229" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T229" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T229" s="98" t="n"/>
       <c r="U229">
         <f>IF(AND($J229&lt;&gt;"",OR(조회_주기="전체",$R229=조회_주기),$J229&gt;=조회_최소,$J229&lt;=조회_최대),1,0)</f>
         <v/>
@@ -28956,9 +28560,7 @@
       <c r="S230" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T230" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T230" s="98" t="n"/>
       <c r="U230">
         <f>IF(AND($J230&lt;&gt;"",OR(조회_주기="전체",$R230=조회_주기),$J230&gt;=조회_최소,$J230&lt;=조회_최대),1,0)</f>
         <v/>
@@ -29058,9 +28660,7 @@
       <c r="S231" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T231" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T231" s="98" t="n"/>
       <c r="U231">
         <f>IF(AND($J231&lt;&gt;"",OR(조회_주기="전체",$R231=조회_주기),$J231&gt;=조회_최소,$J231&lt;=조회_최대),1,0)</f>
         <v/>
@@ -29160,9 +28760,7 @@
       <c r="S232" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T232" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T232" s="98" t="n"/>
       <c r="U232">
         <f>IF(AND($J232&lt;&gt;"",OR(조회_주기="전체",$R232=조회_주기),$J232&gt;=조회_최소,$J232&lt;=조회_최대),1,0)</f>
         <v/>
@@ -29262,9 +28860,7 @@
       <c r="S233" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T233" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T233" s="98" t="n"/>
       <c r="U233">
         <f>IF(AND($J233&lt;&gt;"",OR(조회_주기="전체",$R233=조회_주기),$J233&gt;=조회_최소,$J233&lt;=조회_최대),1,0)</f>
         <v/>
@@ -29364,9 +28960,7 @@
       <c r="S234" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T234" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T234" s="98" t="n"/>
       <c r="U234">
         <f>IF(AND($J234&lt;&gt;"",OR(조회_주기="전체",$R234=조회_주기),$J234&gt;=조회_최소,$J234&lt;=조회_최대),1,0)</f>
         <v/>
@@ -29466,9 +29060,7 @@
       <c r="S235" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T235" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T235" s="98" t="n"/>
       <c r="U235">
         <f>IF(AND($J235&lt;&gt;"",OR(조회_주기="전체",$R235=조회_주기),$J235&gt;=조회_최소,$J235&lt;=조회_최대),1,0)</f>
         <v/>
@@ -29568,9 +29160,7 @@
       <c r="S236" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T236" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T236" s="98" t="n"/>
       <c r="U236">
         <f>IF(AND($J236&lt;&gt;"",OR(조회_주기="전체",$R236=조회_주기),$J236&gt;=조회_최소,$J236&lt;=조회_최대),1,0)</f>
         <v/>
@@ -29670,9 +29260,7 @@
       <c r="S237" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T237" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T237" s="98" t="n"/>
       <c r="U237">
         <f>IF(AND($J237&lt;&gt;"",OR(조회_주기="전체",$R237=조회_주기),$J237&gt;=조회_최소,$J237&lt;=조회_최대),1,0)</f>
         <v/>
@@ -29772,9 +29360,7 @@
       <c r="S238" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T238" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T238" s="98" t="n"/>
       <c r="U238">
         <f>IF(AND($J238&lt;&gt;"",OR(조회_주기="전체",$R238=조회_주기),$J238&gt;=조회_최소,$J238&lt;=조회_최대),1,0)</f>
         <v/>
@@ -29874,9 +29460,7 @@
       <c r="S239" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T239" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T239" s="98" t="n"/>
       <c r="U239">
         <f>IF(AND($J239&lt;&gt;"",OR(조회_주기="전체",$R239=조회_주기),$J239&gt;=조회_최소,$J239&lt;=조회_최대),1,0)</f>
         <v/>
@@ -29976,9 +29560,7 @@
       <c r="S240" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T240" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T240" s="98" t="n"/>
       <c r="U240">
         <f>IF(AND($J240&lt;&gt;"",OR(조회_주기="전체",$R240=조회_주기),$J240&gt;=조회_최소,$J240&lt;=조회_최대),1,0)</f>
         <v/>
@@ -30078,9 +29660,7 @@
       <c r="S241" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T241" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T241" s="98" t="n"/>
       <c r="U241">
         <f>IF(AND($J241&lt;&gt;"",OR(조회_주기="전체",$R241=조회_주기),$J241&gt;=조회_최소,$J241&lt;=조회_최대),1,0)</f>
         <v/>
@@ -30180,9 +29760,7 @@
       <c r="S242" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T242" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T242" s="98" t="n"/>
       <c r="U242">
         <f>IF(AND($J242&lt;&gt;"",OR(조회_주기="전체",$R242=조회_주기),$J242&gt;=조회_최소,$J242&lt;=조회_최대),1,0)</f>
         <v/>
@@ -30282,9 +29860,7 @@
       <c r="S243" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T243" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T243" s="98" t="n"/>
       <c r="U243">
         <f>IF(AND($J243&lt;&gt;"",OR(조회_주기="전체",$R243=조회_주기),$J243&gt;=조회_최소,$J243&lt;=조회_최대),1,0)</f>
         <v/>
@@ -30384,9 +29960,7 @@
       <c r="S244" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T244" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T244" s="98" t="n"/>
       <c r="U244">
         <f>IF(AND($J244&lt;&gt;"",OR(조회_주기="전체",$R244=조회_주기),$J244&gt;=조회_최소,$J244&lt;=조회_최대),1,0)</f>
         <v/>
@@ -30486,9 +30060,7 @@
       <c r="S245" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T245" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T245" s="98" t="n"/>
       <c r="U245">
         <f>IF(AND($J245&lt;&gt;"",OR(조회_주기="전체",$R245=조회_주기),$J245&gt;=조회_최소,$J245&lt;=조회_최대),1,0)</f>
         <v/>
@@ -30588,9 +30160,7 @@
       <c r="S246" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T246" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T246" s="98" t="n"/>
       <c r="U246">
         <f>IF(AND($J246&lt;&gt;"",OR(조회_주기="전체",$R246=조회_주기),$J246&gt;=조회_최소,$J246&lt;=조회_최대),1,0)</f>
         <v/>
@@ -30690,9 +30260,7 @@
       <c r="S247" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T247" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T247" s="98" t="n"/>
       <c r="U247">
         <f>IF(AND($J247&lt;&gt;"",OR(조회_주기="전체",$R247=조회_주기),$J247&gt;=조회_최소,$J247&lt;=조회_최대),1,0)</f>
         <v/>
@@ -30792,9 +30360,7 @@
       <c r="S248" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T248" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T248" s="98" t="n"/>
       <c r="U248">
         <f>IF(AND($J248&lt;&gt;"",OR(조회_주기="전체",$R248=조회_주기),$J248&gt;=조회_최소,$J248&lt;=조회_최대),1,0)</f>
         <v/>
@@ -30894,9 +30460,7 @@
       <c r="S249" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="T249" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T249" s="98" t="n"/>
       <c r="U249">
         <f>IF(AND($J249&lt;&gt;"",OR(조회_주기="전체",$R249=조회_주기),$J249&gt;=조회_최소,$J249&lt;=조회_최대),1,0)</f>
         <v/>
@@ -30996,9 +30560,7 @@
       <c r="S250" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T250" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T250" s="98" t="n"/>
       <c r="U250">
         <f>IF(AND($J250&lt;&gt;"",OR(조회_주기="전체",$R250=조회_주기),$J250&gt;=조회_최소,$J250&lt;=조회_최대),1,0)</f>
         <v/>
@@ -31098,9 +30660,7 @@
       <c r="S251" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T251" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T251" s="98" t="n"/>
       <c r="U251">
         <f>IF(AND($J251&lt;&gt;"",OR(조회_주기="전체",$R251=조회_주기),$J251&gt;=조회_최소,$J251&lt;=조회_최대),1,0)</f>
         <v/>
@@ -31200,9 +30760,7 @@
       <c r="S252" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T252" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T252" s="98" t="n"/>
       <c r="U252">
         <f>IF(AND($J252&lt;&gt;"",OR(조회_주기="전체",$R252=조회_주기),$J252&gt;=조회_최소,$J252&lt;=조회_최대),1,0)</f>
         <v/>
@@ -31302,9 +30860,7 @@
       <c r="S253" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T253" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T253" s="98" t="n"/>
       <c r="U253">
         <f>IF(AND($J253&lt;&gt;"",OR(조회_주기="전체",$R253=조회_주기),$J253&gt;=조회_최소,$J253&lt;=조회_최대),1,0)</f>
         <v/>
@@ -31404,9 +30960,7 @@
       <c r="S254" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T254" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T254" s="98" t="n"/>
       <c r="U254">
         <f>IF(AND($J254&lt;&gt;"",OR(조회_주기="전체",$R254=조회_주기),$J254&gt;=조회_최소,$J254&lt;=조회_최대),1,0)</f>
         <v/>
@@ -31506,9 +31060,7 @@
       <c r="S255" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T255" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T255" s="98" t="n"/>
       <c r="U255">
         <f>IF(AND($J255&lt;&gt;"",OR(조회_주기="전체",$R255=조회_주기),$J255&gt;=조회_최소,$J255&lt;=조회_최대),1,0)</f>
         <v/>
@@ -31608,9 +31160,7 @@
       <c r="S256" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T256" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T256" s="98" t="n"/>
       <c r="U256">
         <f>IF(AND($J256&lt;&gt;"",OR(조회_주기="전체",$R256=조회_주기),$J256&gt;=조회_최소,$J256&lt;=조회_최대),1,0)</f>
         <v/>
@@ -31710,9 +31260,7 @@
       <c r="S257" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T257" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T257" s="98" t="n"/>
       <c r="U257">
         <f>IF(AND($J257&lt;&gt;"",OR(조회_주기="전체",$R257=조회_주기),$J257&gt;=조회_최소,$J257&lt;=조회_최대),1,0)</f>
         <v/>
@@ -31812,9 +31360,7 @@
       <c r="S258" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T258" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T258" s="98" t="n"/>
       <c r="U258">
         <f>IF(AND($J258&lt;&gt;"",OR(조회_주기="전체",$R258=조회_주기),$J258&gt;=조회_최소,$J258&lt;=조회_최대),1,0)</f>
         <v/>
@@ -31914,9 +31460,7 @@
       <c r="S259" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T259" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T259" s="98" t="n"/>
       <c r="U259">
         <f>IF(AND($J259&lt;&gt;"",OR(조회_주기="전체",$R259=조회_주기),$J259&gt;=조회_최소,$J259&lt;=조회_최대),1,0)</f>
         <v/>
@@ -32016,9 +31560,7 @@
       <c r="S260" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T260" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T260" s="98" t="n"/>
       <c r="U260">
         <f>IF(AND($J260&lt;&gt;"",OR(조회_주기="전체",$R260=조회_주기),$J260&gt;=조회_최소,$J260&lt;=조회_최대),1,0)</f>
         <v/>
@@ -32118,9 +31660,7 @@
       <c r="S261" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T261" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T261" s="98" t="n"/>
       <c r="U261">
         <f>IF(AND($J261&lt;&gt;"",OR(조회_주기="전체",$R261=조회_주기),$J261&gt;=조회_최소,$J261&lt;=조회_최대),1,0)</f>
         <v/>
@@ -32220,9 +31760,7 @@
       <c r="S262" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T262" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T262" s="98" t="n"/>
       <c r="U262">
         <f>IF(AND($J262&lt;&gt;"",OR(조회_주기="전체",$R262=조회_주기),$J262&gt;=조회_최소,$J262&lt;=조회_최대),1,0)</f>
         <v/>
@@ -32322,9 +31860,7 @@
       <c r="S263" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T263" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T263" s="98" t="n"/>
       <c r="U263">
         <f>IF(AND($J263&lt;&gt;"",OR(조회_주기="전체",$R263=조회_주기),$J263&gt;=조회_최소,$J263&lt;=조회_최대),1,0)</f>
         <v/>
@@ -32424,9 +31960,7 @@
       <c r="S264" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T264" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T264" s="98" t="n"/>
       <c r="U264">
         <f>IF(AND($J264&lt;&gt;"",OR(조회_주기="전체",$R264=조회_주기),$J264&gt;=조회_최소,$J264&lt;=조회_최대),1,0)</f>
         <v/>
@@ -32526,9 +32060,7 @@
       <c r="S265" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T265" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T265" s="98" t="n"/>
       <c r="U265">
         <f>IF(AND($J265&lt;&gt;"",OR(조회_주기="전체",$R265=조회_주기),$J265&gt;=조회_최소,$J265&lt;=조회_최대),1,0)</f>
         <v/>
@@ -32628,9 +32160,7 @@
       <c r="S266" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T266" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T266" s="98" t="n"/>
       <c r="U266">
         <f>IF(AND($J266&lt;&gt;"",OR(조회_주기="전체",$R266=조회_주기),$J266&gt;=조회_최소,$J266&lt;=조회_최대),1,0)</f>
         <v/>
@@ -32730,9 +32260,7 @@
       <c r="S267" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T267" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T267" s="98" t="n"/>
       <c r="U267">
         <f>IF(AND($J267&lt;&gt;"",OR(조회_주기="전체",$R267=조회_주기),$J267&gt;=조회_최소,$J267&lt;=조회_최대),1,0)</f>
         <v/>
@@ -32832,9 +32360,7 @@
       <c r="S268" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T268" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T268" s="98" t="n"/>
       <c r="U268">
         <f>IF(AND($J268&lt;&gt;"",OR(조회_주기="전체",$R268=조회_주기),$J268&gt;=조회_최소,$J268&lt;=조회_최대),1,0)</f>
         <v/>
@@ -32934,9 +32460,7 @@
       <c r="S269" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T269" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T269" s="98" t="n"/>
       <c r="U269">
         <f>IF(AND($J269&lt;&gt;"",OR(조회_주기="전체",$R269=조회_주기),$J269&gt;=조회_최소,$J269&lt;=조회_최대),1,0)</f>
         <v/>
@@ -33036,9 +32560,7 @@
       <c r="S270" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T270" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T270" s="98" t="n"/>
       <c r="U270">
         <f>IF(AND($J270&lt;&gt;"",OR(조회_주기="전체",$R270=조회_주기),$J270&gt;=조회_최소,$J270&lt;=조회_최대),1,0)</f>
         <v/>
@@ -33138,9 +32660,7 @@
       <c r="S271" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T271" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T271" s="98" t="n"/>
       <c r="U271">
         <f>IF(AND($J271&lt;&gt;"",OR(조회_주기="전체",$R271=조회_주기),$J271&gt;=조회_최소,$J271&lt;=조회_최대),1,0)</f>
         <v/>
@@ -33240,9 +32760,7 @@
       <c r="S272" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T272" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T272" s="98" t="n"/>
       <c r="U272">
         <f>IF(AND($J272&lt;&gt;"",OR(조회_주기="전체",$R272=조회_주기),$J272&gt;=조회_최소,$J272&lt;=조회_최대),1,0)</f>
         <v/>
@@ -33342,9 +32860,7 @@
       <c r="S273" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T273" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T273" s="98" t="n"/>
       <c r="U273">
         <f>IF(AND($J273&lt;&gt;"",OR(조회_주기="전체",$R273=조회_주기),$J273&gt;=조회_최소,$J273&lt;=조회_최대),1,0)</f>
         <v/>
@@ -33444,9 +32960,7 @@
       <c r="S274" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T274" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T274" s="98" t="n"/>
       <c r="U274">
         <f>IF(AND($J274&lt;&gt;"",OR(조회_주기="전체",$R274=조회_주기),$J274&gt;=조회_최소,$J274&lt;=조회_최대),1,0)</f>
         <v/>
@@ -33546,9 +33060,7 @@
       <c r="S275" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T275" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T275" s="98" t="n"/>
       <c r="U275">
         <f>IF(AND($J275&lt;&gt;"",OR(조회_주기="전체",$R275=조회_주기),$J275&gt;=조회_최소,$J275&lt;=조회_최대),1,0)</f>
         <v/>
@@ -33648,9 +33160,7 @@
       <c r="S276" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T276" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T276" s="98" t="n"/>
       <c r="U276">
         <f>IF(AND($J276&lt;&gt;"",OR(조회_주기="전체",$R276=조회_주기),$J276&gt;=조회_최소,$J276&lt;=조회_최대),1,0)</f>
         <v/>
@@ -33750,9 +33260,7 @@
       <c r="S277" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T277" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T277" s="98" t="n"/>
       <c r="U277">
         <f>IF(AND($J277&lt;&gt;"",OR(조회_주기="전체",$R277=조회_주기),$J277&gt;=조회_최소,$J277&lt;=조회_최대),1,0)</f>
         <v/>
@@ -33852,9 +33360,7 @@
       <c r="S278" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T278" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T278" s="98" t="n"/>
       <c r="U278">
         <f>IF(AND($J278&lt;&gt;"",OR(조회_주기="전체",$R278=조회_주기),$J278&gt;=조회_최소,$J278&lt;=조회_최대),1,0)</f>
         <v/>
@@ -33954,9 +33460,7 @@
       <c r="S279" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T279" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T279" s="98" t="n"/>
       <c r="U279">
         <f>IF(AND($J279&lt;&gt;"",OR(조회_주기="전체",$R279=조회_주기),$J279&gt;=조회_최소,$J279&lt;=조회_최대),1,0)</f>
         <v/>
@@ -34056,9 +33560,7 @@
       <c r="S280" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T280" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T280" s="98" t="n"/>
       <c r="U280">
         <f>IF(AND($J280&lt;&gt;"",OR(조회_주기="전체",$R280=조회_주기),$J280&gt;=조회_최소,$J280&lt;=조회_최대),1,0)</f>
         <v/>
@@ -34158,9 +33660,7 @@
       <c r="S281" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T281" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T281" s="98" t="n"/>
       <c r="U281">
         <f>IF(AND($J281&lt;&gt;"",OR(조회_주기="전체",$R281=조회_주기),$J281&gt;=조회_최소,$J281&lt;=조회_최대),1,0)</f>
         <v/>
@@ -34260,9 +33760,7 @@
       <c r="S282" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T282" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T282" s="98" t="n"/>
       <c r="U282">
         <f>IF(AND($J282&lt;&gt;"",OR(조회_주기="전체",$R282=조회_주기),$J282&gt;=조회_최소,$J282&lt;=조회_최대),1,0)</f>
         <v/>
@@ -34362,9 +33860,7 @@
       <c r="S283" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T283" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T283" s="98" t="n"/>
       <c r="U283">
         <f>IF(AND($J283&lt;&gt;"",OR(조회_주기="전체",$R283=조회_주기),$J283&gt;=조회_최소,$J283&lt;=조회_최대),1,0)</f>
         <v/>
@@ -34464,9 +33960,7 @@
       <c r="S284" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T284" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T284" s="98" t="n"/>
       <c r="U284">
         <f>IF(AND($J284&lt;&gt;"",OR(조회_주기="전체",$R284=조회_주기),$J284&gt;=조회_최소,$J284&lt;=조회_최대),1,0)</f>
         <v/>
@@ -34566,9 +34060,7 @@
       <c r="S285" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T285" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T285" s="98" t="n"/>
       <c r="U285">
         <f>IF(AND($J285&lt;&gt;"",OR(조회_주기="전체",$R285=조회_주기),$J285&gt;=조회_최소,$J285&lt;=조회_최대),1,0)</f>
         <v/>
@@ -34668,9 +34160,7 @@
       <c r="S286" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T286" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T286" s="98" t="n"/>
       <c r="U286">
         <f>IF(AND($J286&lt;&gt;"",OR(조회_주기="전체",$R286=조회_주기),$J286&gt;=조회_최소,$J286&lt;=조회_최대),1,0)</f>
         <v/>
@@ -34770,9 +34260,7 @@
       <c r="S287" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T287" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T287" s="98" t="n"/>
       <c r="U287">
         <f>IF(AND($J287&lt;&gt;"",OR(조회_주기="전체",$R287=조회_주기),$J287&gt;=조회_최소,$J287&lt;=조회_최대),1,0)</f>
         <v/>
@@ -34872,9 +34360,7 @@
       <c r="S288" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T288" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T288" s="98" t="n"/>
       <c r="U288">
         <f>IF(AND($J288&lt;&gt;"",OR(조회_주기="전체",$R288=조회_주기),$J288&gt;=조회_최소,$J288&lt;=조회_최대),1,0)</f>
         <v/>
@@ -34974,9 +34460,7 @@
       <c r="S289" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T289" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T289" s="98" t="n"/>
       <c r="U289">
         <f>IF(AND($J289&lt;&gt;"",OR(조회_주기="전체",$R289=조회_주기),$J289&gt;=조회_최소,$J289&lt;=조회_최대),1,0)</f>
         <v/>
@@ -35076,9 +34560,7 @@
       <c r="S290" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T290" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T290" s="98" t="n"/>
       <c r="U290">
         <f>IF(AND($J290&lt;&gt;"",OR(조회_주기="전체",$R290=조회_주기),$J290&gt;=조회_최소,$J290&lt;=조회_최대),1,0)</f>
         <v/>
@@ -35178,9 +34660,7 @@
       <c r="S291" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T291" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T291" s="98" t="n"/>
       <c r="U291">
         <f>IF(AND($J291&lt;&gt;"",OR(조회_주기="전체",$R291=조회_주기),$J291&gt;=조회_최소,$J291&lt;=조회_최대),1,0)</f>
         <v/>
@@ -35280,9 +34760,7 @@
       <c r="S292" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T292" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T292" s="98" t="n"/>
       <c r="U292">
         <f>IF(AND($J292&lt;&gt;"",OR(조회_주기="전체",$R292=조회_주기),$J292&gt;=조회_최소,$J292&lt;=조회_최대),1,0)</f>
         <v/>
@@ -35382,9 +34860,7 @@
       <c r="S293" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T293" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T293" s="98" t="n"/>
       <c r="U293">
         <f>IF(AND($J293&lt;&gt;"",OR(조회_주기="전체",$R293=조회_주기),$J293&gt;=조회_최소,$J293&lt;=조회_최대),1,0)</f>
         <v/>
@@ -35484,9 +34960,7 @@
       <c r="S294" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T294" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T294" s="98" t="n"/>
       <c r="U294">
         <f>IF(AND($J294&lt;&gt;"",OR(조회_주기="전체",$R294=조회_주기),$J294&gt;=조회_최소,$J294&lt;=조회_최대),1,0)</f>
         <v/>
@@ -35586,9 +35060,7 @@
       <c r="S295" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T295" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T295" s="98" t="n"/>
       <c r="U295">
         <f>IF(AND($J295&lt;&gt;"",OR(조회_주기="전체",$R295=조회_주기),$J295&gt;=조회_최소,$J295&lt;=조회_최대),1,0)</f>
         <v/>
@@ -35688,9 +35160,7 @@
       <c r="S296" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T296" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T296" s="98" t="n"/>
       <c r="U296">
         <f>IF(AND($J296&lt;&gt;"",OR(조회_주기="전체",$R296=조회_주기),$J296&gt;=조회_최소,$J296&lt;=조회_최대),1,0)</f>
         <v/>
@@ -35790,9 +35260,7 @@
       <c r="S297" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T297" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T297" s="98" t="n"/>
       <c r="U297">
         <f>IF(AND($J297&lt;&gt;"",OR(조회_주기="전체",$R297=조회_주기),$J297&gt;=조회_최소,$J297&lt;=조회_최대),1,0)</f>
         <v/>
@@ -35892,9 +35360,7 @@
       <c r="S298" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T298" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T298" s="98" t="n"/>
       <c r="U298">
         <f>IF(AND($J298&lt;&gt;"",OR(조회_주기="전체",$R298=조회_주기),$J298&gt;=조회_최소,$J298&lt;=조회_최대),1,0)</f>
         <v/>
@@ -35994,9 +35460,7 @@
       <c r="S299" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T299" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T299" s="98" t="n"/>
       <c r="U299">
         <f>IF(AND($J299&lt;&gt;"",OR(조회_주기="전체",$R299=조회_주기),$J299&gt;=조회_최소,$J299&lt;=조회_최대),1,0)</f>
         <v/>
@@ -36096,9 +35560,7 @@
       <c r="S300" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T300" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T300" s="98" t="n"/>
       <c r="U300">
         <f>IF(AND($J300&lt;&gt;"",OR(조회_주기="전체",$R300=조회_주기),$J300&gt;=조회_최소,$J300&lt;=조회_최대),1,0)</f>
         <v/>
@@ -36198,9 +35660,7 @@
       <c r="S301" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T301" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T301" s="98" t="n"/>
       <c r="U301">
         <f>IF(AND($J301&lt;&gt;"",OR(조회_주기="전체",$R301=조회_주기),$J301&gt;=조회_최소,$J301&lt;=조회_최대),1,0)</f>
         <v/>
@@ -36300,9 +35760,7 @@
       <c r="S302" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T302" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T302" s="98" t="n"/>
       <c r="U302">
         <f>IF(AND($J302&lt;&gt;"",OR(조회_주기="전체",$R302=조회_주기),$J302&gt;=조회_최소,$J302&lt;=조회_최대),1,0)</f>
         <v/>
@@ -36402,9 +35860,7 @@
       <c r="S303" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T303" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T303" s="98" t="n"/>
       <c r="U303">
         <f>IF(AND($J303&lt;&gt;"",OR(조회_주기="전체",$R303=조회_주기),$J303&gt;=조회_최소,$J303&lt;=조회_최대),1,0)</f>
         <v/>
@@ -36504,9 +35960,7 @@
       <c r="S304" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T304" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T304" s="98" t="n"/>
       <c r="U304">
         <f>IF(AND($J304&lt;&gt;"",OR(조회_주기="전체",$R304=조회_주기),$J304&gt;=조회_최소,$J304&lt;=조회_최대),1,0)</f>
         <v/>
@@ -36606,9 +36060,7 @@
       <c r="S305" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T305" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T305" s="98" t="n"/>
       <c r="U305">
         <f>IF(AND($J305&lt;&gt;"",OR(조회_주기="전체",$R305=조회_주기),$J305&gt;=조회_최소,$J305&lt;=조회_최대),1,0)</f>
         <v/>
@@ -36708,9 +36160,7 @@
       <c r="S306" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T306" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T306" s="98" t="n"/>
       <c r="U306">
         <f>IF(AND($J306&lt;&gt;"",OR(조회_주기="전체",$R306=조회_주기),$J306&gt;=조회_최소,$J306&lt;=조회_최대),1,0)</f>
         <v/>
@@ -36810,9 +36260,7 @@
       <c r="S307" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T307" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T307" s="98" t="n"/>
       <c r="U307">
         <f>IF(AND($J307&lt;&gt;"",OR(조회_주기="전체",$R307=조회_주기),$J307&gt;=조회_최소,$J307&lt;=조회_최대),1,0)</f>
         <v/>
@@ -36912,9 +36360,7 @@
       <c r="S308" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T308" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T308" s="98" t="n"/>
       <c r="U308">
         <f>IF(AND($J308&lt;&gt;"",OR(조회_주기="전체",$R308=조회_주기),$J308&gt;=조회_최소,$J308&lt;=조회_최대),1,0)</f>
         <v/>
@@ -37014,9 +36460,7 @@
       <c r="S309" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T309" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T309" s="98" t="n"/>
       <c r="U309">
         <f>IF(AND($J309&lt;&gt;"",OR(조회_주기="전체",$R309=조회_주기),$J309&gt;=조회_최소,$J309&lt;=조회_최대),1,0)</f>
         <v/>
@@ -37116,9 +36560,7 @@
       <c r="S310" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T310" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T310" s="98" t="n"/>
       <c r="U310">
         <f>IF(AND($J310&lt;&gt;"",OR(조회_주기="전체",$R310=조회_주기),$J310&gt;=조회_최소,$J310&lt;=조회_최대),1,0)</f>
         <v/>
@@ -37218,9 +36660,7 @@
       <c r="S311" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T311" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T311" s="98" t="n"/>
       <c r="U311">
         <f>IF(AND($J311&lt;&gt;"",OR(조회_주기="전체",$R311=조회_주기),$J311&gt;=조회_최소,$J311&lt;=조회_최대),1,0)</f>
         <v/>
@@ -37320,9 +36760,7 @@
       <c r="S312" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T312" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T312" s="98" t="n"/>
       <c r="U312">
         <f>IF(AND($J312&lt;&gt;"",OR(조회_주기="전체",$R312=조회_주기),$J312&gt;=조회_최소,$J312&lt;=조회_최대),1,0)</f>
         <v/>
@@ -37422,9 +36860,7 @@
       <c r="S313" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T313" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T313" s="98" t="n"/>
       <c r="U313">
         <f>IF(AND($J313&lt;&gt;"",OR(조회_주기="전체",$R313=조회_주기),$J313&gt;=조회_최소,$J313&lt;=조회_최대),1,0)</f>
         <v/>
@@ -37524,9 +36960,7 @@
       <c r="S314" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T314" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T314" s="98" t="n"/>
       <c r="U314">
         <f>IF(AND($J314&lt;&gt;"",OR(조회_주기="전체",$R314=조회_주기),$J314&gt;=조회_최소,$J314&lt;=조회_최대),1,0)</f>
         <v/>
@@ -37626,9 +37060,7 @@
       <c r="S315" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T315" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T315" s="98" t="n"/>
       <c r="U315">
         <f>IF(AND($J315&lt;&gt;"",OR(조회_주기="전체",$R315=조회_주기),$J315&gt;=조회_최소,$J315&lt;=조회_최대),1,0)</f>
         <v/>
@@ -37728,9 +37160,7 @@
       <c r="S316" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T316" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T316" s="98" t="n"/>
       <c r="U316">
         <f>IF(AND($J316&lt;&gt;"",OR(조회_주기="전체",$R316=조회_주기),$J316&gt;=조회_최소,$J316&lt;=조회_최대),1,0)</f>
         <v/>
@@ -37830,9 +37260,7 @@
       <c r="S317" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T317" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T317" s="98" t="n"/>
       <c r="U317">
         <f>IF(AND($J317&lt;&gt;"",OR(조회_주기="전체",$R317=조회_주기),$J317&gt;=조회_최소,$J317&lt;=조회_최대),1,0)</f>
         <v/>
@@ -37932,9 +37360,7 @@
       <c r="S318" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T318" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T318" s="98" t="n"/>
       <c r="U318">
         <f>IF(AND($J318&lt;&gt;"",OR(조회_주기="전체",$R318=조회_주기),$J318&gt;=조회_최소,$J318&lt;=조회_최대),1,0)</f>
         <v/>
@@ -38034,9 +37460,7 @@
       <c r="S319" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T319" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T319" s="98" t="n"/>
       <c r="U319">
         <f>IF(AND($J319&lt;&gt;"",OR(조회_주기="전체",$R319=조회_주기),$J319&gt;=조회_최소,$J319&lt;=조회_최대),1,0)</f>
         <v/>
@@ -38136,9 +37560,7 @@
       <c r="S320" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T320" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T320" s="98" t="n"/>
       <c r="U320">
         <f>IF(AND($J320&lt;&gt;"",OR(조회_주기="전체",$R320=조회_주기),$J320&gt;=조회_최소,$J320&lt;=조회_최대),1,0)</f>
         <v/>
@@ -38238,9 +37660,7 @@
       <c r="S321" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T321" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T321" s="98" t="n"/>
       <c r="U321">
         <f>IF(AND($J321&lt;&gt;"",OR(조회_주기="전체",$R321=조회_주기),$J321&gt;=조회_최소,$J321&lt;=조회_최대),1,0)</f>
         <v/>
@@ -38340,9 +37760,7 @@
       <c r="S322" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T322" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T322" s="98" t="n"/>
       <c r="U322">
         <f>IF(AND($J322&lt;&gt;"",OR(조회_주기="전체",$R322=조회_주기),$J322&gt;=조회_최소,$J322&lt;=조회_최대),1,0)</f>
         <v/>
@@ -38442,9 +37860,7 @@
       <c r="S323" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T323" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T323" s="98" t="n"/>
       <c r="U323">
         <f>IF(AND($J323&lt;&gt;"",OR(조회_주기="전체",$R323=조회_주기),$J323&gt;=조회_최소,$J323&lt;=조회_최대),1,0)</f>
         <v/>
@@ -38544,9 +37960,7 @@
       <c r="S324" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T324" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T324" s="98" t="n"/>
       <c r="U324">
         <f>IF(AND($J324&lt;&gt;"",OR(조회_주기="전체",$R324=조회_주기),$J324&gt;=조회_최소,$J324&lt;=조회_최대),1,0)</f>
         <v/>
@@ -38646,9 +38060,7 @@
       <c r="S325" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T325" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T325" s="98" t="n"/>
       <c r="U325">
         <f>IF(AND($J325&lt;&gt;"",OR(조회_주기="전체",$R325=조회_주기),$J325&gt;=조회_최소,$J325&lt;=조회_최대),1,0)</f>
         <v/>
@@ -38748,9 +38160,7 @@
       <c r="S326" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T326" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T326" s="98" t="n"/>
       <c r="U326">
         <f>IF(AND($J326&lt;&gt;"",OR(조회_주기="전체",$R326=조회_주기),$J326&gt;=조회_최소,$J326&lt;=조회_최대),1,0)</f>
         <v/>
@@ -38850,9 +38260,7 @@
       <c r="S327" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T327" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T327" s="98" t="n"/>
       <c r="U327">
         <f>IF(AND($J327&lt;&gt;"",OR(조회_주기="전체",$R327=조회_주기),$J327&gt;=조회_최소,$J327&lt;=조회_최대),1,0)</f>
         <v/>
@@ -38952,9 +38360,7 @@
       <c r="S328" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T328" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T328" s="98" t="n"/>
       <c r="U328">
         <f>IF(AND($J328&lt;&gt;"",OR(조회_주기="전체",$R328=조회_주기),$J328&gt;=조회_최소,$J328&lt;=조회_최대),1,0)</f>
         <v/>
@@ -39054,9 +38460,7 @@
       <c r="S329" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T329" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T329" s="98" t="n"/>
       <c r="U329">
         <f>IF(AND($J329&lt;&gt;"",OR(조회_주기="전체",$R329=조회_주기),$J329&gt;=조회_최소,$J329&lt;=조회_최대),1,0)</f>
         <v/>
@@ -39156,9 +38560,7 @@
       <c r="S330" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T330" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T330" s="98" t="n"/>
       <c r="U330">
         <f>IF(AND($J330&lt;&gt;"",OR(조회_주기="전체",$R330=조회_주기),$J330&gt;=조회_최소,$J330&lt;=조회_최대),1,0)</f>
         <v/>
@@ -39258,9 +38660,7 @@
       <c r="S331" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T331" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T331" s="98" t="n"/>
       <c r="U331">
         <f>IF(AND($J331&lt;&gt;"",OR(조회_주기="전체",$R331=조회_주기),$J331&gt;=조회_최소,$J331&lt;=조회_최대),1,0)</f>
         <v/>
@@ -39360,9 +38760,7 @@
       <c r="S332" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T332" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T332" s="98" t="n"/>
       <c r="U332">
         <f>IF(AND($J332&lt;&gt;"",OR(조회_주기="전체",$R332=조회_주기),$J332&gt;=조회_최소,$J332&lt;=조회_최대),1,0)</f>
         <v/>
@@ -39462,9 +38860,7 @@
       <c r="S333" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T333" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T333" s="98" t="n"/>
       <c r="U333">
         <f>IF(AND($J333&lt;&gt;"",OR(조회_주기="전체",$R333=조회_주기),$J333&gt;=조회_최소,$J333&lt;=조회_최대),1,0)</f>
         <v/>
@@ -39564,9 +38960,7 @@
       <c r="S334" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T334" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T334" s="98" t="n"/>
       <c r="U334">
         <f>IF(AND($J334&lt;&gt;"",OR(조회_주기="전체",$R334=조회_주기),$J334&gt;=조회_최소,$J334&lt;=조회_최대),1,0)</f>
         <v/>
@@ -39666,9 +39060,7 @@
       <c r="S335" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T335" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T335" s="98" t="n"/>
       <c r="U335">
         <f>IF(AND($J335&lt;&gt;"",OR(조회_주기="전체",$R335=조회_주기),$J335&gt;=조회_최소,$J335&lt;=조회_최대),1,0)</f>
         <v/>
@@ -39768,9 +39160,7 @@
       <c r="S336" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T336" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T336" s="98" t="n"/>
       <c r="U336">
         <f>IF(AND($J336&lt;&gt;"",OR(조회_주기="전체",$R336=조회_주기),$J336&gt;=조회_최소,$J336&lt;=조회_최대),1,0)</f>
         <v/>
@@ -39870,9 +39260,7 @@
       <c r="S337" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T337" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T337" s="98" t="n"/>
       <c r="U337">
         <f>IF(AND($J337&lt;&gt;"",OR(조회_주기="전체",$R337=조회_주기),$J337&gt;=조회_최소,$J337&lt;=조회_최대),1,0)</f>
         <v/>
@@ -39972,9 +39360,7 @@
       <c r="S338" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T338" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T338" s="98" t="n"/>
       <c r="U338">
         <f>IF(AND($J338&lt;&gt;"",OR(조회_주기="전체",$R338=조회_주기),$J338&gt;=조회_최소,$J338&lt;=조회_최대),1,0)</f>
         <v/>
@@ -40074,9 +39460,7 @@
       <c r="S339" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T339" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T339" s="98" t="n"/>
       <c r="U339">
         <f>IF(AND($J339&lt;&gt;"",OR(조회_주기="전체",$R339=조회_주기),$J339&gt;=조회_최소,$J339&lt;=조회_최대),1,0)</f>
         <v/>
@@ -40176,9 +39560,7 @@
       <c r="S340" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T340" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T340" s="98" t="n"/>
       <c r="U340">
         <f>IF(AND($J340&lt;&gt;"",OR(조회_주기="전체",$R340=조회_주기),$J340&gt;=조회_최소,$J340&lt;=조회_최대),1,0)</f>
         <v/>
@@ -40278,9 +39660,7 @@
       <c r="S341" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="T341" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T341" s="98" t="n"/>
       <c r="U341">
         <f>IF(AND($J341&lt;&gt;"",OR(조회_주기="전체",$R341=조회_주기),$J341&gt;=조회_최소,$J341&lt;=조회_최대),1,0)</f>
         <v/>
@@ -40380,9 +39760,7 @@
       <c r="S342" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T342" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T342" s="98" t="n"/>
       <c r="U342">
         <f>IF(AND($J342&lt;&gt;"",OR(조회_주기="전체",$R342=조회_주기),$J342&gt;=조회_최소,$J342&lt;=조회_최대),1,0)</f>
         <v/>
@@ -40482,9 +39860,7 @@
       <c r="S343" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T343" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T343" s="98" t="n"/>
       <c r="U343">
         <f>IF(AND($J343&lt;&gt;"",OR(조회_주기="전체",$R343=조회_주기),$J343&gt;=조회_최소,$J343&lt;=조회_최대),1,0)</f>
         <v/>
@@ -40584,9 +39960,7 @@
       <c r="S344" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T344" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T344" s="98" t="n"/>
       <c r="U344">
         <f>IF(AND($J344&lt;&gt;"",OR(조회_주기="전체",$R344=조회_주기),$J344&gt;=조회_최소,$J344&lt;=조회_최대),1,0)</f>
         <v/>
@@ -40686,9 +40060,7 @@
       <c r="S345" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T345" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T345" s="98" t="n"/>
       <c r="U345">
         <f>IF(AND($J345&lt;&gt;"",OR(조회_주기="전체",$R345=조회_주기),$J345&gt;=조회_최소,$J345&lt;=조회_최대),1,0)</f>
         <v/>
@@ -40788,9 +40160,7 @@
       <c r="S346" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T346" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T346" s="98" t="n"/>
       <c r="U346">
         <f>IF(AND($J346&lt;&gt;"",OR(조회_주기="전체",$R346=조회_주기),$J346&gt;=조회_최소,$J346&lt;=조회_최대),1,0)</f>
         <v/>
@@ -40890,9 +40260,7 @@
       <c r="S347" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T347" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T347" s="98" t="n"/>
       <c r="U347">
         <f>IF(AND($J347&lt;&gt;"",OR(조회_주기="전체",$R347=조회_주기),$J347&gt;=조회_최소,$J347&lt;=조회_최대),1,0)</f>
         <v/>
@@ -40992,9 +40360,7 @@
       <c r="S348" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T348" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T348" s="98" t="n"/>
       <c r="U348">
         <f>IF(AND($J348&lt;&gt;"",OR(조회_주기="전체",$R348=조회_주기),$J348&gt;=조회_최소,$J348&lt;=조회_최대),1,0)</f>
         <v/>
@@ -41094,9 +40460,7 @@
       <c r="S349" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T349" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T349" s="98" t="n"/>
       <c r="U349">
         <f>IF(AND($J349&lt;&gt;"",OR(조회_주기="전체",$R349=조회_주기),$J349&gt;=조회_최소,$J349&lt;=조회_최대),1,0)</f>
         <v/>
@@ -41298,9 +40662,7 @@
       <c r="S351" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T351" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T351" s="98" t="n"/>
       <c r="U351">
         <f>IF(AND($J351&lt;&gt;"",OR(조회_주기="전체",$R351=조회_주기),$J351&gt;=조회_최소,$J351&lt;=조회_최대),1,0)</f>
         <v/>
@@ -41400,9 +40762,7 @@
       <c r="S352" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="T352" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T352" s="98" t="n"/>
       <c r="U352">
         <f>IF(AND($J352&lt;&gt;"",OR(조회_주기="전체",$R352=조회_주기),$J352&gt;=조회_최소,$J352&lt;=조회_최대),1,0)</f>
         <v/>
@@ -41502,9 +40862,7 @@
       <c r="S353" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T353" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T353" s="98" t="n"/>
       <c r="U353">
         <f>IF(AND($J353&lt;&gt;"",OR(조회_주기="전체",$R353=조회_주기),$J353&gt;=조회_최소,$J353&lt;=조회_최대),1,0)</f>
         <v/>
@@ -41604,9 +40962,7 @@
       <c r="S354" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T354" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T354" s="98" t="n"/>
       <c r="U354">
         <f>IF(AND($J354&lt;&gt;"",OR(조회_주기="전체",$R354=조회_주기),$J354&gt;=조회_최소,$J354&lt;=조회_최대),1,0)</f>
         <v/>
@@ -41706,9 +41062,7 @@
       <c r="S355" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T355" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T355" s="98" t="n"/>
       <c r="U355">
         <f>IF(AND($J355&lt;&gt;"",OR(조회_주기="전체",$R355=조회_주기),$J355&gt;=조회_최소,$J355&lt;=조회_최대),1,0)</f>
         <v/>
@@ -41808,9 +41162,7 @@
       <c r="S356" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T356" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T356" s="98" t="n"/>
       <c r="U356">
         <f>IF(AND($J356&lt;&gt;"",OR(조회_주기="전체",$R356=조회_주기),$J356&gt;=조회_최소,$J356&lt;=조회_최대),1,0)</f>
         <v/>
@@ -41910,9 +41262,7 @@
       <c r="S357" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T357" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T357" s="98" t="n"/>
       <c r="U357">
         <f>IF(AND($J357&lt;&gt;"",OR(조회_주기="전체",$R357=조회_주기),$J357&gt;=조회_최소,$J357&lt;=조회_최대),1,0)</f>
         <v/>
@@ -42012,9 +41362,7 @@
       <c r="S358" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T358" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T358" s="98" t="n"/>
       <c r="U358">
         <f>IF(AND($J358&lt;&gt;"",OR(조회_주기="전체",$R358=조회_주기),$J358&gt;=조회_최소,$J358&lt;=조회_최대),1,0)</f>
         <v/>
@@ -42114,9 +41462,7 @@
       <c r="S359" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T359" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T359" s="98" t="n"/>
       <c r="U359">
         <f>IF(AND($J359&lt;&gt;"",OR(조회_주기="전체",$R359=조회_주기),$J359&gt;=조회_최소,$J359&lt;=조회_최대),1,0)</f>
         <v/>
@@ -42216,9 +41562,7 @@
       <c r="S360" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T360" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T360" s="98" t="n"/>
       <c r="U360">
         <f>IF(AND($J360&lt;&gt;"",OR(조회_주기="전체",$R360=조회_주기),$J360&gt;=조회_최소,$J360&lt;=조회_최대),1,0)</f>
         <v/>
@@ -42318,9 +41662,7 @@
       <c r="S361" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T361" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T361" s="98" t="n"/>
       <c r="U361">
         <f>IF(AND($J361&lt;&gt;"",OR(조회_주기="전체",$R361=조회_주기),$J361&gt;=조회_최소,$J361&lt;=조회_최대),1,0)</f>
         <v/>
@@ -42420,9 +41762,7 @@
       <c r="S362" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T362" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T362" s="98" t="n"/>
       <c r="U362">
         <f>IF(AND($J362&lt;&gt;"",OR(조회_주기="전체",$R362=조회_주기),$J362&gt;=조회_최소,$J362&lt;=조회_최대),1,0)</f>
         <v/>
@@ -42522,9 +41862,7 @@
       <c r="S363" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T363" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T363" s="98" t="n"/>
       <c r="U363">
         <f>IF(AND($J363&lt;&gt;"",OR(조회_주기="전체",$R363=조회_주기),$J363&gt;=조회_최소,$J363&lt;=조회_최대),1,0)</f>
         <v/>
@@ -42624,9 +41962,7 @@
       <c r="S364" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T364" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T364" s="98" t="n"/>
       <c r="U364">
         <f>IF(AND($J364&lt;&gt;"",OR(조회_주기="전체",$R364=조회_주기),$J364&gt;=조회_최소,$J364&lt;=조회_최대),1,0)</f>
         <v/>
@@ -42726,9 +42062,7 @@
       <c r="S365" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T365" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T365" s="98" t="n"/>
       <c r="U365">
         <f>IF(AND($J365&lt;&gt;"",OR(조회_주기="전체",$R365=조회_주기),$J365&gt;=조회_최소,$J365&lt;=조회_최대),1,0)</f>
         <v/>
@@ -42828,9 +42162,7 @@
       <c r="S366" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T366" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T366" s="98" t="n"/>
       <c r="U366">
         <f>IF(AND($J366&lt;&gt;"",OR(조회_주기="전체",$R366=조회_주기),$J366&gt;=조회_최소,$J366&lt;=조회_최대),1,0)</f>
         <v/>
@@ -43032,9 +42364,7 @@
       <c r="S368" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T368" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T368" s="98" t="n"/>
       <c r="U368">
         <f>IF(AND($J368&lt;&gt;"",OR(조회_주기="전체",$R368=조회_주기),$J368&gt;=조회_최소,$J368&lt;=조회_최대),1,0)</f>
         <v/>
@@ -43134,9 +42464,7 @@
       <c r="S369" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T369" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T369" s="98" t="n"/>
       <c r="U369">
         <f>IF(AND($J369&lt;&gt;"",OR(조회_주기="전체",$R369=조회_주기),$J369&gt;=조회_최소,$J369&lt;=조회_최대),1,0)</f>
         <v/>
@@ -43236,9 +42564,7 @@
       <c r="S370" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T370" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T370" s="98" t="n"/>
       <c r="U370">
         <f>IF(AND($J370&lt;&gt;"",OR(조회_주기="전체",$R370=조회_주기),$J370&gt;=조회_최소,$J370&lt;=조회_최대),1,0)</f>
         <v/>
@@ -43338,9 +42664,7 @@
       <c r="S371" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T371" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T371" s="98" t="n"/>
       <c r="U371">
         <f>IF(AND($J371&lt;&gt;"",OR(조회_주기="전체",$R371=조회_주기),$J371&gt;=조회_최소,$J371&lt;=조회_최대),1,0)</f>
         <v/>
@@ -43440,9 +42764,7 @@
       <c r="S372" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T372" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T372" s="98" t="n"/>
       <c r="U372">
         <f>IF(AND($J372&lt;&gt;"",OR(조회_주기="전체",$R372=조회_주기),$J372&gt;=조회_최소,$J372&lt;=조회_최대),1,0)</f>
         <v/>
@@ -43542,9 +42864,7 @@
       <c r="S373" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T373" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T373" s="98" t="n"/>
       <c r="U373">
         <f>IF(AND($J373&lt;&gt;"",OR(조회_주기="전체",$R373=조회_주기),$J373&gt;=조회_최소,$J373&lt;=조회_최대),1,0)</f>
         <v/>
@@ -43644,9 +42964,7 @@
       <c r="S374" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T374" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T374" s="98" t="n"/>
       <c r="U374">
         <f>IF(AND($J374&lt;&gt;"",OR(조회_주기="전체",$R374=조회_주기),$J374&gt;=조회_최소,$J374&lt;=조회_최대),1,0)</f>
         <v/>
@@ -43746,9 +43064,7 @@
       <c r="S375" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T375" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T375" s="98" t="n"/>
       <c r="U375">
         <f>IF(AND($J375&lt;&gt;"",OR(조회_주기="전체",$R375=조회_주기),$J375&gt;=조회_최소,$J375&lt;=조회_최대),1,0)</f>
         <v/>
@@ -43848,9 +43164,7 @@
       <c r="S376" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T376" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T376" s="98" t="n"/>
       <c r="U376">
         <f>IF(AND($J376&lt;&gt;"",OR(조회_주기="전체",$R376=조회_주기),$J376&gt;=조회_최소,$J376&lt;=조회_최대),1,0)</f>
         <v/>
@@ -43950,9 +43264,7 @@
       <c r="S377" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T377" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T377" s="98" t="n"/>
       <c r="U377">
         <f>IF(AND($J377&lt;&gt;"",OR(조회_주기="전체",$R377=조회_주기),$J377&gt;=조회_최소,$J377&lt;=조회_최대),1,0)</f>
         <v/>
@@ -44052,9 +43364,7 @@
       <c r="S378" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T378" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T378" s="98" t="n"/>
       <c r="U378">
         <f>IF(AND($J378&lt;&gt;"",OR(조회_주기="전체",$R378=조회_주기),$J378&gt;=조회_최소,$J378&lt;=조회_최대),1,0)</f>
         <v/>
@@ -44154,9 +43464,7 @@
       <c r="S379" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T379" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T379" s="98" t="n"/>
       <c r="U379">
         <f>IF(AND($J379&lt;&gt;"",OR(조회_주기="전체",$R379=조회_주기),$J379&gt;=조회_최소,$J379&lt;=조회_최대),1,0)</f>
         <v/>
@@ -44256,9 +43564,7 @@
       <c r="S380" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T380" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T380" s="98" t="n"/>
       <c r="U380">
         <f>IF(AND($J380&lt;&gt;"",OR(조회_주기="전체",$R380=조회_주기),$J380&gt;=조회_최소,$J380&lt;=조회_최대),1,0)</f>
         <v/>
@@ -44358,9 +43664,7 @@
       <c r="S381" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T381" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T381" s="98" t="n"/>
       <c r="U381">
         <f>IF(AND($J381&lt;&gt;"",OR(조회_주기="전체",$R381=조회_주기),$J381&gt;=조회_최소,$J381&lt;=조회_최대),1,0)</f>
         <v/>
@@ -44460,9 +43764,7 @@
       <c r="S382" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T382" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T382" s="98" t="n"/>
       <c r="U382">
         <f>IF(AND($J382&lt;&gt;"",OR(조회_주기="전체",$R382=조회_주기),$J382&gt;=조회_최소,$J382&lt;=조회_최대),1,0)</f>
         <v/>
@@ -44562,9 +43864,7 @@
       <c r="S383" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T383" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T383" s="98" t="n"/>
       <c r="U383">
         <f>IF(AND($J383&lt;&gt;"",OR(조회_주기="전체",$R383=조회_주기),$J383&gt;=조회_최소,$J383&lt;=조회_최대),1,0)</f>
         <v/>
@@ -44664,9 +43964,7 @@
       <c r="S384" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T384" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T384" s="98" t="n"/>
       <c r="U384">
         <f>IF(AND($J384&lt;&gt;"",OR(조회_주기="전체",$R384=조회_주기),$J384&gt;=조회_최소,$J384&lt;=조회_최대),1,0)</f>
         <v/>
@@ -44766,9 +44064,7 @@
       <c r="S385" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T385" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T385" s="98" t="n"/>
       <c r="U385">
         <f>IF(AND($J385&lt;&gt;"",OR(조회_주기="전체",$R385=조회_주기),$J385&gt;=조회_최소,$J385&lt;=조회_최대),1,0)</f>
         <v/>
@@ -44868,9 +44164,7 @@
       <c r="S386" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T386" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T386" s="98" t="n"/>
       <c r="U386">
         <f>IF(AND($J386&lt;&gt;"",OR(조회_주기="전체",$R386=조회_주기),$J386&gt;=조회_최소,$J386&lt;=조회_최대),1,0)</f>
         <v/>
@@ -44970,9 +44264,7 @@
       <c r="S387" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T387" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T387" s="98" t="n"/>
       <c r="U387">
         <f>IF(AND($J387&lt;&gt;"",OR(조회_주기="전체",$R387=조회_주기),$J387&gt;=조회_최소,$J387&lt;=조회_최대),1,0)</f>
         <v/>
@@ -45072,9 +44364,7 @@
       <c r="S388" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T388" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T388" s="98" t="n"/>
       <c r="U388">
         <f>IF(AND($J388&lt;&gt;"",OR(조회_주기="전체",$R388=조회_주기),$J388&gt;=조회_최소,$J388&lt;=조회_최대),1,0)</f>
         <v/>
@@ -45174,9 +44464,7 @@
       <c r="S389" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T389" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T389" s="98" t="n"/>
       <c r="U389">
         <f>IF(AND($J389&lt;&gt;"",OR(조회_주기="전체",$R389=조회_주기),$J389&gt;=조회_최소,$J389&lt;=조회_최대),1,0)</f>
         <v/>
@@ -45276,9 +44564,7 @@
       <c r="S390" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T390" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T390" s="98" t="n"/>
       <c r="U390">
         <f>IF(AND($J390&lt;&gt;"",OR(조회_주기="전체",$R390=조회_주기),$J390&gt;=조회_최소,$J390&lt;=조회_최대),1,0)</f>
         <v/>
@@ -45378,9 +44664,7 @@
       <c r="S391" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T391" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T391" s="98" t="n"/>
       <c r="U391">
         <f>IF(AND($J391&lt;&gt;"",OR(조회_주기="전체",$R391=조회_주기),$J391&gt;=조회_최소,$J391&lt;=조회_최대),1,0)</f>
         <v/>
@@ -45480,9 +44764,7 @@
       <c r="S392" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T392" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T392" s="98" t="n"/>
       <c r="U392">
         <f>IF(AND($J392&lt;&gt;"",OR(조회_주기="전체",$R392=조회_주기),$J392&gt;=조회_최소,$J392&lt;=조회_최대),1,0)</f>
         <v/>
@@ -45582,9 +44864,7 @@
       <c r="S393" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T393" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T393" s="98" t="n"/>
       <c r="U393">
         <f>IF(AND($J393&lt;&gt;"",OR(조회_주기="전체",$R393=조회_주기),$J393&gt;=조회_최소,$J393&lt;=조회_최대),1,0)</f>
         <v/>
@@ -45684,9 +44964,7 @@
       <c r="S394" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T394" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T394" s="98" t="n"/>
       <c r="U394">
         <f>IF(AND($J394&lt;&gt;"",OR(조회_주기="전체",$R394=조회_주기),$J394&gt;=조회_최소,$J394&lt;=조회_최대),1,0)</f>
         <v/>
@@ -45786,9 +45064,7 @@
       <c r="S395" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T395" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T395" s="98" t="n"/>
       <c r="U395">
         <f>IF(AND($J395&lt;&gt;"",OR(조회_주기="전체",$R395=조회_주기),$J395&gt;=조회_최소,$J395&lt;=조회_최대),1,0)</f>
         <v/>
@@ -45888,9 +45164,7 @@
       <c r="S396" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T396" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T396" s="98" t="n"/>
       <c r="U396">
         <f>IF(AND($J396&lt;&gt;"",OR(조회_주기="전체",$R396=조회_주기),$J396&gt;=조회_최소,$J396&lt;=조회_최대),1,0)</f>
         <v/>
@@ -45990,9 +45264,7 @@
       <c r="S397" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T397" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T397" s="98" t="n"/>
       <c r="U397">
         <f>IF(AND($J397&lt;&gt;"",OR(조회_주기="전체",$R397=조회_주기),$J397&gt;=조회_최소,$J397&lt;=조회_최대),1,0)</f>
         <v/>
@@ -46092,9 +45364,7 @@
       <c r="S398" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T398" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T398" s="98" t="n"/>
       <c r="U398">
         <f>IF(AND($J398&lt;&gt;"",OR(조회_주기="전체",$R398=조회_주기),$J398&gt;=조회_최소,$J398&lt;=조회_최대),1,0)</f>
         <v/>
@@ -46194,9 +45464,7 @@
       <c r="S399" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T399" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T399" s="98" t="n"/>
       <c r="U399">
         <f>IF(AND($J399&lt;&gt;"",OR(조회_주기="전체",$R399=조회_주기),$J399&gt;=조회_최소,$J399&lt;=조회_최대),1,0)</f>
         <v/>
@@ -46296,9 +45564,7 @@
       <c r="S400" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T400" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T400" s="98" t="n"/>
       <c r="U400">
         <f>IF(AND($J400&lt;&gt;"",OR(조회_주기="전체",$R400=조회_주기),$J400&gt;=조회_최소,$J400&lt;=조회_최대),1,0)</f>
         <v/>
@@ -46398,9 +45664,7 @@
       <c r="S401" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T401" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T401" s="98" t="n"/>
       <c r="U401">
         <f>IF(AND($J401&lt;&gt;"",OR(조회_주기="전체",$R401=조회_주기),$J401&gt;=조회_최소,$J401&lt;=조회_최대),1,0)</f>
         <v/>
@@ -46500,9 +45764,7 @@
       <c r="S402" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T402" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T402" s="98" t="n"/>
       <c r="U402">
         <f>IF(AND($J402&lt;&gt;"",OR(조회_주기="전체",$R402=조회_주기),$J402&gt;=조회_최소,$J402&lt;=조회_최대),1,0)</f>
         <v/>
@@ -46602,9 +45864,7 @@
       <c r="S403" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T403" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T403" s="98" t="n"/>
       <c r="U403">
         <f>IF(AND($J403&lt;&gt;"",OR(조회_주기="전체",$R403=조회_주기),$J403&gt;=조회_최소,$J403&lt;=조회_최대),1,0)</f>
         <v/>
@@ -46704,9 +45964,7 @@
       <c r="S404" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T404" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T404" s="98" t="n"/>
       <c r="U404">
         <f>IF(AND($J404&lt;&gt;"",OR(조회_주기="전체",$R404=조회_주기),$J404&gt;=조회_최소,$J404&lt;=조회_최대),1,0)</f>
         <v/>
@@ -46806,9 +46064,7 @@
       <c r="S405" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T405" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T405" s="98" t="n"/>
       <c r="U405">
         <f>IF(AND($J405&lt;&gt;"",OR(조회_주기="전체",$R405=조회_주기),$J405&gt;=조회_최소,$J405&lt;=조회_최대),1,0)</f>
         <v/>
@@ -46908,9 +46164,7 @@
       <c r="S406" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T406" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T406" s="98" t="n"/>
       <c r="U406">
         <f>IF(AND($J406&lt;&gt;"",OR(조회_주기="전체",$R406=조회_주기),$J406&gt;=조회_최소,$J406&lt;=조회_최대),1,0)</f>
         <v/>
@@ -47010,9 +46264,7 @@
       <c r="S407" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T407" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T407" s="98" t="n"/>
       <c r="U407">
         <f>IF(AND($J407&lt;&gt;"",OR(조회_주기="전체",$R407=조회_주기),$J407&gt;=조회_최소,$J407&lt;=조회_최대),1,0)</f>
         <v/>
@@ -47112,9 +46364,7 @@
       <c r="S408" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T408" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T408" s="98" t="n"/>
       <c r="U408">
         <f>IF(AND($J408&lt;&gt;"",OR(조회_주기="전체",$R408=조회_주기),$J408&gt;=조회_최소,$J408&lt;=조회_최대),1,0)</f>
         <v/>
@@ -47316,9 +46566,7 @@
       <c r="S410" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T410" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T410" s="98" t="n"/>
       <c r="U410">
         <f>IF(AND($J410&lt;&gt;"",OR(조회_주기="전체",$R410=조회_주기),$J410&gt;=조회_최소,$J410&lt;=조회_최대),1,0)</f>
         <v/>
@@ -47418,9 +46666,7 @@
       <c r="S411" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T411" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T411" s="98" t="n"/>
       <c r="U411">
         <f>IF(AND($J411&lt;&gt;"",OR(조회_주기="전체",$R411=조회_주기),$J411&gt;=조회_최소,$J411&lt;=조회_최대),1,0)</f>
         <v/>
@@ -47520,9 +46766,7 @@
       <c r="S412" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T412" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T412" s="98" t="n"/>
       <c r="U412">
         <f>IF(AND($J412&lt;&gt;"",OR(조회_주기="전체",$R412=조회_주기),$J412&gt;=조회_최소,$J412&lt;=조회_최대),1,0)</f>
         <v/>
@@ -47622,9 +46866,7 @@
       <c r="S413" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T413" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T413" s="98" t="n"/>
       <c r="U413">
         <f>IF(AND($J413&lt;&gt;"",OR(조회_주기="전체",$R413=조회_주기),$J413&gt;=조회_최소,$J413&lt;=조회_최대),1,0)</f>
         <v/>
@@ -47724,9 +46966,7 @@
       <c r="S414" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T414" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T414" s="98" t="n"/>
       <c r="U414">
         <f>IF(AND($J414&lt;&gt;"",OR(조회_주기="전체",$R414=조회_주기),$J414&gt;=조회_최소,$J414&lt;=조회_최대),1,0)</f>
         <v/>
@@ -47826,9 +47066,7 @@
       <c r="S415" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T415" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T415" s="98" t="n"/>
       <c r="U415">
         <f>IF(AND($J415&lt;&gt;"",OR(조회_주기="전체",$R415=조회_주기),$J415&gt;=조회_최소,$J415&lt;=조회_최대),1,0)</f>
         <v/>
@@ -47928,9 +47166,7 @@
       <c r="S416" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T416" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T416" s="98" t="n"/>
       <c r="U416">
         <f>IF(AND($J416&lt;&gt;"",OR(조회_주기="전체",$R416=조회_주기),$J416&gt;=조회_최소,$J416&lt;=조회_최대),1,0)</f>
         <v/>
@@ -48030,9 +47266,7 @@
       <c r="S417" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T417" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T417" s="98" t="n"/>
       <c r="U417">
         <f>IF(AND($J417&lt;&gt;"",OR(조회_주기="전체",$R417=조회_주기),$J417&gt;=조회_최소,$J417&lt;=조회_최대),1,0)</f>
         <v/>
@@ -48132,9 +47366,7 @@
       <c r="S418" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T418" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T418" s="98" t="n"/>
       <c r="U418">
         <f>IF(AND($J418&lt;&gt;"",OR(조회_주기="전체",$R418=조회_주기),$J418&gt;=조회_최소,$J418&lt;=조회_최대),1,0)</f>
         <v/>
@@ -48234,9 +47466,7 @@
       <c r="S419" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T419" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T419" s="98" t="n"/>
       <c r="U419">
         <f>IF(AND($J419&lt;&gt;"",OR(조회_주기="전체",$R419=조회_주기),$J419&gt;=조회_최소,$J419&lt;=조회_최대),1,0)</f>
         <v/>
@@ -48336,9 +47566,7 @@
       <c r="S420" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T420" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T420" s="98" t="n"/>
       <c r="U420">
         <f>IF(AND($J420&lt;&gt;"",OR(조회_주기="전체",$R420=조회_주기),$J420&gt;=조회_최소,$J420&lt;=조회_최대),1,0)</f>
         <v/>
@@ -48438,9 +47666,7 @@
       <c r="S421" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T421" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T421" s="98" t="n"/>
       <c r="U421">
         <f>IF(AND($J421&lt;&gt;"",OR(조회_주기="전체",$R421=조회_주기),$J421&gt;=조회_최소,$J421&lt;=조회_최대),1,0)</f>
         <v/>
@@ -48540,9 +47766,7 @@
       <c r="S422" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T422" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T422" s="98" t="n"/>
       <c r="U422">
         <f>IF(AND($J422&lt;&gt;"",OR(조회_주기="전체",$R422=조회_주기),$J422&gt;=조회_최소,$J422&lt;=조회_최대),1,0)</f>
         <v/>
@@ -48642,9 +47866,7 @@
       <c r="S423" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T423" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T423" s="98" t="n"/>
       <c r="U423">
         <f>IF(AND($J423&lt;&gt;"",OR(조회_주기="전체",$R423=조회_주기),$J423&gt;=조회_최소,$J423&lt;=조회_최대),1,0)</f>
         <v/>
@@ -48744,9 +47966,7 @@
       <c r="S424" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T424" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T424" s="98" t="n"/>
       <c r="U424">
         <f>IF(AND($J424&lt;&gt;"",OR(조회_주기="전체",$R424=조회_주기),$J424&gt;=조회_최소,$J424&lt;=조회_최대),1,0)</f>
         <v/>
@@ -48846,9 +48066,7 @@
       <c r="S425" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T425" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T425" s="98" t="n"/>
       <c r="U425">
         <f>IF(AND($J425&lt;&gt;"",OR(조회_주기="전체",$R425=조회_주기),$J425&gt;=조회_최소,$J425&lt;=조회_최대),1,0)</f>
         <v/>
@@ -48948,9 +48166,7 @@
       <c r="S426" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T426" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T426" s="98" t="n"/>
       <c r="U426">
         <f>IF(AND($J426&lt;&gt;"",OR(조회_주기="전체",$R426=조회_주기),$J426&gt;=조회_최소,$J426&lt;=조회_최대),1,0)</f>
         <v/>
@@ -49050,9 +48266,7 @@
       <c r="S427" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T427" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T427" s="98" t="n"/>
       <c r="U427">
         <f>IF(AND($J427&lt;&gt;"",OR(조회_주기="전체",$R427=조회_주기),$J427&gt;=조회_최소,$J427&lt;=조회_최대),1,0)</f>
         <v/>
@@ -49152,9 +48366,7 @@
       <c r="S428" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T428" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T428" s="98" t="n"/>
       <c r="U428">
         <f>IF(AND($J428&lt;&gt;"",OR(조회_주기="전체",$R428=조회_주기),$J428&gt;=조회_최소,$J428&lt;=조회_최대),1,0)</f>
         <v/>
@@ -49254,9 +48466,7 @@
       <c r="S429" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T429" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T429" s="98" t="n"/>
       <c r="U429">
         <f>IF(AND($J429&lt;&gt;"",OR(조회_주기="전체",$R429=조회_주기),$J429&gt;=조회_최소,$J429&lt;=조회_최대),1,0)</f>
         <v/>
@@ -49356,9 +48566,7 @@
       <c r="S430" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T430" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T430" s="98" t="n"/>
       <c r="U430">
         <f>IF(AND($J430&lt;&gt;"",OR(조회_주기="전체",$R430=조회_주기),$J430&gt;=조회_최소,$J430&lt;=조회_최대),1,0)</f>
         <v/>
@@ -49458,9 +48666,7 @@
       <c r="S431" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T431" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T431" s="98" t="n"/>
       <c r="U431">
         <f>IF(AND($J431&lt;&gt;"",OR(조회_주기="전체",$R431=조회_주기),$J431&gt;=조회_최소,$J431&lt;=조회_최대),1,0)</f>
         <v/>
@@ -49560,9 +48766,7 @@
       <c r="S432" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T432" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T432" s="98" t="n"/>
       <c r="U432">
         <f>IF(AND($J432&lt;&gt;"",OR(조회_주기="전체",$R432=조회_주기),$J432&gt;=조회_최소,$J432&lt;=조회_최대),1,0)</f>
         <v/>
@@ -49662,9 +48866,7 @@
       <c r="S433" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T433" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T433" s="98" t="n"/>
       <c r="U433">
         <f>IF(AND($J433&lt;&gt;"",OR(조회_주기="전체",$R433=조회_주기),$J433&gt;=조회_최소,$J433&lt;=조회_최대),1,0)</f>
         <v/>
@@ -49764,9 +48966,7 @@
       <c r="S434" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T434" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T434" s="98" t="n"/>
       <c r="U434">
         <f>IF(AND($J434&lt;&gt;"",OR(조회_주기="전체",$R434=조회_주기),$J434&gt;=조회_최소,$J434&lt;=조회_최대),1,0)</f>
         <v/>
@@ -49866,9 +49066,7 @@
       <c r="S435" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T435" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T435" s="98" t="n"/>
       <c r="U435">
         <f>IF(AND($J435&lt;&gt;"",OR(조회_주기="전체",$R435=조회_주기),$J435&gt;=조회_최소,$J435&lt;=조회_최대),1,0)</f>
         <v/>
@@ -49968,9 +49166,7 @@
       <c r="S436" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T436" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T436" s="98" t="n"/>
       <c r="U436">
         <f>IF(AND($J436&lt;&gt;"",OR(조회_주기="전체",$R436=조회_주기),$J436&gt;=조회_최소,$J436&lt;=조회_최대),1,0)</f>
         <v/>
@@ -50070,9 +49266,7 @@
       <c r="S437" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T437" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T437" s="98" t="n"/>
       <c r="U437">
         <f>IF(AND($J437&lt;&gt;"",OR(조회_주기="전체",$R437=조회_주기),$J437&gt;=조회_최소,$J437&lt;=조회_최대),1,0)</f>
         <v/>
@@ -50172,9 +49366,7 @@
       <c r="S438" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T438" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T438" s="98" t="n"/>
       <c r="U438">
         <f>IF(AND($J438&lt;&gt;"",OR(조회_주기="전체",$R438=조회_주기),$J438&gt;=조회_최소,$J438&lt;=조회_최대),1,0)</f>
         <v/>
@@ -50274,9 +49466,7 @@
       <c r="S439" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T439" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T439" s="98" t="n"/>
       <c r="U439">
         <f>IF(AND($J439&lt;&gt;"",OR(조회_주기="전체",$R439=조회_주기),$J439&gt;=조회_최소,$J439&lt;=조회_최대),1,0)</f>
         <v/>
@@ -50376,9 +49566,7 @@
       <c r="S440" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T440" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T440" s="98" t="n"/>
       <c r="U440">
         <f>IF(AND($J440&lt;&gt;"",OR(조회_주기="전체",$R440=조회_주기),$J440&gt;=조회_최소,$J440&lt;=조회_최대),1,0)</f>
         <v/>
@@ -50478,9 +49666,7 @@
       <c r="S441" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T441" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T441" s="98" t="n"/>
       <c r="U441">
         <f>IF(AND($J441&lt;&gt;"",OR(조회_주기="전체",$R441=조회_주기),$J441&gt;=조회_최소,$J441&lt;=조회_최대),1,0)</f>
         <v/>
@@ -50580,9 +49766,7 @@
       <c r="S442" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T442" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T442" s="98" t="n"/>
       <c r="U442">
         <f>IF(AND($J442&lt;&gt;"",OR(조회_주기="전체",$R442=조회_주기),$J442&gt;=조회_최소,$J442&lt;=조회_최대),1,0)</f>
         <v/>
@@ -50682,9 +49866,7 @@
       <c r="S443" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T443" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T443" s="98" t="n"/>
       <c r="U443">
         <f>IF(AND($J443&lt;&gt;"",OR(조회_주기="전체",$R443=조회_주기),$J443&gt;=조회_최소,$J443&lt;=조회_최대),1,0)</f>
         <v/>
@@ -50784,9 +49966,7 @@
       <c r="S444" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T444" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T444" s="98" t="n"/>
       <c r="U444">
         <f>IF(AND($J444&lt;&gt;"",OR(조회_주기="전체",$R444=조회_주기),$J444&gt;=조회_최소,$J444&lt;=조회_최대),1,0)</f>
         <v/>
@@ -50886,9 +50066,7 @@
       <c r="S445" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T445" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T445" s="98" t="n"/>
       <c r="U445">
         <f>IF(AND($J445&lt;&gt;"",OR(조회_주기="전체",$R445=조회_주기),$J445&gt;=조회_최소,$J445&lt;=조회_최대),1,0)</f>
         <v/>
@@ -50988,9 +50166,7 @@
       <c r="S446" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T446" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T446" s="98" t="n"/>
       <c r="U446">
         <f>IF(AND($J446&lt;&gt;"",OR(조회_주기="전체",$R446=조회_주기),$J446&gt;=조회_최소,$J446&lt;=조회_최대),1,0)</f>
         <v/>
@@ -51090,9 +50266,7 @@
       <c r="S447" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T447" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T447" s="98" t="n"/>
       <c r="U447">
         <f>IF(AND($J447&lt;&gt;"",OR(조회_주기="전체",$R447=조회_주기),$J447&gt;=조회_최소,$J447&lt;=조회_최대),1,0)</f>
         <v/>
@@ -51192,9 +50366,7 @@
       <c r="S448" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T448" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T448" s="98" t="n"/>
       <c r="U448">
         <f>IF(AND($J448&lt;&gt;"",OR(조회_주기="전체",$R448=조회_주기),$J448&gt;=조회_최소,$J448&lt;=조회_최대),1,0)</f>
         <v/>
@@ -51294,9 +50466,7 @@
       <c r="S449" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T449" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T449" s="98" t="n"/>
       <c r="U449">
         <f>IF(AND($J449&lt;&gt;"",OR(조회_주기="전체",$R449=조회_주기),$J449&gt;=조회_최소,$J449&lt;=조회_최대),1,0)</f>
         <v/>
@@ -51396,9 +50566,7 @@
       <c r="S450" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T450" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T450" s="98" t="n"/>
       <c r="U450">
         <f>IF(AND($J450&lt;&gt;"",OR(조회_주기="전체",$R450=조회_주기),$J450&gt;=조회_최소,$J450&lt;=조회_최대),1,0)</f>
         <v/>
@@ -51498,9 +50666,7 @@
       <c r="S451" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T451" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T451" s="98" t="n"/>
       <c r="U451">
         <f>IF(AND($J451&lt;&gt;"",OR(조회_주기="전체",$R451=조회_주기),$J451&gt;=조회_최소,$J451&lt;=조회_최대),1,0)</f>
         <v/>
@@ -51600,9 +50766,7 @@
       <c r="S452" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T452" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T452" s="98" t="n"/>
       <c r="U452">
         <f>IF(AND($J452&lt;&gt;"",OR(조회_주기="전체",$R452=조회_주기),$J452&gt;=조회_최소,$J452&lt;=조회_최대),1,0)</f>
         <v/>
@@ -51702,9 +50866,7 @@
       <c r="S453" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T453" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T453" s="98" t="n"/>
       <c r="U453">
         <f>IF(AND($J453&lt;&gt;"",OR(조회_주기="전체",$R453=조회_주기),$J453&gt;=조회_최소,$J453&lt;=조회_최대),1,0)</f>
         <v/>
@@ -51804,9 +50966,7 @@
       <c r="S454" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T454" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T454" s="98" t="n"/>
       <c r="U454">
         <f>IF(AND($J454&lt;&gt;"",OR(조회_주기="전체",$R454=조회_주기),$J454&gt;=조회_최소,$J454&lt;=조회_최대),1,0)</f>
         <v/>
@@ -51906,9 +51066,7 @@
       <c r="S455" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T455" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T455" s="98" t="n"/>
       <c r="U455">
         <f>IF(AND($J455&lt;&gt;"",OR(조회_주기="전체",$R455=조회_주기),$J455&gt;=조회_최소,$J455&lt;=조회_최대),1,0)</f>
         <v/>
@@ -52008,9 +51166,7 @@
       <c r="S456" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T456" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T456" s="98" t="n"/>
       <c r="U456">
         <f>IF(AND($J456&lt;&gt;"",OR(조회_주기="전체",$R456=조회_주기),$J456&gt;=조회_최소,$J456&lt;=조회_최대),1,0)</f>
         <v/>
@@ -52110,9 +51266,7 @@
       <c r="S457" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T457" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T457" s="98" t="n"/>
       <c r="U457">
         <f>IF(AND($J457&lt;&gt;"",OR(조회_주기="전체",$R457=조회_주기),$J457&gt;=조회_최소,$J457&lt;=조회_최대),1,0)</f>
         <v/>
@@ -52212,9 +51366,7 @@
       <c r="S458" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T458" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T458" s="98" t="n"/>
       <c r="U458">
         <f>IF(AND($J458&lt;&gt;"",OR(조회_주기="전체",$R458=조회_주기),$J458&gt;=조회_최소,$J458&lt;=조회_최대),1,0)</f>
         <v/>
@@ -52314,9 +51466,7 @@
       <c r="S459" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T459" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T459" s="98" t="n"/>
       <c r="U459">
         <f>IF(AND($J459&lt;&gt;"",OR(조회_주기="전체",$R459=조회_주기),$J459&gt;=조회_최소,$J459&lt;=조회_최대),1,0)</f>
         <v/>
@@ -52416,9 +51566,7 @@
       <c r="S460" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T460" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T460" s="98" t="n"/>
       <c r="U460">
         <f>IF(AND($J460&lt;&gt;"",OR(조회_주기="전체",$R460=조회_주기),$J460&gt;=조회_최소,$J460&lt;=조회_최대),1,0)</f>
         <v/>
@@ -52518,9 +51666,7 @@
       <c r="S461" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T461" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T461" s="98" t="n"/>
       <c r="U461">
         <f>IF(AND($J461&lt;&gt;"",OR(조회_주기="전체",$R461=조회_주기),$J461&gt;=조회_최소,$J461&lt;=조회_최대),1,0)</f>
         <v/>
@@ -52620,9 +51766,7 @@
       <c r="S462" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T462" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T462" s="98" t="n"/>
       <c r="U462">
         <f>IF(AND($J462&lt;&gt;"",OR(조회_주기="전체",$R462=조회_주기),$J462&gt;=조회_최소,$J462&lt;=조회_최대),1,0)</f>
         <v/>
@@ -52722,9 +51866,7 @@
       <c r="S463" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T463" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T463" s="98" t="n"/>
       <c r="U463">
         <f>IF(AND($J463&lt;&gt;"",OR(조회_주기="전체",$R463=조회_주기),$J463&gt;=조회_최소,$J463&lt;=조회_최대),1,0)</f>
         <v/>
@@ -52824,9 +51966,7 @@
       <c r="S464" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T464" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T464" s="98" t="n"/>
       <c r="U464">
         <f>IF(AND($J464&lt;&gt;"",OR(조회_주기="전체",$R464=조회_주기),$J464&gt;=조회_최소,$J464&lt;=조회_최대),1,0)</f>
         <v/>
@@ -52926,9 +52066,7 @@
       <c r="S465" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T465" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T465" s="98" t="n"/>
       <c r="U465">
         <f>IF(AND($J465&lt;&gt;"",OR(조회_주기="전체",$R465=조회_주기),$J465&gt;=조회_최소,$J465&lt;=조회_최대),1,0)</f>
         <v/>
@@ -53028,9 +52166,7 @@
       <c r="S466" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T466" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T466" s="98" t="n"/>
       <c r="U466">
         <f>IF(AND($J466&lt;&gt;"",OR(조회_주기="전체",$R466=조회_주기),$J466&gt;=조회_최소,$J466&lt;=조회_최대),1,0)</f>
         <v/>
@@ -53130,9 +52266,7 @@
       <c r="S467" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T467" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T467" s="98" t="n"/>
       <c r="U467">
         <f>IF(AND($J467&lt;&gt;"",OR(조회_주기="전체",$R467=조회_주기),$J467&gt;=조회_최소,$J467&lt;=조회_최대),1,0)</f>
         <v/>
@@ -53232,9 +52366,7 @@
       <c r="S468" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T468" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T468" s="98" t="n"/>
       <c r="U468">
         <f>IF(AND($J468&lt;&gt;"",OR(조회_주기="전체",$R468=조회_주기),$J468&gt;=조회_최소,$J468&lt;=조회_최대),1,0)</f>
         <v/>
@@ -53334,9 +52466,7 @@
       <c r="S469" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T469" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T469" s="98" t="n"/>
       <c r="U469">
         <f>IF(AND($J469&lt;&gt;"",OR(조회_주기="전체",$R469=조회_주기),$J469&gt;=조회_최소,$J469&lt;=조회_최대),1,0)</f>
         <v/>
@@ -53436,9 +52566,7 @@
       <c r="S470" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T470" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T470" s="98" t="n"/>
       <c r="U470">
         <f>IF(AND($J470&lt;&gt;"",OR(조회_주기="전체",$R470=조회_주기),$J470&gt;=조회_최소,$J470&lt;=조회_최대),1,0)</f>
         <v/>
@@ -53538,9 +52666,7 @@
       <c r="S471" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T471" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T471" s="98" t="n"/>
       <c r="U471">
         <f>IF(AND($J471&lt;&gt;"",OR(조회_주기="전체",$R471=조회_주기),$J471&gt;=조회_최소,$J471&lt;=조회_최대),1,0)</f>
         <v/>
@@ -53640,9 +52766,7 @@
       <c r="S472" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T472" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T472" s="98" t="n"/>
       <c r="U472">
         <f>IF(AND($J472&lt;&gt;"",OR(조회_주기="전체",$R472=조회_주기),$J472&gt;=조회_최소,$J472&lt;=조회_최대),1,0)</f>
         <v/>
@@ -53742,9 +52866,7 @@
       <c r="S473" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T473" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T473" s="98" t="n"/>
       <c r="U473">
         <f>IF(AND($J473&lt;&gt;"",OR(조회_주기="전체",$R473=조회_주기),$J473&gt;=조회_최소,$J473&lt;=조회_최대),1,0)</f>
         <v/>
@@ -53844,9 +52966,7 @@
       <c r="S474" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T474" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T474" s="98" t="n"/>
       <c r="U474">
         <f>IF(AND($J474&lt;&gt;"",OR(조회_주기="전체",$R474=조회_주기),$J474&gt;=조회_최소,$J474&lt;=조회_최대),1,0)</f>
         <v/>
@@ -53946,9 +53066,7 @@
       <c r="S475" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T475" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T475" s="98" t="n"/>
       <c r="U475">
         <f>IF(AND($J475&lt;&gt;"",OR(조회_주기="전체",$R475=조회_주기),$J475&gt;=조회_최소,$J475&lt;=조회_최대),1,0)</f>
         <v/>
@@ -54048,9 +53166,7 @@
       <c r="S476" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T476" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T476" s="98" t="n"/>
       <c r="U476">
         <f>IF(AND($J476&lt;&gt;"",OR(조회_주기="전체",$R476=조회_주기),$J476&gt;=조회_최소,$J476&lt;=조회_최대),1,0)</f>
         <v/>
@@ -54150,9 +53266,7 @@
       <c r="S477" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T477" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T477" s="98" t="n"/>
       <c r="U477">
         <f>IF(AND($J477&lt;&gt;"",OR(조회_주기="전체",$R477=조회_주기),$J477&gt;=조회_최소,$J477&lt;=조회_최대),1,0)</f>
         <v/>
@@ -54252,9 +53366,7 @@
       <c r="S478" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T478" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T478" s="98" t="n"/>
       <c r="U478">
         <f>IF(AND($J478&lt;&gt;"",OR(조회_주기="전체",$R478=조회_주기),$J478&gt;=조회_최소,$J478&lt;=조회_최대),1,0)</f>
         <v/>
@@ -54354,9 +53466,7 @@
       <c r="S479" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T479" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T479" s="98" t="n"/>
       <c r="U479">
         <f>IF(AND($J479&lt;&gt;"",OR(조회_주기="전체",$R479=조회_주기),$J479&gt;=조회_최소,$J479&lt;=조회_최대),1,0)</f>
         <v/>
@@ -54456,9 +53566,7 @@
       <c r="S480" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T480" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T480" s="98" t="n"/>
       <c r="U480">
         <f>IF(AND($J480&lt;&gt;"",OR(조회_주기="전체",$R480=조회_주기),$J480&gt;=조회_최소,$J480&lt;=조회_최대),1,0)</f>
         <v/>
@@ -54558,9 +53666,7 @@
       <c r="S481" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T481" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T481" s="98" t="n"/>
       <c r="U481">
         <f>IF(AND($J481&lt;&gt;"",OR(조회_주기="전체",$R481=조회_주기),$J481&gt;=조회_최소,$J481&lt;=조회_최대),1,0)</f>
         <v/>
@@ -54660,9 +53766,7 @@
       <c r="S482" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T482" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T482" s="98" t="n"/>
       <c r="U482">
         <f>IF(AND($J482&lt;&gt;"",OR(조회_주기="전체",$R482=조회_주기),$J482&gt;=조회_최소,$J482&lt;=조회_최대),1,0)</f>
         <v/>
@@ -54762,9 +53866,7 @@
       <c r="S483" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T483" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T483" s="98" t="n"/>
       <c r="U483">
         <f>IF(AND($J483&lt;&gt;"",OR(조회_주기="전체",$R483=조회_주기),$J483&gt;=조회_최소,$J483&lt;=조회_최대),1,0)</f>
         <v/>
@@ -54864,9 +53966,7 @@
       <c r="S484" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T484" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T484" s="98" t="n"/>
       <c r="U484">
         <f>IF(AND($J484&lt;&gt;"",OR(조회_주기="전체",$R484=조회_주기),$J484&gt;=조회_최소,$J484&lt;=조회_최대),1,0)</f>
         <v/>
@@ -54966,9 +54066,7 @@
       <c r="S485" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T485" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T485" s="98" t="n"/>
       <c r="U485">
         <f>IF(AND($J485&lt;&gt;"",OR(조회_주기="전체",$R485=조회_주기),$J485&gt;=조회_최소,$J485&lt;=조회_최대),1,0)</f>
         <v/>
@@ -55068,9 +54166,7 @@
       <c r="S486" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T486" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T486" s="98" t="n"/>
       <c r="U486">
         <f>IF(AND($J486&lt;&gt;"",OR(조회_주기="전체",$R486=조회_주기),$J486&gt;=조회_최소,$J486&lt;=조회_최대),1,0)</f>
         <v/>
@@ -55170,9 +54266,7 @@
       <c r="S487" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T487" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T487" s="98" t="n"/>
       <c r="U487">
         <f>IF(AND($J487&lt;&gt;"",OR(조회_주기="전체",$R487=조회_주기),$J487&gt;=조회_최소,$J487&lt;=조회_최대),1,0)</f>
         <v/>
@@ -55272,9 +54366,7 @@
       <c r="S488" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T488" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T488" s="98" t="n"/>
       <c r="U488">
         <f>IF(AND($J488&lt;&gt;"",OR(조회_주기="전체",$R488=조회_주기),$J488&gt;=조회_최소,$J488&lt;=조회_최대),1,0)</f>
         <v/>
@@ -55374,9 +54466,7 @@
       <c r="S489" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T489" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T489" s="98" t="n"/>
       <c r="U489">
         <f>IF(AND($J489&lt;&gt;"",OR(조회_주기="전체",$R489=조회_주기),$J489&gt;=조회_최소,$J489&lt;=조회_최대),1,0)</f>
         <v/>
@@ -55476,9 +54566,7 @@
       <c r="S490" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T490" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T490" s="98" t="n"/>
       <c r="U490">
         <f>IF(AND($J490&lt;&gt;"",OR(조회_주기="전체",$R490=조회_주기),$J490&gt;=조회_최소,$J490&lt;=조회_최대),1,0)</f>
         <v/>
@@ -55578,9 +54666,7 @@
       <c r="S491" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T491" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T491" s="98" t="n"/>
       <c r="U491">
         <f>IF(AND($J491&lt;&gt;"",OR(조회_주기="전체",$R491=조회_주기),$J491&gt;=조회_최소,$J491&lt;=조회_최대),1,0)</f>
         <v/>
@@ -55680,9 +54766,7 @@
       <c r="S492" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T492" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T492" s="98" t="n"/>
       <c r="U492">
         <f>IF(AND($J492&lt;&gt;"",OR(조회_주기="전체",$R492=조회_주기),$J492&gt;=조회_최소,$J492&lt;=조회_최대),1,0)</f>
         <v/>
@@ -55782,9 +54866,7 @@
       <c r="S493" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T493" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T493" s="98" t="n"/>
       <c r="U493">
         <f>IF(AND($J493&lt;&gt;"",OR(조회_주기="전체",$R493=조회_주기),$J493&gt;=조회_최소,$J493&lt;=조회_최대),1,0)</f>
         <v/>
@@ -55884,9 +54966,7 @@
       <c r="S494" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T494" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T494" s="98" t="n"/>
       <c r="U494">
         <f>IF(AND($J494&lt;&gt;"",OR(조회_주기="전체",$R494=조회_주기),$J494&gt;=조회_최소,$J494&lt;=조회_최대),1,0)</f>
         <v/>
@@ -55986,9 +55066,7 @@
       <c r="S495" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T495" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T495" s="98" t="n"/>
       <c r="U495">
         <f>IF(AND($J495&lt;&gt;"",OR(조회_주기="전체",$R495=조회_주기),$J495&gt;=조회_최소,$J495&lt;=조회_최대),1,0)</f>
         <v/>
@@ -56088,9 +55166,7 @@
       <c r="S496" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T496" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T496" s="98" t="n"/>
       <c r="U496">
         <f>IF(AND($J496&lt;&gt;"",OR(조회_주기="전체",$R496=조회_주기),$J496&gt;=조회_최소,$J496&lt;=조회_최대),1,0)</f>
         <v/>
@@ -56190,9 +55266,7 @@
       <c r="S497" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T497" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T497" s="98" t="n"/>
       <c r="U497">
         <f>IF(AND($J497&lt;&gt;"",OR(조회_주기="전체",$R497=조회_주기),$J497&gt;=조회_최소,$J497&lt;=조회_최대),1,0)</f>
         <v/>
@@ -56292,9 +55366,7 @@
       <c r="S498" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T498" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T498" s="98" t="n"/>
       <c r="U498">
         <f>IF(AND($J498&lt;&gt;"",OR(조회_주기="전체",$R498=조회_주기),$J498&gt;=조회_최소,$J498&lt;=조회_최대),1,0)</f>
         <v/>
@@ -56394,9 +55466,7 @@
       <c r="S499" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T499" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T499" s="98" t="n"/>
       <c r="U499">
         <f>IF(AND($J499&lt;&gt;"",OR(조회_주기="전체",$R499=조회_주기),$J499&gt;=조회_최소,$J499&lt;=조회_최대),1,0)</f>
         <v/>
@@ -56496,9 +55566,7 @@
       <c r="S500" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T500" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T500" s="98" t="n"/>
       <c r="U500">
         <f>IF(AND($J500&lt;&gt;"",OR(조회_주기="전체",$R500=조회_주기),$J500&gt;=조회_최소,$J500&lt;=조회_최대),1,0)</f>
         <v/>
@@ -56598,9 +55666,7 @@
       <c r="S501" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T501" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T501" s="98" t="n"/>
       <c r="U501">
         <f>IF(AND($J501&lt;&gt;"",OR(조회_주기="전체",$R501=조회_주기),$J501&gt;=조회_최소,$J501&lt;=조회_최대),1,0)</f>
         <v/>
@@ -56700,9 +55766,7 @@
       <c r="S502" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T502" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T502" s="98" t="n"/>
       <c r="U502">
         <f>IF(AND($J502&lt;&gt;"",OR(조회_주기="전체",$R502=조회_주기),$J502&gt;=조회_최소,$J502&lt;=조회_최대),1,0)</f>
         <v/>
@@ -56802,9 +55866,7 @@
       <c r="S503" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T503" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T503" s="98" t="n"/>
       <c r="U503">
         <f>IF(AND($J503&lt;&gt;"",OR(조회_주기="전체",$R503=조회_주기),$J503&gt;=조회_최소,$J503&lt;=조회_최대),1,0)</f>
         <v/>
@@ -56904,9 +55966,7 @@
       <c r="S504" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T504" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T504" s="98" t="n"/>
       <c r="U504">
         <f>IF(AND($J504&lt;&gt;"",OR(조회_주기="전체",$R504=조회_주기),$J504&gt;=조회_최소,$J504&lt;=조회_최대),1,0)</f>
         <v/>
@@ -57006,9 +56066,7 @@
       <c r="S505" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T505" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T505" s="98" t="n"/>
       <c r="U505">
         <f>IF(AND($J505&lt;&gt;"",OR(조회_주기="전체",$R505=조회_주기),$J505&gt;=조회_최소,$J505&lt;=조회_최대),1,0)</f>
         <v/>
@@ -57108,9 +56166,7 @@
       <c r="S506" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T506" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T506" s="98" t="n"/>
       <c r="U506">
         <f>IF(AND($J506&lt;&gt;"",OR(조회_주기="전체",$R506=조회_주기),$J506&gt;=조회_최소,$J506&lt;=조회_최대),1,0)</f>
         <v/>
@@ -57210,9 +56266,7 @@
       <c r="S507" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T507" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T507" s="98" t="n"/>
       <c r="U507">
         <f>IF(AND($J507&lt;&gt;"",OR(조회_주기="전체",$R507=조회_주기),$J507&gt;=조회_최소,$J507&lt;=조회_최대),1,0)</f>
         <v/>
@@ -57312,9 +56366,7 @@
       <c r="S508" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T508" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T508" s="98" t="n"/>
       <c r="U508">
         <f>IF(AND($J508&lt;&gt;"",OR(조회_주기="전체",$R508=조회_주기),$J508&gt;=조회_최소,$J508&lt;=조회_최대),1,0)</f>
         <v/>
@@ -57414,9 +56466,7 @@
       <c r="S509" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T509" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T509" s="98" t="n"/>
       <c r="U509">
         <f>IF(AND($J509&lt;&gt;"",OR(조회_주기="전체",$R509=조회_주기),$J509&gt;=조회_최소,$J509&lt;=조회_최대),1,0)</f>
         <v/>
@@ -57516,9 +56566,7 @@
       <c r="S510" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T510" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T510" s="98" t="n"/>
       <c r="U510">
         <f>IF(AND($J510&lt;&gt;"",OR(조회_주기="전체",$R510=조회_주기),$J510&gt;=조회_최소,$J510&lt;=조회_최대),1,0)</f>
         <v/>
@@ -57618,9 +56666,7 @@
       <c r="S511" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T511" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T511" s="98" t="n"/>
       <c r="U511">
         <f>IF(AND($J511&lt;&gt;"",OR(조회_주기="전체",$R511=조회_주기),$J511&gt;=조회_최소,$J511&lt;=조회_최대),1,0)</f>
         <v/>
@@ -57720,9 +56766,7 @@
       <c r="S512" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T512" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T512" s="98" t="n"/>
       <c r="U512">
         <f>IF(AND($J512&lt;&gt;"",OR(조회_주기="전체",$R512=조회_주기),$J512&gt;=조회_최소,$J512&lt;=조회_최대),1,0)</f>
         <v/>
@@ -57822,9 +56866,7 @@
       <c r="S513" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T513" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T513" s="98" t="n"/>
       <c r="U513">
         <f>IF(AND($J513&lt;&gt;"",OR(조회_주기="전체",$R513=조회_주기),$J513&gt;=조회_최소,$J513&lt;=조회_최대),1,0)</f>
         <v/>
@@ -57924,9 +56966,7 @@
       <c r="S514" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T514" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T514" s="98" t="n"/>
       <c r="U514">
         <f>IF(AND($J514&lt;&gt;"",OR(조회_주기="전체",$R514=조회_주기),$J514&gt;=조회_최소,$J514&lt;=조회_최대),1,0)</f>
         <v/>
@@ -58026,9 +57066,7 @@
       <c r="S515" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T515" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T515" s="98" t="n"/>
       <c r="U515">
         <f>IF(AND($J515&lt;&gt;"",OR(조회_주기="전체",$R515=조회_주기),$J515&gt;=조회_최소,$J515&lt;=조회_최대),1,0)</f>
         <v/>
@@ -58128,9 +57166,7 @@
       <c r="S516" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T516" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T516" s="98" t="n"/>
       <c r="U516">
         <f>IF(AND($J516&lt;&gt;"",OR(조회_주기="전체",$R516=조회_주기),$J516&gt;=조회_최소,$J516&lt;=조회_최대),1,0)</f>
         <v/>
@@ -58230,9 +57266,7 @@
       <c r="S517" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T517" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T517" s="98" t="n"/>
       <c r="U517">
         <f>IF(AND($J517&lt;&gt;"",OR(조회_주기="전체",$R517=조회_주기),$J517&gt;=조회_최소,$J517&lt;=조회_최대),1,0)</f>
         <v/>
@@ -58332,9 +57366,7 @@
       <c r="S518" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T518" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T518" s="98" t="n"/>
       <c r="U518">
         <f>IF(AND($J518&lt;&gt;"",OR(조회_주기="전체",$R518=조회_주기),$J518&gt;=조회_최소,$J518&lt;=조회_최대),1,0)</f>
         <v/>
@@ -58434,9 +57466,7 @@
       <c r="S519" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T519" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T519" s="98" t="n"/>
       <c r="U519">
         <f>IF(AND($J519&lt;&gt;"",OR(조회_주기="전체",$R519=조회_주기),$J519&gt;=조회_최소,$J519&lt;=조회_최대),1,0)</f>
         <v/>
@@ -58536,9 +57566,7 @@
       <c r="S520" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T520" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T520" s="98" t="n"/>
       <c r="U520">
         <f>IF(AND($J520&lt;&gt;"",OR(조회_주기="전체",$R520=조회_주기),$J520&gt;=조회_최소,$J520&lt;=조회_최대),1,0)</f>
         <v/>
@@ -58638,9 +57666,7 @@
       <c r="S521" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T521" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T521" s="98" t="n"/>
       <c r="U521">
         <f>IF(AND($J521&lt;&gt;"",OR(조회_주기="전체",$R521=조회_주기),$J521&gt;=조회_최소,$J521&lt;=조회_최대),1,0)</f>
         <v/>
@@ -58740,9 +57766,7 @@
       <c r="S522" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T522" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T522" s="98" t="n"/>
       <c r="U522">
         <f>IF(AND($J522&lt;&gt;"",OR(조회_주기="전체",$R522=조회_주기),$J522&gt;=조회_최소,$J522&lt;=조회_최대),1,0)</f>
         <v/>
@@ -58842,9 +57866,7 @@
       <c r="S523" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T523" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T523" s="98" t="n"/>
       <c r="U523">
         <f>IF(AND($J523&lt;&gt;"",OR(조회_주기="전체",$R523=조회_주기),$J523&gt;=조회_최소,$J523&lt;=조회_최대),1,0)</f>
         <v/>
@@ -58944,9 +57966,7 @@
       <c r="S524" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T524" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T524" s="98" t="n"/>
       <c r="U524">
         <f>IF(AND($J524&lt;&gt;"",OR(조회_주기="전체",$R524=조회_주기),$J524&gt;=조회_최소,$J524&lt;=조회_최대),1,0)</f>
         <v/>
@@ -59046,9 +58066,7 @@
       <c r="S525" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T525" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T525" s="98" t="n"/>
       <c r="U525">
         <f>IF(AND($J525&lt;&gt;"",OR(조회_주기="전체",$R525=조회_주기),$J525&gt;=조회_최소,$J525&lt;=조회_최대),1,0)</f>
         <v/>
@@ -59148,9 +58166,7 @@
       <c r="S526" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T526" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T526" s="98" t="n"/>
       <c r="U526">
         <f>IF(AND($J526&lt;&gt;"",OR(조회_주기="전체",$R526=조회_주기),$J526&gt;=조회_최소,$J526&lt;=조회_최대),1,0)</f>
         <v/>
@@ -59250,9 +58266,7 @@
       <c r="S527" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T527" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T527" s="98" t="n"/>
       <c r="U527">
         <f>IF(AND($J527&lt;&gt;"",OR(조회_주기="전체",$R527=조회_주기),$J527&gt;=조회_최소,$J527&lt;=조회_최대),1,0)</f>
         <v/>
@@ -59352,9 +58366,7 @@
       <c r="S528" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T528" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T528" s="98" t="n"/>
       <c r="U528">
         <f>IF(AND($J528&lt;&gt;"",OR(조회_주기="전체",$R528=조회_주기),$J528&gt;=조회_최소,$J528&lt;=조회_최대),1,0)</f>
         <v/>
@@ -59454,9 +58466,7 @@
       <c r="S529" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T529" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T529" s="98" t="n"/>
       <c r="U529">
         <f>IF(AND($J529&lt;&gt;"",OR(조회_주기="전체",$R529=조회_주기),$J529&gt;=조회_최소,$J529&lt;=조회_최대),1,0)</f>
         <v/>
@@ -59556,9 +58566,7 @@
       <c r="S530" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T530" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T530" s="98" t="n"/>
       <c r="U530">
         <f>IF(AND($J530&lt;&gt;"",OR(조회_주기="전체",$R530=조회_주기),$J530&gt;=조회_최소,$J530&lt;=조회_최대),1,0)</f>
         <v/>
@@ -59658,9 +58666,7 @@
       <c r="S531" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T531" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T531" s="98" t="n"/>
       <c r="U531">
         <f>IF(AND($J531&lt;&gt;"",OR(조회_주기="전체",$R531=조회_주기),$J531&gt;=조회_최소,$J531&lt;=조회_최대),1,0)</f>
         <v/>
@@ -59760,9 +58766,7 @@
       <c r="S532" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T532" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T532" s="98" t="n"/>
       <c r="U532">
         <f>IF(AND($J532&lt;&gt;"",OR(조회_주기="전체",$R532=조회_주기),$J532&gt;=조회_최소,$J532&lt;=조회_최대),1,0)</f>
         <v/>
@@ -59862,9 +58866,7 @@
       <c r="S533" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T533" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T533" s="98" t="n"/>
       <c r="U533">
         <f>IF(AND($J533&lt;&gt;"",OR(조회_주기="전체",$R533=조회_주기),$J533&gt;=조회_최소,$J533&lt;=조회_최대),1,0)</f>
         <v/>
@@ -59964,9 +58966,7 @@
       <c r="S534" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T534" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T534" s="98" t="n"/>
       <c r="U534">
         <f>IF(AND($J534&lt;&gt;"",OR(조회_주기="전체",$R534=조회_주기),$J534&gt;=조회_최소,$J534&lt;=조회_최대),1,0)</f>
         <v/>
@@ -60066,9 +59066,7 @@
       <c r="S535" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T535" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T535" s="98" t="n"/>
       <c r="U535">
         <f>IF(AND($J535&lt;&gt;"",OR(조회_주기="전체",$R535=조회_주기),$J535&gt;=조회_최소,$J535&lt;=조회_최대),1,0)</f>
         <v/>
@@ -60168,9 +59166,7 @@
       <c r="S536" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T536" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T536" s="98" t="n"/>
       <c r="U536">
         <f>IF(AND($J536&lt;&gt;"",OR(조회_주기="전체",$R536=조회_주기),$J536&gt;=조회_최소,$J536&lt;=조회_최대),1,0)</f>
         <v/>
@@ -60270,9 +59266,7 @@
       <c r="S537" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T537" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T537" s="98" t="n"/>
       <c r="U537">
         <f>IF(AND($J537&lt;&gt;"",OR(조회_주기="전체",$R537=조회_주기),$J537&gt;=조회_최소,$J537&lt;=조회_최대),1,0)</f>
         <v/>
@@ -60372,9 +59366,7 @@
       <c r="S538" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T538" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T538" s="98" t="n"/>
       <c r="U538">
         <f>IF(AND($J538&lt;&gt;"",OR(조회_주기="전체",$R538=조회_주기),$J538&gt;=조회_최소,$J538&lt;=조회_최대),1,0)</f>
         <v/>
@@ -60474,9 +59466,7 @@
       <c r="S539" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T539" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T539" s="98" t="n"/>
       <c r="U539">
         <f>IF(AND($J539&lt;&gt;"",OR(조회_주기="전체",$R539=조회_주기),$J539&gt;=조회_최소,$J539&lt;=조회_최대),1,0)</f>
         <v/>
@@ -60576,9 +59566,7 @@
       <c r="S540" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T540" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T540" s="98" t="n"/>
       <c r="U540">
         <f>IF(AND($J540&lt;&gt;"",OR(조회_주기="전체",$R540=조회_주기),$J540&gt;=조회_최소,$J540&lt;=조회_최대),1,0)</f>
         <v/>
@@ -60678,9 +59666,7 @@
       <c r="S541" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T541" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T541" s="98" t="n"/>
       <c r="U541">
         <f>IF(AND($J541&lt;&gt;"",OR(조회_주기="전체",$R541=조회_주기),$J541&gt;=조회_최소,$J541&lt;=조회_최대),1,0)</f>
         <v/>
@@ -60780,9 +59766,7 @@
       <c r="S542" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T542" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T542" s="98" t="n"/>
       <c r="U542">
         <f>IF(AND($J542&lt;&gt;"",OR(조회_주기="전체",$R542=조회_주기),$J542&gt;=조회_최소,$J542&lt;=조회_최대),1,0)</f>
         <v/>
@@ -60882,9 +59866,7 @@
       <c r="S543" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T543" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T543" s="98" t="n"/>
       <c r="U543">
         <f>IF(AND($J543&lt;&gt;"",OR(조회_주기="전체",$R543=조회_주기),$J543&gt;=조회_최소,$J543&lt;=조회_최대),1,0)</f>
         <v/>
@@ -60984,9 +59966,7 @@
       <c r="S544" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T544" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T544" s="98" t="n"/>
       <c r="U544">
         <f>IF(AND($J544&lt;&gt;"",OR(조회_주기="전체",$R544=조회_주기),$J544&gt;=조회_최소,$J544&lt;=조회_최대),1,0)</f>
         <v/>
@@ -61086,9 +60066,7 @@
       <c r="S545" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T545" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T545" s="98" t="n"/>
       <c r="U545">
         <f>IF(AND($J545&lt;&gt;"",OR(조회_주기="전체",$R545=조회_주기),$J545&gt;=조회_최소,$J545&lt;=조회_최대),1,0)</f>
         <v/>
@@ -61188,9 +60166,7 @@
       <c r="S546" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T546" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T546" s="98" t="n"/>
       <c r="U546">
         <f>IF(AND($J546&lt;&gt;"",OR(조회_주기="전체",$R546=조회_주기),$J546&gt;=조회_최소,$J546&lt;=조회_최대),1,0)</f>
         <v/>
@@ -61290,9 +60266,7 @@
       <c r="S547" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T547" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T547" s="98" t="n"/>
       <c r="U547">
         <f>IF(AND($J547&lt;&gt;"",OR(조회_주기="전체",$R547=조회_주기),$J547&gt;=조회_최소,$J547&lt;=조회_최대),1,0)</f>
         <v/>
@@ -61392,9 +60366,7 @@
       <c r="S548" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T548" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T548" s="98" t="n"/>
       <c r="U548">
         <f>IF(AND($J548&lt;&gt;"",OR(조회_주기="전체",$R548=조회_주기),$J548&gt;=조회_최소,$J548&lt;=조회_최대),1,0)</f>
         <v/>
@@ -61494,9 +60466,7 @@
       <c r="S549" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T549" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T549" s="98" t="n"/>
       <c r="U549">
         <f>IF(AND($J549&lt;&gt;"",OR(조회_주기="전체",$R549=조회_주기),$J549&gt;=조회_최소,$J549&lt;=조회_최대),1,0)</f>
         <v/>
@@ -61596,9 +60566,7 @@
       <c r="S550" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T550" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T550" s="98" t="n"/>
       <c r="U550">
         <f>IF(AND($J550&lt;&gt;"",OR(조회_주기="전체",$R550=조회_주기),$J550&gt;=조회_최소,$J550&lt;=조회_최대),1,0)</f>
         <v/>
@@ -61698,9 +60666,7 @@
       <c r="S551" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T551" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T551" s="98" t="n"/>
       <c r="U551">
         <f>IF(AND($J551&lt;&gt;"",OR(조회_주기="전체",$R551=조회_주기),$J551&gt;=조회_최소,$J551&lt;=조회_최대),1,0)</f>
         <v/>
@@ -61800,9 +60766,7 @@
       <c r="S552" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T552" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T552" s="98" t="n"/>
       <c r="U552">
         <f>IF(AND($J552&lt;&gt;"",OR(조회_주기="전체",$R552=조회_주기),$J552&gt;=조회_최소,$J552&lt;=조회_최대),1,0)</f>
         <v/>
@@ -61902,9 +60866,7 @@
       <c r="S553" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T553" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T553" s="98" t="n"/>
       <c r="U553">
         <f>IF(AND($J553&lt;&gt;"",OR(조회_주기="전체",$R553=조회_주기),$J553&gt;=조회_최소,$J553&lt;=조회_최대),1,0)</f>
         <v/>
@@ -62004,9 +60966,7 @@
       <c r="S554" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T554" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T554" s="98" t="n"/>
       <c r="U554">
         <f>IF(AND($J554&lt;&gt;"",OR(조회_주기="전체",$R554=조회_주기),$J554&gt;=조회_최소,$J554&lt;=조회_최대),1,0)</f>
         <v/>
@@ -62106,9 +61066,7 @@
       <c r="S555" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T555" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T555" s="98" t="n"/>
       <c r="U555">
         <f>IF(AND($J555&lt;&gt;"",OR(조회_주기="전체",$R555=조회_주기),$J555&gt;=조회_최소,$J555&lt;=조회_최대),1,0)</f>
         <v/>
@@ -62208,9 +61166,7 @@
       <c r="S556" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T556" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T556" s="98" t="n"/>
       <c r="U556">
         <f>IF(AND($J556&lt;&gt;"",OR(조회_주기="전체",$R556=조회_주기),$J556&gt;=조회_최소,$J556&lt;=조회_최대),1,0)</f>
         <v/>
@@ -62310,9 +61266,7 @@
       <c r="S557" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T557" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T557" s="98" t="n"/>
       <c r="U557">
         <f>IF(AND($J557&lt;&gt;"",OR(조회_주기="전체",$R557=조회_주기),$J557&gt;=조회_최소,$J557&lt;=조회_최대),1,0)</f>
         <v/>
@@ -62412,9 +61366,7 @@
       <c r="S558" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T558" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T558" s="98" t="n"/>
       <c r="U558">
         <f>IF(AND($J558&lt;&gt;"",OR(조회_주기="전체",$R558=조회_주기),$J558&gt;=조회_최소,$J558&lt;=조회_최대),1,0)</f>
         <v/>
@@ -62514,9 +61466,7 @@
       <c r="S559" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T559" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T559" s="98" t="n"/>
       <c r="U559">
         <f>IF(AND($J559&lt;&gt;"",OR(조회_주기="전체",$R559=조회_주기),$J559&gt;=조회_최소,$J559&lt;=조회_최대),1,0)</f>
         <v/>
@@ -62616,9 +61566,7 @@
       <c r="S560" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T560" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T560" s="98" t="n"/>
       <c r="U560">
         <f>IF(AND($J560&lt;&gt;"",OR(조회_주기="전체",$R560=조회_주기),$J560&gt;=조회_최소,$J560&lt;=조회_최대),1,0)</f>
         <v/>
@@ -62718,9 +61666,7 @@
       <c r="S561" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T561" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T561" s="98" t="n"/>
       <c r="U561">
         <f>IF(AND($J561&lt;&gt;"",OR(조회_주기="전체",$R561=조회_주기),$J561&gt;=조회_최소,$J561&lt;=조회_최대),1,0)</f>
         <v/>
@@ -62820,9 +61766,7 @@
       <c r="S562" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T562" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T562" s="98" t="n"/>
       <c r="U562">
         <f>IF(AND($J562&lt;&gt;"",OR(조회_주기="전체",$R562=조회_주기),$J562&gt;=조회_최소,$J562&lt;=조회_최대),1,0)</f>
         <v/>
@@ -62922,9 +61866,7 @@
       <c r="S563" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T563" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T563" s="98" t="n"/>
       <c r="U563">
         <f>IF(AND($J563&lt;&gt;"",OR(조회_주기="전체",$R563=조회_주기),$J563&gt;=조회_최소,$J563&lt;=조회_최대),1,0)</f>
         <v/>
@@ -63024,9 +61966,7 @@
       <c r="S564" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T564" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T564" s="98" t="n"/>
       <c r="U564">
         <f>IF(AND($J564&lt;&gt;"",OR(조회_주기="전체",$R564=조회_주기),$J564&gt;=조회_최소,$J564&lt;=조회_최대),1,0)</f>
         <v/>
@@ -63126,9 +62066,7 @@
       <c r="S565" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T565" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T565" s="98" t="n"/>
       <c r="U565">
         <f>IF(AND($J565&lt;&gt;"",OR(조회_주기="전체",$R565=조회_주기),$J565&gt;=조회_최소,$J565&lt;=조회_최대),1,0)</f>
         <v/>
@@ -63228,9 +62166,7 @@
       <c r="S566" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T566" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T566" s="98" t="n"/>
       <c r="U566">
         <f>IF(AND($J566&lt;&gt;"",OR(조회_주기="전체",$R566=조회_주기),$J566&gt;=조회_최소,$J566&lt;=조회_최대),1,0)</f>
         <v/>
@@ -63330,9 +62266,7 @@
       <c r="S567" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T567" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T567" s="98" t="n"/>
       <c r="U567">
         <f>IF(AND($J567&lt;&gt;"",OR(조회_주기="전체",$R567=조회_주기),$J567&gt;=조회_최소,$J567&lt;=조회_최대),1,0)</f>
         <v/>
@@ -63432,9 +62366,7 @@
       <c r="S568" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T568" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T568" s="98" t="n"/>
       <c r="U568">
         <f>IF(AND($J568&lt;&gt;"",OR(조회_주기="전체",$R568=조회_주기),$J568&gt;=조회_최소,$J568&lt;=조회_최대),1,0)</f>
         <v/>
@@ -63534,9 +62466,7 @@
       <c r="S569" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T569" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T569" s="98" t="n"/>
       <c r="U569">
         <f>IF(AND($J569&lt;&gt;"",OR(조회_주기="전체",$R569=조회_주기),$J569&gt;=조회_최소,$J569&lt;=조회_최대),1,0)</f>
         <v/>
@@ -63636,9 +62566,7 @@
       <c r="S570" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T570" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T570" s="98" t="n"/>
       <c r="U570">
         <f>IF(AND($J570&lt;&gt;"",OR(조회_주기="전체",$R570=조회_주기),$J570&gt;=조회_최소,$J570&lt;=조회_최대),1,0)</f>
         <v/>
@@ -63738,9 +62666,7 @@
       <c r="S571" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T571" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T571" s="98" t="n"/>
       <c r="U571">
         <f>IF(AND($J571&lt;&gt;"",OR(조회_주기="전체",$R571=조회_주기),$J571&gt;=조회_최소,$J571&lt;=조회_최대),1,0)</f>
         <v/>
@@ -63840,9 +62766,7 @@
       <c r="S572" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T572" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T572" s="98" t="n"/>
       <c r="U572">
         <f>IF(AND($J572&lt;&gt;"",OR(조회_주기="전체",$R572=조회_주기),$J572&gt;=조회_최소,$J572&lt;=조회_최대),1,0)</f>
         <v/>
@@ -63942,9 +62866,7 @@
       <c r="S573" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T573" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T573" s="98" t="n"/>
       <c r="U573">
         <f>IF(AND($J573&lt;&gt;"",OR(조회_주기="전체",$R573=조회_주기),$J573&gt;=조회_최소,$J573&lt;=조회_최대),1,0)</f>
         <v/>
@@ -64044,9 +62966,7 @@
       <c r="S574" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T574" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T574" s="98" t="n"/>
       <c r="U574">
         <f>IF(AND($J574&lt;&gt;"",OR(조회_주기="전체",$R574=조회_주기),$J574&gt;=조회_최소,$J574&lt;=조회_최대),1,0)</f>
         <v/>
@@ -64146,9 +63066,7 @@
       <c r="S575" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T575" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T575" s="98" t="n"/>
       <c r="U575">
         <f>IF(AND($J575&lt;&gt;"",OR(조회_주기="전체",$R575=조회_주기),$J575&gt;=조회_최소,$J575&lt;=조회_최대),1,0)</f>
         <v/>
@@ -64248,9 +63166,7 @@
       <c r="S576" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T576" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T576" s="98" t="n"/>
       <c r="U576">
         <f>IF(AND($J576&lt;&gt;"",OR(조회_주기="전체",$R576=조회_주기),$J576&gt;=조회_최소,$J576&lt;=조회_최대),1,0)</f>
         <v/>
@@ -64316,9 +63232,7 @@
       <c r="Q577" s="96" t="inlineStr"/>
       <c r="R577" s="96" t="inlineStr"/>
       <c r="S577" s="97" t="n"/>
-      <c r="T577" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T577" s="98" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="96" t="inlineStr">
@@ -64396,9 +63310,7 @@
       <c r="S578" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="T578" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T578" s="98" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="96" t="inlineStr">
@@ -64476,9 +63388,7 @@
       <c r="S579" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="T579" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T579" s="98" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="96" t="inlineStr">
@@ -64526,9 +63436,7 @@
       <c r="Q580" s="96" t="inlineStr"/>
       <c r="R580" s="96" t="inlineStr"/>
       <c r="S580" s="97" t="n"/>
-      <c r="T580" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T580" s="98" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="96" t="inlineStr">
@@ -64606,9 +63514,7 @@
       <c r="S581" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="T581" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T581" s="98" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="96" t="inlineStr">
@@ -64686,9 +63592,7 @@
       <c r="S582" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T582" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T582" s="98" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="96" t="inlineStr">
@@ -64766,9 +63670,7 @@
       <c r="S583" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="T583" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T583" s="98" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="96" t="inlineStr">
@@ -64846,9 +63748,7 @@
       <c r="S584" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="T584" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T584" s="98" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="96" t="inlineStr">
@@ -64926,9 +63826,7 @@
       <c r="S585" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="T585" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T585" s="98" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="96" t="inlineStr">
@@ -65006,9 +63904,7 @@
       <c r="S586" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T586" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T586" s="98" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="96" t="inlineStr">
@@ -65086,9 +63982,7 @@
       <c r="S587" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="T587" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T587" s="98" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="96" t="inlineStr">
@@ -65166,9 +64060,7 @@
       <c r="S588" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T588" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T588" s="98" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="96" t="inlineStr">
@@ -65246,9 +64138,7 @@
       <c r="S589" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="T589" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T589" s="98" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="96" t="inlineStr">
@@ -65324,9 +64214,7 @@
       <c r="S590" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T590" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T590" s="98" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="96" t="inlineStr">
@@ -65404,9 +64292,7 @@
       <c r="S591" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T591" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T591" s="98" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="96" t="inlineStr">
@@ -65484,9 +64370,7 @@
       <c r="S592" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="T592" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T592" s="98" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="96" t="inlineStr">
@@ -65564,9 +64448,7 @@
       <c r="S593" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="T593" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T593" s="98" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="96" t="inlineStr">
@@ -65640,9 +64522,7 @@
       <c r="S594" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T594" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T594" s="98" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="96" t="inlineStr">
@@ -65720,9 +64600,7 @@
       <c r="S595" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="T595" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T595" s="98" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="96" t="inlineStr">
@@ -65800,9 +64678,7 @@
       <c r="S596" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T596" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T596" s="98" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="96" t="inlineStr">
@@ -65876,9 +64752,7 @@
       <c r="S597" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T597" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T597" s="98" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="96" t="inlineStr">
@@ -65956,9 +64830,7 @@
       <c r="S598" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="T598" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T598" s="98" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="96" t="inlineStr">
@@ -66036,9 +64908,7 @@
       <c r="S599" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="T599" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T599" s="98" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="96" t="inlineStr">
@@ -66116,9 +64986,7 @@
       <c r="S600" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="T600" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T600" s="98" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="96" t="inlineStr">
@@ -66196,9 +65064,7 @@
       <c r="S601" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T601" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T601" s="98" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="96" t="inlineStr">
@@ -66276,9 +65142,7 @@
       <c r="S602" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="T602" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T602" s="98" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="96" t="inlineStr">
@@ -66352,9 +65216,7 @@
       <c r="S603" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T603" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T603" s="98" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="96" t="inlineStr">
@@ -66432,9 +65294,7 @@
       <c r="S604" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="T604" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T604" s="98" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="96" t="inlineStr">
@@ -66512,9 +65372,7 @@
       <c r="S605" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="T605" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T605" s="98" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="96" t="inlineStr">
@@ -66592,9 +65450,7 @@
       <c r="S606" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="T606" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T606" s="98" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="96" t="inlineStr">
@@ -66670,9 +65526,7 @@
       <c r="S607" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T607" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T607" s="98" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="96" t="inlineStr">
@@ -66750,9 +65604,7 @@
       <c r="S608" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="T608" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T608" s="98" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="96" t="inlineStr">
@@ -66830,9 +65682,7 @@
       <c r="S609" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T609" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T609" s="98" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="96" t="inlineStr">
@@ -66910,9 +65760,7 @@
       <c r="S610" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T610" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T610" s="98" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="96" t="inlineStr">
@@ -66990,9 +65838,7 @@
       <c r="S611" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T611" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T611" s="98" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="96" t="inlineStr">
@@ -67068,9 +65914,7 @@
       <c r="S612" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T612" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T612" s="98" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="96" t="inlineStr">
@@ -67148,9 +65992,7 @@
       <c r="S613" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T613" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T613" s="98" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="96" t="inlineStr">
@@ -67228,9 +66070,7 @@
       <c r="S614" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="T614" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T614" s="98" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="96" t="inlineStr">
@@ -67308,9 +66148,7 @@
       <c r="S615" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="T615" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T615" s="98" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="96" t="inlineStr">
@@ -67388,9 +66226,7 @@
       <c r="S616" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="T616" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T616" s="98" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="96" t="inlineStr">
@@ -67468,9 +66304,7 @@
       <c r="S617" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T617" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T617" s="98" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="96" t="inlineStr">
@@ -67516,9 +66350,7 @@
       <c r="Q618" s="96" t="inlineStr"/>
       <c r="R618" s="96" t="inlineStr"/>
       <c r="S618" s="97" t="n"/>
-      <c r="T618" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T618" s="98" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="96" t="inlineStr">
@@ -67566,9 +66398,7 @@
       <c r="Q619" s="96" t="inlineStr"/>
       <c r="R619" s="96" t="inlineStr"/>
       <c r="S619" s="97" t="n"/>
-      <c r="T619" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T619" s="98" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="96" t="inlineStr">
@@ -67646,9 +66476,7 @@
       <c r="S620" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T620" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T620" s="98" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="96" t="inlineStr">
@@ -67726,9 +66554,7 @@
       <c r="S621" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T621" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T621" s="98" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="96" t="inlineStr">
@@ -67806,9 +66632,7 @@
       <c r="S622" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="T622" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T622" s="98" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="96" t="inlineStr">
@@ -67886,9 +66710,7 @@
       <c r="S623" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T623" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T623" s="98" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="96" t="inlineStr">
@@ -67966,9 +66788,7 @@
       <c r="S624" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T624" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T624" s="98" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="96" t="inlineStr">
@@ -68014,9 +66834,7 @@
       <c r="Q625" s="96" t="inlineStr"/>
       <c r="R625" s="96" t="inlineStr"/>
       <c r="S625" s="97" t="n"/>
-      <c r="T625" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T625" s="98" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="96" t="inlineStr">
@@ -68094,9 +66912,7 @@
       <c r="S626" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T626" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T626" s="98" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="96" t="inlineStr">
@@ -68174,9 +66990,7 @@
       <c r="S627" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T627" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T627" s="98" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="96" t="inlineStr">
@@ -68254,9 +67068,7 @@
       <c r="S628" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T628" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T628" s="98" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="96" t="inlineStr">
@@ -68334,9 +67146,7 @@
       <c r="S629" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="T629" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T629" s="98" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="96" t="inlineStr">
@@ -68414,9 +67224,7 @@
       <c r="S630" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T630" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T630" s="98" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="96" t="inlineStr">
@@ -68494,9 +67302,7 @@
       <c r="S631" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T631" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T631" s="98" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="96" t="inlineStr">
@@ -68574,9 +67380,7 @@
       <c r="S632" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T632" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T632" s="98" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="96" t="inlineStr">
@@ -68654,9 +67458,7 @@
       <c r="S633" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="T633" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T633" s="98" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="96" t="inlineStr">
@@ -68734,9 +67536,7 @@
       <c r="S634" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T634" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T634" s="98" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="96" t="inlineStr">
@@ -68784,9 +67584,7 @@
       <c r="Q635" s="96" t="inlineStr"/>
       <c r="R635" s="96" t="inlineStr"/>
       <c r="S635" s="97" t="n"/>
-      <c r="T635" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T635" s="98" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="96" t="inlineStr">
@@ -68834,9 +67632,7 @@
       <c r="Q636" s="96" t="inlineStr"/>
       <c r="R636" s="96" t="inlineStr"/>
       <c r="S636" s="97" t="n"/>
-      <c r="T636" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T636" s="98" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="96" t="inlineStr">
@@ -68914,9 +67710,7 @@
       <c r="S637" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="T637" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T637" s="98" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="96" t="inlineStr">
@@ -68994,9 +67788,7 @@
       <c r="S638" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T638" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T638" s="98" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="96" t="inlineStr">
@@ -69074,9 +67866,7 @@
       <c r="S639" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T639" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T639" s="98" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="96" t="inlineStr">
@@ -69154,9 +67944,7 @@
       <c r="S640" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T640" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T640" s="98" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="96" t="inlineStr">
@@ -69234,9 +68022,7 @@
       <c r="S641" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T641" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T641" s="98" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="96" t="inlineStr">
@@ -69314,9 +68100,7 @@
       <c r="S642" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T642" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T642" s="98" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="96" t="inlineStr">
@@ -69394,9 +68178,7 @@
       <c r="S643" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T643" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T643" s="98" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="96" t="inlineStr">
@@ -69474,9 +68256,7 @@
       <c r="S644" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T644" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T644" s="98" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="96" t="inlineStr">
@@ -69554,9 +68334,7 @@
       <c r="S645" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T645" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T645" s="98" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="96" t="inlineStr">
@@ -69634,9 +68412,7 @@
       <c r="S646" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T646" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T646" s="98" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="96" t="inlineStr">
@@ -69714,9 +68490,7 @@
       <c r="S647" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T647" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T647" s="98" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="96" t="inlineStr">
@@ -69794,9 +68568,7 @@
       <c r="S648" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T648" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T648" s="98" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="96" t="inlineStr">
@@ -69874,9 +68646,7 @@
       <c r="S649" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="T649" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T649" s="98" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="96" t="inlineStr">
@@ -69954,9 +68724,7 @@
       <c r="S650" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T650" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T650" s="98" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="96" t="inlineStr">
@@ -70034,9 +68802,7 @@
       <c r="S651" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T651" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T651" s="98" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="96" t="inlineStr">
@@ -70114,9 +68880,7 @@
       <c r="S652" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T652" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T652" s="98" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="96" t="inlineStr">
@@ -70194,9 +68958,7 @@
       <c r="S653" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T653" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T653" s="98" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="96" t="inlineStr">
@@ -70274,9 +69036,7 @@
       <c r="S654" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T654" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T654" s="98" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="96" t="inlineStr">
@@ -70354,9 +69114,7 @@
       <c r="S655" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="T655" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T655" s="98" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="96" t="inlineStr">
@@ -70434,9 +69192,7 @@
       <c r="S656" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T656" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T656" s="98" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="96" t="inlineStr">
@@ -70514,9 +69270,7 @@
       <c r="S657" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="T657" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T657" s="98" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="96" t="inlineStr">
@@ -70594,9 +69348,7 @@
       <c r="S658" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T658" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T658" s="98" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="96" t="inlineStr">
@@ -70674,9 +69426,7 @@
       <c r="S659" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T659" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T659" s="98" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="96" t="inlineStr">
@@ -70754,9 +69504,7 @@
       <c r="S660" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="T660" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T660" s="98" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="96" t="inlineStr">
@@ -70834,9 +69582,7 @@
       <c r="S661" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T661" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T661" s="98" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="96" t="inlineStr">
@@ -70914,9 +69660,7 @@
       <c r="S662" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="T662" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T662" s="98" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="96" t="inlineStr">
@@ -70994,9 +69738,7 @@
       <c r="S663" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="T663" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T663" s="98" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="96" t="inlineStr">
@@ -71074,9 +69816,7 @@
       <c r="S664" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="T664" s="98" t="n">
-        <v>1</v>
-      </c>
+      <c r="T664" s="98" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:T664"/>

--- a/고객제안서_월배당ETF.xlsx
+++ b/고객제안서_월배당ETF.xlsx
@@ -15,6 +15,7 @@
   <definedNames>
     <definedName name="선택가능종목">'ETF데이터'!$A$4:$A$253</definedName>
     <definedName name="검색어">'제안서'!$E$17</definedName>
+    <definedName name="검색건수">COUNTIF('ETF데이터'!$W$4:$W$253,1)</definedName>
     <definedName name="검색결과">OFFSET('ETF데이터'!$Y$4,0,0,MAX(1,COUNTIF('ETF데이터'!$W$4:$W$253,1)),1)</definedName>
     <definedName name="담긴목록">'종목조회'!$N$20:$N$79</definedName>
     <definedName name="담긴수">'종목조회'!$M$79</definedName>
@@ -608,23 +609,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="11" fillId="6" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -635,11 +642,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -775,8 +784,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -796,8 +806,9 @@
     <xf numFmtId="171" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -829,8 +840,9 @@
     <xf numFmtId="171" fontId="3" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1430,10 +1442,9 @@
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>← 글자 일부를 넣으면 아래 ▼ 목록이 그만큼만 남습니다 (예: 커버드콜). 비우면 전체.</t>
-        </is>
+      <c r="F17" s="7">
+        <f>IF(검색어="","← 글자 일부를 넣으면 아래 '투자 ETF' 의 ▼ 목록이 그만큼만 남습니다 (예: 커버드콜)",IF(검색건수=0,"→ '"&amp;검색어&amp;"' 에 맞는 종목이 없습니다. 글자를 줄여 보십시오.","→ '"&amp;검색어&amp;"' 로 "&amp;검색건수&amp;"종목. 아래 '투자 ETF' 칸의 ▼ 를 누르십시오."))</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1"/>
@@ -3064,6 +3075,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="25">
     <mergeCell ref="B92:H92"/>
     <mergeCell ref="B95:H95"/>
@@ -6447,6 +6459,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A5:I5"/>
@@ -36887,6 +36900,7 @@
       <c r="T336" s="98" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
   <autoFilter ref="A3:T336"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37160,6 +37174,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/고객제안서_월배당ETF.xlsx
+++ b/고객제안서_월배당ETF.xlsx
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
